--- a/data/rutinas/sucursales/Socios_con_y_sin_rutina__SAN LUIS.xlsx
+++ b/data/rutinas/sucursales/Socios_con_y_sin_rutina__SAN LUIS.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1263" uniqueCount="640">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1478" uniqueCount="738">
   <si>
     <t>IDSocio</t>
   </si>
@@ -109,276 +109,324 @@
     <t>277709</t>
   </si>
   <si>
+    <t>319145</t>
+  </si>
+  <si>
     <t>34113</t>
   </si>
   <si>
+    <t>109430</t>
+  </si>
+  <si>
+    <t>340298</t>
+  </si>
+  <si>
+    <t>339854</t>
+  </si>
+  <si>
     <t>317137</t>
   </si>
   <si>
     <t>330218</t>
   </si>
   <si>
+    <t>340152</t>
+  </si>
+  <si>
+    <t>340160</t>
+  </si>
+  <si>
+    <t>340247</t>
+  </si>
+  <si>
+    <t>340805</t>
+  </si>
+  <si>
     <t>336709</t>
   </si>
   <si>
+    <t>340765</t>
+  </si>
+  <si>
+    <t>341196</t>
+  </si>
+  <si>
+    <t>339746</t>
+  </si>
+  <si>
+    <t>340779</t>
+  </si>
+  <si>
+    <t>340877</t>
+  </si>
+  <si>
+    <t>341271</t>
+  </si>
+  <si>
+    <t>341212</t>
+  </si>
+  <si>
+    <t>341270</t>
+  </si>
+  <si>
     <t>339758</t>
   </si>
   <si>
     <t>339777</t>
   </si>
   <si>
-    <t>339854</t>
-  </si>
-  <si>
-    <t>340298</t>
-  </si>
-  <si>
-    <t>340152</t>
-  </si>
-  <si>
-    <t>340160</t>
-  </si>
-  <si>
-    <t>340247</t>
-  </si>
-  <si>
-    <t>339746</t>
+    <t>340602</t>
+  </si>
+  <si>
+    <t>340730</t>
   </si>
   <si>
     <t>340340</t>
   </si>
   <si>
-    <t>340765</t>
-  </si>
-  <si>
-    <t>340877</t>
-  </si>
-  <si>
-    <t>340805</t>
-  </si>
-  <si>
-    <t>340779</t>
-  </si>
-  <si>
-    <t>341196</t>
-  </si>
-  <si>
-    <t>341271</t>
-  </si>
-  <si>
-    <t>341212</t>
-  </si>
-  <si>
-    <t>340602</t>
-  </si>
-  <si>
-    <t>340730</t>
-  </si>
-  <si>
-    <t>341270</t>
+    <t>341991</t>
+  </si>
+  <si>
+    <t>342245</t>
+  </si>
+  <si>
+    <t>342261</t>
+  </si>
+  <si>
+    <t>342512</t>
+  </si>
+  <si>
+    <t>342828</t>
+  </si>
+  <si>
+    <t>342562</t>
+  </si>
+  <si>
+    <t>342499</t>
+  </si>
+  <si>
+    <t>342548</t>
+  </si>
+  <si>
+    <t>343958</t>
+  </si>
+  <si>
+    <t>342846</t>
+  </si>
+  <si>
+    <t>342849</t>
+  </si>
+  <si>
+    <t>342866</t>
+  </si>
+  <si>
+    <t>343341</t>
   </si>
   <si>
     <t>341197</t>
   </si>
   <si>
-    <t>342245</t>
-  </si>
-  <si>
-    <t>342261</t>
-  </si>
-  <si>
-    <t>342562</t>
-  </si>
-  <si>
-    <t>342499</t>
-  </si>
-  <si>
-    <t>342548</t>
-  </si>
-  <si>
-    <t>342512</t>
+    <t>342497</t>
+  </si>
+  <si>
+    <t>342516</t>
+  </si>
+  <si>
+    <t>343637</t>
+  </si>
+  <si>
+    <t>343531</t>
   </si>
   <si>
     <t>342867</t>
   </si>
   <si>
-    <t>342846</t>
-  </si>
-  <si>
-    <t>342849</t>
-  </si>
-  <si>
-    <t>342828</t>
-  </si>
-  <si>
-    <t>342497</t>
-  </si>
-  <si>
-    <t>342516</t>
-  </si>
-  <si>
-    <t>342866</t>
+    <t>342823</t>
+  </si>
+  <si>
+    <t>344062</t>
+  </si>
+  <si>
+    <t>343813</t>
+  </si>
+  <si>
+    <t>344605</t>
+  </si>
+  <si>
+    <t>344507</t>
+  </si>
+  <si>
+    <t>343837</t>
+  </si>
+  <si>
+    <t>343954</t>
   </si>
   <si>
     <t>342742</t>
   </si>
   <si>
-    <t>342823</t>
-  </si>
-  <si>
-    <t>343341</t>
-  </si>
-  <si>
-    <t>343637</t>
-  </si>
-  <si>
-    <t>343837</t>
-  </si>
-  <si>
-    <t>343531</t>
-  </si>
-  <si>
-    <t>343813</t>
-  </si>
-  <si>
     <t>70597</t>
   </si>
   <si>
     <t>75210</t>
   </si>
   <si>
+    <t>16642</t>
+  </si>
+  <si>
     <t>32029</t>
   </si>
   <si>
+    <t>7171</t>
+  </si>
+  <si>
+    <t>18116</t>
+  </si>
+  <si>
+    <t>17672</t>
+  </si>
+  <si>
     <t>14634</t>
   </si>
   <si>
     <t>15272</t>
   </si>
   <si>
+    <t>17970</t>
+  </si>
+  <si>
+    <t>17978</t>
+  </si>
+  <si>
+    <t>18065</t>
+  </si>
+  <si>
+    <t>18623</t>
+  </si>
+  <si>
     <t>22435</t>
   </si>
   <si>
+    <t>18583</t>
+  </si>
+  <si>
+    <t>19014</t>
+  </si>
+  <si>
+    <t>17564</t>
+  </si>
+  <si>
+    <t>18597</t>
+  </si>
+  <si>
+    <t>18695</t>
+  </si>
+  <si>
+    <t>19089</t>
+  </si>
+  <si>
+    <t>19030</t>
+  </si>
+  <si>
+    <t>19088</t>
+  </si>
+  <si>
     <t>17576</t>
   </si>
   <si>
     <t>17595</t>
   </si>
   <si>
-    <t>17672</t>
-  </si>
-  <si>
-    <t>18116</t>
-  </si>
-  <si>
-    <t>17970</t>
-  </si>
-  <si>
-    <t>17978</t>
-  </si>
-  <si>
-    <t>18065</t>
-  </si>
-  <si>
-    <t>17564</t>
+    <t>18420</t>
+  </si>
+  <si>
+    <t>18548</t>
   </si>
   <si>
     <t>18158</t>
   </si>
   <si>
-    <t>18583</t>
-  </si>
-  <si>
-    <t>18695</t>
-  </si>
-  <si>
-    <t>18623</t>
-  </si>
-  <si>
-    <t>18597</t>
-  </si>
-  <si>
-    <t>19014</t>
-  </si>
-  <si>
-    <t>19089</t>
-  </si>
-  <si>
-    <t>19030</t>
-  </si>
-  <si>
-    <t>18420</t>
-  </si>
-  <si>
-    <t>18548</t>
-  </si>
-  <si>
-    <t>19088</t>
+    <t>19809</t>
+  </si>
+  <si>
+    <t>20063</t>
+  </si>
+  <si>
+    <t>20079</t>
+  </si>
+  <si>
+    <t>20329</t>
+  </si>
+  <si>
+    <t>20645</t>
+  </si>
+  <si>
+    <t>20379</t>
+  </si>
+  <si>
+    <t>20316</t>
+  </si>
+  <si>
+    <t>20365</t>
+  </si>
+  <si>
+    <t>21775</t>
+  </si>
+  <si>
+    <t>20663</t>
+  </si>
+  <si>
+    <t>20666</t>
+  </si>
+  <si>
+    <t>20683</t>
+  </si>
+  <si>
+    <t>21158</t>
   </si>
   <si>
     <t>19015</t>
   </si>
   <si>
-    <t>20063</t>
-  </si>
-  <si>
-    <t>20079</t>
-  </si>
-  <si>
-    <t>20379</t>
-  </si>
-  <si>
-    <t>20316</t>
-  </si>
-  <si>
-    <t>20365</t>
-  </si>
-  <si>
-    <t>20329</t>
+    <t>20314</t>
+  </si>
+  <si>
+    <t>20333</t>
+  </si>
+  <si>
+    <t>21454</t>
+  </si>
+  <si>
+    <t>21348</t>
   </si>
   <si>
     <t>20684</t>
   </si>
   <si>
-    <t>20663</t>
-  </si>
-  <si>
-    <t>20666</t>
-  </si>
-  <si>
-    <t>20645</t>
-  </si>
-  <si>
-    <t>20314</t>
-  </si>
-  <si>
-    <t>20333</t>
-  </si>
-  <si>
-    <t>20683</t>
+    <t>20640</t>
+  </si>
+  <si>
+    <t>21879</t>
+  </si>
+  <si>
+    <t>21630</t>
+  </si>
+  <si>
+    <t>22422</t>
+  </si>
+  <si>
+    <t>22324</t>
+  </si>
+  <si>
+    <t>21654</t>
+  </si>
+  <si>
+    <t>21771</t>
   </si>
   <si>
     <t>20559</t>
   </si>
   <si>
-    <t>20640</t>
-  </si>
-  <si>
-    <t>21158</t>
-  </si>
-  <si>
-    <t>21454</t>
-  </si>
-  <si>
-    <t>21654</t>
-  </si>
-  <si>
-    <t>21348</t>
-  </si>
-  <si>
-    <t>21630</t>
-  </si>
-  <si>
     <t>SAN LUIS</t>
   </si>
   <si>
@@ -388,363 +436,414 @@
     <t>ANGEL ALBERTO</t>
   </si>
   <si>
+    <t>CESAR BERNARDO</t>
+  </si>
+  <si>
     <t>YOVANY</t>
   </si>
   <si>
+    <t>GISELL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DARIO </t>
+  </si>
+  <si>
+    <t>DIEGO ARMANDO</t>
+  </si>
+  <si>
     <t>JOSE IGNACIO</t>
   </si>
   <si>
     <t xml:space="preserve">SILVIA </t>
   </si>
   <si>
+    <t>MARTHA LIDIA</t>
+  </si>
+  <si>
+    <t>ALEJANDRO</t>
+  </si>
+  <si>
+    <t>LESLIE CLARETH</t>
+  </si>
+  <si>
+    <t>RICARDO</t>
+  </si>
+  <si>
     <t>MARIA FERNANDA</t>
   </si>
   <si>
+    <t>VIVIANA</t>
+  </si>
+  <si>
+    <t>ESMERALDA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GRISEL </t>
+  </si>
+  <si>
+    <t>CLAUDIA ITZEL</t>
+  </si>
+  <si>
+    <t>HECTOR ABRAHAM</t>
+  </si>
+  <si>
+    <t>NICOLLE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">YAHIR </t>
+  </si>
+  <si>
+    <t>JUAN MANUEL</t>
+  </si>
+  <si>
     <t>ISABELLA</t>
   </si>
   <si>
     <t>GISSEL LILIAN</t>
   </si>
   <si>
-    <t>DIEGO ARMANDO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DARIO </t>
-  </si>
-  <si>
-    <t>MARTHA LIDIA</t>
-  </si>
-  <si>
-    <t>ALEJANDRO</t>
-  </si>
-  <si>
-    <t>LESLIE CLARETH</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GRISEL </t>
+    <t>DANTE EMILIANO</t>
+  </si>
+  <si>
+    <t>GUADALUPE SHEREZADA</t>
   </si>
   <si>
     <t>FATIMA</t>
   </si>
   <si>
-    <t>VIVIANA</t>
-  </si>
-  <si>
-    <t>HECTOR ABRAHAM</t>
-  </si>
-  <si>
-    <t>RICARDO</t>
-  </si>
-  <si>
-    <t>CLAUDIA ITZEL</t>
-  </si>
-  <si>
-    <t>ESMERALDA</t>
-  </si>
-  <si>
-    <t>NICOLLE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">YAHIR </t>
-  </si>
-  <si>
-    <t>DANTE EMILIANO</t>
-  </si>
-  <si>
-    <t>GUADALUPE SHEREZADA</t>
-  </si>
-  <si>
-    <t>JUAN MANUEL</t>
+    <t>VICTOR HUGO</t>
+  </si>
+  <si>
+    <t>MANUEL ANTONIO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VICTORIA </t>
+  </si>
+  <si>
+    <t>JOSE RICARDO</t>
+  </si>
+  <si>
+    <t>NUBIA GUADALUPE</t>
+  </si>
+  <si>
+    <t>AZALEA ZENYACE</t>
+  </si>
+  <si>
+    <t>ALBERTO</t>
+  </si>
+  <si>
+    <t>CECILIA GUADALUPE</t>
+  </si>
+  <si>
+    <t>ELIZABETH</t>
+  </si>
+  <si>
+    <t>CARLOS JULIAN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PAOLA </t>
+  </si>
+  <si>
+    <t>IAN AXEL</t>
+  </si>
+  <si>
+    <t>JUAN OMAR</t>
   </si>
   <si>
     <t>CARMEN</t>
   </si>
   <si>
-    <t>MANUEL ANTONIO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">VICTORIA </t>
-  </si>
-  <si>
-    <t>AZALEA ZENYACE</t>
-  </si>
-  <si>
-    <t>ALBERTO</t>
-  </si>
-  <si>
-    <t>CECILIA GUADALUPE</t>
-  </si>
-  <si>
-    <t>JOSE RICARDO</t>
+    <t>KARLA VERONICA</t>
+  </si>
+  <si>
+    <t>LUIS</t>
+  </si>
+  <si>
+    <t>RICARDO FRANCISCO</t>
+  </si>
+  <si>
+    <t>URIEL IGNACIO</t>
   </si>
   <si>
     <t>MIGUEL ANGEL</t>
   </si>
   <si>
-    <t>CARLOS JULIAN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PAOLA </t>
-  </si>
-  <si>
-    <t>NUBIA GUADALUPE</t>
-  </si>
-  <si>
-    <t>KARLA VERONICA</t>
-  </si>
-  <si>
-    <t>LUIS</t>
-  </si>
-  <si>
-    <t>IAN AXEL</t>
+    <t>JESUS ABEL</t>
+  </si>
+  <si>
+    <t>RAYMUNDO ISRAEL</t>
+  </si>
+  <si>
+    <t>YOCELIN DEL CARMEN</t>
+  </si>
+  <si>
+    <t>LIZET</t>
+  </si>
+  <si>
+    <t>KAREN ANDREA</t>
+  </si>
+  <si>
+    <t>CLAUDIA GABRIELA</t>
+  </si>
+  <si>
+    <t>LOURDES</t>
   </si>
   <si>
     <t>KARINA</t>
   </si>
   <si>
-    <t>JESUS ABEL</t>
-  </si>
-  <si>
-    <t>JUAN OMAR</t>
-  </si>
-  <si>
-    <t>RICARDO FRANCISCO</t>
-  </si>
-  <si>
-    <t>CLAUDIA GABRIELA</t>
-  </si>
-  <si>
-    <t>URIEL IGNACIO</t>
-  </si>
-  <si>
-    <t>YOCELIN DEL CARMEN</t>
-  </si>
-  <si>
     <t>MURILLO</t>
   </si>
   <si>
     <t>ACOSTA</t>
   </si>
   <si>
+    <t>ELIZONDO</t>
+  </si>
+  <si>
     <t>VALENZUELA</t>
   </si>
   <si>
+    <t>BARO</t>
+  </si>
+  <si>
+    <t>GARCIA</t>
+  </si>
+  <si>
+    <t>MEDINA</t>
+  </si>
+  <si>
     <t>PARRA</t>
   </si>
   <si>
     <t>ZAVALA</t>
   </si>
   <si>
+    <t xml:space="preserve">DURAN </t>
+  </si>
+  <si>
+    <t>ROMERO</t>
+  </si>
+  <si>
+    <t>VEGA</t>
+  </si>
+  <si>
+    <t>TAPIA</t>
+  </si>
+  <si>
     <t>LAZALDE</t>
   </si>
   <si>
+    <t>ARVAYO</t>
+  </si>
+  <si>
+    <t>JAVALERA</t>
+  </si>
+  <si>
+    <t>CUADRAS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DE LA ROSA </t>
+  </si>
+  <si>
+    <t>OJEDA</t>
+  </si>
+  <si>
+    <t>BUSTAMANTE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SALGADO </t>
+  </si>
+  <si>
+    <t>ALONZO</t>
+  </si>
+  <si>
     <t>ALARCON</t>
   </si>
   <si>
     <t>RODRIGUEZ</t>
   </si>
   <si>
-    <t>MEDINA</t>
-  </si>
-  <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DURAN </t>
-  </si>
-  <si>
-    <t>ROMERO</t>
-  </si>
-  <si>
-    <t>VEGA</t>
-  </si>
-  <si>
-    <t>CUADRAS</t>
+    <t>RAMIREZ</t>
   </si>
   <si>
     <t>SANCHEZ</t>
   </si>
   <si>
-    <t>ARVAYO</t>
-  </si>
-  <si>
-    <t>OJEDA</t>
-  </si>
-  <si>
-    <t>TAPIA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DE LA ROSA </t>
-  </si>
-  <si>
-    <t>JAVALERA</t>
-  </si>
-  <si>
-    <t>BUSTAMANTE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SALGADO </t>
-  </si>
-  <si>
-    <t>RAMIREZ</t>
-  </si>
-  <si>
-    <t>ALONZO</t>
+    <t>SALAS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RUIZ </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ZAVALA </t>
+  </si>
+  <si>
+    <t>SOLARES</t>
+  </si>
+  <si>
+    <t>MORENO</t>
+  </si>
+  <si>
+    <t>VINIEGRA</t>
+  </si>
+  <si>
+    <t>CORRAL</t>
+  </si>
+  <si>
+    <t>FLORES</t>
+  </si>
+  <si>
+    <t>NUÑEZ</t>
+  </si>
+  <si>
+    <t>ALONSO</t>
+  </si>
+  <si>
+    <t>SANDOVAL</t>
+  </si>
+  <si>
+    <t>REYES</t>
   </si>
   <si>
     <t>ALICIA</t>
   </si>
   <si>
-    <t xml:space="preserve">RUIZ </t>
-  </si>
-  <si>
-    <t xml:space="preserve">ZAVALA </t>
-  </si>
-  <si>
-    <t>MORENO</t>
-  </si>
-  <si>
-    <t>VINIEGRA</t>
-  </si>
-  <si>
-    <t>CORRAL</t>
+    <t>TORRES</t>
+  </si>
+  <si>
+    <t>LEDESMA</t>
+  </si>
+  <si>
+    <t>SID</t>
   </si>
   <si>
     <t>AMEZCUA</t>
   </si>
   <si>
-    <t>NUÑEZ</t>
-  </si>
-  <si>
-    <t>ALONSO</t>
-  </si>
-  <si>
-    <t>SOLARES</t>
-  </si>
-  <si>
-    <t>TORRES</t>
-  </si>
-  <si>
-    <t>SANDOVAL</t>
+    <t>VALERIO</t>
+  </si>
+  <si>
+    <t>LOPEZ</t>
+  </si>
+  <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>ISAIS</t>
+  </si>
+  <si>
+    <t>ROGEL</t>
   </si>
   <si>
     <t>QUILES</t>
   </si>
   <si>
-    <t>VALERIO</t>
-  </si>
-  <si>
-    <t>REYES</t>
-  </si>
-  <si>
-    <t>LEDESMA</t>
-  </si>
-  <si>
-    <t>ROGEL</t>
-  </si>
-  <si>
-    <t>SID</t>
-  </si>
-  <si>
-    <t>LOPEZ</t>
-  </si>
-  <si>
     <t>RIVAS</t>
   </si>
   <si>
     <t xml:space="preserve">ALVARADO </t>
   </si>
   <si>
+    <t>SOTO</t>
+  </si>
+  <si>
+    <t>PIEDRA</t>
+  </si>
+  <si>
     <t>JAQUEZ</t>
   </si>
   <si>
     <t>PACHECO</t>
   </si>
   <si>
+    <t>CUEN</t>
+  </si>
+  <si>
+    <t>QUEVEDO</t>
+  </si>
+  <si>
+    <t>OLIVO</t>
+  </si>
+  <si>
     <t>ANDRADE</t>
   </si>
   <si>
+    <t>RASCON</t>
+  </si>
+  <si>
+    <t>ALCANTAR</t>
+  </si>
+  <si>
+    <t>FRANCO</t>
+  </si>
+  <si>
+    <t>COVARRUBIAS</t>
+  </si>
+  <si>
+    <t>ARZATE</t>
+  </si>
+  <si>
     <t>ACEVES</t>
   </si>
   <si>
     <t>SILVA</t>
   </si>
   <si>
-    <t>PIEDRA</t>
-  </si>
-  <si>
-    <t>CUEN</t>
-  </si>
-  <si>
-    <t>QUEVEDO</t>
-  </si>
-  <si>
-    <t>RASCON</t>
-  </si>
-  <si>
-    <t>FRANCO</t>
-  </si>
-  <si>
-    <t>OLIVO</t>
-  </si>
-  <si>
-    <t>ALCANTAR</t>
-  </si>
-  <si>
-    <t>ELIZONDO</t>
-  </si>
-  <si>
-    <t>COVARRUBIAS</t>
-  </si>
-  <si>
     <t>GOMEZ</t>
   </si>
   <si>
     <t>CORTEZ</t>
   </si>
   <si>
-    <t>ARZATE</t>
+    <t>BARRIENTOS</t>
+  </si>
+  <si>
+    <t>ANGULO</t>
+  </si>
+  <si>
+    <t>ARVIZU</t>
+  </si>
+  <si>
+    <t>CARRIZOZA</t>
+  </si>
+  <si>
+    <t>BERMUDEZ</t>
+  </si>
+  <si>
+    <t>HERAS</t>
+  </si>
+  <si>
+    <t>MANRIQUEZ</t>
+  </si>
+  <si>
+    <t>RIVERA</t>
   </si>
   <si>
     <t>GIL</t>
   </si>
   <si>
-    <t>BARRIENTOS</t>
-  </si>
-  <si>
-    <t>CARRIZOZA</t>
-  </si>
-  <si>
-    <t>BERMUDEZ</t>
-  </si>
-  <si>
-    <t>ANGULO</t>
-  </si>
-  <si>
-    <t>MANRIQUEZ</t>
-  </si>
-  <si>
-    <t>ARVIZU</t>
-  </si>
-  <si>
     <t>CORONA</t>
   </si>
   <si>
+    <t>PEDROZA</t>
+  </si>
+  <si>
+    <t>AREVALO</t>
+  </si>
+  <si>
+    <t>LIMON</t>
+  </si>
+  <si>
+    <t>ARREOLA</t>
+  </si>
+  <si>
+    <t>MENDEZ</t>
+  </si>
+  <si>
     <t>CAMACHO</t>
   </si>
   <si>
-    <t>LIMON</t>
-  </si>
-  <si>
-    <t>RIVERA</t>
-  </si>
-  <si>
-    <t>PEDROZA</t>
-  </si>
-  <si>
-    <t>AREVALO</t>
-  </si>
-  <si>
     <t>52</t>
   </si>
   <si>
@@ -757,249 +856,291 @@
     <t>6424832255</t>
   </si>
   <si>
+    <t>6862267616</t>
+  </si>
+  <si>
     <t>6531453465</t>
   </si>
   <si>
+    <t>6531135478</t>
+  </si>
+  <si>
+    <t>6531617077</t>
+  </si>
+  <si>
+    <t>6531658872</t>
+  </si>
+  <si>
     <t>6531038638</t>
   </si>
   <si>
     <t>6531211789</t>
   </si>
   <si>
+    <t>6531218668</t>
+  </si>
+  <si>
+    <t>2099007353</t>
+  </si>
+  <si>
+    <t>6531329411</t>
+  </si>
+  <si>
+    <t>6531341539</t>
+  </si>
+  <si>
     <t>6645697047</t>
   </si>
   <si>
+    <t>6531300005</t>
+  </si>
+  <si>
+    <t>6531196345</t>
+  </si>
+  <si>
+    <t>6531315370</t>
+  </si>
+  <si>
+    <t>6642467640</t>
+  </si>
+  <si>
+    <t>6532437111</t>
+  </si>
+  <si>
+    <t>6381121777</t>
+  </si>
+  <si>
+    <t>6531128435</t>
+  </si>
+  <si>
+    <t>6161093843</t>
+  </si>
+  <si>
     <t>6535382487</t>
   </si>
   <si>
     <t>6531466820</t>
   </si>
   <si>
-    <t>6531658872</t>
-  </si>
-  <si>
-    <t>6531617077</t>
-  </si>
-  <si>
-    <t>6531218668</t>
-  </si>
-  <si>
-    <t>2099007353</t>
-  </si>
-  <si>
-    <t>6531329411</t>
-  </si>
-  <si>
-    <t>6531315370</t>
+    <t>9228390416</t>
+  </si>
+  <si>
+    <t>6531304693</t>
   </si>
   <si>
     <t>6531333103</t>
   </si>
   <si>
-    <t>6531300005</t>
-  </si>
-  <si>
-    <t>6532437111</t>
-  </si>
-  <si>
-    <t>6531341539</t>
-  </si>
-  <si>
-    <t>6642467640</t>
-  </si>
-  <si>
-    <t>6531196345</t>
-  </si>
-  <si>
-    <t>6381121777</t>
-  </si>
-  <si>
-    <t>6531128435</t>
-  </si>
-  <si>
-    <t>9228390416</t>
-  </si>
-  <si>
-    <t>6531304693</t>
-  </si>
-  <si>
-    <t>6161093843</t>
+    <t>6531130495</t>
+  </si>
+  <si>
+    <t>6863042514</t>
+  </si>
+  <si>
+    <t>6531231721</t>
+  </si>
+  <si>
+    <t>6531217599</t>
+  </si>
+  <si>
+    <t>6531665151</t>
+  </si>
+  <si>
+    <t>6531038421</t>
+  </si>
+  <si>
+    <t>6532096000</t>
+  </si>
+  <si>
+    <t>6621711231</t>
+  </si>
+  <si>
+    <t>6531288733</t>
+  </si>
+  <si>
+    <t>6531308246</t>
+  </si>
+  <si>
+    <t>6535395572</t>
+  </si>
+  <si>
+    <t>9285501740</t>
+  </si>
+  <si>
+    <t>6865976498</t>
   </si>
   <si>
     <t>6642049795</t>
   </si>
   <si>
-    <t>6863042514</t>
-  </si>
-  <si>
-    <t>6531231721</t>
-  </si>
-  <si>
-    <t>6531038421</t>
-  </si>
-  <si>
-    <t>6532096000</t>
-  </si>
-  <si>
-    <t>6621711231</t>
-  </si>
-  <si>
-    <t>6531217599</t>
+    <t>9285509758</t>
+  </si>
+  <si>
+    <t>6531211788</t>
+  </si>
+  <si>
+    <t>6531121344</t>
+  </si>
+  <si>
+    <t>6531071848</t>
   </si>
   <si>
     <t>6674708281</t>
   </si>
   <si>
-    <t>6531308246</t>
-  </si>
-  <si>
-    <t>6535395572</t>
-  </si>
-  <si>
-    <t>6531665151</t>
-  </si>
-  <si>
-    <t>9285509758</t>
-  </si>
-  <si>
-    <t>6531211788</t>
-  </si>
-  <si>
-    <t>9285501740</t>
+    <t>6531665157</t>
+  </si>
+  <si>
+    <t>6442276514</t>
+  </si>
+  <si>
+    <t>6531305359</t>
+  </si>
+  <si>
+    <t>5412729355</t>
+  </si>
+  <si>
+    <t>6531517509</t>
+  </si>
+  <si>
+    <t>6532075902</t>
+  </si>
+  <si>
+    <t>6531035239</t>
   </si>
   <si>
     <t>6531163674</t>
   </si>
   <si>
-    <t>6531665157</t>
-  </si>
-  <si>
-    <t>6865976498</t>
-  </si>
-  <si>
-    <t>6531121344</t>
-  </si>
-  <si>
-    <t>6532075902</t>
-  </si>
-  <si>
-    <t>6531071848</t>
-  </si>
-  <si>
-    <t>6531305359</t>
-  </si>
-  <si>
     <t>AV COLIMA Y 44</t>
   </si>
   <si>
     <t>CJON 5 DE MAYO 12 Y 13</t>
   </si>
   <si>
+    <t>GUADALUPE VICTORIA Y 31</t>
+  </si>
+  <si>
     <t>LEY DE ALFABETIZACION 9 Y 10</t>
   </si>
   <si>
+    <t>REVOLUCION Y 40</t>
+  </si>
+  <si>
     <t>CALZADA AVIACION 104</t>
   </si>
   <si>
     <t>AV COAHUILA B Y C PESQUEIRA</t>
   </si>
   <si>
+    <t>PRIVADO ROFORMA</t>
+  </si>
+  <si>
+    <t>PRIVADA REFORMA</t>
+  </si>
+  <si>
+    <t>AV NAYARIT 21</t>
+  </si>
+  <si>
+    <t>AV GUERRERO 12</t>
+  </si>
+  <si>
     <t>C ADOLFO LOPEZ MATEOS 6413 C</t>
   </si>
   <si>
+    <t xml:space="preserve">AV COLIMA Y MATAMOROS </t>
+  </si>
+  <si>
+    <t>AV TABASCO 41</t>
+  </si>
+  <si>
+    <t>MEXICO B Y 28</t>
+  </si>
+  <si>
+    <t>DALIAS 18 Y 19</t>
+  </si>
+  <si>
+    <t>LOS ADOBES</t>
+  </si>
+  <si>
+    <t>FRACC ADOBES 75</t>
+  </si>
+  <si>
     <t>MERIDA 1</t>
   </si>
   <si>
-    <t>REVOLUCION Y 40</t>
-  </si>
-  <si>
-    <t>PRIVADO ROFORMA</t>
-  </si>
-  <si>
-    <t>PRIVADA REFORMA</t>
-  </si>
-  <si>
-    <t>AV NAYARIT 21</t>
-  </si>
-  <si>
-    <t>MEXICO B Y 28</t>
-  </si>
-  <si>
     <t>AV TORREON 39</t>
   </si>
   <si>
-    <t xml:space="preserve">AV COLIMA Y MATAMOROS </t>
-  </si>
-  <si>
-    <t>DALIAS 18 Y 19</t>
-  </si>
-  <si>
-    <t>AV GUERRERO 12</t>
-  </si>
-  <si>
-    <t>AV TABASCO 41</t>
-  </si>
-  <si>
-    <t>LOS ADOBES</t>
-  </si>
-  <si>
-    <t>FRACC ADOBES 75</t>
+    <t>SAN MARCOS</t>
+  </si>
+  <si>
+    <t>CJN SAN JUAN Y SAN LUIS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HACIENDA DE LA CRUZ </t>
+  </si>
+  <si>
+    <t>CJON HIDALGO Y 47</t>
+  </si>
+  <si>
+    <t>CARRETERA DEL VALLE</t>
+  </si>
+  <si>
+    <t>CJN CHIHUAHUA 23</t>
+  </si>
+  <si>
+    <t>COLIMA C 26</t>
+  </si>
+  <si>
+    <t>JUAREZ Y 20</t>
+  </si>
+  <si>
+    <t>CJON FLORES Y C 16 SN</t>
+  </si>
+  <si>
+    <t>TORREON 4 Y 5</t>
+  </si>
+  <si>
+    <t>CJN KINO 33</t>
+  </si>
+  <si>
+    <t>CJON NICARAGUA 31</t>
   </si>
   <si>
     <t>AV BENITO JUAREZ 24 Y 25</t>
   </si>
   <si>
-    <t>CJN SAN JUAN Y SAN LUIS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HACIENDA DE LA CRUZ </t>
-  </si>
-  <si>
-    <t>CJN CHIHUAHUA 23</t>
-  </si>
-  <si>
-    <t>COLIMA C 26</t>
-  </si>
-  <si>
-    <t>JUAREZ Y 20</t>
-  </si>
-  <si>
-    <t>CJON HIDALGO Y 47</t>
+    <t xml:space="preserve">COLIMA C 26 </t>
+  </si>
+  <si>
+    <t>EL CHEQUE 8 S/N</t>
+  </si>
+  <si>
+    <t>FELIX CONTRERAS 44</t>
   </si>
   <si>
     <t>FLORES 22</t>
   </si>
   <si>
-    <t>TORREON 4 Y 5</t>
-  </si>
-  <si>
-    <t>CJN KINO 33</t>
-  </si>
-  <si>
-    <t>CARRETERA DEL VALLE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">COLIMA C 26 </t>
+    <t>AV CARRANZA 36</t>
+  </si>
+  <si>
+    <t>JALAPA B 5</t>
+  </si>
+  <si>
+    <t>AV PUEBLA 1RA</t>
+  </si>
+  <si>
+    <t>HUERTAS 7</t>
+  </si>
+  <si>
+    <t>C 5 DE MAYO SN</t>
   </si>
   <si>
     <t>AV PUEBLA 1RA Y HERMOSILLO</t>
   </si>
   <si>
-    <t>CJON NICARAGUA 31</t>
-  </si>
-  <si>
-    <t>EL CHEQUE 8 S/N</t>
-  </si>
-  <si>
-    <t>HUERTAS 7</t>
-  </si>
-  <si>
-    <t>FELIX CONTRERAS 44</t>
-  </si>
-  <si>
-    <t>AV CARRANZA 36</t>
-  </si>
-  <si>
     <t>Femenino</t>
   </si>
   <si>
@@ -1012,412 +1153,487 @@
     <t>06-03-1998</t>
   </si>
   <si>
+    <t>27-07-1992</t>
+  </si>
+  <si>
     <t>30-12-1997</t>
   </si>
   <si>
+    <t>25-01-1999</t>
+  </si>
+  <si>
+    <t>14-03-1986</t>
+  </si>
+  <si>
+    <t>06-03-1989</t>
+  </si>
+  <si>
     <t>13-12-1975</t>
   </si>
   <si>
     <t>15-02-1984</t>
   </si>
   <si>
+    <t>06-08-1960</t>
+  </si>
+  <si>
+    <t>27-03-1957</t>
+  </si>
+  <si>
+    <t>18-08-2006</t>
+  </si>
+  <si>
+    <t>01-04-2000</t>
+  </si>
+  <si>
     <t>21-01-2000</t>
   </si>
   <si>
+    <t>03-01-1979</t>
+  </si>
+  <si>
+    <t>19-03-1975</t>
+  </si>
+  <si>
+    <t>17-02-1980</t>
+  </si>
+  <si>
+    <t>21-11-1988</t>
+  </si>
+  <si>
+    <t>08-01-2005</t>
+  </si>
+  <si>
+    <t>15-12-1997</t>
+  </si>
+  <si>
+    <t>21-08-2004</t>
+  </si>
+  <si>
+    <t>14-02-1995</t>
+  </si>
+  <si>
     <t>04-06-2010</t>
   </si>
   <si>
     <t>02-09-1998</t>
   </si>
   <si>
-    <t>06-03-1989</t>
-  </si>
-  <si>
-    <t>14-03-1986</t>
-  </si>
-  <si>
-    <t>06-08-1960</t>
-  </si>
-  <si>
-    <t>27-03-1957</t>
-  </si>
-  <si>
-    <t>18-08-2006</t>
-  </si>
-  <si>
-    <t>17-02-1980</t>
+    <t>06-12-2010</t>
+  </si>
+  <si>
+    <t>02-07-2000</t>
   </si>
   <si>
     <t>27-08-2003</t>
   </si>
   <si>
-    <t>03-01-1979</t>
-  </si>
-  <si>
-    <t>08-01-2005</t>
-  </si>
-  <si>
-    <t>01-04-2000</t>
-  </si>
-  <si>
-    <t>21-11-1988</t>
-  </si>
-  <si>
-    <t>19-03-1975</t>
-  </si>
-  <si>
-    <t>15-12-1997</t>
-  </si>
-  <si>
-    <t>21-08-2004</t>
-  </si>
-  <si>
-    <t>06-12-2010</t>
-  </si>
-  <si>
-    <t>02-07-2000</t>
-  </si>
-  <si>
-    <t>14-02-1995</t>
+    <t>30-08-2001</t>
+  </si>
+  <si>
+    <t>09-10-1991</t>
+  </si>
+  <si>
+    <t>04-04-1996</t>
+  </si>
+  <si>
+    <t>03-04-1976</t>
+  </si>
+  <si>
+    <t>27-09-2002</t>
+  </si>
+  <si>
+    <t>23-09-1994</t>
+  </si>
+  <si>
+    <t>20-05-1981</t>
+  </si>
+  <si>
+    <t>06-08-1998</t>
+  </si>
+  <si>
+    <t>03-02-1988</t>
+  </si>
+  <si>
+    <t>29-08-2000</t>
+  </si>
+  <si>
+    <t>13-12-1999</t>
+  </si>
+  <si>
+    <t>30-08-2010</t>
+  </si>
+  <si>
+    <t>02-01-1992</t>
   </si>
   <si>
     <t>15-09-1947</t>
   </si>
   <si>
-    <t>09-10-1991</t>
-  </si>
-  <si>
-    <t>04-04-1996</t>
-  </si>
-  <si>
-    <t>23-09-1994</t>
-  </si>
-  <si>
-    <t>20-05-1981</t>
-  </si>
-  <si>
-    <t>06-08-1998</t>
-  </si>
-  <si>
-    <t>03-04-1976</t>
+    <t>19-11-1990</t>
+  </si>
+  <si>
+    <t>12-08-1985</t>
+  </si>
+  <si>
+    <t>07-01-2006</t>
+  </si>
+  <si>
+    <t>02-06-2005</t>
   </si>
   <si>
     <t>21-11-1995</t>
   </si>
   <si>
-    <t>29-08-2000</t>
-  </si>
-  <si>
-    <t>13-12-1999</t>
-  </si>
-  <si>
-    <t>27-09-2002</t>
-  </si>
-  <si>
-    <t>19-11-1990</t>
-  </si>
-  <si>
-    <t>12-08-1985</t>
-  </si>
-  <si>
-    <t>30-08-2010</t>
+    <t>23-07-2004</t>
+  </si>
+  <si>
+    <t>21-05-2010</t>
+  </si>
+  <si>
+    <t>16-07-1999</t>
+  </si>
+  <si>
+    <t>06-06-1998</t>
+  </si>
+  <si>
+    <t>12-02-1999</t>
+  </si>
+  <si>
+    <t>09-12-1991</t>
+  </si>
+  <si>
+    <t>10-01-1986</t>
   </si>
   <si>
     <t>22-02-1975</t>
   </si>
   <si>
-    <t>23-07-2004</t>
-  </si>
-  <si>
-    <t>02-01-1992</t>
-  </si>
-  <si>
-    <t>07-01-2006</t>
-  </si>
-  <si>
-    <t>09-12-1991</t>
-  </si>
-  <si>
-    <t>02-06-2005</t>
-  </si>
-  <si>
-    <t>16-07-1999</t>
-  </si>
-  <si>
     <t>MENDOZA_MURILLOO21@HOTMAIL.COM</t>
   </si>
   <si>
     <t>ACOSTARIVS@GMAIL.COM</t>
   </si>
   <si>
+    <t>CESARBER27@HOTMAIL.COM</t>
+  </si>
+  <si>
     <t>YOVANYALVRADO@GMAIL.COM</t>
   </si>
   <si>
+    <t>GISELBARO@HOTMAIL.COM</t>
+  </si>
+  <si>
+    <t>DARIOGS1486@ICLOUD.COM</t>
+  </si>
+  <si>
+    <t>DIEGO.MEDINA@YAHOO.COM</t>
+  </si>
+  <si>
     <t>JOSEIGNACIOJOAN@GMAIL.COM</t>
   </si>
   <si>
     <t>AALER22398@GMAIL.COM</t>
   </si>
   <si>
+    <t>ROMERO.MARTHA50@ICLOUD.COM</t>
+  </si>
+  <si>
+    <t>ALEX57ROMERO@GMAIL.COM</t>
+  </si>
+  <si>
+    <t>VEGA.LESLIE.3E@GMAIL.COM</t>
+  </si>
+  <si>
+    <t>RICARDITOTAPIA2129@GMAIL.COM</t>
+  </si>
+  <si>
     <t>FERGIE.LAZALDE@GMAIL.COM</t>
   </si>
   <si>
+    <t>VIVIARVAYO@GMAIL.COM</t>
+  </si>
+  <si>
+    <t>ESMERALDA.JAVALERA@HOTMAIL.COM</t>
+  </si>
+  <si>
+    <t>CHACLAUDIA5@HOTMAIL.COM</t>
+  </si>
+  <si>
+    <t>ITZELT.DELAROSA@GMAIL.COM</t>
+  </si>
+  <si>
+    <t>ABRAHAM30510@GMAIL.COM</t>
+  </si>
+  <si>
+    <t>NICOLLE.BUSTAMANTE@UABC.EDU.MX</t>
+  </si>
+  <si>
+    <t>YAHIRSALGADO021@GMAIL.COM</t>
+  </si>
+  <si>
+    <t>JUANM_1495@HOTMAIL.COM</t>
+  </si>
+  <si>
     <t>ALARCONISABELLA347@GMAIL.COM</t>
   </si>
   <si>
     <t>GISSELSILVIA98@GMAIL.COM</t>
   </si>
   <si>
-    <t>DIEGO.MEDINA@YAHOO.COM</t>
-  </si>
-  <si>
-    <t>DARIOGS1486@ICLOUD.COM</t>
-  </si>
-  <si>
-    <t>ROMERO.MARTHA50@ICLOUD.COM</t>
-  </si>
-  <si>
-    <t>ALEX57ROMERO@GMAIL.COM</t>
-  </si>
-  <si>
-    <t>VEGA.LESLIE.3E@GMAIL.COM</t>
-  </si>
-  <si>
-    <t>CHACLAUDIA5@HOTMAIL.COM</t>
+    <t>DANTE.GARCIA@INSTITUTOKINO.EDU.MX</t>
+  </si>
+  <si>
+    <t>BELLOBAINES.1982@GMAIL.COM</t>
   </si>
   <si>
     <t>FATIMASM2708@GMAIL.COM</t>
   </si>
   <si>
-    <t>VIVIARVAYO@GMAIL.COM</t>
-  </si>
-  <si>
-    <t>ABRAHAM30510@GMAIL.COM</t>
-  </si>
-  <si>
-    <t>RICARDITOTAPIA2129@GMAIL.COM</t>
-  </si>
-  <si>
-    <t>ITZELT.DELAROSA@GMAIL.COM</t>
-  </si>
-  <si>
-    <t>ESMERALDA.JAVALERA@HOTMAIL.COM</t>
-  </si>
-  <si>
-    <t>NICOLLE.BUSTAMANTE@UABC.EDU.MX</t>
-  </si>
-  <si>
-    <t>YAHIRSALGADO021@GMAIL.COM</t>
-  </si>
-  <si>
-    <t>DANTE.GARCIA@INSTITUTOKINO.EDU.MX</t>
-  </si>
-  <si>
-    <t>BELLOBAINES.1982@GMAIL.COM</t>
-  </si>
-  <si>
-    <t>JUANM_1495@HOTMAIL.COM</t>
+    <t>SALASRODRIGUEZVICTORHUGO@GMAIL.COM</t>
+  </si>
+  <si>
+    <t>MANUELANTONIOSILVARUIZ@GMAIL.COM</t>
+  </si>
+  <si>
+    <t>GUADALUPEZAVALAMERCADO@HOTMAIL.COM</t>
+  </si>
+  <si>
+    <t>RRICARDOGARCIA34@ICLOUD.COM</t>
+  </si>
+  <si>
+    <t>NUBIAG3@ICLOUD.COM</t>
+  </si>
+  <si>
+    <t>ZEN_YACE94LIVE@HOTMAIL.COM</t>
+  </si>
+  <si>
+    <t>VIVESISTEMS@GMAIL.COM</t>
+  </si>
+  <si>
+    <t>CECIGPE98@GMAIL.COM</t>
+  </si>
+  <si>
+    <t>VICTORIALLAMAS2000@GMEIL.COM</t>
+  </si>
+  <si>
+    <t>EJNR2E@GMAIL.COM</t>
+  </si>
+  <si>
+    <t>PAOLAALONSOMGZ@GMAIL.COM</t>
+  </si>
+  <si>
+    <t>IAN.SANDOVALTO@GMAIL.COM</t>
+  </si>
+  <si>
+    <t>ELREYES023@GMAIL.COM</t>
   </si>
   <si>
     <t>CARMEN1947@GMAIL.COM</t>
   </si>
   <si>
-    <t>MANUELANTONIOSILVARUIZ@GMAIL.COM</t>
-  </si>
-  <si>
-    <t>GUADALUPEZAVALAMERCADO@HOTMAIL.COM</t>
-  </si>
-  <si>
-    <t>ZEN_YACE94LIVE@HOTMAIL.COM</t>
-  </si>
-  <si>
-    <t>VIVESISTEMS@GMAIL.COM</t>
-  </si>
-  <si>
-    <t>CECIGPE98@GMAIL.COM</t>
-  </si>
-  <si>
-    <t>RRICARDOGARCIA34@ICLOUD.COM</t>
+    <t>KARLILLA15@HOTMAIL.COM</t>
+  </si>
+  <si>
+    <t>COMANCHE87@OUTLOOK.COM</t>
+  </si>
+  <si>
+    <t>RICARDOPZK200@GMAIL.COM</t>
+  </si>
+  <si>
+    <t>URIELIGNACIOSIDDAVERALO@GMAIL.COM</t>
   </si>
   <si>
     <t>MIGUELAMEZCUA21@GMAIL.COM</t>
   </si>
   <si>
-    <t>EJNR2E@GMAIL.COM</t>
-  </si>
-  <si>
-    <t>PAOLAALONSOMGZ@GMAIL.COM</t>
-  </si>
-  <si>
-    <t>NUBIAG3@ICLOUD.COM</t>
-  </si>
-  <si>
-    <t>KARLILLA15@HOTMAIL.COM</t>
-  </si>
-  <si>
-    <t>COMANCHE87@OUTLOOK.COM</t>
-  </si>
-  <si>
-    <t>IAN.SANDOVALTO@GMAIL.COM</t>
+    <t>VALERIOJESUS913@GMAIL.COM</t>
+  </si>
+  <si>
+    <t>RL25090288@BACHILLERESDESONORA.EDU.MX</t>
+  </si>
+  <si>
+    <t>YOCELINLOPEZ490@GMAIL.COM</t>
+  </si>
+  <si>
+    <t>ALONDRAML1998@GMAIL.COM</t>
+  </si>
+  <si>
+    <t>KARENANDREAISAIS1999@GMAIL.COM</t>
+  </si>
+  <si>
+    <t>ROGELCLAUDIA266@GMAIL.COM</t>
+  </si>
+  <si>
+    <t>LULISLOPEZ999@GMAIL.COM</t>
   </si>
   <si>
     <t>KARINAAQUILESC1975@GMAIL.COM</t>
   </si>
   <si>
-    <t>VALERIOJESUS913@GMAIL.COM</t>
-  </si>
-  <si>
-    <t>ELREYES023@GMAIL.COM</t>
-  </si>
-  <si>
-    <t>RICARDOPZK200@GMAIL.COM</t>
-  </si>
-  <si>
-    <t>ROGELCLAUDIA266@GMAIL.COM</t>
-  </si>
-  <si>
-    <t>URIELIGNACIOSIDDAVERALO@GMAIL.COM</t>
-  </si>
-  <si>
-    <t>YOCELINLOPEZ490@GMAIL.COM</t>
-  </si>
-  <si>
     <t>11-01-2025 05:38:19</t>
   </si>
   <si>
     <t>06-02-2025 18:37:15</t>
   </si>
   <si>
+    <t>16-10-2025 19:03:26</t>
+  </si>
+  <si>
     <t>29-06-2021 18:23:17</t>
   </si>
   <si>
+    <t>19-07-2022 07:14:06</t>
+  </si>
+  <si>
+    <t>02-02-2026 17:03:53</t>
+  </si>
+  <si>
+    <t>02-02-2026 05:44:27</t>
+  </si>
+  <si>
     <t>03-10-2025 19:18:42</t>
   </si>
   <si>
     <t>24-12-2025 07:23:05</t>
   </si>
   <si>
+    <t>02-02-2026 13:57:36</t>
+  </si>
+  <si>
+    <t>02-02-2026 14:07:14</t>
+  </si>
+  <si>
+    <t>02-02-2026 16:08:34</t>
+  </si>
+  <si>
+    <t>03-02-2026 19:10:40</t>
+  </si>
+  <si>
     <t>21-01-2026 11:47:08</t>
   </si>
   <si>
+    <t>03-02-2026 18:01:17</t>
+  </si>
+  <si>
+    <t>04-02-2026 21:09:01</t>
+  </si>
+  <si>
+    <t>01-02-2026 09:25:23</t>
+  </si>
+  <si>
+    <t>03-02-2026 18:20:07</t>
+  </si>
+  <si>
+    <t>04-02-2026 07:26:12</t>
+  </si>
+  <si>
+    <t>05-02-2026 10:43:03</t>
+  </si>
+  <si>
+    <t>05-02-2026 05:58:43</t>
+  </si>
+  <si>
+    <t>05-02-2026 10:41:41</t>
+  </si>
+  <si>
     <t>01-02-2026 10:00:33</t>
   </si>
   <si>
     <t>01-02-2026 10:50:32</t>
   </si>
   <si>
-    <t>02-02-2026 05:44:27</t>
-  </si>
-  <si>
-    <t>02-02-2026 17:03:53</t>
-  </si>
-  <si>
-    <t>02-02-2026 13:57:36</t>
-  </si>
-  <si>
-    <t>02-02-2026 14:07:14</t>
-  </si>
-  <si>
-    <t>02-02-2026 16:08:34</t>
-  </si>
-  <si>
-    <t>01-02-2026 09:25:23</t>
+    <t>03-02-2026 14:43:23</t>
+  </si>
+  <si>
+    <t>03-02-2026 17:27:01</t>
   </si>
   <si>
     <t>02-02-2026 18:15:23</t>
   </si>
   <si>
-    <t>03-02-2026 18:01:17</t>
-  </si>
-  <si>
-    <t>04-02-2026 07:26:12</t>
-  </si>
-  <si>
-    <t>03-02-2026 19:10:40</t>
-  </si>
-  <si>
-    <t>03-02-2026 18:20:07</t>
-  </si>
-  <si>
-    <t>04-02-2026 21:09:01</t>
-  </si>
-  <si>
-    <t>05-02-2026 10:43:03</t>
-  </si>
-  <si>
-    <t>05-02-2026 05:58:43</t>
-  </si>
-  <si>
-    <t>03-02-2026 14:43:23</t>
-  </si>
-  <si>
-    <t>03-02-2026 17:27:01</t>
-  </si>
-  <si>
-    <t>05-02-2026 10:41:41</t>
+    <t>09-02-2026 05:08:33</t>
+  </si>
+  <si>
+    <t>09-02-2026 16:10:49</t>
+  </si>
+  <si>
+    <t>09-02-2026 16:34:55</t>
+  </si>
+  <si>
+    <t>10-02-2026 05:34:48</t>
+  </si>
+  <si>
+    <t>10-02-2026 19:11:57</t>
+  </si>
+  <si>
+    <t>10-02-2026 09:19:09</t>
+  </si>
+  <si>
+    <t>09-02-2026 21:13:12</t>
+  </si>
+  <si>
+    <t>10-02-2026 08:25:29</t>
+  </si>
+  <si>
+    <t>16-02-2026 07:59:39</t>
+  </si>
+  <si>
+    <t>10-02-2026 19:39:03</t>
+  </si>
+  <si>
+    <t>10-02-2026 19:41:46</t>
+  </si>
+  <si>
+    <t>10-02-2026 20:35:22</t>
+  </si>
+  <si>
+    <t>12-02-2026 17:35:55</t>
   </si>
   <si>
     <t>04-02-2026 21:10:39</t>
   </si>
   <si>
-    <t>09-02-2026 16:10:49</t>
-  </si>
-  <si>
-    <t>09-02-2026 16:34:55</t>
-  </si>
-  <si>
-    <t>10-02-2026 09:19:09</t>
-  </si>
-  <si>
-    <t>09-02-2026 21:13:12</t>
-  </si>
-  <si>
-    <t>10-02-2026 08:25:29</t>
-  </si>
-  <si>
-    <t>10-02-2026 05:34:48</t>
+    <t>09-02-2026 21:11:28</t>
+  </si>
+  <si>
+    <t>10-02-2026 05:40:54</t>
+  </si>
+  <si>
+    <t>14-02-2026 06:48:50</t>
+  </si>
+  <si>
+    <t>13-02-2026 16:28:37</t>
   </si>
   <si>
     <t>10-02-2026 20:37:24</t>
   </si>
   <si>
-    <t>10-02-2026 19:39:03</t>
-  </si>
-  <si>
-    <t>10-02-2026 19:41:46</t>
-  </si>
-  <si>
-    <t>10-02-2026 19:11:57</t>
-  </si>
-  <si>
-    <t>09-02-2026 21:11:28</t>
-  </si>
-  <si>
-    <t>10-02-2026 05:40:54</t>
-  </si>
-  <si>
-    <t>10-02-2026 20:35:22</t>
+    <t>10-02-2026 19:05:03</t>
+  </si>
+  <si>
+    <t>16-02-2026 13:12:33</t>
+  </si>
+  <si>
+    <t>15-02-2026 11:25:12</t>
+  </si>
+  <si>
+    <t>17-02-2026 17:23:47</t>
+  </si>
+  <si>
+    <t>17-02-2026 14:45:48</t>
+  </si>
+  <si>
+    <t>15-02-2026 12:34:47</t>
+  </si>
+  <si>
+    <t>16-02-2026 07:40:00</t>
   </si>
   <si>
     <t>10-02-2026 17:14:23</t>
   </si>
   <si>
-    <t>10-02-2026 19:05:03</t>
-  </si>
-  <si>
-    <t>12-02-2026 17:35:55</t>
-  </si>
-  <si>
-    <t>14-02-2026 06:48:50</t>
-  </si>
-  <si>
-    <t>15-02-2026 12:34:47</t>
-  </si>
-  <si>
-    <t>13-02-2026 16:28:37</t>
-  </si>
-  <si>
-    <t>15-02-2026 11:25:12</t>
+    <t>inscripcion promo 199</t>
   </si>
   <si>
     <t>Tarifas 2026 LE</t>
@@ -1435,210 +1651,246 @@
     <t>PROMO FEBRERO 12 MESES</t>
   </si>
   <si>
+    <t>1 MES $899</t>
+  </si>
+  <si>
+    <t>CONVENIOS $549</t>
+  </si>
+  <si>
+    <t>PLAN FAMILIAR RECURRENTE $999</t>
+  </si>
+  <si>
     <t>PLAN FAMILIA / AMIGOS X $499</t>
   </si>
   <si>
-    <t>CONVENIOS $549</t>
+    <t>DOMICILIADO 12 MESES $549 LE</t>
+  </si>
+  <si>
+    <t>PLAN RECURRENTE PAGO INCIAL $1,449 LE</t>
   </si>
   <si>
     <t>RECURRENTE $649 LE</t>
   </si>
   <si>
-    <t>PLAN FAMILIAR RECURRENTE $999</t>
-  </si>
-  <si>
-    <t>DOMICILIADO 12 MESES $549 LE</t>
-  </si>
-  <si>
-    <t>PLAN RECURRENTE PAGO INCIAL $1,449 LE</t>
-  </si>
-  <si>
     <t>499</t>
   </si>
   <si>
+    <t>899</t>
+  </si>
+  <si>
     <t>549</t>
   </si>
   <si>
+    <t>999</t>
+  </si>
+  <si>
+    <t>1449</t>
+  </si>
+  <si>
     <t>649</t>
   </si>
   <si>
-    <t>999</t>
-  </si>
-  <si>
-    <t>1449</t>
-  </si>
-  <si>
     <t>13-02-2026 18:16:08</t>
   </si>
   <si>
     <t>13-02-2026 05:21:27</t>
   </si>
   <si>
+    <t>17-02-2026 10:45:09</t>
+  </si>
+  <si>
     <t>12-02-2026 05:24:56</t>
   </si>
   <si>
+    <t>17-02-2026 09:24:03</t>
+  </si>
+  <si>
+    <t>02-02-2026 17:04:52</t>
+  </si>
+  <si>
+    <t>02-02-2026 05:46:51</t>
+  </si>
+  <si>
     <t>13-02-2026 18:41:08</t>
   </si>
   <si>
     <t>10-02-2026 05:56:10</t>
   </si>
   <si>
+    <t>02-02-2026 14:04:27</t>
+  </si>
+  <si>
+    <t>02-02-2026 14:09:30</t>
+  </si>
+  <si>
+    <t>02-02-2026 16:43:55</t>
+  </si>
+  <si>
+    <t>03-02-2026 19:13:30</t>
+  </si>
+  <si>
     <t>11-02-2026 08:22:24</t>
   </si>
   <si>
+    <t>03-02-2026 18:16:20</t>
+  </si>
+  <si>
+    <t>11-02-2026 15:06:43</t>
+  </si>
+  <si>
+    <t>03-02-2026 05:30:52</t>
+  </si>
+  <si>
+    <t>14-02-2026 12:53:49</t>
+  </si>
+  <si>
+    <t>04-02-2026 07:29:18</t>
+  </si>
+  <si>
+    <t>11-02-2026 13:33:23</t>
+  </si>
+  <si>
+    <t>05-02-2026 06:04:50</t>
+  </si>
+  <si>
+    <t>11-02-2026 13:27:47</t>
+  </si>
+  <si>
     <t>01-02-2026 10:05:34</t>
   </si>
   <si>
     <t>01-02-2026 10:53:31</t>
   </si>
   <si>
-    <t>02-02-2026 05:46:51</t>
-  </si>
-  <si>
-    <t>02-02-2026 17:04:52</t>
-  </si>
-  <si>
-    <t>02-02-2026 14:04:27</t>
-  </si>
-  <si>
-    <t>02-02-2026 14:09:30</t>
-  </si>
-  <si>
-    <t>02-02-2026 16:43:55</t>
-  </si>
-  <si>
-    <t>03-02-2026 05:30:52</t>
+    <t>03-02-2026 14:44:52</t>
+  </si>
+  <si>
+    <t>03-02-2026 17:32:11</t>
   </si>
   <si>
     <t>02-02-2026 18:20:31</t>
   </si>
   <si>
-    <t>03-02-2026 18:16:20</t>
-  </si>
-  <si>
-    <t>04-02-2026 07:29:18</t>
-  </si>
-  <si>
-    <t>03-02-2026 19:13:30</t>
-  </si>
-  <si>
-    <t>14-02-2026 12:53:49</t>
-  </si>
-  <si>
-    <t>11-02-2026 15:06:43</t>
-  </si>
-  <si>
-    <t>11-02-2026 13:33:23</t>
-  </si>
-  <si>
-    <t>05-02-2026 06:04:50</t>
-  </si>
-  <si>
-    <t>03-02-2026 14:44:52</t>
-  </si>
-  <si>
-    <t>03-02-2026 17:32:11</t>
-  </si>
-  <si>
-    <t>11-02-2026 13:27:47</t>
+    <t>17-02-2026 16:21:53</t>
+  </si>
+  <si>
+    <t>09-02-2026 16:12:25</t>
+  </si>
+  <si>
+    <t>09-02-2026 16:37:21</t>
+  </si>
+  <si>
+    <t>11-02-2026 06:33:27</t>
+  </si>
+  <si>
+    <t>10-02-2026 19:16:21</t>
+  </si>
+  <si>
+    <t>12-02-2026 18:37:07</t>
+  </si>
+  <si>
+    <t>11-02-2026 21:02:27</t>
+  </si>
+  <si>
+    <t>10-02-2026 08:31:37</t>
+  </si>
+  <si>
+    <t>16-02-2026 08:07:18</t>
+  </si>
+  <si>
+    <t>11-02-2026 19:15:15</t>
+  </si>
+  <si>
+    <t>11-02-2026 19:11:46</t>
+  </si>
+  <si>
+    <t>11-02-2026 21:04:30</t>
+  </si>
+  <si>
+    <t>14-02-2026 10:17:45</t>
   </si>
   <si>
     <t>11-02-2026 15:03:22</t>
   </si>
   <si>
-    <t>09-02-2026 16:12:25</t>
-  </si>
-  <si>
-    <t>09-02-2026 16:37:21</t>
-  </si>
-  <si>
-    <t>12-02-2026 18:37:07</t>
-  </si>
-  <si>
-    <t>11-02-2026 21:02:27</t>
-  </si>
-  <si>
-    <t>10-02-2026 08:31:37</t>
-  </si>
-  <si>
-    <t>11-02-2026 06:33:27</t>
+    <t>11-02-2026 20:58:26</t>
+  </si>
+  <si>
+    <t>10-02-2026 05:52:22</t>
+  </si>
+  <si>
+    <t>14-02-2026 08:02:52</t>
+  </si>
+  <si>
+    <t>13-02-2026 16:34:53</t>
   </si>
   <si>
     <t>12-02-2026 20:00:11</t>
   </si>
   <si>
-    <t>11-02-2026 19:15:15</t>
-  </si>
-  <si>
-    <t>11-02-2026 19:11:46</t>
-  </si>
-  <si>
-    <t>10-02-2026 19:16:21</t>
-  </si>
-  <si>
-    <t>11-02-2026 20:58:26</t>
-  </si>
-  <si>
-    <t>10-02-2026 05:52:22</t>
-  </si>
-  <si>
-    <t>11-02-2026 21:04:30</t>
+    <t>10-02-2026 19:09:25</t>
+  </si>
+  <si>
+    <t>16-02-2026 13:13:37</t>
+  </si>
+  <si>
+    <t>15-02-2026 11:31:12</t>
+  </si>
+  <si>
+    <t>17-02-2026 17:32:20</t>
+  </si>
+  <si>
+    <t>17-02-2026 14:50:44</t>
+  </si>
+  <si>
+    <t>15-02-2026 12:38:45</t>
+  </si>
+  <si>
+    <t>16-02-2026 07:43:57</t>
   </si>
   <si>
     <t>10-02-2026 17:19:39</t>
   </si>
   <si>
-    <t>10-02-2026 19:09:25</t>
-  </si>
-  <si>
-    <t>14-02-2026 10:17:45</t>
-  </si>
-  <si>
-    <t>14-02-2026 08:02:52</t>
-  </si>
-  <si>
-    <t>15-02-2026 12:38:45</t>
-  </si>
-  <si>
-    <t>13-02-2026 16:34:53</t>
-  </si>
-  <si>
-    <t>15-02-2026 11:31:12</t>
-  </si>
-  <si>
     <t>13-03-2026 23:59:59</t>
   </si>
   <si>
     <t>14-03-2026 23:59:59</t>
   </si>
   <si>
+    <t>17-03-2026 23:59:59</t>
+  </si>
+  <si>
     <t>12-03-2026 23:59:59</t>
   </si>
   <si>
+    <t>02-03-2026 23:59:59</t>
+  </si>
+  <si>
     <t>10-03-2026 23:59:59</t>
   </si>
   <si>
+    <t>03-03-2026 23:59:59</t>
+  </si>
+  <si>
     <t>11-03-2026 23:59:59</t>
   </si>
   <si>
+    <t>04-03-2026 23:59:59</t>
+  </si>
+  <si>
+    <t>05-03-2026 23:59:59</t>
+  </si>
+  <si>
     <t>01-03-2026 23:59:59</t>
   </si>
   <si>
-    <t>02-03-2026 23:59:59</t>
-  </si>
-  <si>
-    <t>03-03-2026 23:59:59</t>
-  </si>
-  <si>
-    <t>04-03-2026 23:59:59</t>
-  </si>
-  <si>
-    <t>05-03-2026 23:59:59</t>
-  </si>
-  <si>
     <t>09-03-2026 23:59:59</t>
   </si>
   <si>
+    <t>16-03-2026 23:59:59</t>
+  </si>
+  <si>
     <t>15-03-2026 23:59:59</t>
   </si>
   <si>
@@ -1648,120 +1900,138 @@
     <t>13-02-2026 05:19:56</t>
   </si>
   <si>
+    <t>17-02-2026 10:44:24</t>
+  </si>
+  <si>
     <t>12-02-2026 05:23:53</t>
   </si>
   <si>
+    <t>02-02-2026 05:45:55</t>
+  </si>
+  <si>
     <t>13-02-2026 18:39:22</t>
   </si>
   <si>
     <t>10-02-2026 05:55:08</t>
   </si>
   <si>
+    <t>02-02-2026 14:03:30</t>
+  </si>
+  <si>
+    <t>02-02-2026 14:08:43</t>
+  </si>
+  <si>
+    <t>02-02-2026 16:12:35</t>
+  </si>
+  <si>
+    <t>03-02-2026 19:12:47</t>
+  </si>
+  <si>
     <t>11-02-2026 08:21:44</t>
   </si>
   <si>
+    <t>03-02-2026 18:05:39</t>
+  </si>
+  <si>
+    <t>11-02-2026 15:05:40</t>
+  </si>
+  <si>
+    <t>03-02-2026 05:30:25</t>
+  </si>
+  <si>
+    <t>04-02-2026 07:28:45</t>
+  </si>
+  <si>
+    <t>11-02-2026 13:31:59</t>
+  </si>
+  <si>
+    <t>11-02-2026 13:26:38</t>
+  </si>
+  <si>
     <t>01-02-2026 10:52:55</t>
   </si>
   <si>
-    <t>02-02-2026 05:45:55</t>
-  </si>
-  <si>
-    <t>02-02-2026 14:03:30</t>
-  </si>
-  <si>
-    <t>02-02-2026 14:08:43</t>
-  </si>
-  <si>
-    <t>02-02-2026 16:12:35</t>
-  </si>
-  <si>
-    <t>03-02-2026 05:30:25</t>
-  </si>
-  <si>
     <t>02-02-2026 18:19:16</t>
   </si>
   <si>
-    <t>03-02-2026 18:05:39</t>
-  </si>
-  <si>
-    <t>04-02-2026 07:28:45</t>
-  </si>
-  <si>
-    <t>03-02-2026 19:12:47</t>
-  </si>
-  <si>
-    <t>11-02-2026 15:05:40</t>
-  </si>
-  <si>
-    <t>11-02-2026 13:31:59</t>
-  </si>
-  <si>
-    <t>11-02-2026 13:26:38</t>
+    <t>17-02-2026 16:21:11</t>
+  </si>
+  <si>
+    <t>09-02-2026 16:11:51</t>
+  </si>
+  <si>
+    <t>09-02-2026 16:36:34</t>
+  </si>
+  <si>
+    <t>11-02-2026 06:32:18</t>
+  </si>
+  <si>
+    <t>10-02-2026 19:15:42</t>
+  </si>
+  <si>
+    <t>12-02-2026 18:33:55</t>
+  </si>
+  <si>
+    <t>11-02-2026 21:01:55</t>
+  </si>
+  <si>
+    <t>10-02-2026 08:30:41</t>
+  </si>
+  <si>
+    <t>16-02-2026 08:06:23</t>
+  </si>
+  <si>
+    <t>11-02-2026 19:14:37</t>
+  </si>
+  <si>
+    <t>11-02-2026 19:10:56</t>
+  </si>
+  <si>
+    <t>11-02-2026 21:03:57</t>
+  </si>
+  <si>
+    <t>14-02-2026 10:17:11</t>
   </si>
   <si>
     <t>11-02-2026 15:02:18</t>
   </si>
   <si>
-    <t>09-02-2026 16:11:51</t>
-  </si>
-  <si>
-    <t>09-02-2026 16:36:34</t>
-  </si>
-  <si>
-    <t>12-02-2026 18:33:55</t>
-  </si>
-  <si>
-    <t>11-02-2026 21:01:55</t>
-  </si>
-  <si>
-    <t>10-02-2026 08:30:41</t>
-  </si>
-  <si>
-    <t>11-02-2026 06:32:18</t>
+    <t>11-02-2026 20:57:45</t>
+  </si>
+  <si>
+    <t>10-02-2026 05:49:58</t>
+  </si>
+  <si>
+    <t>14-02-2026 08:01:46</t>
+  </si>
+  <si>
+    <t>13-02-2026 16:34:13</t>
   </si>
   <si>
     <t>12-02-2026 19:59:09</t>
   </si>
   <si>
-    <t>11-02-2026 19:14:37</t>
-  </si>
-  <si>
-    <t>11-02-2026 19:10:56</t>
-  </si>
-  <si>
-    <t>10-02-2026 19:15:42</t>
-  </si>
-  <si>
-    <t>11-02-2026 20:57:45</t>
-  </si>
-  <si>
-    <t>10-02-2026 05:49:58</t>
-  </si>
-  <si>
-    <t>11-02-2026 21:03:57</t>
+    <t>10-02-2026 19:08:45</t>
+  </si>
+  <si>
+    <t>15-02-2026 11:29:38</t>
+  </si>
+  <si>
+    <t>17-02-2026 17:31:40</t>
+  </si>
+  <si>
+    <t>17-02-2026 14:49:35</t>
+  </si>
+  <si>
+    <t>15-02-2026 12:37:38</t>
+  </si>
+  <si>
+    <t>16-02-2026 07:43:12</t>
   </si>
   <si>
     <t>10-02-2026 17:18:56</t>
   </si>
   <si>
-    <t>10-02-2026 19:08:45</t>
-  </si>
-  <si>
-    <t>14-02-2026 10:17:11</t>
-  </si>
-  <si>
-    <t>14-02-2026 08:01:46</t>
-  </si>
-  <si>
-    <t>15-02-2026 12:37:38</t>
-  </si>
-  <si>
-    <t>13-02-2026 16:34:13</t>
-  </si>
-  <si>
-    <t>15-02-2026 11:29:38</t>
-  </si>
-  <si>
     <t>2</t>
   </si>
   <si>
@@ -1771,138 +2041,162 @@
     <t>26150522308700001658</t>
   </si>
   <si>
+    <t>26150522424240001807</t>
+  </si>
+  <si>
     <t>26150522281110001621</t>
   </si>
   <si>
+    <t>26150522422860001804</t>
+  </si>
+  <si>
+    <t>26150522017940001237</t>
+  </si>
+  <si>
+    <t>26150521997870001209</t>
+  </si>
+  <si>
     <t>26150522328580001685</t>
   </si>
   <si>
     <t>26150522222600001523</t>
   </si>
   <si>
+    <t>26150522011860001229</t>
+  </si>
+  <si>
+    <t>26150522012090001230</t>
+  </si>
+  <si>
+    <t>26150522017110001235</t>
+  </si>
+  <si>
+    <t>26150522055450001315</t>
+  </si>
+  <si>
     <t>26070522259520003153</t>
   </si>
   <si>
+    <t>26150522052430001305</t>
+  </si>
+  <si>
+    <t>26150522265920001586</t>
+  </si>
+  <si>
+    <t>26150522029990001268</t>
+  </si>
+  <si>
+    <t>26140522348900001443</t>
+  </si>
+  <si>
+    <t>26150522068240001330</t>
+  </si>
+  <si>
+    <t>26150522264110001579</t>
+  </si>
+  <si>
+    <t>26150522098340001363</t>
+  </si>
+  <si>
+    <t>26150522264040001578</t>
+  </si>
+  <si>
     <t>26150521988630001200</t>
   </si>
   <si>
     <t>26150521989600001201</t>
   </si>
   <si>
-    <t>26150521997870001209</t>
-  </si>
-  <si>
-    <t>26150522017940001237</t>
-  </si>
-  <si>
-    <t>26150522011860001229</t>
-  </si>
-  <si>
-    <t>26150522012090001230</t>
-  </si>
-  <si>
-    <t>26150522017110001235</t>
-  </si>
-  <si>
-    <t>26150522029990001268</t>
+    <t>26150522041730001279</t>
+  </si>
+  <si>
+    <t>26150522049660001299</t>
   </si>
   <si>
     <t>26150522020390001251</t>
   </si>
   <si>
-    <t>26150522052430001305</t>
-  </si>
-  <si>
-    <t>26150522068240001330</t>
-  </si>
-  <si>
-    <t>26150522055450001315</t>
-  </si>
-  <si>
-    <t>26140522348900001443</t>
-  </si>
-  <si>
-    <t>26150522265920001586</t>
-  </si>
-  <si>
-    <t>26150522264110001579</t>
-  </si>
-  <si>
-    <t>26150522098340001363</t>
-  </si>
-  <si>
-    <t>26150522041730001279</t>
-  </si>
-  <si>
-    <t>26150522049660001299</t>
-  </si>
-  <si>
-    <t>26150522264040001578</t>
+    <t>26150522433690001818</t>
+  </si>
+  <si>
+    <t>26150522197240001486</t>
+  </si>
+  <si>
+    <t>26150522198880001489</t>
+  </si>
+  <si>
+    <t>26150522257790001574</t>
+  </si>
+  <si>
+    <t>26150522246290001554</t>
+  </si>
+  <si>
+    <t>26150522302860001640</t>
+  </si>
+  <si>
+    <t>26150522279160001614</t>
+  </si>
+  <si>
+    <t>26150522225760001528</t>
+  </si>
+  <si>
+    <t>26150522380380001737</t>
+  </si>
+  <si>
+    <t>26150522276380001607</t>
+  </si>
+  <si>
+    <t>26150522276280001606</t>
+  </si>
+  <si>
+    <t>26150522279200001615</t>
+  </si>
+  <si>
+    <t>26150522345630001701</t>
   </si>
   <si>
     <t>26150522265830001585</t>
   </si>
   <si>
-    <t>26150522197240001486</t>
-  </si>
-  <si>
-    <t>26150522198880001489</t>
-  </si>
-  <si>
-    <t>26150522302860001640</t>
-  </si>
-  <si>
-    <t>26150522279160001614</t>
-  </si>
-  <si>
-    <t>26150522225760001528</t>
-  </si>
-  <si>
-    <t>26150522257790001574</t>
+    <t>26150522279010001613</t>
+  </si>
+  <si>
+    <t>26150522222520001522</t>
+  </si>
+  <si>
+    <t>26150522343510001694</t>
+  </si>
+  <si>
+    <t>26150522324410001674</t>
   </si>
   <si>
     <t>26150522305570001650</t>
   </si>
   <si>
-    <t>26150522276380001607</t>
-  </si>
-  <si>
-    <t>26150522276280001606</t>
-  </si>
-  <si>
-    <t>26150522246290001554</t>
-  </si>
-  <si>
-    <t>26150522279010001613</t>
-  </si>
-  <si>
-    <t>26150522222520001522</t>
-  </si>
-  <si>
-    <t>26150522279200001615</t>
+    <t>26150522245980001553</t>
+  </si>
+  <si>
+    <t>26150522388250001746</t>
+  </si>
+  <si>
+    <t>26150522364500001715</t>
+  </si>
+  <si>
+    <t>26150522437780001826</t>
+  </si>
+  <si>
+    <t>26150522430060001816</t>
+  </si>
+  <si>
+    <t>26150522365800001718</t>
+  </si>
+  <si>
+    <t>26150522379670001736</t>
   </si>
   <si>
     <t>26150522239320001545</t>
   </si>
   <si>
-    <t>26150522245980001553</t>
-  </si>
-  <si>
-    <t>26150522345630001701</t>
-  </si>
-  <si>
-    <t>26150522343510001694</t>
-  </si>
-  <si>
-    <t>26150522365800001718</t>
-  </si>
-  <si>
-    <t>26150522324410001674</t>
-  </si>
-  <si>
-    <t>26150522364500001715</t>
-  </si>
-  <si>
     <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
   </si>
   <si>
@@ -1918,16 +2212,16 @@
     <t>N/D</t>
   </si>
   <si>
+    <t>Martin Ramiro Quiñonez Jauregui</t>
+  </si>
+  <si>
+    <t>Johan Osvaldo Beltran Quiros</t>
+  </si>
+  <si>
+    <t>Juan Eduardo Torres Alcantar</t>
+  </si>
+  <si>
     <t>Jesus Alejandro  Partida Partida</t>
-  </si>
-  <si>
-    <t>Johan Osvaldo Beltran Quiros</t>
-  </si>
-  <si>
-    <t>Juan Eduardo Torres Alcantar</t>
-  </si>
-  <si>
-    <t>Martin Ramiro Quiñonez Jauregui</t>
   </si>
   <si>
     <t>con rutina</t>
@@ -2291,7 +2585,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AC47"/>
+  <dimension ref="A1:AC55"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:29">
@@ -2388,79 +2682,79 @@
         <v>29</v>
       </c>
       <c r="B2" t="s">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="C2" t="s">
-        <v>121</v>
+        <v>137</v>
       </c>
       <c r="D2" t="s">
-        <v>122</v>
+        <v>138</v>
       </c>
       <c r="E2" t="s">
-        <v>168</v>
+        <v>192</v>
       </c>
       <c r="F2" t="s">
-        <v>182</v>
+        <v>217</v>
       </c>
       <c r="G2" t="s">
-        <v>243</v>
+        <v>276</v>
       </c>
       <c r="H2" t="s">
-        <v>245</v>
+        <v>278</v>
       </c>
       <c r="I2" t="s">
-        <v>291</v>
+        <v>332</v>
       </c>
       <c r="J2" t="s">
-        <v>328</v>
+        <v>375</v>
       </c>
       <c r="K2" t="s">
-        <v>330</v>
+        <v>377</v>
       </c>
       <c r="L2" t="s">
-        <v>376</v>
+        <v>431</v>
       </c>
       <c r="M2" t="s">
-        <v>422</v>
+        <v>485</v>
       </c>
       <c r="O2" t="s">
-        <v>469</v>
+        <v>541</v>
       </c>
       <c r="P2" t="s">
-        <v>472</v>
+        <v>544</v>
       </c>
       <c r="Q2" t="s">
-        <v>479</v>
+        <v>552</v>
       </c>
       <c r="R2" t="s">
-        <v>484</v>
+        <v>558</v>
       </c>
       <c r="S2" t="s">
-        <v>530</v>
+        <v>612</v>
       </c>
       <c r="T2" t="s">
-        <v>542</v>
+        <v>626</v>
       </c>
       <c r="U2" t="s">
-        <v>582</v>
+        <v>672</v>
       </c>
       <c r="V2" t="s">
-        <v>244</v>
+        <v>277</v>
       </c>
       <c r="W2" t="s">
         <v>2</v>
       </c>
       <c r="X2" t="s">
-        <v>583</v>
+        <v>673</v>
       </c>
       <c r="AA2" t="s">
-        <v>479</v>
+        <v>552</v>
       </c>
       <c r="AB2" t="s">
-        <v>632</v>
+        <v>730</v>
       </c>
       <c r="AC2" t="s">
-        <v>638</v>
+        <v>736</v>
       </c>
     </row>
     <row r="3" spans="1:29">
@@ -2468,85 +2762,85 @@
         <v>30</v>
       </c>
       <c r="B3" t="s">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="C3" t="s">
-        <v>121</v>
+        <v>137</v>
       </c>
       <c r="D3" t="s">
-        <v>123</v>
+        <v>139</v>
       </c>
       <c r="E3" t="s">
-        <v>169</v>
+        <v>193</v>
       </c>
       <c r="F3" t="s">
-        <v>211</v>
+        <v>241</v>
       </c>
       <c r="G3" t="s">
-        <v>243</v>
+        <v>276</v>
       </c>
       <c r="H3" t="s">
-        <v>246</v>
+        <v>279</v>
       </c>
       <c r="I3" t="s">
-        <v>292</v>
+        <v>333</v>
       </c>
       <c r="J3" t="s">
-        <v>329</v>
+        <v>376</v>
       </c>
       <c r="K3" t="s">
-        <v>331</v>
+        <v>378</v>
       </c>
       <c r="L3" t="s">
-        <v>377</v>
+        <v>432</v>
       </c>
       <c r="M3" t="s">
-        <v>423</v>
+        <v>486</v>
       </c>
       <c r="O3" t="s">
-        <v>469</v>
+        <v>541</v>
       </c>
       <c r="P3" t="s">
-        <v>472</v>
+        <v>544</v>
       </c>
       <c r="Q3" t="s">
-        <v>479</v>
+        <v>552</v>
       </c>
       <c r="R3" t="s">
-        <v>485</v>
+        <v>559</v>
       </c>
       <c r="S3" t="s">
-        <v>531</v>
+        <v>613</v>
       </c>
       <c r="T3" t="s">
-        <v>543</v>
+        <v>627</v>
       </c>
       <c r="U3" t="s">
-        <v>582</v>
+        <v>672</v>
       </c>
       <c r="V3" t="s">
-        <v>582</v>
+        <v>672</v>
       </c>
       <c r="W3" t="s">
         <v>2</v>
       </c>
       <c r="X3" t="s">
-        <v>584</v>
+        <v>674</v>
       </c>
       <c r="Y3" t="s">
-        <v>629</v>
+        <v>727</v>
       </c>
       <c r="Z3" t="s">
-        <v>630</v>
+        <v>728</v>
       </c>
       <c r="AA3" t="s">
-        <v>479</v>
+        <v>552</v>
       </c>
       <c r="AB3" t="s">
-        <v>633</v>
+        <v>731</v>
       </c>
       <c r="AC3" t="s">
-        <v>639</v>
+        <v>737</v>
       </c>
     </row>
     <row r="4" spans="1:29">
@@ -2554,79 +2848,88 @@
         <v>31</v>
       </c>
       <c r="B4" t="s">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="C4" t="s">
-        <v>121</v>
+        <v>137</v>
       </c>
       <c r="D4" t="s">
-        <v>124</v>
+        <v>140</v>
       </c>
       <c r="E4" t="s">
-        <v>170</v>
+        <v>194</v>
       </c>
       <c r="F4" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="G4" t="s">
-        <v>243</v>
+        <v>276</v>
       </c>
       <c r="H4" t="s">
-        <v>247</v>
+        <v>280</v>
       </c>
       <c r="I4" t="s">
-        <v>293</v>
+        <v>334</v>
       </c>
       <c r="J4" t="s">
-        <v>329</v>
+        <v>376</v>
       </c>
       <c r="K4" t="s">
-        <v>332</v>
+        <v>379</v>
       </c>
       <c r="L4" t="s">
-        <v>378</v>
+        <v>433</v>
       </c>
       <c r="M4" t="s">
-        <v>424</v>
+        <v>487</v>
+      </c>
+      <c r="N4" t="s">
+        <v>539</v>
       </c>
       <c r="O4" t="s">
-        <v>469</v>
+        <v>541</v>
       </c>
       <c r="P4" t="s">
-        <v>472</v>
+        <v>544</v>
       </c>
       <c r="Q4" t="s">
-        <v>479</v>
+        <v>552</v>
       </c>
       <c r="R4" t="s">
-        <v>486</v>
+        <v>560</v>
       </c>
       <c r="S4" t="s">
-        <v>532</v>
+        <v>614</v>
       </c>
       <c r="T4" t="s">
-        <v>544</v>
+        <v>628</v>
       </c>
       <c r="U4" t="s">
-        <v>582</v>
+        <v>672</v>
       </c>
       <c r="V4" t="s">
-        <v>244</v>
+        <v>672</v>
       </c>
       <c r="W4" t="s">
         <v>2</v>
       </c>
       <c r="X4" t="s">
-        <v>585</v>
+        <v>675</v>
+      </c>
+      <c r="Y4" t="s">
+        <v>727</v>
+      </c>
+      <c r="Z4" t="s">
+        <v>729</v>
       </c>
       <c r="AA4" t="s">
-        <v>479</v>
+        <v>552</v>
       </c>
       <c r="AB4" t="s">
-        <v>633</v>
+        <v>731</v>
       </c>
       <c r="AC4" t="s">
-        <v>639</v>
+        <v>737</v>
       </c>
     </row>
     <row r="5" spans="1:29">
@@ -2634,85 +2937,79 @@
         <v>32</v>
       </c>
       <c r="B5" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="C5" t="s">
-        <v>121</v>
+        <v>137</v>
       </c>
       <c r="D5" t="s">
-        <v>125</v>
+        <v>141</v>
       </c>
       <c r="E5" t="s">
-        <v>171</v>
+        <v>195</v>
       </c>
       <c r="F5" t="s">
-        <v>213</v>
+        <v>242</v>
       </c>
       <c r="G5" t="s">
-        <v>243</v>
+        <v>276</v>
       </c>
       <c r="H5" t="s">
-        <v>248</v>
+        <v>281</v>
       </c>
       <c r="I5" t="s">
-        <v>294</v>
+        <v>335</v>
       </c>
       <c r="J5" t="s">
-        <v>329</v>
+        <v>376</v>
       </c>
       <c r="K5" t="s">
-        <v>333</v>
+        <v>380</v>
       </c>
       <c r="L5" t="s">
-        <v>379</v>
+        <v>434</v>
       </c>
       <c r="M5" t="s">
-        <v>425</v>
+        <v>488</v>
       </c>
       <c r="O5" t="s">
-        <v>469</v>
+        <v>541</v>
       </c>
       <c r="P5" t="s">
-        <v>472</v>
+        <v>544</v>
       </c>
       <c r="Q5" t="s">
-        <v>479</v>
+        <v>552</v>
       </c>
       <c r="R5" t="s">
-        <v>487</v>
+        <v>561</v>
       </c>
       <c r="S5" t="s">
-        <v>530</v>
+        <v>615</v>
       </c>
       <c r="T5" t="s">
-        <v>545</v>
+        <v>629</v>
       </c>
       <c r="U5" t="s">
-        <v>582</v>
+        <v>672</v>
       </c>
       <c r="V5" t="s">
-        <v>244</v>
+        <v>277</v>
       </c>
       <c r="W5" t="s">
         <v>2</v>
       </c>
       <c r="X5" t="s">
-        <v>586</v>
-      </c>
-      <c r="Y5" t="s">
-        <v>629</v>
-      </c>
-      <c r="Z5" t="s">
-        <v>631</v>
+        <v>676</v>
       </c>
       <c r="AA5" t="s">
-        <v>479</v>
+        <v>552</v>
       </c>
       <c r="AB5" t="s">
-        <v>632</v>
+        <v>731</v>
       </c>
       <c r="AC5" t="s">
-        <v>638</v>
+        <v>737</v>
       </c>
     </row>
     <row r="6" spans="1:29">
@@ -2720,85 +3017,76 @@
         <v>33</v>
       </c>
       <c r="B6" t="s">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="C6" t="s">
-        <v>121</v>
+        <v>137</v>
       </c>
       <c r="D6" t="s">
-        <v>126</v>
+        <v>142</v>
       </c>
       <c r="E6" t="s">
-        <v>172</v>
+        <v>196</v>
       </c>
       <c r="F6" t="s">
-        <v>214</v>
+        <v>243</v>
       </c>
       <c r="G6" t="s">
-        <v>243</v>
+        <v>276</v>
       </c>
       <c r="H6" t="s">
-        <v>249</v>
+        <v>282</v>
       </c>
       <c r="I6" t="s">
-        <v>295</v>
+        <v>137</v>
       </c>
       <c r="J6" t="s">
-        <v>328</v>
+        <v>375</v>
       </c>
       <c r="K6" t="s">
-        <v>334</v>
+        <v>381</v>
       </c>
       <c r="L6" t="s">
-        <v>380</v>
+        <v>435</v>
       </c>
       <c r="M6" t="s">
-        <v>426</v>
+        <v>489</v>
+      </c>
+      <c r="N6" t="s">
+        <v>540</v>
       </c>
       <c r="O6" t="s">
-        <v>469</v>
+        <v>542</v>
       </c>
       <c r="P6" t="s">
-        <v>473</v>
+        <v>545</v>
       </c>
       <c r="Q6" t="s">
-        <v>479</v>
+        <v>553</v>
       </c>
       <c r="R6" t="s">
-        <v>488</v>
+        <v>562</v>
       </c>
       <c r="S6" t="s">
-        <v>533</v>
-      </c>
-      <c r="T6" t="s">
-        <v>546</v>
+        <v>614</v>
       </c>
       <c r="U6" t="s">
-        <v>582</v>
-      </c>
-      <c r="V6" t="s">
-        <v>244</v>
+        <v>672</v>
       </c>
       <c r="W6" t="s">
         <v>2</v>
       </c>
       <c r="X6" t="s">
-        <v>587</v>
-      </c>
-      <c r="Y6" t="s">
-        <v>629</v>
-      </c>
-      <c r="Z6" t="s">
-        <v>630</v>
+        <v>677</v>
       </c>
       <c r="AA6" t="s">
-        <v>479</v>
+        <v>553</v>
       </c>
       <c r="AB6" t="s">
-        <v>633</v>
+        <v>732</v>
       </c>
       <c r="AC6" t="s">
-        <v>639</v>
+        <v>736</v>
       </c>
     </row>
     <row r="7" spans="1:29">
@@ -2806,82 +3094,73 @@
         <v>34</v>
       </c>
       <c r="B7" t="s">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="C7" t="s">
-        <v>121</v>
+        <v>137</v>
       </c>
       <c r="D7" t="s">
-        <v>127</v>
+        <v>143</v>
       </c>
       <c r="E7" t="s">
-        <v>173</v>
+        <v>197</v>
       </c>
       <c r="F7" t="s">
-        <v>215</v>
+        <v>197</v>
       </c>
       <c r="G7" t="s">
-        <v>243</v>
+        <v>276</v>
       </c>
       <c r="H7" t="s">
-        <v>250</v>
-      </c>
-      <c r="I7" t="s">
-        <v>296</v>
+        <v>283</v>
       </c>
       <c r="J7" t="s">
-        <v>328</v>
+        <v>375</v>
       </c>
       <c r="K7" t="s">
-        <v>335</v>
+        <v>382</v>
       </c>
       <c r="L7" t="s">
-        <v>381</v>
+        <v>436</v>
       </c>
       <c r="M7" t="s">
-        <v>427</v>
+        <v>490</v>
+      </c>
+      <c r="N7" t="s">
+        <v>540</v>
       </c>
       <c r="O7" t="s">
-        <v>469</v>
+        <v>542</v>
       </c>
       <c r="P7" t="s">
-        <v>472</v>
+        <v>546</v>
       </c>
       <c r="Q7" t="s">
-        <v>479</v>
+        <v>554</v>
       </c>
       <c r="R7" t="s">
-        <v>489</v>
+        <v>563</v>
       </c>
       <c r="S7" t="s">
-        <v>534</v>
-      </c>
-      <c r="T7" t="s">
-        <v>547</v>
+        <v>616</v>
       </c>
       <c r="U7" t="s">
-        <v>582</v>
-      </c>
-      <c r="V7" t="s">
-        <v>582</v>
+        <v>277</v>
       </c>
       <c r="W7" t="s">
         <v>2</v>
       </c>
       <c r="X7" t="s">
-        <v>588</v>
-      </c>
-      <c r="Y7" t="s">
-        <v>629</v>
+        <v>678</v>
       </c>
       <c r="AA7" t="s">
-        <v>479</v>
+        <v>554</v>
       </c>
       <c r="AB7" t="s">
-        <v>634</v>
+        <v>733</v>
       </c>
       <c r="AC7" t="s">
-        <v>638</v>
+        <v>736</v>
       </c>
     </row>
     <row r="8" spans="1:29">
@@ -2889,73 +3168,82 @@
         <v>35</v>
       </c>
       <c r="B8" t="s">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="C8" t="s">
-        <v>121</v>
+        <v>137</v>
       </c>
       <c r="D8" t="s">
-        <v>128</v>
+        <v>144</v>
       </c>
       <c r="E8" t="s">
-        <v>174</v>
+        <v>198</v>
       </c>
       <c r="F8" t="s">
-        <v>216</v>
+        <v>244</v>
       </c>
       <c r="G8" t="s">
-        <v>243</v>
+        <v>276</v>
       </c>
       <c r="H8" t="s">
-        <v>251</v>
+        <v>284</v>
+      </c>
+      <c r="I8" t="s">
+        <v>336</v>
       </c>
       <c r="J8" t="s">
-        <v>328</v>
+        <v>376</v>
       </c>
       <c r="K8" t="s">
-        <v>336</v>
+        <v>383</v>
       </c>
       <c r="L8" t="s">
-        <v>382</v>
+        <v>437</v>
       </c>
       <c r="M8" t="s">
-        <v>428</v>
+        <v>491</v>
       </c>
       <c r="N8" t="s">
-        <v>468</v>
+        <v>540</v>
       </c>
       <c r="O8" t="s">
-        <v>470</v>
+        <v>543</v>
       </c>
       <c r="P8" t="s">
-        <v>474</v>
+        <v>547</v>
       </c>
       <c r="Q8" t="s">
-        <v>480</v>
+        <v>555</v>
       </c>
       <c r="R8" t="s">
-        <v>490</v>
+        <v>564</v>
       </c>
       <c r="S8" t="s">
-        <v>535</v>
+        <v>616</v>
+      </c>
+      <c r="T8" t="s">
+        <v>630</v>
       </c>
       <c r="U8" t="s">
-        <v>582</v>
+        <v>672</v>
+      </c>
+      <c r="V8" t="s">
+        <v>672</v>
       </c>
       <c r="W8" t="s">
         <v>2</v>
       </c>
       <c r="X8" t="s">
-        <v>589</v>
+        <v>679</v>
       </c>
       <c r="AA8" t="s">
-        <v>480</v>
+        <v>555</v>
       </c>
       <c r="AB8" t="s">
-        <v>632</v>
+        <v>731</v>
       </c>
       <c r="AC8" t="s">
-        <v>638</v>
+        <v>737</v>
       </c>
     </row>
     <row r="9" spans="1:29">
@@ -2963,82 +3251,85 @@
         <v>36</v>
       </c>
       <c r="B9" t="s">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="C9" t="s">
-        <v>121</v>
+        <v>137</v>
       </c>
       <c r="D9" t="s">
-        <v>129</v>
+        <v>145</v>
       </c>
       <c r="E9" t="s">
-        <v>175</v>
+        <v>199</v>
       </c>
       <c r="F9" t="s">
-        <v>217</v>
+        <v>245</v>
       </c>
       <c r="G9" t="s">
-        <v>243</v>
+        <v>276</v>
       </c>
       <c r="H9" t="s">
-        <v>252</v>
+        <v>285</v>
       </c>
       <c r="I9" t="s">
-        <v>297</v>
+        <v>337</v>
       </c>
       <c r="J9" t="s">
-        <v>328</v>
+        <v>376</v>
       </c>
       <c r="K9" t="s">
-        <v>337</v>
+        <v>384</v>
       </c>
       <c r="L9" t="s">
-        <v>383</v>
+        <v>438</v>
       </c>
       <c r="M9" t="s">
-        <v>429</v>
-      </c>
-      <c r="N9" t="s">
-        <v>468</v>
+        <v>492</v>
       </c>
       <c r="O9" t="s">
-        <v>471</v>
+        <v>541</v>
       </c>
       <c r="P9" t="s">
-        <v>475</v>
+        <v>544</v>
       </c>
       <c r="Q9" t="s">
-        <v>481</v>
+        <v>552</v>
       </c>
       <c r="R9" t="s">
-        <v>491</v>
+        <v>565</v>
       </c>
       <c r="S9" t="s">
-        <v>535</v>
+        <v>612</v>
       </c>
       <c r="T9" t="s">
-        <v>548</v>
+        <v>631</v>
       </c>
       <c r="U9" t="s">
-        <v>582</v>
+        <v>672</v>
       </c>
       <c r="V9" t="s">
-        <v>244</v>
+        <v>277</v>
       </c>
       <c r="W9" t="s">
         <v>2</v>
       </c>
       <c r="X9" t="s">
-        <v>590</v>
+        <v>680</v>
+      </c>
+      <c r="Y9" t="s">
+        <v>727</v>
+      </c>
+      <c r="Z9" t="s">
+        <v>729</v>
       </c>
       <c r="AA9" t="s">
-        <v>481</v>
+        <v>552</v>
       </c>
       <c r="AB9" t="s">
-        <v>632</v>
+        <v>730</v>
       </c>
       <c r="AC9" t="s">
-        <v>638</v>
+        <v>736</v>
       </c>
     </row>
     <row r="10" spans="1:29">
@@ -3046,82 +3337,85 @@
         <v>37</v>
       </c>
       <c r="B10" t="s">
-        <v>83</v>
+        <v>91</v>
       </c>
       <c r="C10" t="s">
-        <v>121</v>
+        <v>137</v>
       </c>
       <c r="D10" t="s">
-        <v>130</v>
+        <v>146</v>
       </c>
       <c r="E10" t="s">
-        <v>176</v>
+        <v>200</v>
       </c>
       <c r="F10" t="s">
-        <v>218</v>
+        <v>246</v>
       </c>
       <c r="G10" t="s">
-        <v>243</v>
+        <v>276</v>
       </c>
       <c r="H10" t="s">
-        <v>253</v>
+        <v>286</v>
       </c>
       <c r="I10" t="s">
-        <v>298</v>
+        <v>338</v>
       </c>
       <c r="J10" t="s">
-        <v>329</v>
+        <v>375</v>
       </c>
       <c r="K10" t="s">
-        <v>338</v>
+        <v>385</v>
       </c>
       <c r="L10" t="s">
-        <v>384</v>
+        <v>439</v>
       </c>
       <c r="M10" t="s">
-        <v>430</v>
-      </c>
-      <c r="N10" t="s">
-        <v>468</v>
+        <v>493</v>
       </c>
       <c r="O10" t="s">
-        <v>471</v>
+        <v>541</v>
       </c>
       <c r="P10" t="s">
-        <v>476</v>
+        <v>548</v>
       </c>
       <c r="Q10" t="s">
-        <v>482</v>
+        <v>552</v>
       </c>
       <c r="R10" t="s">
-        <v>492</v>
+        <v>566</v>
       </c>
       <c r="S10" t="s">
-        <v>536</v>
+        <v>617</v>
       </c>
       <c r="T10" t="s">
-        <v>549</v>
+        <v>632</v>
       </c>
       <c r="U10" t="s">
-        <v>582</v>
+        <v>672</v>
       </c>
       <c r="V10" t="s">
-        <v>582</v>
+        <v>277</v>
       </c>
       <c r="W10" t="s">
         <v>2</v>
       </c>
       <c r="X10" t="s">
-        <v>591</v>
+        <v>681</v>
+      </c>
+      <c r="Y10" t="s">
+        <v>727</v>
+      </c>
+      <c r="Z10" t="s">
+        <v>728</v>
       </c>
       <c r="AA10" t="s">
-        <v>482</v>
+        <v>552</v>
       </c>
       <c r="AB10" t="s">
-        <v>633</v>
+        <v>731</v>
       </c>
       <c r="AC10" t="s">
-        <v>639</v>
+        <v>737</v>
       </c>
     </row>
     <row r="11" spans="1:29">
@@ -3129,73 +3423,79 @@
         <v>38</v>
       </c>
       <c r="B11" t="s">
-        <v>84</v>
+        <v>92</v>
       </c>
       <c r="C11" t="s">
-        <v>121</v>
+        <v>137</v>
       </c>
       <c r="D11" t="s">
-        <v>131</v>
+        <v>147</v>
       </c>
       <c r="E11" t="s">
-        <v>177</v>
+        <v>201</v>
       </c>
       <c r="F11" t="s">
-        <v>177</v>
+        <v>247</v>
       </c>
       <c r="G11" t="s">
-        <v>243</v>
+        <v>276</v>
       </c>
       <c r="H11" t="s">
-        <v>254</v>
+        <v>287</v>
+      </c>
+      <c r="I11" t="s">
+        <v>339</v>
       </c>
       <c r="J11" t="s">
-        <v>328</v>
+        <v>376</v>
       </c>
       <c r="K11" t="s">
-        <v>339</v>
+        <v>386</v>
       </c>
       <c r="L11" t="s">
-        <v>385</v>
+        <v>440</v>
       </c>
       <c r="M11" t="s">
-        <v>431</v>
-      </c>
-      <c r="N11" t="s">
-        <v>468</v>
+        <v>494</v>
       </c>
       <c r="O11" t="s">
-        <v>470</v>
+        <v>541</v>
       </c>
       <c r="P11" t="s">
-        <v>474</v>
+        <v>544</v>
       </c>
       <c r="Q11" t="s">
-        <v>480</v>
+        <v>552</v>
       </c>
       <c r="R11" t="s">
-        <v>493</v>
+        <v>567</v>
       </c>
       <c r="S11" t="s">
-        <v>536</v>
+        <v>616</v>
+      </c>
+      <c r="T11" t="s">
+        <v>633</v>
       </c>
       <c r="U11" t="s">
-        <v>244</v>
+        <v>672</v>
+      </c>
+      <c r="V11" t="s">
+        <v>672</v>
       </c>
       <c r="W11" t="s">
         <v>2</v>
       </c>
       <c r="X11" t="s">
-        <v>592</v>
+        <v>682</v>
       </c>
       <c r="AA11" t="s">
-        <v>480</v>
+        <v>552</v>
       </c>
       <c r="AB11" t="s">
-        <v>635</v>
+        <v>730</v>
       </c>
       <c r="AC11" t="s">
-        <v>638</v>
+        <v>736</v>
       </c>
     </row>
     <row r="12" spans="1:29">
@@ -3203,79 +3503,79 @@
         <v>39</v>
       </c>
       <c r="B12" t="s">
-        <v>85</v>
+        <v>93</v>
       </c>
       <c r="C12" t="s">
-        <v>121</v>
+        <v>137</v>
       </c>
       <c r="D12" t="s">
-        <v>132</v>
+        <v>148</v>
       </c>
       <c r="E12" t="s">
-        <v>178</v>
+        <v>202</v>
       </c>
       <c r="F12" t="s">
-        <v>219</v>
+        <v>197</v>
       </c>
       <c r="G12" t="s">
-        <v>243</v>
+        <v>277</v>
       </c>
       <c r="H12" t="s">
-        <v>255</v>
+        <v>288</v>
       </c>
       <c r="I12" t="s">
-        <v>299</v>
+        <v>340</v>
       </c>
       <c r="J12" t="s">
-        <v>329</v>
+        <v>376</v>
       </c>
       <c r="K12" t="s">
-        <v>340</v>
+        <v>387</v>
       </c>
       <c r="L12" t="s">
-        <v>386</v>
+        <v>441</v>
       </c>
       <c r="M12" t="s">
-        <v>432</v>
+        <v>495</v>
       </c>
       <c r="O12" t="s">
-        <v>469</v>
+        <v>541</v>
       </c>
       <c r="P12" t="s">
-        <v>472</v>
+        <v>544</v>
       </c>
       <c r="Q12" t="s">
-        <v>479</v>
+        <v>552</v>
       </c>
       <c r="R12" t="s">
-        <v>494</v>
+        <v>568</v>
       </c>
       <c r="S12" t="s">
-        <v>536</v>
+        <v>616</v>
       </c>
       <c r="T12" t="s">
-        <v>550</v>
+        <v>634</v>
       </c>
       <c r="U12" t="s">
-        <v>582</v>
+        <v>672</v>
       </c>
       <c r="V12" t="s">
-        <v>582</v>
+        <v>672</v>
       </c>
       <c r="W12" t="s">
         <v>2</v>
       </c>
       <c r="X12" t="s">
-        <v>593</v>
+        <v>683</v>
       </c>
       <c r="AA12" t="s">
-        <v>479</v>
+        <v>552</v>
       </c>
       <c r="AB12" t="s">
-        <v>632</v>
+        <v>730</v>
       </c>
       <c r="AC12" t="s">
-        <v>638</v>
+        <v>736</v>
       </c>
     </row>
     <row r="13" spans="1:29">
@@ -3283,79 +3583,82 @@
         <v>40</v>
       </c>
       <c r="B13" t="s">
-        <v>86</v>
+        <v>94</v>
       </c>
       <c r="C13" t="s">
-        <v>121</v>
+        <v>137</v>
       </c>
       <c r="D13" t="s">
-        <v>133</v>
+        <v>149</v>
       </c>
       <c r="E13" t="s">
-        <v>179</v>
+        <v>203</v>
       </c>
       <c r="F13" t="s">
-        <v>177</v>
+        <v>248</v>
       </c>
       <c r="G13" t="s">
-        <v>244</v>
+        <v>276</v>
       </c>
       <c r="H13" t="s">
-        <v>256</v>
+        <v>289</v>
       </c>
       <c r="I13" t="s">
-        <v>300</v>
+        <v>341</v>
       </c>
       <c r="J13" t="s">
-        <v>329</v>
+        <v>375</v>
       </c>
       <c r="K13" t="s">
-        <v>341</v>
+        <v>388</v>
       </c>
       <c r="L13" t="s">
-        <v>387</v>
+        <v>442</v>
       </c>
       <c r="M13" t="s">
-        <v>433</v>
+        <v>496</v>
+      </c>
+      <c r="N13" t="s">
+        <v>540</v>
       </c>
       <c r="O13" t="s">
-        <v>469</v>
+        <v>541</v>
       </c>
       <c r="P13" t="s">
-        <v>472</v>
+        <v>549</v>
       </c>
       <c r="Q13" t="s">
-        <v>479</v>
+        <v>554</v>
       </c>
       <c r="R13" t="s">
-        <v>495</v>
+        <v>569</v>
       </c>
       <c r="S13" t="s">
-        <v>536</v>
+        <v>616</v>
       </c>
       <c r="T13" t="s">
-        <v>551</v>
+        <v>635</v>
       </c>
       <c r="U13" t="s">
-        <v>582</v>
+        <v>672</v>
       </c>
       <c r="V13" t="s">
-        <v>582</v>
+        <v>277</v>
       </c>
       <c r="W13" t="s">
         <v>2</v>
       </c>
       <c r="X13" t="s">
-        <v>594</v>
+        <v>684</v>
       </c>
       <c r="AA13" t="s">
-        <v>479</v>
+        <v>554</v>
       </c>
       <c r="AB13" t="s">
-        <v>632</v>
+        <v>734</v>
       </c>
       <c r="AC13" t="s">
-        <v>638</v>
+        <v>736</v>
       </c>
     </row>
     <row r="14" spans="1:29">
@@ -3363,82 +3666,82 @@
         <v>41</v>
       </c>
       <c r="B14" t="s">
-        <v>87</v>
+        <v>95</v>
       </c>
       <c r="C14" t="s">
-        <v>121</v>
+        <v>137</v>
       </c>
       <c r="D14" t="s">
-        <v>134</v>
+        <v>150</v>
       </c>
       <c r="E14" t="s">
-        <v>180</v>
+        <v>204</v>
       </c>
       <c r="F14" t="s">
-        <v>220</v>
+        <v>249</v>
       </c>
       <c r="G14" t="s">
-        <v>243</v>
+        <v>276</v>
       </c>
       <c r="H14" t="s">
-        <v>257</v>
+        <v>290</v>
       </c>
       <c r="I14" t="s">
-        <v>301</v>
+        <v>342</v>
       </c>
       <c r="J14" t="s">
-        <v>328</v>
+        <v>376</v>
       </c>
       <c r="K14" t="s">
-        <v>342</v>
+        <v>389</v>
       </c>
       <c r="L14" t="s">
-        <v>388</v>
+        <v>443</v>
       </c>
       <c r="M14" t="s">
-        <v>434</v>
+        <v>497</v>
       </c>
       <c r="N14" t="s">
-        <v>468</v>
+        <v>540</v>
       </c>
       <c r="O14" t="s">
-        <v>469</v>
+        <v>541</v>
       </c>
       <c r="P14" t="s">
-        <v>477</v>
+        <v>549</v>
       </c>
       <c r="Q14" t="s">
-        <v>480</v>
+        <v>554</v>
       </c>
       <c r="R14" t="s">
-        <v>496</v>
+        <v>570</v>
       </c>
       <c r="S14" t="s">
-        <v>536</v>
+        <v>618</v>
       </c>
       <c r="T14" t="s">
-        <v>552</v>
+        <v>636</v>
       </c>
       <c r="U14" t="s">
-        <v>582</v>
+        <v>672</v>
       </c>
       <c r="V14" t="s">
-        <v>244</v>
+        <v>672</v>
       </c>
       <c r="W14" t="s">
         <v>2</v>
       </c>
       <c r="X14" t="s">
-        <v>595</v>
+        <v>685</v>
       </c>
       <c r="AA14" t="s">
-        <v>480</v>
+        <v>554</v>
       </c>
       <c r="AB14" t="s">
-        <v>636</v>
+        <v>732</v>
       </c>
       <c r="AC14" t="s">
-        <v>638</v>
+        <v>736</v>
       </c>
     </row>
     <row r="15" spans="1:29">
@@ -3446,88 +3749,82 @@
         <v>42</v>
       </c>
       <c r="B15" t="s">
-        <v>88</v>
+        <v>96</v>
       </c>
       <c r="C15" t="s">
-        <v>121</v>
+        <v>137</v>
       </c>
       <c r="D15" t="s">
-        <v>135</v>
+        <v>151</v>
       </c>
       <c r="E15" t="s">
-        <v>181</v>
+        <v>205</v>
       </c>
       <c r="F15" t="s">
-        <v>181</v>
+        <v>250</v>
       </c>
       <c r="G15" t="s">
-        <v>243</v>
+        <v>276</v>
       </c>
       <c r="H15" t="s">
-        <v>258</v>
+        <v>291</v>
       </c>
       <c r="I15" t="s">
-        <v>302</v>
+        <v>343</v>
       </c>
       <c r="J15" t="s">
-        <v>328</v>
+        <v>375</v>
       </c>
       <c r="K15" t="s">
-        <v>343</v>
+        <v>390</v>
       </c>
       <c r="L15" t="s">
-        <v>389</v>
+        <v>444</v>
       </c>
       <c r="M15" t="s">
-        <v>435</v>
-      </c>
-      <c r="N15" t="s">
-        <v>468</v>
+        <v>498</v>
       </c>
       <c r="O15" t="s">
-        <v>471</v>
+        <v>541</v>
       </c>
       <c r="P15" t="s">
-        <v>475</v>
+        <v>544</v>
       </c>
       <c r="Q15" t="s">
-        <v>481</v>
+        <v>552</v>
       </c>
       <c r="R15" t="s">
-        <v>497</v>
+        <v>571</v>
       </c>
       <c r="S15" t="s">
-        <v>537</v>
+        <v>619</v>
       </c>
       <c r="T15" t="s">
-        <v>553</v>
+        <v>637</v>
       </c>
       <c r="U15" t="s">
-        <v>582</v>
+        <v>672</v>
       </c>
       <c r="V15" t="s">
-        <v>244</v>
+        <v>672</v>
       </c>
       <c r="W15" t="s">
         <v>2</v>
       </c>
       <c r="X15" t="s">
-        <v>596</v>
+        <v>686</v>
       </c>
       <c r="Y15" t="s">
-        <v>629</v>
-      </c>
-      <c r="Z15" t="s">
-        <v>631</v>
+        <v>727</v>
       </c>
       <c r="AA15" t="s">
-        <v>481</v>
+        <v>552</v>
       </c>
       <c r="AB15" t="s">
-        <v>633</v>
+        <v>735</v>
       </c>
       <c r="AC15" t="s">
-        <v>639</v>
+        <v>736</v>
       </c>
     </row>
     <row r="16" spans="1:29">
@@ -3535,82 +3832,82 @@
         <v>43</v>
       </c>
       <c r="B16" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="C16" t="s">
-        <v>121</v>
+        <v>137</v>
       </c>
       <c r="D16" t="s">
-        <v>136</v>
+        <v>152</v>
       </c>
       <c r="E16" t="s">
-        <v>182</v>
+        <v>206</v>
       </c>
       <c r="F16" t="s">
-        <v>176</v>
+        <v>251</v>
       </c>
       <c r="G16" t="s">
-        <v>243</v>
+        <v>276</v>
       </c>
       <c r="H16" t="s">
-        <v>259</v>
+        <v>292</v>
       </c>
       <c r="I16" t="s">
-        <v>303</v>
+        <v>344</v>
       </c>
       <c r="J16" t="s">
-        <v>328</v>
+        <v>375</v>
       </c>
       <c r="K16" t="s">
-        <v>344</v>
+        <v>391</v>
       </c>
       <c r="L16" t="s">
-        <v>390</v>
+        <v>445</v>
       </c>
       <c r="M16" t="s">
-        <v>436</v>
+        <v>499</v>
       </c>
       <c r="N16" t="s">
-        <v>468</v>
+        <v>540</v>
       </c>
       <c r="O16" t="s">
-        <v>469</v>
+        <v>543</v>
       </c>
       <c r="P16" t="s">
-        <v>477</v>
+        <v>550</v>
       </c>
       <c r="Q16" t="s">
-        <v>480</v>
+        <v>556</v>
       </c>
       <c r="R16" t="s">
-        <v>498</v>
+        <v>572</v>
       </c>
       <c r="S16" t="s">
-        <v>536</v>
+        <v>618</v>
       </c>
       <c r="T16" t="s">
-        <v>554</v>
+        <v>638</v>
       </c>
       <c r="U16" t="s">
-        <v>582</v>
+        <v>672</v>
       </c>
       <c r="V16" t="s">
-        <v>244</v>
+        <v>277</v>
       </c>
       <c r="W16" t="s">
         <v>2</v>
       </c>
       <c r="X16" t="s">
-        <v>597</v>
+        <v>687</v>
       </c>
       <c r="AA16" t="s">
-        <v>480</v>
+        <v>556</v>
       </c>
       <c r="AB16" t="s">
-        <v>635</v>
+        <v>731</v>
       </c>
       <c r="AC16" t="s">
-        <v>638</v>
+        <v>737</v>
       </c>
     </row>
     <row r="17" spans="1:29">
@@ -3618,82 +3915,85 @@
         <v>44</v>
       </c>
       <c r="B17" t="s">
-        <v>90</v>
+        <v>98</v>
       </c>
       <c r="C17" t="s">
-        <v>121</v>
+        <v>137</v>
       </c>
       <c r="D17" t="s">
-        <v>137</v>
+        <v>153</v>
       </c>
       <c r="E17" t="s">
-        <v>183</v>
+        <v>207</v>
       </c>
       <c r="F17" t="s">
-        <v>221</v>
+        <v>252</v>
       </c>
       <c r="G17" t="s">
-        <v>243</v>
+        <v>276</v>
       </c>
       <c r="H17" t="s">
-        <v>260</v>
+        <v>293</v>
       </c>
       <c r="I17" t="s">
-        <v>304</v>
+        <v>345</v>
       </c>
       <c r="J17" t="s">
-        <v>328</v>
+        <v>375</v>
       </c>
       <c r="K17" t="s">
-        <v>345</v>
+        <v>392</v>
       </c>
       <c r="L17" t="s">
-        <v>391</v>
+        <v>446</v>
       </c>
       <c r="M17" t="s">
-        <v>437</v>
-      </c>
-      <c r="N17" t="s">
-        <v>468</v>
+        <v>500</v>
       </c>
       <c r="O17" t="s">
-        <v>471</v>
+        <v>541</v>
       </c>
       <c r="P17" t="s">
-        <v>478</v>
+        <v>544</v>
       </c>
       <c r="Q17" t="s">
-        <v>483</v>
+        <v>552</v>
       </c>
       <c r="R17" t="s">
-        <v>499</v>
+        <v>573</v>
       </c>
       <c r="S17" t="s">
-        <v>537</v>
+        <v>619</v>
       </c>
       <c r="T17" t="s">
-        <v>555</v>
+        <v>639</v>
       </c>
       <c r="U17" t="s">
-        <v>582</v>
+        <v>672</v>
       </c>
       <c r="V17" t="s">
-        <v>244</v>
+        <v>277</v>
       </c>
       <c r="W17" t="s">
         <v>2</v>
       </c>
       <c r="X17" t="s">
-        <v>598</v>
+        <v>688</v>
+      </c>
+      <c r="Y17" t="s">
+        <v>727</v>
+      </c>
+      <c r="Z17" t="s">
+        <v>729</v>
       </c>
       <c r="AA17" t="s">
-        <v>483</v>
+        <v>552</v>
       </c>
       <c r="AB17" t="s">
-        <v>633</v>
+        <v>734</v>
       </c>
       <c r="AC17" t="s">
-        <v>639</v>
+        <v>736</v>
       </c>
     </row>
     <row r="18" spans="1:29">
@@ -3701,82 +4001,88 @@
         <v>45</v>
       </c>
       <c r="B18" t="s">
-        <v>91</v>
+        <v>99</v>
       </c>
       <c r="C18" t="s">
-        <v>121</v>
+        <v>137</v>
       </c>
       <c r="D18" t="s">
-        <v>138</v>
+        <v>154</v>
       </c>
       <c r="E18" t="s">
-        <v>184</v>
+        <v>208</v>
       </c>
       <c r="F18" t="s">
-        <v>222</v>
+        <v>208</v>
       </c>
       <c r="G18" t="s">
-        <v>243</v>
+        <v>276</v>
       </c>
       <c r="H18" t="s">
-        <v>261</v>
+        <v>294</v>
       </c>
       <c r="I18" t="s">
-        <v>305</v>
+        <v>346</v>
       </c>
       <c r="J18" t="s">
-        <v>329</v>
+        <v>375</v>
       </c>
       <c r="K18" t="s">
-        <v>346</v>
+        <v>393</v>
       </c>
       <c r="L18" t="s">
-        <v>392</v>
+        <v>447</v>
       </c>
       <c r="M18" t="s">
-        <v>438</v>
+        <v>501</v>
       </c>
       <c r="N18" t="s">
-        <v>468</v>
+        <v>540</v>
       </c>
       <c r="O18" t="s">
-        <v>469</v>
+        <v>543</v>
       </c>
       <c r="P18" t="s">
-        <v>477</v>
+        <v>551</v>
       </c>
       <c r="Q18" t="s">
-        <v>480</v>
+        <v>557</v>
       </c>
       <c r="R18" t="s">
-        <v>500</v>
+        <v>574</v>
       </c>
       <c r="S18" t="s">
-        <v>538</v>
+        <v>618</v>
       </c>
       <c r="T18" t="s">
-        <v>556</v>
+        <v>640</v>
       </c>
       <c r="U18" t="s">
-        <v>582</v>
+        <v>672</v>
       </c>
       <c r="V18" t="s">
-        <v>244</v>
+        <v>277</v>
       </c>
       <c r="W18" t="s">
         <v>2</v>
       </c>
       <c r="X18" t="s">
-        <v>599</v>
+        <v>689</v>
+      </c>
+      <c r="Y18" t="s">
+        <v>727</v>
+      </c>
+      <c r="Z18" t="s">
+        <v>729</v>
       </c>
       <c r="AA18" t="s">
-        <v>480</v>
+        <v>557</v>
       </c>
       <c r="AB18" t="s">
-        <v>633</v>
+        <v>732</v>
       </c>
       <c r="AC18" t="s">
-        <v>639</v>
+        <v>736</v>
       </c>
     </row>
     <row r="19" spans="1:29">
@@ -3784,82 +4090,76 @@
         <v>46</v>
       </c>
       <c r="B19" t="s">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="C19" t="s">
-        <v>121</v>
+        <v>137</v>
       </c>
       <c r="D19" t="s">
-        <v>139</v>
+        <v>155</v>
       </c>
       <c r="E19" t="s">
-        <v>185</v>
+        <v>209</v>
       </c>
       <c r="F19" t="s">
-        <v>223</v>
+        <v>217</v>
       </c>
       <c r="G19" t="s">
-        <v>243</v>
+        <v>276</v>
       </c>
       <c r="H19" t="s">
-        <v>262</v>
-      </c>
-      <c r="I19" t="s">
-        <v>306</v>
+        <v>295</v>
       </c>
       <c r="J19" t="s">
-        <v>329</v>
+        <v>375</v>
       </c>
       <c r="K19" t="s">
-        <v>347</v>
+        <v>394</v>
       </c>
       <c r="L19" t="s">
-        <v>393</v>
+        <v>448</v>
       </c>
       <c r="M19" t="s">
-        <v>439</v>
+        <v>502</v>
       </c>
       <c r="N19" t="s">
-        <v>468</v>
+        <v>540</v>
       </c>
       <c r="O19" t="s">
-        <v>469</v>
+        <v>542</v>
       </c>
       <c r="P19" t="s">
-        <v>477</v>
+        <v>546</v>
       </c>
       <c r="Q19" t="s">
-        <v>480</v>
+        <v>554</v>
       </c>
       <c r="R19" t="s">
-        <v>501</v>
+        <v>575</v>
       </c>
       <c r="S19" t="s">
-        <v>537</v>
-      </c>
-      <c r="T19" t="s">
-        <v>557</v>
+        <v>613</v>
       </c>
       <c r="U19" t="s">
-        <v>582</v>
-      </c>
-      <c r="V19" t="s">
-        <v>582</v>
+        <v>672</v>
       </c>
       <c r="W19" t="s">
         <v>2</v>
       </c>
       <c r="X19" t="s">
-        <v>600</v>
+        <v>690</v>
+      </c>
+      <c r="Y19" t="s">
+        <v>727</v>
       </c>
       <c r="AA19" t="s">
-        <v>480</v>
+        <v>554</v>
       </c>
       <c r="AB19" t="s">
-        <v>633</v>
+        <v>731</v>
       </c>
       <c r="AC19" t="s">
-        <v>639</v>
+        <v>737</v>
       </c>
     </row>
     <row r="20" spans="1:29">
@@ -3867,76 +4167,82 @@
         <v>47</v>
       </c>
       <c r="B20" t="s">
-        <v>93</v>
+        <v>101</v>
       </c>
       <c r="C20" t="s">
-        <v>121</v>
+        <v>137</v>
       </c>
       <c r="D20" t="s">
-        <v>140</v>
+        <v>156</v>
       </c>
       <c r="E20" t="s">
-        <v>186</v>
+        <v>210</v>
       </c>
       <c r="F20" t="s">
-        <v>182</v>
+        <v>253</v>
       </c>
       <c r="G20" t="s">
-        <v>243</v>
+        <v>276</v>
       </c>
       <c r="H20" t="s">
-        <v>263</v>
+        <v>296</v>
+      </c>
+      <c r="I20" t="s">
+        <v>347</v>
       </c>
       <c r="J20" t="s">
-        <v>328</v>
+        <v>376</v>
       </c>
       <c r="K20" t="s">
-        <v>348</v>
+        <v>395</v>
       </c>
       <c r="L20" t="s">
-        <v>394</v>
+        <v>449</v>
       </c>
       <c r="M20" t="s">
-        <v>440</v>
+        <v>503</v>
       </c>
       <c r="N20" t="s">
-        <v>468</v>
+        <v>540</v>
       </c>
       <c r="O20" t="s">
-        <v>470</v>
+        <v>541</v>
       </c>
       <c r="P20" t="s">
-        <v>474</v>
+        <v>549</v>
       </c>
       <c r="Q20" t="s">
-        <v>480</v>
+        <v>554</v>
       </c>
       <c r="R20" t="s">
-        <v>502</v>
+        <v>576</v>
       </c>
       <c r="S20" t="s">
-        <v>531</v>
+        <v>620</v>
+      </c>
+      <c r="T20" t="s">
+        <v>641</v>
       </c>
       <c r="U20" t="s">
-        <v>582</v>
+        <v>672</v>
+      </c>
+      <c r="V20" t="s">
+        <v>277</v>
       </c>
       <c r="W20" t="s">
         <v>2</v>
       </c>
       <c r="X20" t="s">
-        <v>601</v>
-      </c>
-      <c r="Y20" t="s">
-        <v>629</v>
+        <v>691</v>
       </c>
       <c r="AA20" t="s">
-        <v>480</v>
+        <v>554</v>
       </c>
       <c r="AB20" t="s">
-        <v>633</v>
+        <v>732</v>
       </c>
       <c r="AC20" t="s">
-        <v>639</v>
+        <v>736</v>
       </c>
     </row>
     <row r="21" spans="1:29">
@@ -3944,85 +4250,85 @@
         <v>48</v>
       </c>
       <c r="B21" t="s">
-        <v>94</v>
+        <v>102</v>
       </c>
       <c r="C21" t="s">
-        <v>121</v>
+        <v>137</v>
       </c>
       <c r="D21" t="s">
-        <v>141</v>
+        <v>157</v>
       </c>
       <c r="E21" t="s">
-        <v>187</v>
+        <v>211</v>
       </c>
       <c r="F21" t="s">
-        <v>224</v>
+        <v>194</v>
       </c>
       <c r="G21" t="s">
-        <v>243</v>
+        <v>276</v>
       </c>
       <c r="H21" t="s">
-        <v>264</v>
+        <v>297</v>
       </c>
       <c r="I21" t="s">
-        <v>307</v>
+        <v>348</v>
       </c>
       <c r="J21" t="s">
-        <v>328</v>
+        <v>375</v>
       </c>
       <c r="K21" t="s">
-        <v>349</v>
+        <v>396</v>
       </c>
       <c r="L21" t="s">
-        <v>395</v>
+        <v>450</v>
       </c>
       <c r="M21" t="s">
-        <v>441</v>
+        <v>504</v>
       </c>
       <c r="O21" t="s">
-        <v>469</v>
+        <v>541</v>
       </c>
       <c r="P21" t="s">
-        <v>472</v>
+        <v>544</v>
       </c>
       <c r="Q21" t="s">
-        <v>479</v>
+        <v>552</v>
       </c>
       <c r="R21" t="s">
-        <v>503</v>
+        <v>577</v>
       </c>
       <c r="S21" t="s">
-        <v>534</v>
+        <v>619</v>
       </c>
       <c r="T21" t="s">
-        <v>558</v>
+        <v>642</v>
       </c>
       <c r="U21" t="s">
-        <v>582</v>
+        <v>672</v>
       </c>
       <c r="V21" t="s">
-        <v>244</v>
+        <v>672</v>
       </c>
       <c r="W21" t="s">
         <v>2</v>
       </c>
       <c r="X21" t="s">
-        <v>602</v>
+        <v>692</v>
       </c>
       <c r="Y21" t="s">
-        <v>629</v>
+        <v>727</v>
       </c>
       <c r="Z21" t="s">
-        <v>631</v>
+        <v>728</v>
       </c>
       <c r="AA21" t="s">
-        <v>479</v>
+        <v>552</v>
       </c>
       <c r="AB21" t="s">
-        <v>633</v>
+        <v>730</v>
       </c>
       <c r="AC21" t="s">
-        <v>639</v>
+        <v>736</v>
       </c>
     </row>
     <row r="22" spans="1:29">
@@ -4030,85 +4336,73 @@
         <v>49</v>
       </c>
       <c r="B22" t="s">
-        <v>95</v>
+        <v>103</v>
       </c>
       <c r="C22" t="s">
-        <v>121</v>
+        <v>137</v>
       </c>
       <c r="D22" t="s">
-        <v>142</v>
+        <v>158</v>
       </c>
       <c r="E22" t="s">
-        <v>188</v>
+        <v>212</v>
       </c>
       <c r="F22" t="s">
-        <v>225</v>
+        <v>254</v>
       </c>
       <c r="G22" t="s">
-        <v>243</v>
+        <v>276</v>
       </c>
       <c r="H22" t="s">
-        <v>265</v>
-      </c>
-      <c r="I22" t="s">
-        <v>308</v>
+        <v>298</v>
       </c>
       <c r="J22" t="s">
-        <v>328</v>
+        <v>376</v>
       </c>
       <c r="K22" t="s">
-        <v>350</v>
+        <v>397</v>
       </c>
       <c r="L22" t="s">
-        <v>396</v>
+        <v>451</v>
       </c>
       <c r="M22" t="s">
-        <v>442</v>
+        <v>505</v>
+      </c>
+      <c r="N22" t="s">
+        <v>540</v>
       </c>
       <c r="O22" t="s">
-        <v>469</v>
+        <v>542</v>
       </c>
       <c r="P22" t="s">
-        <v>472</v>
+        <v>546</v>
       </c>
       <c r="Q22" t="s">
-        <v>479</v>
+        <v>554</v>
       </c>
       <c r="R22" t="s">
-        <v>504</v>
+        <v>578</v>
       </c>
       <c r="S22" t="s">
-        <v>534</v>
-      </c>
-      <c r="T22" t="s">
-        <v>559</v>
+        <v>621</v>
       </c>
       <c r="U22" t="s">
-        <v>582</v>
-      </c>
-      <c r="V22" t="s">
-        <v>582</v>
+        <v>672</v>
       </c>
       <c r="W22" t="s">
         <v>2</v>
       </c>
       <c r="X22" t="s">
-        <v>603</v>
-      </c>
-      <c r="Y22" t="s">
-        <v>629</v>
-      </c>
-      <c r="Z22" t="s">
-        <v>630</v>
+        <v>693</v>
       </c>
       <c r="AA22" t="s">
-        <v>479</v>
+        <v>554</v>
       </c>
       <c r="AB22" t="s">
-        <v>632</v>
+        <v>734</v>
       </c>
       <c r="AC22" t="s">
-        <v>638</v>
+        <v>736</v>
       </c>
     </row>
     <row r="23" spans="1:29">
@@ -4116,73 +4410,85 @@
         <v>50</v>
       </c>
       <c r="B23" t="s">
-        <v>96</v>
+        <v>104</v>
       </c>
       <c r="C23" t="s">
-        <v>121</v>
+        <v>137</v>
       </c>
       <c r="D23" t="s">
-        <v>143</v>
+        <v>159</v>
       </c>
       <c r="E23" t="s">
-        <v>189</v>
+        <v>213</v>
       </c>
       <c r="F23" t="s">
-        <v>226</v>
+        <v>255</v>
       </c>
       <c r="G23" t="s">
-        <v>243</v>
+        <v>276</v>
       </c>
       <c r="H23" t="s">
-        <v>266</v>
+        <v>299</v>
+      </c>
+      <c r="I23" t="s">
+        <v>349</v>
       </c>
       <c r="J23" t="s">
-        <v>329</v>
+        <v>376</v>
       </c>
       <c r="K23" t="s">
-        <v>351</v>
+        <v>398</v>
       </c>
       <c r="L23" t="s">
-        <v>397</v>
+        <v>452</v>
       </c>
       <c r="M23" t="s">
-        <v>443</v>
-      </c>
-      <c r="N23" t="s">
-        <v>468</v>
+        <v>506</v>
       </c>
       <c r="O23" t="s">
-        <v>470</v>
+        <v>541</v>
       </c>
       <c r="P23" t="s">
-        <v>474</v>
+        <v>544</v>
       </c>
       <c r="Q23" t="s">
-        <v>480</v>
+        <v>552</v>
       </c>
       <c r="R23" t="s">
-        <v>505</v>
+        <v>579</v>
       </c>
       <c r="S23" t="s">
-        <v>539</v>
+        <v>619</v>
+      </c>
+      <c r="T23" t="s">
+        <v>643</v>
       </c>
       <c r="U23" t="s">
-        <v>582</v>
+        <v>672</v>
+      </c>
+      <c r="V23" t="s">
+        <v>672</v>
       </c>
       <c r="W23" t="s">
         <v>2</v>
       </c>
       <c r="X23" t="s">
-        <v>604</v>
+        <v>694</v>
+      </c>
+      <c r="Y23" t="s">
+        <v>727</v>
+      </c>
+      <c r="Z23" t="s">
+        <v>728</v>
       </c>
       <c r="AA23" t="s">
-        <v>480</v>
+        <v>552</v>
       </c>
       <c r="AB23" t="s">
-        <v>636</v>
+        <v>730</v>
       </c>
       <c r="AC23" t="s">
-        <v>638</v>
+        <v>736</v>
       </c>
     </row>
     <row r="24" spans="1:29">
@@ -4190,73 +4496,73 @@
         <v>51</v>
       </c>
       <c r="B24" t="s">
-        <v>97</v>
+        <v>105</v>
       </c>
       <c r="C24" t="s">
-        <v>121</v>
+        <v>137</v>
       </c>
       <c r="D24" t="s">
-        <v>144</v>
+        <v>160</v>
       </c>
       <c r="E24" t="s">
-        <v>177</v>
+        <v>214</v>
       </c>
       <c r="F24" t="s">
-        <v>227</v>
+        <v>256</v>
       </c>
       <c r="G24" t="s">
-        <v>244</v>
+        <v>276</v>
       </c>
       <c r="H24" t="s">
-        <v>267</v>
+        <v>300</v>
       </c>
       <c r="J24" t="s">
-        <v>329</v>
+        <v>375</v>
       </c>
       <c r="K24" t="s">
-        <v>352</v>
+        <v>399</v>
       </c>
       <c r="L24" t="s">
-        <v>398</v>
+        <v>453</v>
       </c>
       <c r="M24" t="s">
-        <v>444</v>
+        <v>507</v>
       </c>
       <c r="N24" t="s">
-        <v>468</v>
+        <v>540</v>
       </c>
       <c r="O24" t="s">
-        <v>470</v>
+        <v>542</v>
       </c>
       <c r="P24" t="s">
-        <v>474</v>
+        <v>546</v>
       </c>
       <c r="Q24" t="s">
-        <v>480</v>
+        <v>554</v>
       </c>
       <c r="R24" t="s">
-        <v>506</v>
+        <v>580</v>
       </c>
       <c r="S24" t="s">
-        <v>537</v>
+        <v>622</v>
       </c>
       <c r="U24" t="s">
-        <v>582</v>
+        <v>672</v>
       </c>
       <c r="W24" t="s">
         <v>2</v>
       </c>
       <c r="X24" t="s">
-        <v>605</v>
+        <v>695</v>
       </c>
       <c r="AA24" t="s">
-        <v>480</v>
+        <v>554</v>
       </c>
       <c r="AB24" t="s">
-        <v>632</v>
+        <v>730</v>
       </c>
       <c r="AC24" t="s">
-        <v>638</v>
+        <v>736</v>
       </c>
     </row>
     <row r="25" spans="1:29">
@@ -4264,73 +4570,82 @@
         <v>52</v>
       </c>
       <c r="B25" t="s">
-        <v>98</v>
+        <v>106</v>
       </c>
       <c r="C25" t="s">
-        <v>121</v>
+        <v>137</v>
       </c>
       <c r="D25" t="s">
-        <v>145</v>
+        <v>161</v>
       </c>
       <c r="E25" t="s">
-        <v>190</v>
+        <v>215</v>
       </c>
       <c r="F25" t="s">
-        <v>228</v>
+        <v>257</v>
       </c>
       <c r="G25" t="s">
-        <v>243</v>
+        <v>276</v>
       </c>
       <c r="H25" t="s">
-        <v>268</v>
+        <v>301</v>
+      </c>
+      <c r="I25" t="s">
+        <v>350</v>
       </c>
       <c r="J25" t="s">
-        <v>328</v>
+        <v>375</v>
       </c>
       <c r="K25" t="s">
-        <v>353</v>
+        <v>400</v>
       </c>
       <c r="L25" t="s">
-        <v>399</v>
+        <v>454</v>
       </c>
       <c r="M25" t="s">
-        <v>445</v>
+        <v>508</v>
       </c>
       <c r="N25" t="s">
-        <v>468</v>
+        <v>540</v>
       </c>
       <c r="O25" t="s">
-        <v>470</v>
+        <v>543</v>
       </c>
       <c r="P25" t="s">
-        <v>474</v>
+        <v>551</v>
       </c>
       <c r="Q25" t="s">
-        <v>480</v>
+        <v>557</v>
       </c>
       <c r="R25" t="s">
-        <v>507</v>
+        <v>581</v>
       </c>
       <c r="S25" t="s">
-        <v>537</v>
+        <v>622</v>
+      </c>
+      <c r="T25" t="s">
+        <v>644</v>
       </c>
       <c r="U25" t="s">
-        <v>582</v>
+        <v>672</v>
+      </c>
+      <c r="V25" t="s">
+        <v>277</v>
       </c>
       <c r="W25" t="s">
         <v>2</v>
       </c>
       <c r="X25" t="s">
-        <v>606</v>
+        <v>696</v>
       </c>
       <c r="AA25" t="s">
-        <v>480</v>
+        <v>557</v>
       </c>
       <c r="AB25" t="s">
-        <v>632</v>
+        <v>730</v>
       </c>
       <c r="AC25" t="s">
-        <v>638</v>
+        <v>736</v>
       </c>
     </row>
     <row r="26" spans="1:29">
@@ -4338,85 +4653,73 @@
         <v>53</v>
       </c>
       <c r="B26" t="s">
-        <v>99</v>
+        <v>107</v>
       </c>
       <c r="C26" t="s">
-        <v>121</v>
+        <v>137</v>
       </c>
       <c r="D26" t="s">
-        <v>146</v>
+        <v>162</v>
       </c>
       <c r="E26" t="s">
-        <v>191</v>
+        <v>197</v>
       </c>
       <c r="F26" t="s">
-        <v>229</v>
+        <v>258</v>
       </c>
       <c r="G26" t="s">
-        <v>243</v>
+        <v>277</v>
       </c>
       <c r="H26" t="s">
-        <v>269</v>
-      </c>
-      <c r="I26" t="s">
-        <v>309</v>
+        <v>302</v>
       </c>
       <c r="J26" t="s">
-        <v>329</v>
+        <v>376</v>
       </c>
       <c r="K26" t="s">
-        <v>354</v>
+        <v>401</v>
       </c>
       <c r="L26" t="s">
-        <v>400</v>
+        <v>455</v>
       </c>
       <c r="M26" t="s">
-        <v>446</v>
+        <v>509</v>
+      </c>
+      <c r="N26" t="s">
+        <v>540</v>
       </c>
       <c r="O26" t="s">
-        <v>469</v>
+        <v>542</v>
       </c>
       <c r="P26" t="s">
-        <v>472</v>
+        <v>546</v>
       </c>
       <c r="Q26" t="s">
-        <v>479</v>
+        <v>554</v>
       </c>
       <c r="R26" t="s">
-        <v>508</v>
+        <v>582</v>
       </c>
       <c r="S26" t="s">
-        <v>534</v>
-      </c>
-      <c r="T26" t="s">
-        <v>560</v>
+        <v>618</v>
       </c>
       <c r="U26" t="s">
-        <v>582</v>
-      </c>
-      <c r="V26" t="s">
-        <v>582</v>
+        <v>672</v>
       </c>
       <c r="W26" t="s">
         <v>2</v>
       </c>
       <c r="X26" t="s">
-        <v>607</v>
-      </c>
-      <c r="Y26" t="s">
-        <v>629</v>
-      </c>
-      <c r="Z26" t="s">
-        <v>630</v>
+        <v>697</v>
       </c>
       <c r="AA26" t="s">
-        <v>479</v>
+        <v>554</v>
       </c>
       <c r="AB26" t="s">
-        <v>632</v>
+        <v>730</v>
       </c>
       <c r="AC26" t="s">
-        <v>638</v>
+        <v>736</v>
       </c>
     </row>
     <row r="27" spans="1:29">
@@ -4424,85 +4727,73 @@
         <v>54</v>
       </c>
       <c r="B27" t="s">
-        <v>100</v>
+        <v>108</v>
       </c>
       <c r="C27" t="s">
-        <v>121</v>
+        <v>137</v>
       </c>
       <c r="D27" t="s">
-        <v>147</v>
+        <v>163</v>
       </c>
       <c r="E27" t="s">
-        <v>192</v>
+        <v>216</v>
       </c>
       <c r="F27" t="s">
-        <v>230</v>
+        <v>259</v>
       </c>
       <c r="G27" t="s">
-        <v>243</v>
+        <v>276</v>
       </c>
       <c r="H27" t="s">
-        <v>270</v>
-      </c>
-      <c r="I27" t="s">
-        <v>310</v>
+        <v>303</v>
       </c>
       <c r="J27" t="s">
-        <v>328</v>
+        <v>375</v>
       </c>
       <c r="K27" t="s">
-        <v>355</v>
+        <v>402</v>
       </c>
       <c r="L27" t="s">
-        <v>401</v>
+        <v>456</v>
       </c>
       <c r="M27" t="s">
-        <v>447</v>
+        <v>510</v>
+      </c>
+      <c r="N27" t="s">
+        <v>540</v>
       </c>
       <c r="O27" t="s">
-        <v>469</v>
+        <v>542</v>
       </c>
       <c r="P27" t="s">
-        <v>472</v>
+        <v>546</v>
       </c>
       <c r="Q27" t="s">
-        <v>479</v>
+        <v>554</v>
       </c>
       <c r="R27" t="s">
-        <v>509</v>
+        <v>583</v>
       </c>
       <c r="S27" t="s">
-        <v>534</v>
-      </c>
-      <c r="T27" t="s">
-        <v>561</v>
+        <v>618</v>
       </c>
       <c r="U27" t="s">
-        <v>582</v>
-      </c>
-      <c r="V27" t="s">
-        <v>244</v>
+        <v>672</v>
       </c>
       <c r="W27" t="s">
         <v>2</v>
       </c>
       <c r="X27" t="s">
-        <v>608</v>
-      </c>
-      <c r="Y27" t="s">
-        <v>629</v>
-      </c>
-      <c r="Z27" t="s">
-        <v>631</v>
+        <v>698</v>
       </c>
       <c r="AA27" t="s">
-        <v>479</v>
+        <v>554</v>
       </c>
       <c r="AB27" t="s">
-        <v>636</v>
+        <v>730</v>
       </c>
       <c r="AC27" t="s">
-        <v>638</v>
+        <v>736</v>
       </c>
     </row>
     <row r="28" spans="1:29">
@@ -4510,82 +4801,82 @@
         <v>55</v>
       </c>
       <c r="B28" t="s">
-        <v>101</v>
+        <v>109</v>
       </c>
       <c r="C28" t="s">
-        <v>121</v>
+        <v>137</v>
       </c>
       <c r="D28" t="s">
-        <v>148</v>
+        <v>164</v>
       </c>
       <c r="E28" t="s">
-        <v>193</v>
+        <v>217</v>
       </c>
       <c r="F28" t="s">
-        <v>217</v>
+        <v>198</v>
       </c>
       <c r="G28" t="s">
-        <v>243</v>
+        <v>276</v>
       </c>
       <c r="H28" t="s">
-        <v>271</v>
+        <v>304</v>
       </c>
       <c r="I28" t="s">
-        <v>311</v>
+        <v>351</v>
       </c>
       <c r="J28" t="s">
-        <v>329</v>
+        <v>375</v>
       </c>
       <c r="K28" t="s">
-        <v>356</v>
+        <v>403</v>
       </c>
       <c r="L28" t="s">
-        <v>402</v>
+        <v>457</v>
       </c>
       <c r="M28" t="s">
-        <v>448</v>
+        <v>511</v>
       </c>
       <c r="N28" t="s">
-        <v>468</v>
+        <v>540</v>
       </c>
       <c r="O28" t="s">
-        <v>471</v>
+        <v>541</v>
       </c>
       <c r="P28" t="s">
-        <v>475</v>
+        <v>549</v>
       </c>
       <c r="Q28" t="s">
-        <v>481</v>
+        <v>554</v>
       </c>
       <c r="R28" t="s">
-        <v>510</v>
+        <v>584</v>
       </c>
       <c r="S28" t="s">
-        <v>540</v>
+        <v>616</v>
       </c>
       <c r="T28" t="s">
-        <v>562</v>
+        <v>645</v>
       </c>
       <c r="U28" t="s">
-        <v>582</v>
+        <v>672</v>
       </c>
       <c r="V28" t="s">
-        <v>582</v>
+        <v>277</v>
       </c>
       <c r="W28" t="s">
         <v>2</v>
       </c>
       <c r="X28" t="s">
-        <v>609</v>
+        <v>699</v>
       </c>
       <c r="AA28" t="s">
-        <v>481</v>
+        <v>554</v>
       </c>
       <c r="AB28" t="s">
-        <v>635</v>
+        <v>733</v>
       </c>
       <c r="AC28" t="s">
-        <v>638</v>
+        <v>736</v>
       </c>
     </row>
     <row r="29" spans="1:29">
@@ -4593,82 +4884,88 @@
         <v>56</v>
       </c>
       <c r="B29" t="s">
-        <v>102</v>
+        <v>110</v>
       </c>
       <c r="C29" t="s">
-        <v>121</v>
+        <v>137</v>
       </c>
       <c r="D29" t="s">
-        <v>149</v>
+        <v>165</v>
       </c>
       <c r="E29" t="s">
-        <v>194</v>
+        <v>218</v>
       </c>
       <c r="F29" t="s">
-        <v>231</v>
+        <v>215</v>
       </c>
       <c r="G29" t="s">
-        <v>243</v>
+        <v>276</v>
       </c>
       <c r="H29" t="s">
-        <v>272</v>
+        <v>305</v>
       </c>
       <c r="I29" t="s">
-        <v>312</v>
+        <v>352</v>
       </c>
       <c r="J29" t="s">
-        <v>328</v>
+        <v>376</v>
       </c>
       <c r="K29" t="s">
-        <v>357</v>
+        <v>404</v>
       </c>
       <c r="L29" t="s">
-        <v>403</v>
+        <v>458</v>
       </c>
       <c r="M29" t="s">
-        <v>449</v>
+        <v>512</v>
       </c>
       <c r="N29" t="s">
-        <v>468</v>
+        <v>539</v>
       </c>
       <c r="O29" t="s">
-        <v>469</v>
+        <v>541</v>
       </c>
       <c r="P29" t="s">
-        <v>477</v>
+        <v>544</v>
       </c>
       <c r="Q29" t="s">
-        <v>480</v>
+        <v>552</v>
       </c>
       <c r="R29" t="s">
-        <v>511</v>
+        <v>585</v>
       </c>
       <c r="S29" t="s">
-        <v>540</v>
+        <v>614</v>
       </c>
       <c r="T29" t="s">
-        <v>563</v>
+        <v>646</v>
       </c>
       <c r="U29" t="s">
-        <v>582</v>
+        <v>672</v>
       </c>
       <c r="V29" t="s">
-        <v>582</v>
+        <v>277</v>
       </c>
       <c r="W29" t="s">
         <v>2</v>
       </c>
       <c r="X29" t="s">
-        <v>610</v>
+        <v>700</v>
+      </c>
+      <c r="Y29" t="s">
+        <v>727</v>
+      </c>
+      <c r="Z29" t="s">
+        <v>728</v>
       </c>
       <c r="AA29" t="s">
-        <v>480</v>
+        <v>552</v>
       </c>
       <c r="AB29" t="s">
-        <v>635</v>
+        <v>731</v>
       </c>
       <c r="AC29" t="s">
-        <v>638</v>
+        <v>737</v>
       </c>
     </row>
     <row r="30" spans="1:29">
@@ -4676,85 +4973,82 @@
         <v>57</v>
       </c>
       <c r="B30" t="s">
-        <v>103</v>
+        <v>111</v>
       </c>
       <c r="C30" t="s">
-        <v>121</v>
+        <v>137</v>
       </c>
       <c r="D30" t="s">
-        <v>150</v>
+        <v>166</v>
       </c>
       <c r="E30" t="s">
-        <v>195</v>
+        <v>219</v>
       </c>
       <c r="F30" t="s">
-        <v>232</v>
+        <v>257</v>
       </c>
       <c r="G30" t="s">
-        <v>243</v>
+        <v>276</v>
       </c>
       <c r="H30" t="s">
-        <v>273</v>
+        <v>306</v>
       </c>
       <c r="I30" t="s">
-        <v>313</v>
+        <v>353</v>
       </c>
       <c r="J30" t="s">
-        <v>328</v>
+        <v>376</v>
       </c>
       <c r="K30" t="s">
-        <v>358</v>
+        <v>405</v>
       </c>
       <c r="L30" t="s">
-        <v>404</v>
+        <v>459</v>
       </c>
       <c r="M30" t="s">
-        <v>450</v>
+        <v>513</v>
+      </c>
+      <c r="N30" t="s">
+        <v>540</v>
       </c>
       <c r="O30" t="s">
-        <v>469</v>
+        <v>543</v>
       </c>
       <c r="P30" t="s">
-        <v>472</v>
+        <v>551</v>
       </c>
       <c r="Q30" t="s">
-        <v>479</v>
+        <v>557</v>
       </c>
       <c r="R30" t="s">
-        <v>512</v>
+        <v>586</v>
       </c>
       <c r="S30" t="s">
-        <v>532</v>
+        <v>623</v>
       </c>
       <c r="T30" t="s">
-        <v>564</v>
+        <v>647</v>
       </c>
       <c r="U30" t="s">
-        <v>582</v>
+        <v>672</v>
       </c>
       <c r="V30" t="s">
-        <v>244</v>
+        <v>672</v>
       </c>
       <c r="W30" t="s">
         <v>2</v>
       </c>
       <c r="X30" t="s">
-        <v>611</v>
-      </c>
-      <c r="Y30" t="s">
-        <v>629</v>
-      </c>
-      <c r="Z30" t="s">
-        <v>630</v>
+        <v>701</v>
       </c>
       <c r="AA30" t="s">
-        <v>479</v>
+        <v>557</v>
       </c>
       <c r="AB30" t="s">
-        <v>632</v>
+        <v>733</v>
       </c>
       <c r="AC30" t="s">
-        <v>638</v>
+        <v>736</v>
       </c>
     </row>
     <row r="31" spans="1:29">
@@ -4762,85 +5056,82 @@
         <v>58</v>
       </c>
       <c r="B31" t="s">
-        <v>104</v>
+        <v>112</v>
       </c>
       <c r="C31" t="s">
-        <v>121</v>
+        <v>137</v>
       </c>
       <c r="D31" t="s">
-        <v>151</v>
+        <v>167</v>
       </c>
       <c r="E31" t="s">
-        <v>196</v>
+        <v>220</v>
       </c>
       <c r="F31" t="s">
-        <v>233</v>
+        <v>260</v>
       </c>
       <c r="G31" t="s">
-        <v>243</v>
+        <v>276</v>
       </c>
       <c r="H31" t="s">
-        <v>274</v>
+        <v>307</v>
       </c>
       <c r="I31" t="s">
-        <v>314</v>
+        <v>354</v>
       </c>
       <c r="J31" t="s">
-        <v>329</v>
+        <v>375</v>
       </c>
       <c r="K31" t="s">
-        <v>359</v>
+        <v>406</v>
       </c>
       <c r="L31" t="s">
-        <v>405</v>
+        <v>460</v>
       </c>
       <c r="M31" t="s">
-        <v>451</v>
+        <v>514</v>
+      </c>
+      <c r="N31" t="s">
+        <v>540</v>
       </c>
       <c r="O31" t="s">
-        <v>469</v>
+        <v>541</v>
       </c>
       <c r="P31" t="s">
-        <v>472</v>
+        <v>549</v>
       </c>
       <c r="Q31" t="s">
-        <v>479</v>
+        <v>554</v>
       </c>
       <c r="R31" t="s">
-        <v>513</v>
+        <v>587</v>
       </c>
       <c r="S31" t="s">
-        <v>534</v>
+        <v>623</v>
       </c>
       <c r="T31" t="s">
-        <v>565</v>
+        <v>648</v>
       </c>
       <c r="U31" t="s">
-        <v>582</v>
+        <v>672</v>
       </c>
       <c r="V31" t="s">
-        <v>244</v>
+        <v>672</v>
       </c>
       <c r="W31" t="s">
         <v>2</v>
       </c>
       <c r="X31" t="s">
-        <v>612</v>
-      </c>
-      <c r="Y31" t="s">
-        <v>629</v>
-      </c>
-      <c r="Z31" t="s">
-        <v>631</v>
+        <v>702</v>
       </c>
       <c r="AA31" t="s">
-        <v>479</v>
+        <v>554</v>
       </c>
       <c r="AB31" t="s">
-        <v>632</v>
+        <v>733</v>
       </c>
       <c r="AC31" t="s">
-        <v>638</v>
+        <v>736</v>
       </c>
     </row>
     <row r="32" spans="1:29">
@@ -4848,82 +5139,88 @@
         <v>59</v>
       </c>
       <c r="B32" t="s">
-        <v>105</v>
+        <v>113</v>
       </c>
       <c r="C32" t="s">
-        <v>121</v>
+        <v>137</v>
       </c>
       <c r="D32" t="s">
-        <v>152</v>
+        <v>168</v>
       </c>
       <c r="E32" t="s">
         <v>197</v>
       </c>
       <c r="F32" t="s">
-        <v>176</v>
+        <v>261</v>
       </c>
       <c r="G32" t="s">
-        <v>243</v>
+        <v>276</v>
       </c>
       <c r="H32" t="s">
-        <v>275</v>
+        <v>308</v>
       </c>
       <c r="I32" t="s">
-        <v>315</v>
+        <v>355</v>
       </c>
       <c r="J32" t="s">
-        <v>328</v>
+        <v>376</v>
       </c>
       <c r="K32" t="s">
-        <v>360</v>
+        <v>407</v>
       </c>
       <c r="L32" t="s">
-        <v>406</v>
+        <v>461</v>
       </c>
       <c r="M32" t="s">
-        <v>452</v>
+        <v>515</v>
       </c>
       <c r="N32" t="s">
-        <v>468</v>
+        <v>540</v>
       </c>
       <c r="O32" t="s">
-        <v>471</v>
+        <v>543</v>
       </c>
       <c r="P32" t="s">
-        <v>475</v>
+        <v>551</v>
       </c>
       <c r="Q32" t="s">
-        <v>481</v>
+        <v>557</v>
       </c>
       <c r="R32" t="s">
-        <v>514</v>
+        <v>588</v>
       </c>
       <c r="S32" t="s">
-        <v>533</v>
+        <v>619</v>
       </c>
       <c r="T32" t="s">
-        <v>566</v>
+        <v>649</v>
       </c>
       <c r="U32" t="s">
-        <v>582</v>
+        <v>672</v>
       </c>
       <c r="V32" t="s">
-        <v>244</v>
+        <v>277</v>
       </c>
       <c r="W32" t="s">
         <v>2</v>
       </c>
       <c r="X32" t="s">
-        <v>613</v>
+        <v>703</v>
+      </c>
+      <c r="Y32" t="s">
+        <v>727</v>
+      </c>
+      <c r="Z32" t="s">
+        <v>728</v>
       </c>
       <c r="AA32" t="s">
-        <v>481</v>
+        <v>557</v>
       </c>
       <c r="AB32" t="s">
-        <v>633</v>
+        <v>734</v>
       </c>
       <c r="AC32" t="s">
-        <v>639</v>
+        <v>736</v>
       </c>
     </row>
     <row r="33" spans="1:29">
@@ -4931,88 +5228,79 @@
         <v>60</v>
       </c>
       <c r="B33" t="s">
-        <v>106</v>
+        <v>114</v>
       </c>
       <c r="C33" t="s">
-        <v>121</v>
+        <v>137</v>
       </c>
       <c r="D33" t="s">
-        <v>153</v>
+        <v>169</v>
       </c>
       <c r="E33" t="s">
-        <v>177</v>
+        <v>221</v>
       </c>
       <c r="F33" t="s">
-        <v>234</v>
+        <v>262</v>
       </c>
       <c r="G33" t="s">
-        <v>243</v>
+        <v>276</v>
       </c>
       <c r="H33" t="s">
-        <v>276</v>
+        <v>309</v>
       </c>
       <c r="I33" t="s">
-        <v>316</v>
+        <v>356</v>
       </c>
       <c r="J33" t="s">
-        <v>329</v>
+        <v>375</v>
       </c>
       <c r="K33" t="s">
-        <v>361</v>
+        <v>408</v>
       </c>
       <c r="L33" t="s">
-        <v>407</v>
+        <v>462</v>
       </c>
       <c r="M33" t="s">
-        <v>453</v>
-      </c>
-      <c r="N33" t="s">
-        <v>468</v>
+        <v>516</v>
       </c>
       <c r="O33" t="s">
-        <v>471</v>
+        <v>541</v>
       </c>
       <c r="P33" t="s">
-        <v>475</v>
+        <v>544</v>
       </c>
       <c r="Q33" t="s">
-        <v>481</v>
+        <v>552</v>
       </c>
       <c r="R33" t="s">
-        <v>515</v>
+        <v>589</v>
       </c>
       <c r="S33" t="s">
-        <v>534</v>
+        <v>617</v>
       </c>
       <c r="T33" t="s">
-        <v>567</v>
+        <v>650</v>
       </c>
       <c r="U33" t="s">
-        <v>582</v>
+        <v>672</v>
       </c>
       <c r="V33" t="s">
-        <v>244</v>
+        <v>277</v>
       </c>
       <c r="W33" t="s">
         <v>2</v>
       </c>
       <c r="X33" t="s">
-        <v>614</v>
-      </c>
-      <c r="Y33" t="s">
-        <v>629</v>
-      </c>
-      <c r="Z33" t="s">
-        <v>630</v>
+        <v>704</v>
       </c>
       <c r="AA33" t="s">
-        <v>481</v>
+        <v>552</v>
       </c>
       <c r="AB33" t="s">
-        <v>633</v>
+        <v>733</v>
       </c>
       <c r="AC33" t="s">
-        <v>639</v>
+        <v>736</v>
       </c>
     </row>
     <row r="34" spans="1:29">
@@ -5020,85 +5308,85 @@
         <v>61</v>
       </c>
       <c r="B34" t="s">
-        <v>107</v>
+        <v>115</v>
       </c>
       <c r="C34" t="s">
-        <v>121</v>
+        <v>137</v>
       </c>
       <c r="D34" t="s">
-        <v>154</v>
+        <v>170</v>
       </c>
       <c r="E34" t="s">
-        <v>198</v>
+        <v>222</v>
       </c>
       <c r="F34" t="s">
-        <v>202</v>
+        <v>263</v>
       </c>
       <c r="G34" t="s">
-        <v>243</v>
+        <v>276</v>
       </c>
       <c r="H34" t="s">
+        <v>310</v>
+      </c>
+      <c r="I34" t="s">
+        <v>357</v>
+      </c>
+      <c r="J34" t="s">
+        <v>375</v>
+      </c>
+      <c r="K34" t="s">
+        <v>409</v>
+      </c>
+      <c r="L34" t="s">
+        <v>463</v>
+      </c>
+      <c r="M34" t="s">
+        <v>517</v>
+      </c>
+      <c r="O34" t="s">
+        <v>541</v>
+      </c>
+      <c r="P34" t="s">
+        <v>544</v>
+      </c>
+      <c r="Q34" t="s">
+        <v>552</v>
+      </c>
+      <c r="R34" t="s">
+        <v>590</v>
+      </c>
+      <c r="S34" t="s">
+        <v>615</v>
+      </c>
+      <c r="T34" t="s">
+        <v>651</v>
+      </c>
+      <c r="U34" t="s">
+        <v>672</v>
+      </c>
+      <c r="V34" t="s">
         <v>277</v>
-      </c>
-      <c r="I34" t="s">
-        <v>317</v>
-      </c>
-      <c r="J34" t="s">
-        <v>329</v>
-      </c>
-      <c r="K34" t="s">
-        <v>362</v>
-      </c>
-      <c r="L34" t="s">
-        <v>408</v>
-      </c>
-      <c r="M34" t="s">
-        <v>454</v>
-      </c>
-      <c r="O34" t="s">
-        <v>469</v>
-      </c>
-      <c r="P34" t="s">
-        <v>472</v>
-      </c>
-      <c r="Q34" t="s">
-        <v>479</v>
-      </c>
-      <c r="R34" t="s">
-        <v>516</v>
-      </c>
-      <c r="S34" t="s">
-        <v>532</v>
-      </c>
-      <c r="T34" t="s">
-        <v>568</v>
-      </c>
-      <c r="U34" t="s">
-        <v>582</v>
-      </c>
-      <c r="V34" t="s">
-        <v>244</v>
       </c>
       <c r="W34" t="s">
         <v>2</v>
       </c>
       <c r="X34" t="s">
-        <v>615</v>
+        <v>705</v>
       </c>
       <c r="Y34" t="s">
-        <v>629</v>
+        <v>727</v>
       </c>
       <c r="Z34" t="s">
-        <v>631</v>
+        <v>728</v>
       </c>
       <c r="AA34" t="s">
-        <v>479</v>
+        <v>552</v>
       </c>
       <c r="AB34" t="s">
-        <v>633</v>
+        <v>730</v>
       </c>
       <c r="AC34" t="s">
-        <v>639</v>
+        <v>736</v>
       </c>
     </row>
     <row r="35" spans="1:29">
@@ -5106,85 +5394,85 @@
         <v>62</v>
       </c>
       <c r="B35" t="s">
-        <v>108</v>
+        <v>116</v>
       </c>
       <c r="C35" t="s">
-        <v>121</v>
+        <v>137</v>
       </c>
       <c r="D35" t="s">
-        <v>155</v>
+        <v>171</v>
       </c>
       <c r="E35" t="s">
-        <v>199</v>
+        <v>223</v>
       </c>
       <c r="F35" t="s">
-        <v>179</v>
+        <v>264</v>
       </c>
       <c r="G35" t="s">
-        <v>243</v>
+        <v>276</v>
       </c>
       <c r="H35" t="s">
-        <v>278</v>
+        <v>311</v>
       </c>
       <c r="I35" t="s">
-        <v>318</v>
+        <v>358</v>
       </c>
       <c r="J35" t="s">
-        <v>328</v>
+        <v>376</v>
       </c>
       <c r="K35" t="s">
-        <v>363</v>
+        <v>410</v>
       </c>
       <c r="L35" t="s">
-        <v>409</v>
+        <v>464</v>
       </c>
       <c r="M35" t="s">
-        <v>455</v>
+        <v>518</v>
       </c>
       <c r="O35" t="s">
-        <v>469</v>
+        <v>541</v>
       </c>
       <c r="P35" t="s">
-        <v>472</v>
+        <v>544</v>
       </c>
       <c r="Q35" t="s">
-        <v>479</v>
+        <v>552</v>
       </c>
       <c r="R35" t="s">
-        <v>517</v>
+        <v>591</v>
       </c>
       <c r="S35" t="s">
-        <v>534</v>
+        <v>619</v>
       </c>
       <c r="T35" t="s">
-        <v>569</v>
+        <v>652</v>
       </c>
       <c r="U35" t="s">
-        <v>582</v>
+        <v>672</v>
       </c>
       <c r="V35" t="s">
-        <v>244</v>
+        <v>277</v>
       </c>
       <c r="W35" t="s">
         <v>2</v>
       </c>
       <c r="X35" t="s">
-        <v>616</v>
+        <v>706</v>
       </c>
       <c r="Y35" t="s">
-        <v>629</v>
+        <v>727</v>
       </c>
       <c r="Z35" t="s">
-        <v>631</v>
+        <v>729</v>
       </c>
       <c r="AA35" t="s">
-        <v>479</v>
+        <v>552</v>
       </c>
       <c r="AB35" t="s">
-        <v>632</v>
+        <v>730</v>
       </c>
       <c r="AC35" t="s">
-        <v>638</v>
+        <v>736</v>
       </c>
     </row>
     <row r="36" spans="1:29">
@@ -5192,85 +5480,82 @@
         <v>63</v>
       </c>
       <c r="B36" t="s">
-        <v>109</v>
+        <v>117</v>
       </c>
       <c r="C36" t="s">
-        <v>121</v>
+        <v>137</v>
       </c>
       <c r="D36" t="s">
-        <v>156</v>
+        <v>172</v>
       </c>
       <c r="E36" t="s">
-        <v>200</v>
+        <v>224</v>
       </c>
       <c r="F36" t="s">
-        <v>235</v>
+        <v>198</v>
       </c>
       <c r="G36" t="s">
-        <v>243</v>
+        <v>276</v>
       </c>
       <c r="H36" t="s">
-        <v>279</v>
+        <v>312</v>
       </c>
       <c r="I36" t="s">
-        <v>319</v>
+        <v>359</v>
       </c>
       <c r="J36" t="s">
-        <v>328</v>
+        <v>375</v>
       </c>
       <c r="K36" t="s">
-        <v>364</v>
+        <v>411</v>
       </c>
       <c r="L36" t="s">
-        <v>410</v>
+        <v>465</v>
       </c>
       <c r="M36" t="s">
-        <v>456</v>
+        <v>519</v>
+      </c>
+      <c r="N36" t="s">
+        <v>540</v>
       </c>
       <c r="O36" t="s">
-        <v>469</v>
+        <v>543</v>
       </c>
       <c r="P36" t="s">
-        <v>472</v>
+        <v>551</v>
       </c>
       <c r="Q36" t="s">
-        <v>479</v>
+        <v>557</v>
       </c>
       <c r="R36" t="s">
-        <v>518</v>
+        <v>592</v>
       </c>
       <c r="S36" t="s">
-        <v>534</v>
+        <v>617</v>
       </c>
       <c r="T36" t="s">
-        <v>570</v>
+        <v>653</v>
       </c>
       <c r="U36" t="s">
-        <v>582</v>
+        <v>672</v>
       </c>
       <c r="V36" t="s">
-        <v>244</v>
+        <v>277</v>
       </c>
       <c r="W36" t="s">
         <v>2</v>
       </c>
       <c r="X36" t="s">
-        <v>617</v>
-      </c>
-      <c r="Y36" t="s">
-        <v>629</v>
-      </c>
-      <c r="Z36" t="s">
-        <v>631</v>
+        <v>707</v>
       </c>
       <c r="AA36" t="s">
-        <v>479</v>
+        <v>557</v>
       </c>
       <c r="AB36" t="s">
-        <v>632</v>
+        <v>734</v>
       </c>
       <c r="AC36" t="s">
-        <v>638</v>
+        <v>736</v>
       </c>
     </row>
     <row r="37" spans="1:29">
@@ -5278,79 +5563,82 @@
         <v>64</v>
       </c>
       <c r="B37" t="s">
-        <v>110</v>
+        <v>118</v>
       </c>
       <c r="C37" t="s">
-        <v>121</v>
+        <v>137</v>
       </c>
       <c r="D37" t="s">
-        <v>157</v>
+        <v>173</v>
       </c>
       <c r="E37" t="s">
-        <v>201</v>
+        <v>225</v>
       </c>
       <c r="F37" t="s">
-        <v>236</v>
+        <v>265</v>
       </c>
       <c r="G37" t="s">
-        <v>243</v>
+        <v>276</v>
       </c>
       <c r="H37" t="s">
-        <v>280</v>
+        <v>313</v>
       </c>
       <c r="I37" t="s">
-        <v>320</v>
+        <v>360</v>
       </c>
       <c r="J37" t="s">
-        <v>328</v>
+        <v>375</v>
       </c>
       <c r="K37" t="s">
-        <v>365</v>
+        <v>412</v>
       </c>
       <c r="L37" t="s">
-        <v>411</v>
+        <v>466</v>
       </c>
       <c r="M37" t="s">
-        <v>457</v>
+        <v>520</v>
+      </c>
+      <c r="N37" t="s">
+        <v>540</v>
       </c>
       <c r="O37" t="s">
-        <v>469</v>
+        <v>543</v>
       </c>
       <c r="P37" t="s">
-        <v>472</v>
+        <v>551</v>
       </c>
       <c r="Q37" t="s">
-        <v>479</v>
+        <v>557</v>
       </c>
       <c r="R37" t="s">
-        <v>519</v>
+        <v>593</v>
       </c>
       <c r="S37" t="s">
-        <v>533</v>
+        <v>624</v>
       </c>
       <c r="T37" t="s">
-        <v>571</v>
+        <v>654</v>
       </c>
       <c r="U37" t="s">
-        <v>582</v>
+        <v>672</v>
       </c>
       <c r="V37" t="s">
-        <v>244</v>
+        <v>277</v>
       </c>
       <c r="W37" t="s">
         <v>2</v>
       </c>
       <c r="X37" t="s">
-        <v>618</v>
+        <v>708</v>
       </c>
       <c r="AA37" t="s">
-        <v>479</v>
+        <v>557</v>
       </c>
       <c r="AB37" t="s">
-        <v>635</v>
+        <v>731</v>
       </c>
       <c r="AC37" t="s">
-        <v>638</v>
+        <v>737</v>
       </c>
     </row>
     <row r="38" spans="1:29">
@@ -5358,85 +5646,85 @@
         <v>65</v>
       </c>
       <c r="B38" t="s">
-        <v>111</v>
+        <v>119</v>
       </c>
       <c r="C38" t="s">
-        <v>121</v>
+        <v>137</v>
       </c>
       <c r="D38" t="s">
-        <v>158</v>
+        <v>174</v>
       </c>
       <c r="E38" t="s">
+        <v>226</v>
+      </c>
+      <c r="F38" t="s">
         <v>202</v>
       </c>
-      <c r="F38" t="s">
-        <v>237</v>
-      </c>
       <c r="G38" t="s">
-        <v>244</v>
+        <v>276</v>
       </c>
       <c r="H38" t="s">
-        <v>281</v>
+        <v>314</v>
       </c>
       <c r="I38" t="s">
-        <v>321</v>
+        <v>361</v>
       </c>
       <c r="J38" t="s">
-        <v>328</v>
+        <v>375</v>
       </c>
       <c r="K38" t="s">
-        <v>366</v>
+        <v>413</v>
       </c>
       <c r="L38" t="s">
-        <v>412</v>
+        <v>467</v>
       </c>
       <c r="M38" t="s">
-        <v>458</v>
+        <v>521</v>
       </c>
       <c r="O38" t="s">
-        <v>469</v>
+        <v>541</v>
       </c>
       <c r="P38" t="s">
-        <v>472</v>
+        <v>544</v>
       </c>
       <c r="Q38" t="s">
-        <v>479</v>
+        <v>552</v>
       </c>
       <c r="R38" t="s">
-        <v>520</v>
+        <v>594</v>
       </c>
       <c r="S38" t="s">
-        <v>534</v>
+        <v>619</v>
       </c>
       <c r="T38" t="s">
-        <v>572</v>
+        <v>655</v>
       </c>
       <c r="U38" t="s">
-        <v>582</v>
+        <v>672</v>
       </c>
       <c r="V38" t="s">
-        <v>244</v>
+        <v>277</v>
       </c>
       <c r="W38" t="s">
         <v>2</v>
       </c>
       <c r="X38" t="s">
-        <v>619</v>
+        <v>709</v>
       </c>
       <c r="Y38" t="s">
-        <v>629</v>
+        <v>727</v>
       </c>
       <c r="Z38" t="s">
-        <v>631</v>
+        <v>729</v>
       </c>
       <c r="AA38" t="s">
-        <v>479</v>
+        <v>552</v>
       </c>
       <c r="AB38" t="s">
-        <v>632</v>
+        <v>730</v>
       </c>
       <c r="AC38" t="s">
-        <v>638</v>
+        <v>736</v>
       </c>
     </row>
     <row r="39" spans="1:29">
@@ -5444,79 +5732,85 @@
         <v>66</v>
       </c>
       <c r="B39" t="s">
-        <v>112</v>
+        <v>120</v>
       </c>
       <c r="C39" t="s">
-        <v>121</v>
+        <v>137</v>
       </c>
       <c r="D39" t="s">
-        <v>159</v>
+        <v>175</v>
       </c>
       <c r="E39" t="s">
-        <v>175</v>
+        <v>227</v>
       </c>
       <c r="F39" t="s">
-        <v>177</v>
+        <v>266</v>
       </c>
       <c r="G39" t="s">
-        <v>243</v>
+        <v>276</v>
       </c>
       <c r="H39" t="s">
-        <v>282</v>
+        <v>315</v>
       </c>
       <c r="I39" t="s">
-        <v>295</v>
+        <v>362</v>
       </c>
       <c r="J39" t="s">
-        <v>329</v>
+        <v>375</v>
       </c>
       <c r="K39" t="s">
-        <v>367</v>
+        <v>414</v>
       </c>
       <c r="L39" t="s">
-        <v>413</v>
+        <v>468</v>
       </c>
       <c r="M39" t="s">
-        <v>459</v>
+        <v>522</v>
       </c>
       <c r="O39" t="s">
-        <v>469</v>
+        <v>541</v>
       </c>
       <c r="P39" t="s">
-        <v>473</v>
+        <v>544</v>
       </c>
       <c r="Q39" t="s">
-        <v>479</v>
+        <v>552</v>
       </c>
       <c r="R39" t="s">
-        <v>521</v>
+        <v>595</v>
       </c>
       <c r="S39" t="s">
-        <v>533</v>
+        <v>619</v>
       </c>
       <c r="T39" t="s">
-        <v>573</v>
+        <v>656</v>
       </c>
       <c r="U39" t="s">
-        <v>582</v>
+        <v>672</v>
       </c>
       <c r="V39" t="s">
-        <v>244</v>
+        <v>277</v>
       </c>
       <c r="W39" t="s">
         <v>2</v>
       </c>
       <c r="X39" t="s">
-        <v>620</v>
+        <v>710</v>
+      </c>
+      <c r="Y39" t="s">
+        <v>727</v>
+      </c>
+      <c r="Z39" t="s">
+        <v>729</v>
       </c>
       <c r="AA39" t="s">
-        <v>479</v>
+        <v>552</v>
       </c>
       <c r="AB39" t="s">
-        <v>633</v>
+        <v>730</v>
       </c>
       <c r="AC39" t="s">
-        <v>639</v>
+        <v>736</v>
       </c>
     </row>
     <row r="40" spans="1:29">
@@ -5524,85 +5818,85 @@
         <v>67</v>
       </c>
       <c r="B40" t="s">
-        <v>113</v>
+        <v>121</v>
       </c>
       <c r="C40" t="s">
-        <v>121</v>
+        <v>137</v>
       </c>
       <c r="D40" t="s">
-        <v>160</v>
+        <v>176</v>
       </c>
       <c r="E40" t="s">
-        <v>203</v>
+        <v>228</v>
       </c>
       <c r="F40" t="s">
-        <v>202</v>
+        <v>231</v>
       </c>
       <c r="G40" t="s">
-        <v>244</v>
+        <v>277</v>
       </c>
       <c r="H40" t="s">
-        <v>283</v>
+        <v>316</v>
       </c>
       <c r="I40" t="s">
-        <v>314</v>
+        <v>358</v>
       </c>
       <c r="J40" t="s">
-        <v>329</v>
+        <v>376</v>
       </c>
       <c r="K40" t="s">
-        <v>368</v>
+        <v>415</v>
       </c>
       <c r="L40" t="s">
-        <v>414</v>
+        <v>469</v>
       </c>
       <c r="M40" t="s">
-        <v>460</v>
+        <v>523</v>
       </c>
       <c r="O40" t="s">
-        <v>469</v>
+        <v>541</v>
       </c>
       <c r="P40" t="s">
-        <v>472</v>
+        <v>544</v>
       </c>
       <c r="Q40" t="s">
-        <v>479</v>
+        <v>552</v>
       </c>
       <c r="R40" t="s">
-        <v>522</v>
+        <v>596</v>
       </c>
       <c r="S40" t="s">
-        <v>534</v>
+        <v>619</v>
       </c>
       <c r="T40" t="s">
-        <v>574</v>
+        <v>657</v>
       </c>
       <c r="U40" t="s">
-        <v>582</v>
+        <v>672</v>
       </c>
       <c r="V40" t="s">
-        <v>244</v>
+        <v>277</v>
       </c>
       <c r="W40" t="s">
         <v>2</v>
       </c>
       <c r="X40" t="s">
-        <v>621</v>
+        <v>711</v>
       </c>
       <c r="Y40" t="s">
-        <v>629</v>
+        <v>727</v>
       </c>
       <c r="Z40" t="s">
-        <v>631</v>
+        <v>729</v>
       </c>
       <c r="AA40" t="s">
-        <v>479</v>
+        <v>552</v>
       </c>
       <c r="AB40" t="s">
-        <v>632</v>
+        <v>730</v>
       </c>
       <c r="AC40" t="s">
-        <v>638</v>
+        <v>736</v>
       </c>
     </row>
     <row r="41" spans="1:29">
@@ -5610,79 +5904,85 @@
         <v>68</v>
       </c>
       <c r="B41" t="s">
-        <v>114</v>
+        <v>122</v>
       </c>
       <c r="C41" t="s">
-        <v>121</v>
+        <v>137</v>
       </c>
       <c r="D41" t="s">
-        <v>161</v>
+        <v>177</v>
       </c>
       <c r="E41" t="s">
-        <v>204</v>
+        <v>229</v>
       </c>
       <c r="F41" t="s">
-        <v>238</v>
+        <v>267</v>
       </c>
       <c r="G41" t="s">
-        <v>243</v>
+        <v>276</v>
       </c>
       <c r="H41" t="s">
-        <v>284</v>
+        <v>317</v>
       </c>
       <c r="I41" t="s">
-        <v>322</v>
+        <v>363</v>
       </c>
       <c r="J41" t="s">
-        <v>328</v>
+        <v>376</v>
       </c>
       <c r="K41" t="s">
-        <v>369</v>
+        <v>416</v>
       </c>
       <c r="L41" t="s">
-        <v>415</v>
+        <v>470</v>
       </c>
       <c r="M41" t="s">
-        <v>461</v>
+        <v>524</v>
       </c>
       <c r="O41" t="s">
-        <v>469</v>
+        <v>541</v>
       </c>
       <c r="P41" t="s">
-        <v>472</v>
+        <v>544</v>
       </c>
       <c r="Q41" t="s">
-        <v>479</v>
+        <v>552</v>
       </c>
       <c r="R41" t="s">
-        <v>523</v>
+        <v>597</v>
       </c>
       <c r="S41" t="s">
-        <v>533</v>
+        <v>613</v>
       </c>
       <c r="T41" t="s">
-        <v>575</v>
+        <v>658</v>
       </c>
       <c r="U41" t="s">
-        <v>582</v>
+        <v>672</v>
       </c>
       <c r="V41" t="s">
-        <v>582</v>
+        <v>672</v>
       </c>
       <c r="W41" t="s">
         <v>2</v>
       </c>
       <c r="X41" t="s">
-        <v>622</v>
+        <v>712</v>
+      </c>
+      <c r="Y41" t="s">
+        <v>727</v>
+      </c>
+      <c r="Z41" t="s">
+        <v>729</v>
       </c>
       <c r="AA41" t="s">
-        <v>479</v>
+        <v>552</v>
       </c>
       <c r="AB41" t="s">
-        <v>637</v>
+        <v>730</v>
       </c>
       <c r="AC41" t="s">
-        <v>638</v>
+        <v>736</v>
       </c>
     </row>
     <row r="42" spans="1:29">
@@ -5690,79 +5990,85 @@
         <v>69</v>
       </c>
       <c r="B42" t="s">
-        <v>115</v>
+        <v>123</v>
       </c>
       <c r="C42" t="s">
-        <v>121</v>
+        <v>137</v>
       </c>
       <c r="D42" t="s">
-        <v>162</v>
+        <v>178</v>
       </c>
       <c r="E42" t="s">
-        <v>205</v>
+        <v>230</v>
       </c>
       <c r="F42" t="s">
-        <v>239</v>
+        <v>268</v>
       </c>
       <c r="G42" t="s">
-        <v>243</v>
+        <v>276</v>
       </c>
       <c r="H42" t="s">
-        <v>285</v>
+        <v>318</v>
       </c>
       <c r="I42" t="s">
-        <v>320</v>
+        <v>364</v>
       </c>
       <c r="J42" t="s">
-        <v>329</v>
+        <v>375</v>
       </c>
       <c r="K42" t="s">
-        <v>370</v>
+        <v>417</v>
       </c>
       <c r="L42" t="s">
-        <v>416</v>
+        <v>471</v>
       </c>
       <c r="M42" t="s">
-        <v>462</v>
+        <v>525</v>
       </c>
       <c r="O42" t="s">
-        <v>469</v>
+        <v>541</v>
       </c>
       <c r="P42" t="s">
-        <v>472</v>
+        <v>544</v>
       </c>
       <c r="Q42" t="s">
-        <v>479</v>
+        <v>552</v>
       </c>
       <c r="R42" t="s">
-        <v>524</v>
+        <v>598</v>
       </c>
       <c r="S42" t="s">
-        <v>533</v>
+        <v>619</v>
       </c>
       <c r="T42" t="s">
-        <v>576</v>
+        <v>659</v>
       </c>
       <c r="U42" t="s">
-        <v>582</v>
+        <v>672</v>
       </c>
       <c r="V42" t="s">
-        <v>244</v>
+        <v>277</v>
       </c>
       <c r="W42" t="s">
         <v>2</v>
       </c>
       <c r="X42" t="s">
-        <v>623</v>
+        <v>713</v>
+      </c>
+      <c r="Y42" t="s">
+        <v>727</v>
+      </c>
+      <c r="Z42" t="s">
+        <v>729</v>
       </c>
       <c r="AA42" t="s">
-        <v>479</v>
+        <v>552</v>
       </c>
       <c r="AB42" t="s">
-        <v>635</v>
+        <v>734</v>
       </c>
       <c r="AC42" t="s">
-        <v>638</v>
+        <v>736</v>
       </c>
     </row>
     <row r="43" spans="1:29">
@@ -5770,85 +6076,85 @@
         <v>70</v>
       </c>
       <c r="B43" t="s">
-        <v>116</v>
+        <v>124</v>
       </c>
       <c r="C43" t="s">
-        <v>121</v>
+        <v>137</v>
       </c>
       <c r="D43" t="s">
-        <v>163</v>
+        <v>179</v>
       </c>
       <c r="E43" t="s">
-        <v>206</v>
+        <v>231</v>
       </c>
       <c r="F43" t="s">
-        <v>240</v>
+        <v>269</v>
       </c>
       <c r="G43" t="s">
-        <v>243</v>
+        <v>277</v>
       </c>
       <c r="H43" t="s">
-        <v>286</v>
+        <v>319</v>
       </c>
       <c r="I43" t="s">
-        <v>323</v>
+        <v>365</v>
       </c>
       <c r="J43" t="s">
-        <v>329</v>
+        <v>375</v>
       </c>
       <c r="K43" t="s">
-        <v>371</v>
+        <v>418</v>
       </c>
       <c r="L43" t="s">
-        <v>417</v>
+        <v>472</v>
       </c>
       <c r="M43" t="s">
-        <v>463</v>
+        <v>526</v>
       </c>
       <c r="O43" t="s">
-        <v>469</v>
+        <v>541</v>
       </c>
       <c r="P43" t="s">
-        <v>472</v>
+        <v>544</v>
       </c>
       <c r="Q43" t="s">
-        <v>479</v>
+        <v>552</v>
       </c>
       <c r="R43" t="s">
-        <v>525</v>
+        <v>599</v>
       </c>
       <c r="S43" t="s">
-        <v>531</v>
+        <v>619</v>
       </c>
       <c r="T43" t="s">
-        <v>577</v>
+        <v>660</v>
       </c>
       <c r="U43" t="s">
-        <v>582</v>
+        <v>672</v>
       </c>
       <c r="V43" t="s">
-        <v>582</v>
+        <v>277</v>
       </c>
       <c r="W43" t="s">
         <v>2</v>
       </c>
       <c r="X43" t="s">
-        <v>624</v>
+        <v>714</v>
       </c>
       <c r="Y43" t="s">
-        <v>629</v>
+        <v>727</v>
       </c>
       <c r="Z43" t="s">
-        <v>631</v>
+        <v>729</v>
       </c>
       <c r="AA43" t="s">
-        <v>479</v>
+        <v>552</v>
       </c>
       <c r="AB43" t="s">
-        <v>632</v>
+        <v>730</v>
       </c>
       <c r="AC43" t="s">
-        <v>638</v>
+        <v>736</v>
       </c>
     </row>
     <row r="44" spans="1:29">
@@ -5856,85 +6162,79 @@
         <v>71</v>
       </c>
       <c r="B44" t="s">
-        <v>117</v>
+        <v>125</v>
       </c>
       <c r="C44" t="s">
-        <v>121</v>
+        <v>137</v>
       </c>
       <c r="D44" t="s">
-        <v>164</v>
+        <v>180</v>
       </c>
       <c r="E44" t="s">
-        <v>207</v>
+        <v>215</v>
       </c>
       <c r="F44" t="s">
-        <v>241</v>
+        <v>197</v>
       </c>
       <c r="G44" t="s">
-        <v>243</v>
+        <v>276</v>
       </c>
       <c r="H44" t="s">
-        <v>287</v>
+        <v>320</v>
       </c>
       <c r="I44" t="s">
-        <v>324</v>
+        <v>338</v>
       </c>
       <c r="J44" t="s">
-        <v>329</v>
+        <v>376</v>
       </c>
       <c r="K44" t="s">
-        <v>372</v>
+        <v>419</v>
       </c>
       <c r="L44" t="s">
-        <v>418</v>
+        <v>473</v>
       </c>
       <c r="M44" t="s">
-        <v>464</v>
+        <v>527</v>
       </c>
       <c r="O44" t="s">
-        <v>469</v>
+        <v>541</v>
       </c>
       <c r="P44" t="s">
-        <v>472</v>
+        <v>548</v>
       </c>
       <c r="Q44" t="s">
-        <v>479</v>
+        <v>552</v>
       </c>
       <c r="R44" t="s">
-        <v>526</v>
+        <v>600</v>
       </c>
       <c r="S44" t="s">
-        <v>541</v>
+        <v>617</v>
       </c>
       <c r="T44" t="s">
-        <v>578</v>
+        <v>661</v>
       </c>
       <c r="U44" t="s">
-        <v>582</v>
+        <v>672</v>
       </c>
       <c r="V44" t="s">
-        <v>244</v>
+        <v>277</v>
       </c>
       <c r="W44" t="s">
         <v>2</v>
       </c>
       <c r="X44" t="s">
-        <v>625</v>
-      </c>
-      <c r="Y44" t="s">
-        <v>629</v>
-      </c>
-      <c r="Z44" t="s">
-        <v>630</v>
+        <v>715</v>
       </c>
       <c r="AA44" t="s">
-        <v>479</v>
+        <v>552</v>
       </c>
       <c r="AB44" t="s">
-        <v>633</v>
+        <v>731</v>
       </c>
       <c r="AC44" t="s">
-        <v>639</v>
+        <v>737</v>
       </c>
     </row>
     <row r="45" spans="1:29">
@@ -5942,79 +6242,85 @@
         <v>72</v>
       </c>
       <c r="B45" t="s">
-        <v>118</v>
+        <v>126</v>
       </c>
       <c r="C45" t="s">
-        <v>121</v>
+        <v>137</v>
       </c>
       <c r="D45" t="s">
-        <v>165</v>
+        <v>181</v>
       </c>
       <c r="E45" t="s">
-        <v>208</v>
+        <v>232</v>
       </c>
       <c r="F45" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="G45" t="s">
-        <v>243</v>
+        <v>276</v>
       </c>
       <c r="H45" t="s">
-        <v>288</v>
+        <v>321</v>
       </c>
       <c r="I45" t="s">
-        <v>325</v>
+        <v>366</v>
       </c>
       <c r="J45" t="s">
-        <v>328</v>
+        <v>376</v>
       </c>
       <c r="K45" t="s">
-        <v>373</v>
+        <v>420</v>
       </c>
       <c r="L45" t="s">
-        <v>419</v>
+        <v>474</v>
       </c>
       <c r="M45" t="s">
-        <v>465</v>
+        <v>528</v>
       </c>
       <c r="O45" t="s">
-        <v>469</v>
+        <v>541</v>
       </c>
       <c r="P45" t="s">
-        <v>472</v>
+        <v>544</v>
       </c>
       <c r="Q45" t="s">
-        <v>479</v>
+        <v>552</v>
       </c>
       <c r="R45" t="s">
-        <v>527</v>
+        <v>601</v>
       </c>
       <c r="S45" t="s">
-        <v>541</v>
+        <v>625</v>
       </c>
       <c r="T45" t="s">
-        <v>579</v>
+        <v>662</v>
       </c>
       <c r="U45" t="s">
-        <v>582</v>
+        <v>672</v>
       </c>
       <c r="V45" t="s">
-        <v>244</v>
+        <v>277</v>
       </c>
       <c r="W45" t="s">
         <v>2</v>
       </c>
       <c r="X45" t="s">
-        <v>626</v>
+        <v>716</v>
+      </c>
+      <c r="Y45" t="s">
+        <v>727</v>
+      </c>
+      <c r="Z45" t="s">
+        <v>728</v>
       </c>
       <c r="AA45" t="s">
-        <v>479</v>
+        <v>552</v>
       </c>
       <c r="AB45" t="s">
-        <v>632</v>
+        <v>731</v>
       </c>
       <c r="AC45" t="s">
-        <v>638</v>
+        <v>737</v>
       </c>
     </row>
     <row r="46" spans="1:29">
@@ -6022,79 +6328,79 @@
         <v>73</v>
       </c>
       <c r="B46" t="s">
-        <v>119</v>
+        <v>127</v>
       </c>
       <c r="C46" t="s">
-        <v>121</v>
+        <v>137</v>
       </c>
       <c r="D46" t="s">
-        <v>166</v>
+        <v>182</v>
       </c>
       <c r="E46" t="s">
-        <v>209</v>
+        <v>233</v>
       </c>
       <c r="F46" t="s">
-        <v>242</v>
+        <v>271</v>
       </c>
       <c r="G46" t="s">
-        <v>243</v>
+        <v>276</v>
       </c>
       <c r="H46" t="s">
-        <v>289</v>
+        <v>322</v>
       </c>
       <c r="I46" t="s">
-        <v>326</v>
+        <v>367</v>
       </c>
       <c r="J46" t="s">
-        <v>329</v>
+        <v>376</v>
       </c>
       <c r="K46" t="s">
-        <v>374</v>
+        <v>421</v>
       </c>
       <c r="L46" t="s">
-        <v>420</v>
+        <v>475</v>
       </c>
       <c r="M46" t="s">
-        <v>466</v>
+        <v>529</v>
       </c>
       <c r="O46" t="s">
-        <v>469</v>
+        <v>541</v>
       </c>
       <c r="P46" t="s">
-        <v>472</v>
+        <v>544</v>
       </c>
       <c r="Q46" t="s">
-        <v>479</v>
+        <v>552</v>
       </c>
       <c r="R46" t="s">
-        <v>528</v>
+        <v>602</v>
       </c>
       <c r="S46" t="s">
-        <v>530</v>
+        <v>612</v>
       </c>
       <c r="T46" t="s">
-        <v>580</v>
+        <v>663</v>
       </c>
       <c r="U46" t="s">
-        <v>582</v>
+        <v>672</v>
       </c>
       <c r="V46" t="s">
-        <v>244</v>
+        <v>277</v>
       </c>
       <c r="W46" t="s">
         <v>2</v>
       </c>
       <c r="X46" t="s">
-        <v>627</v>
+        <v>717</v>
       </c>
       <c r="AA46" t="s">
-        <v>479</v>
+        <v>552</v>
       </c>
       <c r="AB46" t="s">
-        <v>632</v>
+        <v>730</v>
       </c>
       <c r="AC46" t="s">
-        <v>638</v>
+        <v>736</v>
       </c>
     </row>
     <row r="47" spans="1:29">
@@ -6102,79 +6408,728 @@
         <v>74</v>
       </c>
       <c r="B47" t="s">
-        <v>120</v>
+        <v>128</v>
       </c>
       <c r="C47" t="s">
-        <v>121</v>
+        <v>137</v>
       </c>
       <c r="D47" t="s">
-        <v>167</v>
+        <v>183</v>
       </c>
       <c r="E47" t="s">
-        <v>210</v>
+        <v>234</v>
       </c>
       <c r="F47" t="s">
-        <v>170</v>
+        <v>231</v>
       </c>
       <c r="G47" t="s">
-        <v>243</v>
+        <v>276</v>
       </c>
       <c r="H47" t="s">
-        <v>290</v>
+        <v>323</v>
       </c>
       <c r="I47" t="s">
-        <v>327</v>
+        <v>368</v>
       </c>
       <c r="J47" t="s">
-        <v>328</v>
+        <v>376</v>
       </c>
       <c r="K47" t="s">
-        <v>375</v>
+        <v>422</v>
       </c>
       <c r="L47" t="s">
-        <v>421</v>
+        <v>476</v>
       </c>
       <c r="M47" t="s">
-        <v>467</v>
+        <v>530</v>
       </c>
       <c r="O47" t="s">
-        <v>469</v>
+        <v>541</v>
       </c>
       <c r="P47" t="s">
-        <v>472</v>
+        <v>544</v>
       </c>
       <c r="Q47" t="s">
-        <v>479</v>
+        <v>552</v>
       </c>
       <c r="R47" t="s">
-        <v>529</v>
+        <v>603</v>
       </c>
       <c r="S47" t="s">
-        <v>541</v>
+        <v>615</v>
       </c>
       <c r="T47" t="s">
-        <v>581</v>
+        <v>664</v>
       </c>
       <c r="U47" t="s">
-        <v>582</v>
+        <v>672</v>
       </c>
       <c r="V47" t="s">
-        <v>244</v>
+        <v>277</v>
       </c>
       <c r="W47" t="s">
         <v>2</v>
       </c>
       <c r="X47" t="s">
-        <v>628</v>
+        <v>718</v>
+      </c>
+      <c r="Y47" t="s">
+        <v>727</v>
+      </c>
+      <c r="Z47" t="s">
+        <v>729</v>
       </c>
       <c r="AA47" t="s">
+        <v>552</v>
+      </c>
+      <c r="AB47" t="s">
+        <v>731</v>
+      </c>
+      <c r="AC47" t="s">
+        <v>737</v>
+      </c>
+    </row>
+    <row r="48" spans="1:29">
+      <c r="A48" t="s">
+        <v>75</v>
+      </c>
+      <c r="B48" t="s">
+        <v>129</v>
+      </c>
+      <c r="C48" t="s">
+        <v>137</v>
+      </c>
+      <c r="D48" t="s">
+        <v>184</v>
+      </c>
+      <c r="E48" t="s">
+        <v>235</v>
+      </c>
+      <c r="F48" t="s">
+        <v>272</v>
+      </c>
+      <c r="G48" t="s">
+        <v>276</v>
+      </c>
+      <c r="H48" t="s">
+        <v>324</v>
+      </c>
+      <c r="I48" t="s">
+        <v>356</v>
+      </c>
+      <c r="J48" t="s">
+        <v>376</v>
+      </c>
+      <c r="K48" t="s">
+        <v>423</v>
+      </c>
+      <c r="L48" t="s">
+        <v>477</v>
+      </c>
+      <c r="M48" t="s">
+        <v>531</v>
+      </c>
+      <c r="O48" t="s">
+        <v>541</v>
+      </c>
+      <c r="P48" t="s">
+        <v>544</v>
+      </c>
+      <c r="Q48" t="s">
+        <v>552</v>
+      </c>
+      <c r="R48" t="s">
+        <v>604</v>
+      </c>
+      <c r="S48" t="s">
+        <v>617</v>
+      </c>
+      <c r="T48" t="s">
+        <v>665</v>
+      </c>
+      <c r="U48" t="s">
+        <v>672</v>
+      </c>
+      <c r="V48" t="s">
+        <v>277</v>
+      </c>
+      <c r="W48" t="s">
+        <v>2</v>
+      </c>
+      <c r="X48" t="s">
+        <v>719</v>
+      </c>
+      <c r="AA48" t="s">
+        <v>552</v>
+      </c>
+      <c r="AB48" t="s">
+        <v>733</v>
+      </c>
+      <c r="AC48" t="s">
+        <v>736</v>
+      </c>
+    </row>
+    <row r="49" spans="1:29">
+      <c r="A49" t="s">
+        <v>76</v>
+      </c>
+      <c r="B49" t="s">
+        <v>130</v>
+      </c>
+      <c r="C49" t="s">
+        <v>137</v>
+      </c>
+      <c r="D49" t="s">
+        <v>185</v>
+      </c>
+      <c r="E49" t="s">
+        <v>236</v>
+      </c>
+      <c r="F49" t="s">
+        <v>273</v>
+      </c>
+      <c r="G49" t="s">
+        <v>276</v>
+      </c>
+      <c r="H49" t="s">
+        <v>325</v>
+      </c>
+      <c r="J49" t="s">
+        <v>376</v>
+      </c>
+      <c r="K49" t="s">
+        <v>424</v>
+      </c>
+      <c r="L49" t="s">
+        <v>478</v>
+      </c>
+      <c r="M49" t="s">
+        <v>532</v>
+      </c>
+      <c r="N49" t="s">
+        <v>540</v>
+      </c>
+      <c r="O49" t="s">
+        <v>542</v>
+      </c>
+      <c r="P49" t="s">
+        <v>546</v>
+      </c>
+      <c r="Q49" t="s">
+        <v>554</v>
+      </c>
+      <c r="R49" t="s">
+        <v>605</v>
+      </c>
+      <c r="S49" t="s">
+        <v>624</v>
+      </c>
+      <c r="U49" t="s">
+        <v>672</v>
+      </c>
+      <c r="W49" t="s">
+        <v>2</v>
+      </c>
+      <c r="X49" t="s">
+        <v>720</v>
+      </c>
+      <c r="AA49" t="s">
+        <v>554</v>
+      </c>
+      <c r="AB49" t="s">
+        <v>730</v>
+      </c>
+      <c r="AC49" t="s">
+        <v>736</v>
+      </c>
+    </row>
+    <row r="50" spans="1:29">
+      <c r="A50" t="s">
+        <v>77</v>
+      </c>
+      <c r="B50" t="s">
+        <v>131</v>
+      </c>
+      <c r="C50" t="s">
+        <v>137</v>
+      </c>
+      <c r="D50" t="s">
+        <v>186</v>
+      </c>
+      <c r="E50" t="s">
+        <v>236</v>
+      </c>
+      <c r="F50" t="s">
+        <v>195</v>
+      </c>
+      <c r="G50" t="s">
+        <v>276</v>
+      </c>
+      <c r="H50" t="s">
+        <v>326</v>
+      </c>
+      <c r="I50" t="s">
+        <v>369</v>
+      </c>
+      <c r="J50" t="s">
+        <v>375</v>
+      </c>
+      <c r="K50" t="s">
+        <v>425</v>
+      </c>
+      <c r="L50" t="s">
         <v>479</v>
       </c>
-      <c r="AB47" t="s">
-        <v>632</v>
-      </c>
-      <c r="AC47" t="s">
-        <v>638</v>
+      <c r="M50" t="s">
+        <v>533</v>
+      </c>
+      <c r="O50" t="s">
+        <v>541</v>
+      </c>
+      <c r="P50" t="s">
+        <v>544</v>
+      </c>
+      <c r="Q50" t="s">
+        <v>552</v>
+      </c>
+      <c r="R50" t="s">
+        <v>606</v>
+      </c>
+      <c r="S50" t="s">
+        <v>625</v>
+      </c>
+      <c r="T50" t="s">
+        <v>666</v>
+      </c>
+      <c r="U50" t="s">
+        <v>672</v>
+      </c>
+      <c r="V50" t="s">
+        <v>277</v>
+      </c>
+      <c r="W50" t="s">
+        <v>2</v>
+      </c>
+      <c r="X50" t="s">
+        <v>721</v>
+      </c>
+      <c r="AA50" t="s">
+        <v>552</v>
+      </c>
+      <c r="AB50" t="s">
+        <v>730</v>
+      </c>
+      <c r="AC50" t="s">
+        <v>736</v>
+      </c>
+    </row>
+    <row r="51" spans="1:29">
+      <c r="A51" t="s">
+        <v>78</v>
+      </c>
+      <c r="B51" t="s">
+        <v>132</v>
+      </c>
+      <c r="C51" t="s">
+        <v>137</v>
+      </c>
+      <c r="D51" t="s">
+        <v>187</v>
+      </c>
+      <c r="E51" t="s">
+        <v>237</v>
+      </c>
+      <c r="F51" t="s">
+        <v>274</v>
+      </c>
+      <c r="G51" t="s">
+        <v>277</v>
+      </c>
+      <c r="H51" t="s">
+        <v>327</v>
+      </c>
+      <c r="I51" t="s">
+        <v>370</v>
+      </c>
+      <c r="J51" t="s">
+        <v>375</v>
+      </c>
+      <c r="K51" t="s">
+        <v>426</v>
+      </c>
+      <c r="L51" t="s">
+        <v>480</v>
+      </c>
+      <c r="M51" t="s">
+        <v>534</v>
+      </c>
+      <c r="N51" t="s">
+        <v>539</v>
+      </c>
+      <c r="O51" t="s">
+        <v>541</v>
+      </c>
+      <c r="P51" t="s">
+        <v>544</v>
+      </c>
+      <c r="Q51" t="s">
+        <v>552</v>
+      </c>
+      <c r="R51" t="s">
+        <v>607</v>
+      </c>
+      <c r="S51" t="s">
+        <v>614</v>
+      </c>
+      <c r="T51" t="s">
+        <v>667</v>
+      </c>
+      <c r="U51" t="s">
+        <v>672</v>
+      </c>
+      <c r="V51" t="s">
+        <v>277</v>
+      </c>
+      <c r="W51" t="s">
+        <v>2</v>
+      </c>
+      <c r="X51" t="s">
+        <v>722</v>
+      </c>
+      <c r="AA51" t="s">
+        <v>552</v>
+      </c>
+      <c r="AB51" t="s">
+        <v>731</v>
+      </c>
+      <c r="AC51" t="s">
+        <v>737</v>
+      </c>
+    </row>
+    <row r="52" spans="1:29">
+      <c r="A52" t="s">
+        <v>79</v>
+      </c>
+      <c r="B52" t="s">
+        <v>133</v>
+      </c>
+      <c r="C52" t="s">
+        <v>137</v>
+      </c>
+      <c r="D52" t="s">
+        <v>188</v>
+      </c>
+      <c r="E52" t="s">
+        <v>238</v>
+      </c>
+      <c r="F52" t="s">
+        <v>240</v>
+      </c>
+      <c r="G52" t="s">
+        <v>276</v>
+      </c>
+      <c r="H52" t="s">
+        <v>328</v>
+      </c>
+      <c r="I52" t="s">
+        <v>371</v>
+      </c>
+      <c r="J52" t="s">
+        <v>375</v>
+      </c>
+      <c r="K52" t="s">
+        <v>427</v>
+      </c>
+      <c r="L52" t="s">
+        <v>481</v>
+      </c>
+      <c r="M52" t="s">
+        <v>535</v>
+      </c>
+      <c r="N52" t="s">
+        <v>540</v>
+      </c>
+      <c r="O52" t="s">
+        <v>543</v>
+      </c>
+      <c r="P52" t="s">
+        <v>550</v>
+      </c>
+      <c r="Q52" t="s">
+        <v>556</v>
+      </c>
+      <c r="R52" t="s">
+        <v>608</v>
+      </c>
+      <c r="S52" t="s">
+        <v>614</v>
+      </c>
+      <c r="T52" t="s">
+        <v>668</v>
+      </c>
+      <c r="U52" t="s">
+        <v>672</v>
+      </c>
+      <c r="V52" t="s">
+        <v>277</v>
+      </c>
+      <c r="W52" t="s">
+        <v>2</v>
+      </c>
+      <c r="X52" t="s">
+        <v>723</v>
+      </c>
+      <c r="AA52" t="s">
+        <v>556</v>
+      </c>
+      <c r="AB52" t="s">
+        <v>731</v>
+      </c>
+      <c r="AC52" t="s">
+        <v>737</v>
+      </c>
+    </row>
+    <row r="53" spans="1:29">
+      <c r="A53" t="s">
+        <v>80</v>
+      </c>
+      <c r="B53" t="s">
+        <v>134</v>
+      </c>
+      <c r="C53" t="s">
+        <v>137</v>
+      </c>
+      <c r="D53" t="s">
+        <v>189</v>
+      </c>
+      <c r="E53" t="s">
+        <v>239</v>
+      </c>
+      <c r="F53" t="s">
+        <v>228</v>
+      </c>
+      <c r="G53" t="s">
+        <v>276</v>
+      </c>
+      <c r="H53" t="s">
+        <v>329</v>
+      </c>
+      <c r="I53" t="s">
+        <v>372</v>
+      </c>
+      <c r="J53" t="s">
+        <v>375</v>
+      </c>
+      <c r="K53" t="s">
+        <v>428</v>
+      </c>
+      <c r="L53" t="s">
+        <v>482</v>
+      </c>
+      <c r="M53" t="s">
+        <v>536</v>
+      </c>
+      <c r="O53" t="s">
+        <v>541</v>
+      </c>
+      <c r="P53" t="s">
+        <v>544</v>
+      </c>
+      <c r="Q53" t="s">
+        <v>552</v>
+      </c>
+      <c r="R53" t="s">
+        <v>609</v>
+      </c>
+      <c r="S53" t="s">
+        <v>625</v>
+      </c>
+      <c r="T53" t="s">
+        <v>669</v>
+      </c>
+      <c r="U53" t="s">
+        <v>672</v>
+      </c>
+      <c r="V53" t="s">
+        <v>277</v>
+      </c>
+      <c r="W53" t="s">
+        <v>2</v>
+      </c>
+      <c r="X53" t="s">
+        <v>724</v>
+      </c>
+      <c r="AA53" t="s">
+        <v>552</v>
+      </c>
+      <c r="AB53" t="s">
+        <v>730</v>
+      </c>
+      <c r="AC53" t="s">
+        <v>736</v>
+      </c>
+    </row>
+    <row r="54" spans="1:29">
+      <c r="A54" t="s">
+        <v>81</v>
+      </c>
+      <c r="B54" t="s">
+        <v>135</v>
+      </c>
+      <c r="C54" t="s">
+        <v>137</v>
+      </c>
+      <c r="D54" t="s">
+        <v>190</v>
+      </c>
+      <c r="E54" t="s">
+        <v>236</v>
+      </c>
+      <c r="F54" t="s">
+        <v>217</v>
+      </c>
+      <c r="G54" t="s">
+        <v>276</v>
+      </c>
+      <c r="H54" t="s">
+        <v>330</v>
+      </c>
+      <c r="I54" t="s">
+        <v>373</v>
+      </c>
+      <c r="J54" t="s">
+        <v>375</v>
+      </c>
+      <c r="K54" t="s">
+        <v>429</v>
+      </c>
+      <c r="L54" t="s">
+        <v>483</v>
+      </c>
+      <c r="M54" t="s">
+        <v>537</v>
+      </c>
+      <c r="N54" t="s">
+        <v>539</v>
+      </c>
+      <c r="O54" t="s">
+        <v>541</v>
+      </c>
+      <c r="P54" t="s">
+        <v>544</v>
+      </c>
+      <c r="Q54" t="s">
+        <v>552</v>
+      </c>
+      <c r="R54" t="s">
+        <v>610</v>
+      </c>
+      <c r="S54" t="s">
+        <v>624</v>
+      </c>
+      <c r="T54" t="s">
+        <v>670</v>
+      </c>
+      <c r="U54" t="s">
+        <v>672</v>
+      </c>
+      <c r="V54" t="s">
+        <v>277</v>
+      </c>
+      <c r="W54" t="s">
+        <v>2</v>
+      </c>
+      <c r="X54" t="s">
+        <v>725</v>
+      </c>
+      <c r="AA54" t="s">
+        <v>552</v>
+      </c>
+      <c r="AB54" t="s">
+        <v>734</v>
+      </c>
+      <c r="AC54" t="s">
+        <v>736</v>
+      </c>
+    </row>
+    <row r="55" spans="1:29">
+      <c r="A55" t="s">
+        <v>82</v>
+      </c>
+      <c r="B55" t="s">
+        <v>136</v>
+      </c>
+      <c r="C55" t="s">
+        <v>137</v>
+      </c>
+      <c r="D55" t="s">
+        <v>191</v>
+      </c>
+      <c r="E55" t="s">
+        <v>240</v>
+      </c>
+      <c r="F55" t="s">
+        <v>275</v>
+      </c>
+      <c r="G55" t="s">
+        <v>276</v>
+      </c>
+      <c r="H55" t="s">
+        <v>331</v>
+      </c>
+      <c r="I55" t="s">
+        <v>374</v>
+      </c>
+      <c r="J55" t="s">
+        <v>375</v>
+      </c>
+      <c r="K55" t="s">
+        <v>430</v>
+      </c>
+      <c r="L55" t="s">
+        <v>484</v>
+      </c>
+      <c r="M55" t="s">
+        <v>538</v>
+      </c>
+      <c r="O55" t="s">
+        <v>541</v>
+      </c>
+      <c r="P55" t="s">
+        <v>544</v>
+      </c>
+      <c r="Q55" t="s">
+        <v>552</v>
+      </c>
+      <c r="R55" t="s">
+        <v>611</v>
+      </c>
+      <c r="S55" t="s">
+        <v>617</v>
+      </c>
+      <c r="T55" t="s">
+        <v>671</v>
+      </c>
+      <c r="U55" t="s">
+        <v>672</v>
+      </c>
+      <c r="V55" t="s">
+        <v>672</v>
+      </c>
+      <c r="W55" t="s">
+        <v>2</v>
+      </c>
+      <c r="X55" t="s">
+        <v>726</v>
+      </c>
+      <c r="AA55" t="s">
+        <v>552</v>
+      </c>
+      <c r="AB55" t="s">
+        <v>732</v>
+      </c>
+      <c r="AC55" t="s">
+        <v>736</v>
       </c>
     </row>
   </sheetData>

--- a/data/rutinas/sucursales/Socios_con_y_sin_rutina__SAN LUIS.xlsx
+++ b/data/rutinas/sucursales/Socios_con_y_sin_rutina__SAN LUIS.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC58"/>
+  <dimension ref="A1:AC65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -848,24 +848,24 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Juan Eduardo Torres Alcantar</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>325230</t>
+          <t>317137</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>22169</t>
+          <t>14634</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -875,17 +875,17 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">GLORIA </t>
+          <t>JOSE IGNACIO</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>SANTOS</t>
+          <t>PARRA</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>PEREZ</t>
+          <t>JAQUEZ</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -895,39 +895,35 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>6531642345</t>
+          <t>6531038638</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>AV NUEVO LEON N9 Y 10</t>
+          <t>CALZADA AVIACION 104</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>09-08-1984</t>
+          <t>13-12-1975</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>PRICESASANTOS8409@GMAIL.COM</t>
+          <t>JOSEIGNACIOJOAN@GMAIL.COM</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>25-11-2025 12:03:46</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>inscripcion promo 199</t>
-        </is>
-      </c>
+          <t>03-10-2025 19:18:42</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr">
         <is>
           <t>Forzoso</t>
@@ -945,17 +941,17 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>18-02-2026 18:24:56</t>
+          <t>13-02-2026 18:41:08</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>18-03-2026 23:59:59</t>
+          <t>13-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>18-02-2026 18:24:16</t>
+          <t>13-02-2026 18:39:22</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -975,7 +971,7 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>26150522472400001881</t>
+          <t>26150522328580001685</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
@@ -995,24 +991,24 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Juan Pablo Romero Andrade</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>317137</t>
+          <t>34113</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>14634</t>
+          <t>32029</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1022,17 +1018,17 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>JOSE IGNACIO</t>
+          <t>YOVANY</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>PARRA</t>
+          <t>VALENZUELA</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>JAQUEZ</t>
+          <t xml:space="preserve">ALVARADO </t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -1042,12 +1038,12 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>6531038638</t>
+          <t>6531453465</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>CALZADA AVIACION 104</t>
+          <t>LEY DE ALFABETIZACION 9 Y 10</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1057,17 +1053,17 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>13-12-1975</t>
+          <t>30-12-1997</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>JOSEIGNACIOJOAN@GMAIL.COM</t>
+          <t>YOVANYALVRADO@GMAIL.COM</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>03-10-2025 19:18:42</t>
+          <t>29-06-2021 18:23:17</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -1088,17 +1084,17 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>13-02-2026 18:41:08</t>
+          <t>12-02-2026 05:24:56</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>13-03-2026 23:59:59</t>
+          <t>12-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>13-02-2026 18:39:22</t>
+          <t>12-02-2026 05:23:53</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -1118,19 +1114,11 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>26150522328580001685</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>GISSEL ANAHY REYES GERMAN</t>
-        </is>
-      </c>
+          <t>26150522281110001621</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr"/>
+      <c r="Z5" t="inlineStr"/>
       <c r="AA5" t="inlineStr">
         <is>
           <t>499</t>
@@ -1138,7 +1126,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>Juan Pablo Romero Andrade</t>
+          <t>Juan Eduardo Torres Alcantar</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -1150,12 +1138,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>330218</t>
+          <t>109430</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>15272</t>
+          <t>7171</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1165,17 +1153,17 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">SILVIA </t>
+          <t>GISELL</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>ZAVALA</t>
+          <t>BARO</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>PACHECO</t>
+          <t>SOTO</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -1185,12 +1173,12 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>6531211789</t>
+          <t>6531135478</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>AV COAHUILA B Y C PESQUEIRA</t>
+          <t>SAN LUIS</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1200,60 +1188,56 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>15-02-1984</t>
+          <t>25-01-1999</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>AALER22398@GMAIL.COM</t>
+          <t>GISELBARO@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>24-12-2025 07:23:05</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr"/>
+          <t>19-07-2022 07:14:06</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>PLAN FAMILIA / AMIGOS X $499</t>
+          <t>1 MES $899</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>899</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>10-02-2026 05:56:10</t>
+          <t>17-02-2026 09:24:03</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>10-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t>10-02-2026 05:55:08</t>
-        </is>
-      </c>
+          <t>17-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr"/>
       <c r="U6" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="V6" t="inlineStr"/>
       <c r="W6" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -1261,44 +1245,36 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>26150522222600001523</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>RAUL FELIX VAZQUEZ</t>
-        </is>
-      </c>
+          <t>26150522422860001804</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr"/>
+      <c r="Z6" t="inlineStr"/>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>899</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Martin Ramiro Quiñonez Jauregui</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>339758</t>
+          <t>330218</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>17576</t>
+          <t>15272</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1308,17 +1284,17 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>ISABELLA</t>
+          <t xml:space="preserve">SILVIA </t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>ALARCON</t>
+          <t>ZAVALA</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>ACEVES</t>
+          <t>PACHECO</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -1328,10 +1304,14 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>6535382487</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>6531211789</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>AV COAHUILA B Y C PESQUEIRA</t>
+        </is>
+      </c>
       <c r="J7" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -1339,56 +1319,60 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>04-06-2010</t>
+          <t>15-02-1984</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>ALARCONISABELLA347@GMAIL.COM</t>
+          <t>AALER22398@GMAIL.COM</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>01-02-2026 10:00:33</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>Tarifas 2026 LE</t>
-        </is>
-      </c>
+          <t>24-12-2025 07:23:05</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>PLAN FAMILIA / AMIGOS X $499</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>01-02-2026 10:05:34</t>
+          <t>10-02-2026 05:56:10</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>01-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T7" t="inlineStr"/>
+          <t>10-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>10-02-2026 05:55:08</t>
+        </is>
+      </c>
       <c r="U7" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V7" t="inlineStr"/>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W7" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -1396,19 +1380,27 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>26150521988630001200</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr"/>
-      <c r="Z7" t="inlineStr"/>
+          <t>26150522222600001523</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>RAUL FELIX VAZQUEZ</t>
+        </is>
+      </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>Juan Pablo Romero Andrade</t>
+          <t>Juan Eduardo Torres Alcantar</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
@@ -1420,12 +1412,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>339777</t>
+          <t>339758</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>17595</t>
+          <t>17576</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1435,17 +1427,17 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>GISSEL LILIAN</t>
+          <t>ISABELLA</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>RODRIGUEZ</t>
+          <t>ALARCON</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>SILVA</t>
+          <t>ACEVES</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -1455,14 +1447,10 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>6531466820</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>MERIDA 1</t>
-        </is>
-      </c>
+          <t>6535382487</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -1470,17 +1458,17 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>02-09-1998</t>
+          <t>04-06-2010</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>GISSELSILVIA98@GMAIL.COM</t>
+          <t>ALARCONISABELLA347@GMAIL.COM</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>01-02-2026 10:50:32</t>
+          <t>01-02-2026 10:00:33</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1490,22 +1478,22 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>No Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>RECURRENTE $649 LE</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>01-02-2026 10:53:31</t>
+          <t>01-02-2026 10:05:34</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
@@ -1513,21 +1501,13 @@
           <t>01-03-2026 23:59:59</t>
         </is>
       </c>
-      <c r="T8" t="inlineStr">
-        <is>
-          <t>01-02-2026 10:52:55</t>
-        </is>
-      </c>
+      <c r="T8" t="inlineStr"/>
       <c r="U8" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="V8" t="inlineStr"/>
       <c r="W8" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -1535,14 +1515,14 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>26150521989600001201</t>
+          <t>26150521988630001200</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr"/>
       <c r="Z8" t="inlineStr"/>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -1559,12 +1539,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>34113</t>
+          <t>339777</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>32029</t>
+          <t>17595</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1574,17 +1554,17 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>YOVANY</t>
+          <t>GISSEL LILIAN</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>VALENZUELA</t>
+          <t>RODRIGUEZ</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t xml:space="preserve">ALVARADO </t>
+          <t>SILVA</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -1594,63 +1574,67 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>6531453465</t>
+          <t>6531466820</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>LEY DE ALFABETIZACION 9 Y 10</t>
+          <t>MERIDA 1</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>30-12-1997</t>
+          <t>02-09-1998</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>YOVANYALVRADO@GMAIL.COM</t>
+          <t>GISSELSILVIA98@GMAIL.COM</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>29-06-2021 18:23:17</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr"/>
+          <t>01-02-2026 10:50:32</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>No Forzoso</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>RECURRENTE $649 LE</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>649</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>12-02-2026 05:24:56</t>
+          <t>01-02-2026 10:53:31</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>12-03-2026 23:59:59</t>
+          <t>01-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>12-02-2026 05:23:53</t>
+          <t>01-02-2026 10:52:55</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
@@ -1670,36 +1654,36 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>26150522281110001621</t>
+          <t>26150521989600001201</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr"/>
       <c r="Z9" t="inlineStr"/>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>649</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Juan Pablo Romero Andrade</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>109430</t>
+          <t>277709</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>7171</t>
+          <t>75210</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1709,17 +1693,17 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>GISELL</t>
+          <t>ANGEL ALBERTO</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>BARO</t>
+          <t>ACOSTA</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>SOTO</t>
+          <t>RIVAS</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -1729,71 +1713,75 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>6531135478</t>
+          <t>6424832255</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>SAN LUIS</t>
+          <t>CJON 5 DE MAYO 12 Y 13</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>25-01-1999</t>
+          <t>06-03-1998</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>GISELBARO@HOTMAIL.COM</t>
+          <t>ACOSTARIVS@GMAIL.COM</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>19-07-2022 07:14:06</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>Tarifas 2026 LE</t>
-        </is>
-      </c>
+          <t>06-02-2025 18:37:15</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>1 MES $899</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>17-02-2026 09:24:03</t>
+          <t>13-02-2026 05:21:27</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>17-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T10" t="inlineStr"/>
+          <t>14-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>13-02-2026 05:19:56</t>
+        </is>
+      </c>
       <c r="U10" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V10" t="inlineStr"/>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="W10" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -1801,19 +1789,27 @@
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>26150522422860001804</t>
-        </is>
-      </c>
-      <c r="Y10" t="inlineStr"/>
-      <c r="Z10" t="inlineStr"/>
+          <t>26150522308700001658</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>RAUL FELIX VAZQUEZ</t>
+        </is>
+      </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>Martin Ramiro Quiñonez Jauregui</t>
+          <t>Juan Eduardo Torres Alcantar</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
@@ -1825,12 +1821,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>340340</t>
+          <t>340298</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>18158</t>
+          <t>18116</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1840,17 +1836,17 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>FATIMA</t>
+          <t xml:space="preserve">DARIO </t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>SANCHEZ</t>
+          <t>GARCIA</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>MEDINA</t>
+          <t>GARCIA</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -1860,14 +1856,10 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>6531333103</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>AV TORREON 39</t>
-        </is>
-      </c>
+          <t>6531617077</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -1875,17 +1867,17 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>27-08-2003</t>
+          <t>14-03-1986</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>FATIMASM2708@GMAIL.COM</t>
+          <t>DARIOGS1486@ICLOUD.COM</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>02-02-2026 18:15:23</t>
+          <t>02-02-2026 17:03:53</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1895,12 +1887,12 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES $549 LE</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
@@ -1910,7 +1902,7 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>02-02-2026 18:20:31</t>
+          <t>02-02-2026 17:04:52</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
@@ -1918,21 +1910,13 @@
           <t>02-03-2026 23:59:59</t>
         </is>
       </c>
-      <c r="T11" t="inlineStr">
-        <is>
-          <t>02-02-2026 18:19:16</t>
-        </is>
-      </c>
+      <c r="T11" t="inlineStr"/>
       <c r="U11" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V11" t="inlineStr">
-        <is>
           <t>1</t>
         </is>
       </c>
+      <c r="V11" t="inlineStr"/>
       <c r="W11" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -1940,7 +1924,7 @@
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>26150522020390001251</t>
+          <t>26150522017940001237</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr"/>
@@ -1964,12 +1948,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>277709</t>
+          <t>339746</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>75210</t>
+          <t>17564</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1979,17 +1963,17 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>ANGEL ALBERTO</t>
+          <t xml:space="preserve">GRISEL </t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>ACOSTA</t>
+          <t>CUADRAS</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>RIVAS</t>
+          <t>CUADRAS</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -1999,63 +1983,67 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>6424832255</t>
+          <t>6531315370</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>CJON 5 DE MAYO 12 Y 13</t>
+          <t>MEXICO B Y 28</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>06-03-1998</t>
+          <t>17-02-1980</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>ACOSTARIVS@GMAIL.COM</t>
+          <t>CHACLAUDIA5@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>06-02-2025 18:37:15</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr"/>
+          <t>01-02-2026 09:25:23</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>No Forzoso</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>RECURRENTE $649 LE</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>649</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>13-02-2026 05:21:27</t>
+          <t>03-02-2026 05:30:52</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>14-03-2026 23:59:59</t>
+          <t>03-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>13-02-2026 05:19:56</t>
+          <t>03-02-2026 05:30:25</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
@@ -2065,7 +2053,7 @@
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W12" t="inlineStr">
@@ -2075,7 +2063,7 @@
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>26150522308700001658</t>
+          <t>26150522029990001268</t>
         </is>
       </c>
       <c r="Y12" t="inlineStr">
@@ -2085,34 +2073,34 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>RAUL FELIX VAZQUEZ</t>
+          <t>GISSEL ANAHY REYES GERMAN</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>649</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Martin Ramiro Quiñonez Jauregui</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>340298</t>
+          <t>340340</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>18116</t>
+          <t>18158</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -2122,17 +2110,17 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t xml:space="preserve">DARIO </t>
+          <t>FATIMA</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>GARCIA</t>
+          <t>SANCHEZ</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>GARCIA</t>
+          <t>MEDINA</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -2142,10 +2130,14 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>6531617077</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>6531333103</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>AV TORREON 39</t>
+        </is>
+      </c>
       <c r="J13" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -2153,17 +2145,17 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>14-03-1986</t>
+          <t>27-08-2003</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>DARIOGS1486@ICLOUD.COM</t>
+          <t>FATIMASM2708@GMAIL.COM</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>02-02-2026 17:03:53</t>
+          <t>02-02-2026 18:15:23</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
@@ -2173,12 +2165,12 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>DOMICILIADO 12 MESES $549 LE</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
@@ -2188,7 +2180,7 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>02-02-2026 17:04:52</t>
+          <t>02-02-2026 18:20:31</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
@@ -2196,13 +2188,21 @@
           <t>02-03-2026 23:59:59</t>
         </is>
       </c>
-      <c r="T13" t="inlineStr"/>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>02-02-2026 18:19:16</t>
+        </is>
+      </c>
       <c r="U13" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="V13" t="inlineStr"/>
       <c r="W13" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -2210,7 +2210,7 @@
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>26150522017940001237</t>
+          <t>26150522020390001251</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr"/>
@@ -2234,12 +2234,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>339746</t>
+          <t>336709</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>17564</t>
+          <t>22435</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -2249,17 +2249,17 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t xml:space="preserve">GRISEL </t>
+          <t>MARIA FERNANDA</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>CUADRAS</t>
+          <t>LAZALDE</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>CUADRAS</t>
+          <t>ANDRADE</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -2269,12 +2269,12 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>6531315370</t>
+          <t>6645697047</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>MEXICO B Y 28</t>
+          <t>C ADOLFO LOPEZ MATEOS 6413 C</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -2284,52 +2284,48 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>17-02-1980</t>
+          <t>21-01-2000</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>CHACLAUDIA5@HOTMAIL.COM</t>
+          <t>FERGIE.LAZALDE@GMAIL.COM</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>01-02-2026 09:25:23</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>Tarifas 2026 LE</t>
-        </is>
-      </c>
+          <t>21-01-2026 11:47:08</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
       <c r="O14" t="inlineStr">
         <is>
-          <t>No Forzoso</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>RECURRENTE $649 LE</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>03-02-2026 05:30:52</t>
+          <t>11-02-2026 08:22:24</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>03-03-2026 23:59:59</t>
+          <t>11-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>03-02-2026 05:30:25</t>
+          <t>11-02-2026 08:21:44</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
@@ -2339,7 +2335,7 @@
       </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W14" t="inlineStr">
@@ -2349,7 +2345,7 @@
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>26150522029990001268</t>
+          <t>26070522259520003153</t>
         </is>
       </c>
       <c r="Y14" t="inlineStr">
@@ -2357,19 +2353,15 @@
           <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>GISSEL ANAHY REYES GERMAN</t>
-        </is>
-      </c>
+      <c r="Z14" t="inlineStr"/>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>Martin Ramiro Quiñonez Jauregui</t>
+          <t>Jesus Alejandro  Partida Partida</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
@@ -2381,12 +2373,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>340805</t>
+          <t>340602</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>18623</t>
+          <t>18420</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -2396,34 +2388,30 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>RICARDO</t>
+          <t>DANTE EMILIANO</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>TAPIA</t>
+          <t>GARCIA</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>OLIVO</t>
+          <t>GOMEZ</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>6531341539</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>AV GUERRERO 12</t>
-        </is>
-      </c>
+          <t>9228390416</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr">
         <is>
           <t>Masculino</t>
@@ -2431,17 +2419,17 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>01-04-2000</t>
+          <t>06-12-2010</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>RICARDITOTAPIA2129@GMAIL.COM</t>
+          <t>DANTE.GARCIA@INSTITUTOKINO.EDU.MX</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>03-02-2026 19:10:40</t>
+          <t>03-02-2026 14:43:23</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
@@ -2451,12 +2439,12 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES $549 LE</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
@@ -2466,7 +2454,7 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>03-02-2026 19:13:30</t>
+          <t>03-02-2026 14:44:52</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
@@ -2474,21 +2462,13 @@
           <t>03-03-2026 23:59:59</t>
         </is>
       </c>
-      <c r="T15" t="inlineStr">
-        <is>
-          <t>03-02-2026 19:12:47</t>
-        </is>
-      </c>
+      <c r="T15" t="inlineStr"/>
       <c r="U15" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V15" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="V15" t="inlineStr"/>
       <c r="W15" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -2496,7 +2476,7 @@
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>26150522055450001315</t>
+          <t>26150522041730001279</t>
         </is>
       </c>
       <c r="Y15" t="inlineStr"/>
@@ -2508,7 +2488,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>Martin Ramiro Quiñonez Jauregui</t>
+          <t>Juan Pablo Romero Andrade</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
@@ -2520,12 +2500,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>336709</t>
+          <t>340730</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>22435</t>
+          <t>18548</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -2535,17 +2515,17 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>MARIA FERNANDA</t>
+          <t>GUADALUPE SHEREZADA</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>LAZALDE</t>
+          <t>RAMIREZ</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>ANDRADE</t>
+          <t>CORTEZ</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -2555,14 +2535,10 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>6645697047</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>C ADOLFO LOPEZ MATEOS 6413 C</t>
-        </is>
-      </c>
+          <t>6531304693</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -2570,60 +2546,56 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>21-01-2000</t>
+          <t>02-07-2000</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>FERGIE.LAZALDE@GMAIL.COM</t>
+          <t>BELLOBAINES.1982@GMAIL.COM</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>21-01-2026 11:47:08</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr"/>
+          <t>03-02-2026 17:27:01</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>11-02-2026 08:22:24</t>
+          <t>03-02-2026 17:32:11</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>11-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T16" t="inlineStr">
-        <is>
-          <t>11-02-2026 08:21:44</t>
-        </is>
-      </c>
+          <t>03-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr"/>
       <c r="U16" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V16" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="V16" t="inlineStr"/>
       <c r="W16" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -2631,23 +2603,19 @@
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>26070522259520003153</t>
-        </is>
-      </c>
-      <c r="Y16" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
+          <t>26150522049660001299</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr"/>
       <c r="Z16" t="inlineStr"/>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>Jesus Alejandro  Partida Partida</t>
+          <t>Juan Pablo Romero Andrade</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
@@ -2659,12 +2627,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>341196</t>
+          <t>297488</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>19014</t>
+          <t>94986</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -2674,17 +2642,17 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>ESMERALDA</t>
+          <t xml:space="preserve">BRENDA </t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>JAVALERA</t>
+          <t>ROMAN</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>ALCANTAR</t>
+          <t>IBARRA</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -2694,12 +2662,12 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>6531196345</t>
+          <t>6531125544</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>AV TABASCO 41</t>
+          <t>EMILIANO ZAPATA C Y COLOMBIA</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -2709,20 +2677,24 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>19-03-1975</t>
+          <t>04-02-1984</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>ESMERALDA.JAVALERA@HOTMAIL.COM</t>
+          <t>OKCHIQUITA4@GMAIL.COM</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>04-02-2026 21:09:01</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr"/>
+          <t>09-06-2025 20:08:16</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>inscripcion promo 199</t>
+        </is>
+      </c>
       <c r="O17" t="inlineStr">
         <is>
           <t>Forzoso</t>
@@ -2740,17 +2712,17 @@
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>11-02-2026 15:06:43</t>
+          <t>19-02-2026 17:34:15</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>11-03-2026 23:59:59</t>
+          <t>19-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>11-02-2026 15:05:40</t>
+          <t>19-02-2026 17:33:15</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
@@ -2770,7 +2742,7 @@
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>26150522265920001586</t>
+          <t>26150522501710001922</t>
         </is>
       </c>
       <c r="Y17" t="inlineStr">
@@ -2778,11 +2750,7 @@
           <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>GISSEL ANAHY REYES GERMAN</t>
-        </is>
-      </c>
+      <c r="Z17" t="inlineStr"/>
       <c r="AA17" t="inlineStr">
         <is>
           <t>499</t>
@@ -2790,24 +2758,24 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>Juan Eduardo Torres Alcantar</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>341271</t>
+          <t>341197</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>19089</t>
+          <t>19015</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -2817,17 +2785,17 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NICOLLE</t>
+          <t>CARMEN</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>BUSTAMANTE</t>
+          <t>ALICIA</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>ELIZONDO</t>
+          <t>GIL</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -2837,12 +2805,12 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>6381121777</t>
+          <t>6642049795</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>LOS ADOBES</t>
+          <t>AV BENITO JUAREZ 24 Y 25</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -2852,17 +2820,17 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>15-12-1997</t>
+          <t>15-09-1947</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>NICOLLE.BUSTAMANTE@UABC.EDU.MX</t>
+          <t>CARMEN1947@GMAIL.COM</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>05-02-2026 10:43:03</t>
+          <t>04-02-2026 21:10:39</t>
         </is>
       </c>
       <c r="N18" t="inlineStr"/>
@@ -2883,7 +2851,7 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>11-02-2026 13:33:23</t>
+          <t>11-02-2026 15:03:22</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
@@ -2893,7 +2861,7 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>11-02-2026 13:31:59</t>
+          <t>11-02-2026 15:02:18</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
@@ -2903,7 +2871,7 @@
       </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W18" t="inlineStr">
@@ -2913,7 +2881,7 @@
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>26150522264110001579</t>
+          <t>26150522265830001585</t>
         </is>
       </c>
       <c r="Y18" t="inlineStr">
@@ -2923,7 +2891,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>RAUL FELIX VAZQUEZ</t>
+          <t>GISSEL ANAHY REYES GERMAN</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2933,7 +2901,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>Juan Pablo Romero Andrade</t>
+          <t>Juan Eduardo Torres Alcantar</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
@@ -2945,12 +2913,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>340152</t>
+          <t>325230</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>17970</t>
+          <t>22169</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -2960,17 +2928,17 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>MARTHA LIDIA</t>
+          <t xml:space="preserve">GLORIA </t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t xml:space="preserve">DURAN </t>
+          <t>SANTOS</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>CUEN</t>
+          <t>PEREZ</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -2980,35 +2948,39 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>6531218668</t>
+          <t>6531642345</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>PRIVADO ROFORMA</t>
+          <t>AV NUEVO LEON N9 Y 10</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>06-08-1960</t>
+          <t>09-08-1984</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>ROMERO.MARTHA50@ICLOUD.COM</t>
+          <t>PRICESASANTOS8409@GMAIL.COM</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>02-02-2026 13:57:36</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr"/>
+          <t>25-11-2025 12:03:46</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>inscripcion promo 199</t>
+        </is>
+      </c>
       <c r="O19" t="inlineStr">
         <is>
           <t>Forzoso</t>
@@ -3026,17 +2998,17 @@
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>02-02-2026 14:04:27</t>
+          <t>18-02-2026 18:24:56</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>02-03-2026 23:59:59</t>
+          <t>18-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>02-02-2026 14:03:30</t>
+          <t>18-02-2026 18:24:16</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
@@ -3046,7 +3018,7 @@
       </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W19" t="inlineStr">
@@ -3056,11 +3028,19 @@
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>26150522011860001229</t>
-        </is>
-      </c>
-      <c r="Y19" t="inlineStr"/>
-      <c r="Z19" t="inlineStr"/>
+          <t>26150522472400001881</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>GISSEL ANAHY REYES GERMAN</t>
+        </is>
+      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>499</t>
@@ -3080,12 +3060,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>341197</t>
+          <t>341991</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>19015</t>
+          <t>19809</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -3095,17 +3075,17 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>CARMEN</t>
+          <t>VICTOR HUGO</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>ALICIA</t>
+          <t>SALAS</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>GIL</t>
+          <t>RODRIGUEZ</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -3115,35 +3095,39 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>6642049795</t>
+          <t>6531130495</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>AV BENITO JUAREZ 24 Y 25</t>
+          <t>SAN MARCOS</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>15-09-1947</t>
+          <t>30-08-2001</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>CARMEN1947@GMAIL.COM</t>
+          <t>SALASRODRIGUEZVICTORHUGO@GMAIL.COM</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>04-02-2026 21:10:39</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr"/>
+          <t>09-02-2026 05:08:33</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>inscripcion promo 199</t>
+        </is>
+      </c>
       <c r="O20" t="inlineStr">
         <is>
           <t>Forzoso</t>
@@ -3161,17 +3145,17 @@
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>11-02-2026 15:03:22</t>
+          <t>17-02-2026 16:21:53</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>11-03-2026 23:59:59</t>
+          <t>17-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>11-02-2026 15:02:18</t>
+          <t>17-02-2026 16:21:11</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
@@ -3191,7 +3175,7 @@
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>26150522265830001585</t>
+          <t>26150522433690001818</t>
         </is>
       </c>
       <c r="Y20" t="inlineStr">
@@ -3201,7 +3185,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>GISSEL ANAHY REYES GERMAN</t>
+          <t>RAUL FELIX VAZQUEZ</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -3211,24 +3195,24 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>Juan Eduardo Torres Alcantar</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>340602</t>
+          <t>340152</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>18420</t>
+          <t>17970</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -3238,30 +3222,34 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>DANTE EMILIANO</t>
+          <t>MARTHA LIDIA</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>GARCIA</t>
+          <t xml:space="preserve">DURAN </t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>GOMEZ</t>
+          <t>CUEN</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>52</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>9228390416</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>6531218668</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>PRIVADO ROFORMA</t>
+        </is>
+      </c>
       <c r="J21" t="inlineStr">
         <is>
           <t>Masculino</t>
@@ -3269,56 +3257,60 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>06-12-2010</t>
+          <t>06-08-1960</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>DANTE.GARCIA@INSTITUTOKINO.EDU.MX</t>
+          <t>ROMERO.MARTHA50@ICLOUD.COM</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>03-02-2026 14:43:23</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr">
-        <is>
-          <t>Tarifas 2026 LE</t>
-        </is>
-      </c>
+          <t>02-02-2026 13:57:36</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr"/>
       <c r="O21" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>03-02-2026 14:44:52</t>
+          <t>02-02-2026 14:04:27</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>03-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T21" t="inlineStr"/>
+          <t>02-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>02-02-2026 14:03:30</t>
+        </is>
+      </c>
       <c r="U21" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V21" t="inlineStr"/>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="W21" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -3326,14 +3318,14 @@
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>26150522041730001279</t>
+          <t>26150522011860001229</t>
         </is>
       </c>
       <c r="Y21" t="inlineStr"/>
       <c r="Z21" t="inlineStr"/>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
@@ -3350,12 +3342,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>340730</t>
+          <t>342497</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>18548</t>
+          <t>20314</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -3365,30 +3357,34 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>GUADALUPE SHEREZADA</t>
+          <t>KARLA VERONICA</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>RAMIREZ</t>
+          <t>TORRES</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>CORTEZ</t>
+          <t>CORONA</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>6531304693</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>9285509758</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">COLIMA C 26 </t>
+        </is>
+      </c>
       <c r="J22" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -3396,56 +3392,60 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>02-07-2000</t>
+          <t>19-11-1990</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>BELLOBAINES.1982@GMAIL.COM</t>
+          <t>KARLILLA15@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>03-02-2026 17:27:01</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr">
-        <is>
-          <t>Tarifas 2026 LE</t>
-        </is>
-      </c>
+          <t>09-02-2026 21:11:28</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr"/>
       <c r="O22" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>03-02-2026 17:32:11</t>
+          <t>11-02-2026 20:58:26</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>03-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T22" t="inlineStr"/>
+          <t>11-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>11-02-2026 20:57:45</t>
+        </is>
+      </c>
       <c r="U22" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V22" t="inlineStr"/>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W22" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -3453,14 +3453,22 @@
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>26150522049660001299</t>
-        </is>
-      </c>
-      <c r="Y22" t="inlineStr"/>
-      <c r="Z22" t="inlineStr"/>
+          <t>26150522279010001613</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>GISSEL ANAHY REYES GERMAN</t>
+        </is>
+      </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
@@ -3477,12 +3485,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>340765</t>
+          <t>342516</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>18583</t>
+          <t>20333</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -3492,17 +3500,17 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VIVIANA</t>
+          <t>LUIS</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>ARVAYO</t>
+          <t>RODRIGUEZ</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>RASCON</t>
+          <t>GARCIA</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -3512,67 +3520,63 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>6531300005</t>
+          <t>6531211788</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t xml:space="preserve">AV COLIMA Y MATAMOROS </t>
+          <t>AV COAHUILA B Y C PESQUEIRA</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>03-01-1979</t>
+          <t>12-08-1985</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>VIVIARVAYO@GMAIL.COM</t>
+          <t>COMANCHE87@OUTLOOK.COM</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>03-02-2026 18:01:17</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr">
-        <is>
-          <t>Tarifas 2026 LE</t>
-        </is>
-      </c>
+          <t>10-02-2026 05:40:54</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr"/>
       <c r="O23" t="inlineStr">
         <is>
-          <t>No Forzoso</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>PLAN RECURRENTE PAGO INCIAL $1,449 LE</t>
+          <t>PLAN FAMILIA / AMIGOS X $499</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>1449</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>03-02-2026 18:16:20</t>
+          <t>10-02-2026 05:52:22</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>03-03-2026 23:59:59</t>
+          <t>10-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>03-02-2026 18:05:39</t>
+          <t>10-02-2026 05:49:58</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
@@ -3592,14 +3596,14 @@
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>26150522052430001305</t>
+          <t>26150522222520001522</t>
         </is>
       </c>
       <c r="Y23" t="inlineStr"/>
       <c r="Z23" t="inlineStr"/>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>1449</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
@@ -3616,12 +3620,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>342245</t>
+          <t>339854</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>20063</t>
+          <t>17672</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -3631,17 +3635,17 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>MANUEL ANTONIO</t>
+          <t>DIEGO ARMANDO</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t xml:space="preserve">RUIZ </t>
+          <t>MEDINA</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>SILVA</t>
+          <t>PIEDRA</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -3651,12 +3655,12 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>6863042514</t>
+          <t>6531658872</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>CJN SAN JUAN Y SAN LUIS</t>
+          <t>REVOLUCION Y 40</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -3666,17 +3670,17 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>09-10-1991</t>
+          <t>06-03-1989</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>MANUELANTONIOSILVARUIZ@GMAIL.COM</t>
+          <t>DIEGO.MEDINA@YAHOO.COM</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>09-02-2026 16:10:49</t>
+          <t>02-02-2026 05:44:27</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
@@ -3691,27 +3695,27 @@
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>RECURRENTE $649 LE</t>
+          <t>PLAN FAMILIAR RECURRENTE $999</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>999</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>09-02-2026 16:12:25</t>
+          <t>02-02-2026 05:46:51</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>09-03-2026 23:59:59</t>
+          <t>02-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>09-02-2026 16:11:51</t>
+          <t>02-02-2026 05:45:55</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
@@ -3731,36 +3735,36 @@
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>26150522197240001486</t>
+          <t>26150521997870001209</t>
         </is>
       </c>
       <c r="Y24" t="inlineStr"/>
       <c r="Z24" t="inlineStr"/>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>999</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>Johan Osvaldo Beltran Quiros</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>342261</t>
+          <t>342823</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>20079</t>
+          <t>20640</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -3770,17 +3774,17 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t xml:space="preserve">VICTORIA </t>
+          <t>JESUS ABEL</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t xml:space="preserve">ZAVALA </t>
+          <t>VALERIO</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>BARRIENTOS</t>
+          <t>LIMON</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -3790,39 +3794,35 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>6531231721</t>
+          <t>6531665157</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t xml:space="preserve">HACIENDA DE LA CRUZ </t>
+          <t>CARRETERA DEL VALLE</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>04-04-1996</t>
+          <t>23-07-2004</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>GUADALUPEZAVALAMERCADO@HOTMAIL.COM</t>
+          <t>VALERIOJESUS913@GMAIL.COM</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>09-02-2026 16:34:55</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr">
-        <is>
-          <t>Tarifas 2026 LE</t>
-        </is>
-      </c>
+          <t>10-02-2026 19:05:03</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr"/>
       <c r="O25" t="inlineStr">
         <is>
           <t>Forzoso</t>
@@ -3830,27 +3830,27 @@
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES $549 LE</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>09-02-2026 16:37:21</t>
+          <t>10-02-2026 19:09:25</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>09-03-2026 23:59:59</t>
+          <t>10-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>09-02-2026 16:36:34</t>
+          <t>10-02-2026 19:08:45</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
@@ -3860,7 +3860,7 @@
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W25" t="inlineStr">
@@ -3870,14 +3870,14 @@
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>26150522198880001489</t>
+          <t>26150522245980001553</t>
         </is>
       </c>
       <c r="Y25" t="inlineStr"/>
       <c r="Z25" t="inlineStr"/>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr">
@@ -3894,12 +3894,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>340877</t>
+          <t>340765</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>18695</t>
+          <t>18583</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -3909,17 +3909,17 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>HECTOR ABRAHAM</t>
+          <t>VIVIANA</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>OJEDA</t>
+          <t>ARVAYO</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>FRANCO</t>
+          <t>RASCON</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -3929,32 +3929,32 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>6532437111</t>
+          <t>6531300005</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>DALIAS 18 Y 19</t>
+          <t xml:space="preserve">AV COLIMA Y MATAMOROS </t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>08-01-2005</t>
+          <t>03-01-1979</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>ABRAHAM30510@GMAIL.COM</t>
+          <t>VIVIARVAYO@GMAIL.COM</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>04-02-2026 07:26:12</t>
+          <t>03-02-2026 18:01:17</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
@@ -3964,32 +3964,32 @@
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>No Forzoso</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES $549 LE</t>
+          <t>PLAN RECURRENTE PAGO INCIAL $1,449 LE</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>1449</t>
         </is>
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>04-02-2026 07:29:18</t>
+          <t>03-02-2026 18:16:20</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
         <is>
-          <t>04-03-2026 23:59:59</t>
+          <t>03-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>04-02-2026 07:28:45</t>
+          <t>03-02-2026 18:05:39</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
@@ -4009,36 +4009,36 @@
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>26150522068240001330</t>
+          <t>26150522052430001305</t>
         </is>
       </c>
       <c r="Y26" t="inlineStr"/>
       <c r="Z26" t="inlineStr"/>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>1449</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>Martin Ramiro Quiñonez Jauregui</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>342512</t>
+          <t>340877</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>20329</t>
+          <t>18695</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -4048,17 +4048,17 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>JOSE RICARDO</t>
+          <t>HECTOR ABRAHAM</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>GARCIA</t>
+          <t>OJEDA</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>ANGULO</t>
+          <t>FRANCO</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -4068,12 +4068,12 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>6531217599</t>
+          <t>6532437111</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>CJON HIDALGO Y 47</t>
+          <t>DALIAS 18 Y 19</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -4083,17 +4083,17 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>03-04-1976</t>
+          <t>08-01-2005</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>RRICARDOGARCIA34@ICLOUD.COM</t>
+          <t>ABRAHAM30510@GMAIL.COM</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>10-02-2026 05:34:48</t>
+          <t>04-02-2026 07:26:12</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
@@ -4103,32 +4103,32 @@
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>No Forzoso</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>RECURRENTE $649 LE</t>
+          <t>DOMICILIADO 12 MESES $549 LE</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>11-02-2026 06:33:27</t>
+          <t>04-02-2026 07:29:18</t>
         </is>
       </c>
       <c r="S27" t="inlineStr">
         <is>
-          <t>11-03-2026 23:59:59</t>
+          <t>04-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>11-02-2026 06:32:18</t>
+          <t>04-02-2026 07:28:45</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
@@ -4148,27 +4148,19 @@
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>26150522257790001574</t>
-        </is>
-      </c>
-      <c r="Y27" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>RAUL FELIX VAZQUEZ</t>
-        </is>
-      </c>
+          <t>26150522068240001330</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr"/>
+      <c r="Z27" t="inlineStr"/>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>Juan Eduardo Torres Alcantar</t>
+          <t>Martin Ramiro Quiñonez Jauregui</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
@@ -4180,12 +4172,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>342828</t>
+          <t>342742</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>20645</t>
+          <t>20559</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -4195,17 +4187,17 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NUBIA GUADALUPE</t>
+          <t>KARINA</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>SOLARES</t>
+          <t>QUILES</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>ARVIZU</t>
+          <t>CAMACHO</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -4215,12 +4207,12 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>6531665151</t>
+          <t>6531163674</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>CARRETERA DEL VALLE</t>
+          <t>AV PUEBLA 1RA Y HERMOSILLO</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -4230,17 +4222,17 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>27-09-2002</t>
+          <t>22-02-1975</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>NUBIAG3@ICLOUD.COM</t>
+          <t>KARINAAQUILESC1975@GMAIL.COM</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>10-02-2026 19:11:57</t>
+          <t>10-02-2026 17:14:23</t>
         </is>
       </c>
       <c r="N28" t="inlineStr"/>
@@ -4261,7 +4253,7 @@
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>10-02-2026 19:16:21</t>
+          <t>10-02-2026 17:19:39</t>
         </is>
       </c>
       <c r="S28" t="inlineStr">
@@ -4271,7 +4263,7 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>10-02-2026 19:15:42</t>
+          <t>10-02-2026 17:18:56</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
@@ -4281,7 +4273,7 @@
       </c>
       <c r="V28" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W28" t="inlineStr">
@@ -4291,7 +4283,7 @@
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>26150522246290001554</t>
+          <t>26150522239320001545</t>
         </is>
       </c>
       <c r="Y28" t="inlineStr"/>
@@ -4303,7 +4295,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>Johan Osvaldo Beltran Quiros</t>
+          <t>Martin Ramiro Quiñonez Jauregui</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
@@ -4315,12 +4307,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>341991</t>
+          <t>340160</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>19809</t>
+          <t>17978</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -4330,32 +4322,32 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VICTOR HUGO</t>
+          <t>ALEJANDRO</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>SALAS</t>
+          <t>ROMERO</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>RODRIGUEZ</t>
+          <t>GARCIA</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>6531130495</t>
+          <t>2099007353</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>SAN MARCOS</t>
+          <t>PRIVADA REFORMA</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -4365,24 +4357,20 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>30-08-2001</t>
+          <t>27-03-1957</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>SALASRODRIGUEZVICTORHUGO@GMAIL.COM</t>
+          <t>ALEX57ROMERO@GMAIL.COM</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>09-02-2026 05:08:33</t>
-        </is>
-      </c>
-      <c r="N29" t="inlineStr">
-        <is>
-          <t>inscripcion promo 199</t>
-        </is>
-      </c>
+          <t>02-02-2026 14:07:14</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr"/>
       <c r="O29" t="inlineStr">
         <is>
           <t>Forzoso</t>
@@ -4400,17 +4388,17 @@
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>17-02-2026 16:21:53</t>
+          <t>02-02-2026 14:09:30</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>17-03-2026 23:59:59</t>
+          <t>02-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>17-02-2026 16:21:11</t>
+          <t>02-02-2026 14:08:43</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
@@ -4420,7 +4408,7 @@
       </c>
       <c r="V29" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W29" t="inlineStr">
@@ -4430,19 +4418,11 @@
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>26150522433690001818</t>
-        </is>
-      </c>
-      <c r="Y29" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>RAUL FELIX VAZQUEZ</t>
-        </is>
-      </c>
+          <t>26150522012090001230</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr"/>
+      <c r="Z29" t="inlineStr"/>
       <c r="AA29" t="inlineStr">
         <is>
           <t>499</t>
@@ -4450,24 +4430,24 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Juan Pablo Romero Andrade</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>342742</t>
+          <t>340247</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>20559</t>
+          <t>18065</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -4477,17 +4457,17 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>KARINA</t>
+          <t>LESLIE CLARETH</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>QUILES</t>
+          <t>VEGA</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>CAMACHO</t>
+          <t>QUEVEDO</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -4497,12 +4477,12 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>6531163674</t>
+          <t>6531329411</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>AV PUEBLA 1RA Y HERMOSILLO</t>
+          <t>AV NAYARIT 21</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -4512,20 +4492,24 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>22-02-1975</t>
+          <t>18-08-2006</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>KARINAAQUILESC1975@GMAIL.COM</t>
+          <t>VEGA.LESLIE.3E@GMAIL.COM</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>10-02-2026 17:14:23</t>
-        </is>
-      </c>
-      <c r="N30" t="inlineStr"/>
+          <t>02-02-2026 16:08:34</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
       <c r="O30" t="inlineStr">
         <is>
           <t>Forzoso</t>
@@ -4533,27 +4517,27 @@
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>DOMICILIADO 12 MESES $549 LE</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>10-02-2026 17:19:39</t>
+          <t>02-02-2026 16:43:55</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>10-03-2026 23:59:59</t>
+          <t>02-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>10-02-2026 17:18:56</t>
+          <t>02-02-2026 16:12:35</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
@@ -4563,7 +4547,7 @@
       </c>
       <c r="V30" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W30" t="inlineStr">
@@ -4573,19 +4557,19 @@
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>26150522239320001545</t>
+          <t>26150522017110001235</t>
         </is>
       </c>
       <c r="Y30" t="inlineStr"/>
       <c r="Z30" t="inlineStr"/>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>Martin Ramiro Quiñonez Jauregui</t>
+          <t>Juan Eduardo Torres Alcantar</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
@@ -4597,12 +4581,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>342497</t>
+          <t>340805</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>20314</t>
+          <t>18623</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -4612,55 +4596,59 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>KARLA VERONICA</t>
+          <t>RICARDO</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>TORRES</t>
+          <t>TAPIA</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>CORONA</t>
+          <t>OLIVO</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>52</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>9285509758</t>
+          <t>6531341539</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t xml:space="preserve">COLIMA C 26 </t>
+          <t>AV GUERRERO 12</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>19-11-1990</t>
+          <t>01-04-2000</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>KARLILLA15@HOTMAIL.COM</t>
+          <t>RICARDITOTAPIA2129@GMAIL.COM</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>09-02-2026 21:11:28</t>
-        </is>
-      </c>
-      <c r="N31" t="inlineStr"/>
+          <t>03-02-2026 19:10:40</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
       <c r="O31" t="inlineStr">
         <is>
           <t>Forzoso</t>
@@ -4668,27 +4656,27 @@
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>DOMICILIADO 12 MESES $549 LE</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>11-02-2026 20:58:26</t>
+          <t>03-02-2026 19:13:30</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
         <is>
-          <t>11-03-2026 23:59:59</t>
+          <t>03-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>11-02-2026 20:57:45</t>
+          <t>03-02-2026 19:12:47</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
@@ -4698,7 +4686,7 @@
       </c>
       <c r="V31" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W31" t="inlineStr">
@@ -4708,27 +4696,19 @@
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>26150522279010001613</t>
-        </is>
-      </c>
-      <c r="Y31" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>GISSEL ANAHY REYES GERMAN</t>
-        </is>
-      </c>
+          <t>26150522055450001315</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr"/>
+      <c r="Z31" t="inlineStr"/>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>Juan Pablo Romero Andrade</t>
+          <t>Martin Ramiro Quiñonez Jauregui</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
@@ -4740,12 +4720,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>342516</t>
+          <t>342562</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>20333</t>
+          <t>20379</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -4755,17 +4735,17 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LUIS</t>
+          <t>AZALEA ZENYACE</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>RODRIGUEZ</t>
+          <t>MORENO</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>GARCIA</t>
+          <t>CARRIZOZA</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -4775,32 +4755,32 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>6531211788</t>
+          <t>6531038421</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>AV COAHUILA B Y C PESQUEIRA</t>
+          <t>CJN CHIHUAHUA 23</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>12-08-1985</t>
+          <t>23-09-1994</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>COMANCHE87@OUTLOOK.COM</t>
+          <t>ZEN_YACE94LIVE@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>10-02-2026 05:40:54</t>
+          <t>10-02-2026 09:19:09</t>
         </is>
       </c>
       <c r="N32" t="inlineStr"/>
@@ -4811,7 +4791,7 @@
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>PLAN FAMILIA / AMIGOS X $499</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
@@ -4821,17 +4801,17 @@
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>10-02-2026 05:52:22</t>
+          <t>12-02-2026 18:37:07</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>10-03-2026 23:59:59</t>
+          <t>12-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>10-02-2026 05:49:58</t>
+          <t>12-02-2026 18:33:55</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
@@ -4851,11 +4831,19 @@
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>26150522222520001522</t>
-        </is>
-      </c>
-      <c r="Y32" t="inlineStr"/>
-      <c r="Z32" t="inlineStr"/>
+          <t>26150522302860001640</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>RAUL FELIX VAZQUEZ</t>
+        </is>
+      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>499</t>
@@ -4863,24 +4851,24 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Juan Pablo Romero Andrade</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>343958</t>
+          <t>343341</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>21775</t>
+          <t>21158</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -4890,17 +4878,17 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>ELIZABETH</t>
+          <t>JUAN OMAR</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>FLORES</t>
+          <t>REYES</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>HERAS</t>
+          <t>RIVERA</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -4910,67 +4898,63 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>6531288733</t>
+          <t>6865976498</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>CJON FLORES Y C 16 SN</t>
+          <t>CJON NICARAGUA 31</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>03-02-1988</t>
+          <t>02-01-1992</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>VICTORIALLAMAS2000@GMEIL.COM</t>
+          <t>ELREYES023@GMAIL.COM</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>16-02-2026 07:59:39</t>
-        </is>
-      </c>
-      <c r="N33" t="inlineStr">
-        <is>
-          <t>Tarifas 2026 LE</t>
-        </is>
-      </c>
+          <t>12-02-2026 17:35:55</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr"/>
       <c r="O33" t="inlineStr">
         <is>
-          <t>No Forzoso</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>RECURRENTE $649 LE</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>16-02-2026 08:07:18</t>
+          <t>14-02-2026 10:17:45</t>
         </is>
       </c>
       <c r="S33" t="inlineStr">
         <is>
-          <t>16-03-2026 23:59:59</t>
+          <t>14-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>16-02-2026 08:06:23</t>
+          <t>14-02-2026 10:17:11</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
@@ -4980,7 +4964,7 @@
       </c>
       <c r="V33" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W33" t="inlineStr">
@@ -4990,36 +4974,44 @@
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>26150522380380001737</t>
-        </is>
-      </c>
-      <c r="Y33" t="inlineStr"/>
-      <c r="Z33" t="inlineStr"/>
+          <t>26150522345630001701</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>GISSEL ANAHY REYES GERMAN</t>
+        </is>
+      </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Juan Pablo Romero Andrade</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>342823</t>
+          <t>341196</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>20640</t>
+          <t>19014</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -5029,17 +5021,17 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>JESUS ABEL</t>
+          <t>ESMERALDA</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>VALERIO</t>
+          <t>JAVALERA</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>LIMON</t>
+          <t>ALCANTAR</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -5049,32 +5041,32 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>6531665157</t>
+          <t>6531196345</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>CARRETERA DEL VALLE</t>
+          <t>AV TABASCO 41</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>23-07-2004</t>
+          <t>19-03-1975</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>VALERIOJESUS913@GMAIL.COM</t>
+          <t>ESMERALDA.JAVALERA@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>10-02-2026 19:05:03</t>
+          <t>04-02-2026 21:09:01</t>
         </is>
       </c>
       <c r="N34" t="inlineStr"/>
@@ -5095,17 +5087,17 @@
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>10-02-2026 19:09:25</t>
+          <t>11-02-2026 15:06:43</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
         <is>
-          <t>10-03-2026 23:59:59</t>
+          <t>11-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>10-02-2026 19:08:45</t>
+          <t>11-02-2026 15:05:40</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
@@ -5125,11 +5117,19 @@
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>26150522245980001553</t>
-        </is>
-      </c>
-      <c r="Y34" t="inlineStr"/>
-      <c r="Z34" t="inlineStr"/>
+          <t>26150522265920001586</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>GISSEL ANAHY REYES GERMAN</t>
+        </is>
+      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>499</t>
@@ -5137,7 +5137,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>Johan Osvaldo Beltran Quiros</t>
+          <t>Juan Eduardo Torres Alcantar</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
@@ -5149,12 +5149,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>339854</t>
+          <t>341271</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>17672</t>
+          <t>19089</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -5164,17 +5164,17 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>DIEGO ARMANDO</t>
+          <t>NICOLLE</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>MEDINA</t>
+          <t>BUSTAMANTE</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>PIEDRA</t>
+          <t>ELIZONDO</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -5184,67 +5184,63 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>6531658872</t>
+          <t>6381121777</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>REVOLUCION Y 40</t>
+          <t>LOS ADOBES</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>06-03-1989</t>
+          <t>15-12-1997</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>DIEGO.MEDINA@YAHOO.COM</t>
+          <t>NICOLLE.BUSTAMANTE@UABC.EDU.MX</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>02-02-2026 05:44:27</t>
-        </is>
-      </c>
-      <c r="N35" t="inlineStr">
-        <is>
-          <t>Tarifas 2026 LE</t>
-        </is>
-      </c>
+          <t>05-02-2026 10:43:03</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr"/>
       <c r="O35" t="inlineStr">
         <is>
-          <t>No Forzoso</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>PLAN FAMILIAR RECURRENTE $999</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>999</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>02-02-2026 05:46:51</t>
+          <t>11-02-2026 13:33:23</t>
         </is>
       </c>
       <c r="S35" t="inlineStr">
         <is>
-          <t>02-03-2026 23:59:59</t>
+          <t>11-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>02-02-2026 05:45:55</t>
+          <t>11-02-2026 13:31:59</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
@@ -5264,36 +5260,44 @@
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>26150521997870001209</t>
-        </is>
-      </c>
-      <c r="Y35" t="inlineStr"/>
-      <c r="Z35" t="inlineStr"/>
+          <t>26150522264110001579</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>RAUL FELIX VAZQUEZ</t>
+        </is>
+      </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>999</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Juan Pablo Romero Andrade</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>343341</t>
+          <t>343837</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>21158</t>
+          <t>21654</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -5303,17 +5307,17 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>JUAN OMAR</t>
+          <t>CLAUDIA GABRIELA</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>REYES</t>
+          <t>ROGEL</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>RIVERA</t>
+          <t>SANDOVAL</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -5323,32 +5327,32 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>6865976498</t>
+          <t>6532075902</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>CJON NICARAGUA 31</t>
+          <t>HUERTAS 7</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>02-01-1992</t>
+          <t>09-12-1991</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>ELREYES023@GMAIL.COM</t>
+          <t>ROGELCLAUDIA266@GMAIL.COM</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>12-02-2026 17:35:55</t>
+          <t>15-02-2026 12:34:47</t>
         </is>
       </c>
       <c r="N36" t="inlineStr"/>
@@ -5369,17 +5373,17 @@
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>14-02-2026 10:17:45</t>
+          <t>15-02-2026 12:38:45</t>
         </is>
       </c>
       <c r="S36" t="inlineStr">
         <is>
-          <t>14-03-2026 23:59:59</t>
+          <t>15-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>14-02-2026 10:17:11</t>
+          <t>15-02-2026 12:37:38</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
@@ -5389,7 +5393,7 @@
       </c>
       <c r="V36" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W36" t="inlineStr">
@@ -5399,19 +5403,11 @@
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>26150522345630001701</t>
-        </is>
-      </c>
-      <c r="Y36" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z36" t="inlineStr">
-        <is>
-          <t>GISSEL ANAHY REYES GERMAN</t>
-        </is>
-      </c>
+          <t>26150522365800001718</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr"/>
+      <c r="Z36" t="inlineStr"/>
       <c r="AA36" t="inlineStr">
         <is>
           <t>499</t>
@@ -5431,12 +5427,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>343637</t>
+          <t>342867</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>21454</t>
+          <t>20684</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -5446,17 +5442,17 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>RICARDO FRANCISCO</t>
+          <t>MIGUEL ANGEL</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>LEDESMA</t>
+          <t>AMEZCUA</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>PEDROZA</t>
+          <t>TORRES</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -5466,12 +5462,12 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>6531121344</t>
+          <t>6674708281</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>EL CHEQUE 8 S/N</t>
+          <t>FLORES 22</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -5481,17 +5477,17 @@
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>07-01-2006</t>
+          <t>21-11-1995</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>RICARDOPZK200@GMAIL.COM</t>
+          <t>MIGUELAMEZCUA21@GMAIL.COM</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>14-02-2026 06:48:50</t>
+          <t>10-02-2026 20:37:24</t>
         </is>
       </c>
       <c r="N37" t="inlineStr"/>
@@ -5512,17 +5508,17 @@
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>14-02-2026 08:02:52</t>
+          <t>12-02-2026 20:00:11</t>
         </is>
       </c>
       <c r="S37" t="inlineStr">
         <is>
-          <t>15-03-2026 23:59:59</t>
+          <t>12-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>14-02-2026 08:01:46</t>
+          <t>12-02-2026 19:59:09</t>
         </is>
       </c>
       <c r="U37" t="inlineStr">
@@ -5542,7 +5538,7 @@
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>26150522343510001694</t>
+          <t>26150522305570001650</t>
         </is>
       </c>
       <c r="Y37" t="inlineStr">
@@ -5552,7 +5548,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>RAUL FELIX VAZQUEZ</t>
+          <t>GISSEL ANAHY REYES GERMAN</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -5574,12 +5570,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>342867</t>
+          <t>340779</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>20684</t>
+          <t>18597</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -5589,17 +5585,17 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>MIGUEL ANGEL</t>
+          <t>CLAUDIA ITZEL</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AMEZCUA</t>
+          <t xml:space="preserve">DE LA ROSA </t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>TORRES</t>
+          <t>SANCHEZ</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -5609,75 +5605,67 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>6674708281</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>FLORES 22</t>
-        </is>
-      </c>
+          <t>6642467640</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
       <c r="J38" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>21-11-1995</t>
+          <t>21-11-1988</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>MIGUELAMEZCUA21@GMAIL.COM</t>
+          <t>ITZELT.DELAROSA@GMAIL.COM</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>10-02-2026 20:37:24</t>
-        </is>
-      </c>
-      <c r="N38" t="inlineStr"/>
+          <t>03-02-2026 18:20:07</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>12-02-2026 20:00:11</t>
+          <t>14-02-2026 12:53:49</t>
         </is>
       </c>
       <c r="S38" t="inlineStr">
         <is>
-          <t>12-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T38" t="inlineStr">
-        <is>
-          <t>12-02-2026 19:59:09</t>
-        </is>
-      </c>
+          <t>14-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T38" t="inlineStr"/>
       <c r="U38" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V38" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="V38" t="inlineStr"/>
       <c r="W38" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -5685,7 +5673,7 @@
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>26150522305570001650</t>
+          <t>26140522348900001443</t>
         </is>
       </c>
       <c r="Y38" t="inlineStr">
@@ -5693,14 +5681,10 @@
           <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
         </is>
       </c>
-      <c r="Z38" t="inlineStr">
-        <is>
-          <t>GISSEL ANAHY REYES GERMAN</t>
-        </is>
-      </c>
+      <c r="Z38" t="inlineStr"/>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB38" t="inlineStr">
@@ -5717,12 +5701,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>342562</t>
+          <t>343637</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>20379</t>
+          <t>21454</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -5732,17 +5716,17 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>AZALEA ZENYACE</t>
+          <t>RICARDO FRANCISCO</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>MORENO</t>
+          <t>LEDESMA</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>CARRIZOZA</t>
+          <t>PEDROZA</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -5752,32 +5736,32 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>6531038421</t>
+          <t>6531121344</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>CJN CHIHUAHUA 23</t>
+          <t>EL CHEQUE 8 S/N</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>23-09-1994</t>
+          <t>07-01-2006</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>ZEN_YACE94LIVE@HOTMAIL.COM</t>
+          <t>RICARDOPZK200@GMAIL.COM</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>10-02-2026 09:19:09</t>
+          <t>14-02-2026 06:48:50</t>
         </is>
       </c>
       <c r="N39" t="inlineStr"/>
@@ -5798,17 +5782,17 @@
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>12-02-2026 18:37:07</t>
+          <t>14-02-2026 08:02:52</t>
         </is>
       </c>
       <c r="S39" t="inlineStr">
         <is>
-          <t>12-03-2026 23:59:59</t>
+          <t>15-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T39" t="inlineStr">
         <is>
-          <t>12-02-2026 18:33:55</t>
+          <t>14-02-2026 08:01:46</t>
         </is>
       </c>
       <c r="U39" t="inlineStr">
@@ -5828,7 +5812,7 @@
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>26150522302860001640</t>
+          <t>26150522343510001694</t>
         </is>
       </c>
       <c r="Y39" t="inlineStr">
@@ -5848,7 +5832,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>Juan Pablo Romero Andrade</t>
+          <t>Johan Osvaldo Beltran Quiros</t>
         </is>
       </c>
       <c r="AC39" t="inlineStr">
@@ -5860,12 +5844,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>340160</t>
+          <t>343954</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>17978</t>
+          <t>21771</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -5875,95 +5859,99 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>ALEJANDRO</t>
+          <t>LOURDES</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>ROMERO</t>
+          <t>LOPEZ</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>GARCIA</t>
+          <t>SANCHEZ</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>6531035239</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>C 5 DE MAYO SN</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>10-01-1986</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>LULISLOPEZ999@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>16-02-2026 07:40:00</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>inscripcion promo 199</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>PROMO FEBRERO 12 MESES</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>499</t>
+        </is>
+      </c>
+      <c r="R40" t="inlineStr">
+        <is>
+          <t>16-02-2026 07:43:57</t>
+        </is>
+      </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>16-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>16-02-2026 07:43:12</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>2099007353</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>PRIVADA REFORMA</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>Masculino</t>
-        </is>
-      </c>
-      <c r="K40" t="inlineStr">
-        <is>
-          <t>27-03-1957</t>
-        </is>
-      </c>
-      <c r="L40" t="inlineStr">
-        <is>
-          <t>ALEX57ROMERO@GMAIL.COM</t>
-        </is>
-      </c>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>02-02-2026 14:07:14</t>
-        </is>
-      </c>
-      <c r="N40" t="inlineStr"/>
-      <c r="O40" t="inlineStr">
-        <is>
-          <t>Forzoso</t>
-        </is>
-      </c>
-      <c r="P40" t="inlineStr">
-        <is>
-          <t>PROMO FEBRERO 12 MESES</t>
-        </is>
-      </c>
-      <c r="Q40" t="inlineStr">
-        <is>
-          <t>499</t>
-        </is>
-      </c>
-      <c r="R40" t="inlineStr">
-        <is>
-          <t>02-02-2026 14:09:30</t>
-        </is>
-      </c>
-      <c r="S40" t="inlineStr">
-        <is>
-          <t>02-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T40" t="inlineStr">
-        <is>
-          <t>02-02-2026 14:08:43</t>
-        </is>
-      </c>
-      <c r="U40" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V40" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="W40" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -5971,7 +5959,7 @@
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>26150522012090001230</t>
+          <t>26150522379670001736</t>
         </is>
       </c>
       <c r="Y40" t="inlineStr"/>
@@ -5983,7 +5971,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>Juan Pablo Romero Andrade</t>
+          <t>Juan Eduardo Torres Alcantar</t>
         </is>
       </c>
       <c r="AC40" t="inlineStr">
@@ -5995,12 +5983,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>340247</t>
+          <t>344220</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>18065</t>
+          <t>22037</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -6010,17 +5998,17 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LESLIE CLARETH</t>
+          <t>CAROLINA</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>VEGA</t>
+          <t>FERNANDEZ</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>QUEVEDO</t>
+          <t>GUTIERREZ</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -6030,12 +6018,12 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>6531329411</t>
+          <t>6531610904</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>AV NAYARIT 21</t>
+          <t>CJON COLIMA 17 Y 18</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -6045,22 +6033,22 @@
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>18-08-2006</t>
+          <t>21-01-2003</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>VEGA.LESLIE.3E@GMAIL.COM</t>
+          <t>LINA_FDZ@ICLOUD.COM</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>02-02-2026 16:08:34</t>
+          <t>16-02-2026 17:36:28</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>Tarifas 2026 LE</t>
+          <t>inscripcion promo 199</t>
         </is>
       </c>
       <c r="O41" t="inlineStr">
@@ -6070,27 +6058,27 @@
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES $549 LE</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>02-02-2026 16:43:55</t>
+          <t>21-02-2026 06:49:41</t>
         </is>
       </c>
       <c r="S41" t="inlineStr">
         <is>
-          <t>02-03-2026 23:59:59</t>
+          <t>21-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t>02-02-2026 16:12:35</t>
+          <t>21-02-2026 06:48:42</t>
         </is>
       </c>
       <c r="U41" t="inlineStr">
@@ -6100,7 +6088,7 @@
       </c>
       <c r="V41" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W41" t="inlineStr">
@@ -6110,36 +6098,36 @@
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>26150522017110001235</t>
+          <t>26150522547830001961</t>
         </is>
       </c>
       <c r="Y41" t="inlineStr"/>
       <c r="Z41" t="inlineStr"/>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>Juan Eduardo Torres Alcantar</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>342499</t>
+          <t>341212</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>20316</t>
+          <t>19030</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -6149,17 +6137,17 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>ALBERTO</t>
+          <t xml:space="preserve">YAHIR </t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>VINIEGRA</t>
+          <t xml:space="preserve">SALGADO </t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>BERMUDEZ</t>
+          <t>COVARRUBIAS</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -6169,14 +6157,10 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>6532096000</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>COLIMA C 26</t>
-        </is>
-      </c>
+          <t>6531128435</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
       <c r="J42" t="inlineStr">
         <is>
           <t>Masculino</t>
@@ -6184,60 +6168,56 @@
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>20-05-1981</t>
+          <t>21-08-2004</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>VIVESISTEMS@GMAIL.COM</t>
+          <t>YAHIRSALGADO021@GMAIL.COM</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>09-02-2026 21:13:12</t>
-        </is>
-      </c>
-      <c r="N42" t="inlineStr"/>
+          <t>05-02-2026 05:58:43</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>11-02-2026 21:02:27</t>
+          <t>05-02-2026 06:04:50</t>
         </is>
       </c>
       <c r="S42" t="inlineStr">
         <is>
-          <t>11-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T42" t="inlineStr">
-        <is>
-          <t>11-02-2026 21:01:55</t>
-        </is>
-      </c>
+          <t>05-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T42" t="inlineStr"/>
       <c r="U42" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V42" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="V42" t="inlineStr"/>
       <c r="W42" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -6245,27 +6225,19 @@
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>26150522279160001614</t>
-        </is>
-      </c>
-      <c r="Y42" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z42" t="inlineStr">
-        <is>
-          <t>GISSEL ANAHY REYES GERMAN</t>
-        </is>
-      </c>
+          <t>26150522098340001363</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr"/>
+      <c r="Z42" t="inlineStr"/>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>Juan Pablo Romero Andrade</t>
+          <t>Juan Eduardo Torres Alcantar</t>
         </is>
       </c>
       <c r="AC42" t="inlineStr">
@@ -6277,12 +6249,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>342548</t>
+          <t>344062</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>20365</t>
+          <t>21879</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -6292,17 +6264,17 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>CECILIA GUADALUPE</t>
+          <t>RAYMUNDO ISRAEL</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>CORRAL</t>
+          <t>LOPEZ</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>MEDINA</t>
+          <t>ARREOLA</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -6312,32 +6284,28 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>6621711231</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>JUAREZ Y 20</t>
-        </is>
-      </c>
+          <t>6442276514</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
       <c r="J43" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>06-08-1998</t>
+          <t>21-05-2010</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>CECIGPE98@GMAIL.COM</t>
+          <t>RL25090288@BACHILLERESDESONORA.EDU.MX</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>10-02-2026 08:25:29</t>
+          <t>16-02-2026 13:12:33</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
@@ -6347,44 +6315,36 @@
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>No Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>RECURRENTE $649 LE</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R43" t="inlineStr">
         <is>
-          <t>10-02-2026 08:31:37</t>
+          <t>16-02-2026 13:13:37</t>
         </is>
       </c>
       <c r="S43" t="inlineStr">
         <is>
-          <t>10-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T43" t="inlineStr">
-        <is>
-          <t>10-02-2026 08:30:41</t>
-        </is>
-      </c>
+          <t>16-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T43" t="inlineStr"/>
       <c r="U43" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V43" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="V43" t="inlineStr"/>
       <c r="W43" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -6392,19 +6352,19 @@
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>26150522225760001528</t>
+          <t>26150522388250001746</t>
         </is>
       </c>
       <c r="Y43" t="inlineStr"/>
       <c r="Z43" t="inlineStr"/>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>Juan Eduardo Torres Alcantar</t>
+          <t>Juan Pablo Romero Andrade</t>
         </is>
       </c>
       <c r="AC43" t="inlineStr">
@@ -6416,12 +6376,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>344062</t>
+          <t>343947</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>21879</t>
+          <t>21764</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -6431,17 +6391,17 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>RAYMUNDO ISRAEL</t>
+          <t xml:space="preserve">FABIOLA </t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>LOPEZ</t>
+          <t>LUQUE</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>ARREOLA</t>
+          <t>LUQUE</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -6451,67 +6411,79 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>6442276514</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr"/>
+          <t>6531273238</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>AV CANADA Y 3RA</t>
+        </is>
+      </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>21-05-2010</t>
+          <t>05-04-1986</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>RL25090288@BACHILLERESDESONORA.EDU.MX</t>
+          <t>FABIOLALUQUE26@GMAIL.COM</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>16-02-2026 13:12:33</t>
+          <t>16-02-2026 07:08:47</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>Tarifas 2026 LE</t>
+          <t>inscripcion promo 199</t>
         </is>
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q44" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R44" t="inlineStr">
         <is>
-          <t>16-02-2026 13:13:37</t>
+          <t>19-02-2026 07:17:57</t>
         </is>
       </c>
       <c r="S44" t="inlineStr">
         <is>
-          <t>16-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T44" t="inlineStr"/>
+          <t>19-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>19-02-2026 07:16:55</t>
+        </is>
+      </c>
       <c r="U44" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V44" t="inlineStr"/>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W44" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -6519,19 +6491,27 @@
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>26150522388250001746</t>
-        </is>
-      </c>
-      <c r="Y44" t="inlineStr"/>
-      <c r="Z44" t="inlineStr"/>
+          <t>26150522487880001902</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>RAUL FELIX VAZQUEZ</t>
+        </is>
+      </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>Juan Pablo Romero Andrade</t>
+          <t>Martin Ramiro Quiñonez Jauregui</t>
         </is>
       </c>
       <c r="AC44" t="inlineStr">
@@ -6543,12 +6523,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>342846</t>
+          <t>341270</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>20663</t>
+          <t>19088</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -6558,17 +6538,17 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>CARLOS JULIAN</t>
+          <t>JUAN MANUEL</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>NUÑEZ</t>
+          <t>ALONZO</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>ROMERO</t>
+          <t>ARZATE</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -6578,32 +6558,32 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>6531308246</t>
+          <t>6161093843</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>TORREON 4 Y 5</t>
+          <t>FRACC ADOBES 75</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>29-08-2000</t>
+          <t>14-02-1995</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>EJNR2E@GMAIL.COM</t>
+          <t>JUANM_1495@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>10-02-2026 19:39:03</t>
+          <t>05-02-2026 10:41:41</t>
         </is>
       </c>
       <c r="N45" t="inlineStr"/>
@@ -6624,7 +6604,7 @@
       </c>
       <c r="R45" t="inlineStr">
         <is>
-          <t>11-02-2026 19:15:15</t>
+          <t>11-02-2026 13:27:47</t>
         </is>
       </c>
       <c r="S45" t="inlineStr">
@@ -6634,7 +6614,7 @@
       </c>
       <c r="T45" t="inlineStr">
         <is>
-          <t>11-02-2026 19:14:37</t>
+          <t>11-02-2026 13:26:38</t>
         </is>
       </c>
       <c r="U45" t="inlineStr">
@@ -6644,7 +6624,7 @@
       </c>
       <c r="V45" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W45" t="inlineStr">
@@ -6654,7 +6634,7 @@
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>26150522276380001607</t>
+          <t>26150522264040001578</t>
         </is>
       </c>
       <c r="Y45" t="inlineStr">
@@ -6664,7 +6644,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>GISSEL ANAHY REYES GERMAN</t>
+          <t>RAUL FELIX VAZQUEZ</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -6686,12 +6666,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>342849</t>
+          <t>344605</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>20666</t>
+          <t>22422</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -6701,32 +6681,32 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t xml:space="preserve">PAOLA </t>
+          <t>LIZET</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>ALONSO</t>
+          <t>HERNANDEZ</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>MANRIQUEZ</t>
+          <t>MENDEZ</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>6535395572</t>
+          <t>5412729355</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>CJN KINO 33</t>
+          <t>JALAPA B 5</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -6736,20 +6716,24 @@
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>13-12-1999</t>
+          <t>06-06-1998</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>PAOLAALONSOMGZ@GMAIL.COM</t>
+          <t>ALONDRAML1998@GMAIL.COM</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>10-02-2026 19:41:46</t>
-        </is>
-      </c>
-      <c r="N46" t="inlineStr"/>
+          <t>17-02-2026 17:23:47</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>inscripcion promo 199</t>
+        </is>
+      </c>
       <c r="O46" t="inlineStr">
         <is>
           <t>Forzoso</t>
@@ -6767,17 +6751,17 @@
       </c>
       <c r="R46" t="inlineStr">
         <is>
-          <t>11-02-2026 19:11:46</t>
+          <t>17-02-2026 17:32:20</t>
         </is>
       </c>
       <c r="S46" t="inlineStr">
         <is>
-          <t>11-03-2026 23:59:59</t>
+          <t>17-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T46" t="inlineStr">
         <is>
-          <t>11-02-2026 19:10:56</t>
+          <t>17-02-2026 17:31:40</t>
         </is>
       </c>
       <c r="U46" t="inlineStr">
@@ -6797,19 +6781,11 @@
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>26150522276280001606</t>
-        </is>
-      </c>
-      <c r="Y46" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z46" t="inlineStr">
-        <is>
-          <t>GISSEL ANAHY REYES GERMAN</t>
-        </is>
-      </c>
+          <t>26150522437780001826</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr"/>
+      <c r="Z46" t="inlineStr"/>
       <c r="AA46" t="inlineStr">
         <is>
           <t>499</t>
@@ -6817,24 +6793,24 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>Juan Pablo Romero Andrade</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>342866</t>
+          <t>342245</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>20683</t>
+          <t>20063</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -6844,32 +6820,32 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>IAN AXEL</t>
+          <t>MANUEL ANTONIO</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>SANDOVAL</t>
+          <t xml:space="preserve">RUIZ </t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>TORRES</t>
+          <t>SILVA</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>52</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>9285501740</t>
+          <t>6863042514</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>COLIMA C 26</t>
+          <t>CJN SAN JUAN Y SAN LUIS</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -6879,48 +6855,52 @@
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>30-08-2010</t>
+          <t>09-10-1991</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>IAN.SANDOVALTO@GMAIL.COM</t>
+          <t>MANUELANTONIOSILVARUIZ@GMAIL.COM</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>10-02-2026 20:35:22</t>
-        </is>
-      </c>
-      <c r="N47" t="inlineStr"/>
+          <t>09-02-2026 16:10:49</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>No Forzoso</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>RECURRENTE $649 LE</t>
         </is>
       </c>
       <c r="Q47" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>649</t>
         </is>
       </c>
       <c r="R47" t="inlineStr">
         <is>
-          <t>11-02-2026 21:04:30</t>
+          <t>09-02-2026 16:12:25</t>
         </is>
       </c>
       <c r="S47" t="inlineStr">
         <is>
-          <t>11-03-2026 23:59:59</t>
+          <t>09-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T47" t="inlineStr">
         <is>
-          <t>11-02-2026 21:03:57</t>
+          <t>09-02-2026 16:11:51</t>
         </is>
       </c>
       <c r="U47" t="inlineStr">
@@ -6930,7 +6910,7 @@
       </c>
       <c r="V47" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W47" t="inlineStr">
@@ -6940,27 +6920,19 @@
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>26150522279200001615</t>
-        </is>
-      </c>
-      <c r="Y47" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z47" t="inlineStr">
-        <is>
-          <t>GISSEL ANAHY REYES GERMAN</t>
-        </is>
-      </c>
+          <t>26150522197240001486</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr"/>
+      <c r="Z47" t="inlineStr"/>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>649</t>
         </is>
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>Juan Pablo Romero Andrade</t>
+          <t>Johan Osvaldo Beltran Quiros</t>
         </is>
       </c>
       <c r="AC47" t="inlineStr">
@@ -6972,12 +6944,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>343837</t>
+          <t>342261</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>21654</t>
+          <t>20079</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -6987,17 +6959,17 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>CLAUDIA GABRIELA</t>
+          <t xml:space="preserve">VICTORIA </t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>ROGEL</t>
+          <t xml:space="preserve">ZAVALA </t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>SANDOVAL</t>
+          <t>BARRIENTOS</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -7007,12 +6979,12 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>6532075902</t>
+          <t>6531231721</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>HUERTAS 7</t>
+          <t xml:space="preserve">HACIENDA DE LA CRUZ </t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -7022,20 +6994,24 @@
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>09-12-1991</t>
+          <t>04-04-1996</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>ROGELCLAUDIA266@GMAIL.COM</t>
+          <t>GUADALUPEZAVALAMERCADO@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>15-02-2026 12:34:47</t>
-        </is>
-      </c>
-      <c r="N48" t="inlineStr"/>
+          <t>09-02-2026 16:34:55</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
       <c r="O48" t="inlineStr">
         <is>
           <t>Forzoso</t>
@@ -7043,27 +7019,27 @@
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>DOMICILIADO 12 MESES $549 LE</t>
         </is>
       </c>
       <c r="Q48" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R48" t="inlineStr">
         <is>
-          <t>15-02-2026 12:38:45</t>
+          <t>09-02-2026 16:37:21</t>
         </is>
       </c>
       <c r="S48" t="inlineStr">
         <is>
-          <t>15-03-2026 23:59:59</t>
+          <t>09-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T48" t="inlineStr">
         <is>
-          <t>15-02-2026 12:37:38</t>
+          <t>09-02-2026 16:36:34</t>
         </is>
       </c>
       <c r="U48" t="inlineStr">
@@ -7073,7 +7049,7 @@
       </c>
       <c r="V48" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W48" t="inlineStr">
@@ -7083,19 +7059,19 @@
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>26150522365800001718</t>
+          <t>26150522198880001489</t>
         </is>
       </c>
       <c r="Y48" t="inlineStr"/>
       <c r="Z48" t="inlineStr"/>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>Juan Pablo Romero Andrade</t>
+          <t>Johan Osvaldo Beltran Quiros</t>
         </is>
       </c>
       <c r="AC48" t="inlineStr">
@@ -7107,12 +7083,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>343954</t>
+          <t>342499</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>21771</t>
+          <t>20316</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -7122,17 +7098,17 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LOURDES</t>
+          <t>ALBERTO</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>LOPEZ</t>
+          <t>VINIEGRA</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>SANCHEZ</t>
+          <t>BERMUDEZ</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -7142,39 +7118,35 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>6531035239</t>
+          <t>6532096000</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>C 5 DE MAYO SN</t>
+          <t>COLIMA C 26</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>10-01-1986</t>
+          <t>20-05-1981</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>LULISLOPEZ999@GMAIL.COM</t>
+          <t>VIVESISTEMS@GMAIL.COM</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>16-02-2026 07:40:00</t>
-        </is>
-      </c>
-      <c r="N49" t="inlineStr">
-        <is>
-          <t>inscripcion promo 199</t>
-        </is>
-      </c>
+          <t>09-02-2026 21:13:12</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr"/>
       <c r="O49" t="inlineStr">
         <is>
           <t>Forzoso</t>
@@ -7192,17 +7164,17 @@
       </c>
       <c r="R49" t="inlineStr">
         <is>
-          <t>16-02-2026 07:43:57</t>
+          <t>11-02-2026 21:02:27</t>
         </is>
       </c>
       <c r="S49" t="inlineStr">
         <is>
-          <t>16-03-2026 23:59:59</t>
+          <t>11-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T49" t="inlineStr">
         <is>
-          <t>16-02-2026 07:43:12</t>
+          <t>11-02-2026 21:01:55</t>
         </is>
       </c>
       <c r="U49" t="inlineStr">
@@ -7222,11 +7194,19 @@
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>26150522379670001736</t>
-        </is>
-      </c>
-      <c r="Y49" t="inlineStr"/>
-      <c r="Z49" t="inlineStr"/>
+          <t>26150522279160001614</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>GISSEL ANAHY REYES GERMAN</t>
+        </is>
+      </c>
       <c r="AA49" t="inlineStr">
         <is>
           <t>499</t>
@@ -7234,7 +7214,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>Juan Eduardo Torres Alcantar</t>
+          <t>Juan Pablo Romero Andrade</t>
         </is>
       </c>
       <c r="AC49" t="inlineStr">
@@ -7246,12 +7226,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>344605</t>
+          <t>342548</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>22422</t>
+          <t>20365</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -7261,99 +7241,99 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LIZET</t>
+          <t>CECILIA GUADALUPE</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>HERNANDEZ</t>
+          <t>CORRAL</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>MENDEZ</t>
+          <t>MEDINA</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>6621711231</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>JUAREZ Y 20</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>06-08-1998</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>CECIGPE98@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>10-02-2026 08:25:29</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>No Forzoso</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>RECURRENTE $649 LE</t>
+        </is>
+      </c>
+      <c r="Q50" t="inlineStr">
+        <is>
+          <t>649</t>
+        </is>
+      </c>
+      <c r="R50" t="inlineStr">
+        <is>
+          <t>10-02-2026 08:31:37</t>
+        </is>
+      </c>
+      <c r="S50" t="inlineStr">
+        <is>
+          <t>10-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>10-02-2026 08:30:41</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="H50" t="inlineStr">
-        <is>
-          <t>5412729355</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>JALAPA B 5</t>
-        </is>
-      </c>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t>Femenino</t>
-        </is>
-      </c>
-      <c r="K50" t="inlineStr">
-        <is>
-          <t>06-06-1998</t>
-        </is>
-      </c>
-      <c r="L50" t="inlineStr">
-        <is>
-          <t>ALONDRAML1998@GMAIL.COM</t>
-        </is>
-      </c>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>17-02-2026 17:23:47</t>
-        </is>
-      </c>
-      <c r="N50" t="inlineStr">
-        <is>
-          <t>inscripcion promo 199</t>
-        </is>
-      </c>
-      <c r="O50" t="inlineStr">
-        <is>
-          <t>Forzoso</t>
-        </is>
-      </c>
-      <c r="P50" t="inlineStr">
-        <is>
-          <t>PROMO FEBRERO 12 MESES</t>
-        </is>
-      </c>
-      <c r="Q50" t="inlineStr">
-        <is>
-          <t>499</t>
-        </is>
-      </c>
-      <c r="R50" t="inlineStr">
-        <is>
-          <t>17-02-2026 17:32:20</t>
-        </is>
-      </c>
-      <c r="S50" t="inlineStr">
-        <is>
-          <t>17-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T50" t="inlineStr">
-        <is>
-          <t>17-02-2026 17:31:40</t>
-        </is>
-      </c>
-      <c r="U50" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V50" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="W50" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -7361,36 +7341,36 @@
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>26150522437780001826</t>
+          <t>26150522225760001528</t>
         </is>
       </c>
       <c r="Y50" t="inlineStr"/>
       <c r="Z50" t="inlineStr"/>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>649</t>
         </is>
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Juan Eduardo Torres Alcantar</t>
         </is>
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>340779</t>
+          <t>345080</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>18597</t>
+          <t>87245</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -7400,17 +7380,17 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>CLAUDIA ITZEL</t>
+          <t>LIZBETH</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t xml:space="preserve">DE LA ROSA </t>
+          <t>MARTINEZ</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>SANCHEZ</t>
+          <t>MEJIA</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -7420,7 +7400,7 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>6642467640</t>
+          <t>6532094330</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -7431,17 +7411,17 @@
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>21-11-1988</t>
+          <t>01-04-2009</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>ITZELT.DELAROSA@GMAIL.COM</t>
+          <t>LIZBETHMARTINEZMEJIAMX@GMAIL.COM</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>03-02-2026 18:20:07</t>
+          <t>19-02-2026 14:44:45</t>
         </is>
       </c>
       <c r="N51" t="inlineStr">
@@ -7466,12 +7446,12 @@
       </c>
       <c r="R51" t="inlineStr">
         <is>
-          <t>14-02-2026 12:53:49</t>
+          <t>19-02-2026 14:46:32</t>
         </is>
       </c>
       <c r="S51" t="inlineStr">
         <is>
-          <t>14-03-2026 23:59:59</t>
+          <t>19-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T51" t="inlineStr"/>
@@ -7488,14 +7468,10 @@
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>26140522348900001443</t>
-        </is>
-      </c>
-      <c r="Y51" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
+          <t>26150522495630001914</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr"/>
       <c r="Z51" t="inlineStr"/>
       <c r="AA51" t="inlineStr">
         <is>
@@ -7516,12 +7492,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>341212</t>
+          <t>342512</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>19030</t>
+          <t>20329</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -7531,17 +7507,17 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t xml:space="preserve">YAHIR </t>
+          <t>JOSE RICARDO</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t xml:space="preserve">SALGADO </t>
+          <t>GARCIA</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>COVARRUBIAS</t>
+          <t>ANGULO</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -7551,10 +7527,14 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>6531128435</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr"/>
+          <t>6531217599</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>CJON HIDALGO Y 47</t>
+        </is>
+      </c>
       <c r="J52" t="inlineStr">
         <is>
           <t>Masculino</t>
@@ -7562,17 +7542,17 @@
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>21-08-2004</t>
+          <t>03-04-1976</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>YAHIRSALGADO021@GMAIL.COM</t>
+          <t>RRICARDOGARCIA34@ICLOUD.COM</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>05-02-2026 05:58:43</t>
+          <t>10-02-2026 05:34:48</t>
         </is>
       </c>
       <c r="N52" t="inlineStr">
@@ -7582,36 +7562,44 @@
       </c>
       <c r="O52" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>No Forzoso</t>
         </is>
       </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>RECURRENTE $649 LE</t>
         </is>
       </c>
       <c r="Q52" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>649</t>
         </is>
       </c>
       <c r="R52" t="inlineStr">
         <is>
-          <t>05-02-2026 06:04:50</t>
+          <t>11-02-2026 06:33:27</t>
         </is>
       </c>
       <c r="S52" t="inlineStr">
         <is>
-          <t>05-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T52" t="inlineStr"/>
+          <t>11-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>11-02-2026 06:32:18</t>
+        </is>
+      </c>
       <c r="U52" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V52" t="inlineStr"/>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W52" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -7619,14 +7607,22 @@
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>26150522098340001363</t>
-        </is>
-      </c>
-      <c r="Y52" t="inlineStr"/>
-      <c r="Z52" t="inlineStr"/>
+          <t>26150522257790001574</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>RAUL FELIX VAZQUEZ</t>
+        </is>
+      </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>649</t>
         </is>
       </c>
       <c r="AB52" t="inlineStr">
@@ -7643,12 +7639,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>341270</t>
+          <t>344190</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>19088</t>
+          <t>22007</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -7658,17 +7654,17 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>JUAN MANUEL</t>
+          <t xml:space="preserve">SEBASTIAN </t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>ALONZO</t>
+          <t>GARCIA</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>ARZATE</t>
+          <t>GUERRERO</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -7678,14 +7674,10 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>6161093843</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>FRACC ADOBES 75</t>
-        </is>
-      </c>
+          <t>6531058427</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
       <c r="J53" t="inlineStr">
         <is>
           <t>Masculino</t>
@@ -7693,60 +7685,56 @@
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>14-02-1995</t>
+          <t>21-10-2009</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>JUANM_1495@HOTMAIL.COM</t>
+          <t>MONKEEX424@GMAIL.COM</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>05-02-2026 10:41:41</t>
-        </is>
-      </c>
-      <c r="N53" t="inlineStr"/>
+          <t>16-02-2026 17:04:57</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
       <c r="O53" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q53" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R53" t="inlineStr">
         <is>
-          <t>11-02-2026 13:27:47</t>
+          <t>18-02-2026 17:05:10</t>
         </is>
       </c>
       <c r="S53" t="inlineStr">
         <is>
-          <t>11-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T53" t="inlineStr">
-        <is>
-          <t>11-02-2026 13:26:38</t>
-        </is>
-      </c>
+          <t>18-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T53" t="inlineStr"/>
       <c r="U53" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V53" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr"/>
       <c r="W53" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -7754,7 +7742,7 @@
       </c>
       <c r="X53" t="inlineStr">
         <is>
-          <t>26150522264040001578</t>
+          <t>26150522468100001872</t>
         </is>
       </c>
       <c r="Y53" t="inlineStr">
@@ -7764,34 +7752,34 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>RAUL FELIX VAZQUEZ</t>
+          <t>GISSEL ANAHY REYES GERMAN</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>Juan Pablo Romero Andrade</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>344190</t>
+          <t>342846</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>22007</t>
+          <t>20663</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -7801,17 +7789,17 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t xml:space="preserve">SEBASTIAN </t>
+          <t>CARLOS JULIAN</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>GARCIA</t>
+          <t>NUÑEZ</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>GUERRERO</t>
+          <t>ROMERO</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
@@ -7821,67 +7809,75 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>6531058427</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr"/>
+          <t>6531308246</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>TORREON 4 Y 5</t>
+        </is>
+      </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>21-10-2009</t>
+          <t>29-08-2000</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>MONKEEX424@GMAIL.COM</t>
+          <t>EJNR2E@GMAIL.COM</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>16-02-2026 17:04:57</t>
-        </is>
-      </c>
-      <c r="N54" t="inlineStr">
-        <is>
-          <t>Tarifas 2026 LE</t>
-        </is>
-      </c>
+          <t>10-02-2026 19:39:03</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr"/>
       <c r="O54" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q54" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R54" t="inlineStr">
         <is>
-          <t>18-02-2026 17:05:10</t>
+          <t>11-02-2026 19:15:15</t>
         </is>
       </c>
       <c r="S54" t="inlineStr">
         <is>
-          <t>18-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T54" t="inlineStr"/>
+          <t>11-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>11-02-2026 19:14:37</t>
+        </is>
+      </c>
       <c r="U54" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="V54" t="inlineStr"/>
       <c r="W54" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -7889,7 +7885,7 @@
       </c>
       <c r="X54" t="inlineStr">
         <is>
-          <t>26150522468100001872</t>
+          <t>26150522276380001607</t>
         </is>
       </c>
       <c r="Y54" t="inlineStr">
@@ -7904,29 +7900,29 @@
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Juan Pablo Romero Andrade</t>
         </is>
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>344649</t>
+          <t>342849</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>22466</t>
+          <t>20666</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -7936,17 +7932,17 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>ROSA MARIA</t>
+          <t xml:space="preserve">PAOLA </t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>VALADES</t>
+          <t>ALONSO</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>SARMIENTO</t>
+          <t>MANRIQUEZ</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
@@ -7956,12 +7952,12 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>6864265235</t>
+          <t>6535395572</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>AV JACARANDAS 19</t>
+          <t>CJN KINO 33</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
@@ -7971,24 +7967,20 @@
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>26-10-1989</t>
+          <t>13-12-1999</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>GENERICO@GAMIL.COM</t>
+          <t>PAOLAALONSOMGZ@GMAIL.COM</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>17-02-2026 18:13:05</t>
-        </is>
-      </c>
-      <c r="N55" t="inlineStr">
-        <is>
-          <t>inscripcion promo 199</t>
-        </is>
-      </c>
+          <t>10-02-2026 19:41:46</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr"/>
       <c r="O55" t="inlineStr">
         <is>
           <t>Forzoso</t>
@@ -8006,17 +7998,17 @@
       </c>
       <c r="R55" t="inlineStr">
         <is>
-          <t>18-02-2026 19:06:17</t>
+          <t>11-02-2026 19:11:46</t>
         </is>
       </c>
       <c r="S55" t="inlineStr">
         <is>
-          <t>18-03-2026 23:59:59</t>
+          <t>11-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T55" t="inlineStr">
         <is>
-          <t>18-02-2026 19:05:40</t>
+          <t>11-02-2026 19:10:56</t>
         </is>
       </c>
       <c r="U55" t="inlineStr">
@@ -8036,7 +8028,7 @@
       </c>
       <c r="X55" t="inlineStr">
         <is>
-          <t>26150522474170001890</t>
+          <t>26150522276280001606</t>
         </is>
       </c>
       <c r="Y55" t="inlineStr">
@@ -8056,24 +8048,24 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Juan Pablo Romero Andrade</t>
         </is>
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>343531</t>
+          <t>342828</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>21348</t>
+          <t>20645</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -8083,17 +8075,17 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>URIEL IGNACIO</t>
+          <t>NUBIA GUADALUPE</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>SID</t>
+          <t>SOLARES</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>AREVALO</t>
+          <t>ARVIZU</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
@@ -8103,32 +8095,32 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>6531071848</t>
+          <t>6531665151</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>FELIX CONTRERAS 44</t>
+          <t>CARRETERA DEL VALLE</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>02-06-2005</t>
+          <t>27-09-2002</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>URIELIGNACIOSIDDAVERALO@GMAIL.COM</t>
+          <t>NUBIAG3@ICLOUD.COM</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>13-02-2026 16:28:37</t>
+          <t>10-02-2026 19:11:57</t>
         </is>
       </c>
       <c r="N56" t="inlineStr"/>
@@ -8149,17 +8141,17 @@
       </c>
       <c r="R56" t="inlineStr">
         <is>
-          <t>13-02-2026 16:34:53</t>
+          <t>10-02-2026 19:16:21</t>
         </is>
       </c>
       <c r="S56" t="inlineStr">
         <is>
-          <t>13-03-2026 23:59:59</t>
+          <t>10-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T56" t="inlineStr">
         <is>
-          <t>13-02-2026 16:34:13</t>
+          <t>10-02-2026 19:15:42</t>
         </is>
       </c>
       <c r="U56" t="inlineStr">
@@ -8179,7 +8171,7 @@
       </c>
       <c r="X56" t="inlineStr">
         <is>
-          <t>26150522324410001674</t>
+          <t>26150522246290001554</t>
         </is>
       </c>
       <c r="Y56" t="inlineStr"/>
@@ -8191,7 +8183,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>Juan Pablo Romero Andrade</t>
+          <t>Johan Osvaldo Beltran Quiros</t>
         </is>
       </c>
       <c r="AC56" t="inlineStr">
@@ -8203,12 +8195,12 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>343813</t>
+          <t>344649</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>21630</t>
+          <t>22466</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -8218,17 +8210,17 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>YOCELIN DEL CARMEN</t>
+          <t>ROSA MARIA</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>LOPEZ</t>
+          <t>VALADES</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>VALENZUELA</t>
+          <t>SARMIENTO</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -8238,12 +8230,12 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>6531305359</t>
+          <t>6864265235</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>AV CARRANZA 36</t>
+          <t>AV JACARANDAS 19</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
@@ -8253,20 +8245,24 @@
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>16-07-1999</t>
+          <t>26-10-1989</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>YOCELINLOPEZ490@GMAIL.COM</t>
+          <t>GENERICO@GAMIL.COM</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>15-02-2026 11:25:12</t>
-        </is>
-      </c>
-      <c r="N57" t="inlineStr"/>
+          <t>17-02-2026 18:13:05</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>inscripcion promo 199</t>
+        </is>
+      </c>
       <c r="O57" t="inlineStr">
         <is>
           <t>Forzoso</t>
@@ -8284,17 +8280,17 @@
       </c>
       <c r="R57" t="inlineStr">
         <is>
-          <t>15-02-2026 11:31:12</t>
+          <t>18-02-2026 19:06:17</t>
         </is>
       </c>
       <c r="S57" t="inlineStr">
         <is>
-          <t>15-03-2026 23:59:59</t>
+          <t>18-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T57" t="inlineStr">
         <is>
-          <t>15-02-2026 11:29:38</t>
+          <t>18-02-2026 19:05:40</t>
         </is>
       </c>
       <c r="U57" t="inlineStr">
@@ -8314,11 +8310,19 @@
       </c>
       <c r="X57" t="inlineStr">
         <is>
-          <t>26150522364500001715</t>
-        </is>
-      </c>
-      <c r="Y57" t="inlineStr"/>
-      <c r="Z57" t="inlineStr"/>
+          <t>26150522474170001890</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z57" t="inlineStr">
+        <is>
+          <t>GISSEL ANAHY REYES GERMAN</t>
+        </is>
+      </c>
       <c r="AA57" t="inlineStr">
         <is>
           <t>499</t>
@@ -8326,151 +8330,1124 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>Juan Pablo Romero Andrade</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
+          <t>342866</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>20683</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>SAN LUIS</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>IAN AXEL</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>SANDOVAL</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>TORRES</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>9285501740</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>COLIMA C 26</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>30-08-2010</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>IAN.SANDOVALTO@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>10-02-2026 20:35:22</t>
+        </is>
+      </c>
+      <c r="N58" t="inlineStr"/>
+      <c r="O58" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>PROMO FEBRERO 12 MESES</t>
+        </is>
+      </c>
+      <c r="Q58" t="inlineStr">
+        <is>
+          <t>499</t>
+        </is>
+      </c>
+      <c r="R58" t="inlineStr">
+        <is>
+          <t>11-02-2026 21:04:30</t>
+        </is>
+      </c>
+      <c r="S58" t="inlineStr">
+        <is>
+          <t>11-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>11-02-2026 21:03:57</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>26150522279200001615</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z58" t="inlineStr">
+        <is>
+          <t>GISSEL ANAHY REYES GERMAN</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>499</t>
+        </is>
+      </c>
+      <c r="AB58" t="inlineStr">
+        <is>
+          <t>Juan Pablo Romero Andrade</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>343958</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>21775</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>SAN LUIS</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>ELIZABETH</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>FLORES</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>HERAS</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>6531288733</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>CJON FLORES Y C 16 SN</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>03-02-1988</t>
+        </is>
+      </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>VICTORIALLAMAS2000@GMEIL.COM</t>
+        </is>
+      </c>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>16-02-2026 07:59:39</t>
+        </is>
+      </c>
+      <c r="N59" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
+      <c r="O59" t="inlineStr">
+        <is>
+          <t>No Forzoso</t>
+        </is>
+      </c>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>RECURRENTE $649 LE</t>
+        </is>
+      </c>
+      <c r="Q59" t="inlineStr">
+        <is>
+          <t>649</t>
+        </is>
+      </c>
+      <c r="R59" t="inlineStr">
+        <is>
+          <t>16-02-2026 08:07:18</t>
+        </is>
+      </c>
+      <c r="S59" t="inlineStr">
+        <is>
+          <t>16-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>16-02-2026 08:06:23</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X59" t="inlineStr">
+        <is>
+          <t>26150522380380001737</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr"/>
+      <c r="Z59" t="inlineStr"/>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>649</t>
+        </is>
+      </c>
+      <c r="AB59" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>343531</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>21348</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>SAN LUIS</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>URIEL IGNACIO</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>SID</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>AREVALO</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>6531071848</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>FELIX CONTRERAS 44</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>02-06-2005</t>
+        </is>
+      </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>URIELIGNACIOSIDDAVERALO@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>13-02-2026 16:28:37</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr"/>
+      <c r="O60" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>PROMO FEBRERO 12 MESES</t>
+        </is>
+      </c>
+      <c r="Q60" t="inlineStr">
+        <is>
+          <t>499</t>
+        </is>
+      </c>
+      <c r="R60" t="inlineStr">
+        <is>
+          <t>13-02-2026 16:34:53</t>
+        </is>
+      </c>
+      <c r="S60" t="inlineStr">
+        <is>
+          <t>13-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>13-02-2026 16:34:13</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X60" t="inlineStr">
+        <is>
+          <t>26150522324410001674</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr"/>
+      <c r="Z60" t="inlineStr"/>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>499</t>
+        </is>
+      </c>
+      <c r="AB60" t="inlineStr">
+        <is>
+          <t>Juan Pablo Romero Andrade</t>
+        </is>
+      </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>343813</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>21630</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>SAN LUIS</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>YOCELIN DEL CARMEN</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>LOPEZ</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>VALENZUELA</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>6531305359</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>AV CARRANZA 36</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>16-07-1999</t>
+        </is>
+      </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>YOCELINLOPEZ490@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>15-02-2026 11:25:12</t>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr"/>
+      <c r="O61" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>PROMO FEBRERO 12 MESES</t>
+        </is>
+      </c>
+      <c r="Q61" t="inlineStr">
+        <is>
+          <t>499</t>
+        </is>
+      </c>
+      <c r="R61" t="inlineStr">
+        <is>
+          <t>15-02-2026 11:31:12</t>
+        </is>
+      </c>
+      <c r="S61" t="inlineStr">
+        <is>
+          <t>15-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>15-02-2026 11:29:38</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X61" t="inlineStr">
+        <is>
+          <t>26150522364500001715</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr"/>
+      <c r="Z61" t="inlineStr"/>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>499</t>
+        </is>
+      </c>
+      <c r="AB61" t="inlineStr">
+        <is>
+          <t>Juan Pablo Romero Andrade</t>
+        </is>
+      </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>344583</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>22400</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>SAN LUIS</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CARLOS </t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>ACOSTA</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>SANTOS</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>6531202025</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>AV NUEVO LEON 9</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>04-03-2005</t>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>TZELI9535@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>17-02-2026 16:50:12</t>
+        </is>
+      </c>
+      <c r="N62" t="inlineStr">
+        <is>
+          <t>inscripcion promo 199</t>
+        </is>
+      </c>
+      <c r="O62" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>PROMO FEBRERO 12 MESES</t>
+        </is>
+      </c>
+      <c r="Q62" t="inlineStr">
+        <is>
+          <t>499</t>
+        </is>
+      </c>
+      <c r="R62" t="inlineStr">
+        <is>
+          <t>19-02-2026 17:11:32</t>
+        </is>
+      </c>
+      <c r="S62" t="inlineStr">
+        <is>
+          <t>19-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>19-02-2026 17:10:51</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X62" t="inlineStr">
+        <is>
+          <t>26150522500690001919</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z62" t="inlineStr">
+        <is>
+          <t>GISSEL ANAHY REYES GERMAN</t>
+        </is>
+      </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>499</t>
+        </is>
+      </c>
+      <c r="AB62" t="inlineStr">
+        <is>
+          <t>Johan Osvaldo Beltran Quiros</t>
+        </is>
+      </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>345101</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>87266</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>SAN LUIS</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>CAMILA</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>VASQUEZ</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>LOPEZ</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>6531040237</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>08-10-2007</t>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>VASQUEZLOPEZCAMILA@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>19-02-2026 15:31:29</t>
+        </is>
+      </c>
+      <c r="N63" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
+      <c r="O63" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>3 MESES $1,899</t>
+        </is>
+      </c>
+      <c r="Q63" t="inlineStr">
+        <is>
+          <t>633</t>
+        </is>
+      </c>
+      <c r="R63" t="inlineStr">
+        <is>
+          <t>19-02-2026 15:34:34</t>
+        </is>
+      </c>
+      <c r="S63" t="inlineStr">
+        <is>
+          <t>19-05-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T63" t="inlineStr"/>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr"/>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X63" t="inlineStr">
+        <is>
+          <t>26150522497060001917</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr"/>
+      <c r="Z63" t="inlineStr"/>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>1899</t>
+        </is>
+      </c>
+      <c r="AB63" t="inlineStr">
+        <is>
+          <t>Johan Osvaldo Beltran Quiros</t>
+        </is>
+      </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
           <t>344507</t>
         </is>
       </c>
-      <c r="B58" t="inlineStr">
+      <c r="B64" t="inlineStr">
         <is>
           <t>22324</t>
         </is>
       </c>
-      <c r="C58" t="inlineStr">
+      <c r="C64" t="inlineStr">
         <is>
           <t>SAN LUIS</t>
         </is>
       </c>
-      <c r="D58" t="inlineStr">
+      <c r="D64" t="inlineStr">
         <is>
           <t>KAREN ANDREA</t>
         </is>
       </c>
-      <c r="E58" t="inlineStr">
+      <c r="E64" t="inlineStr">
         <is>
           <t>ISAIS</t>
         </is>
       </c>
-      <c r="F58" t="inlineStr">
+      <c r="F64" t="inlineStr">
         <is>
           <t>QUILES</t>
         </is>
       </c>
-      <c r="G58" t="inlineStr">
+      <c r="G64" t="inlineStr">
         <is>
           <t>52</t>
         </is>
       </c>
-      <c r="H58" t="inlineStr">
+      <c r="H64" t="inlineStr">
         <is>
           <t>6531517509</t>
         </is>
       </c>
-      <c r="I58" t="inlineStr">
+      <c r="I64" t="inlineStr">
         <is>
           <t>AV PUEBLA 1RA</t>
         </is>
       </c>
-      <c r="J58" t="inlineStr">
+      <c r="J64" t="inlineStr">
         <is>
           <t>Femenino</t>
         </is>
       </c>
-      <c r="K58" t="inlineStr">
+      <c r="K64" t="inlineStr">
         <is>
           <t>12-02-1999</t>
         </is>
       </c>
-      <c r="L58" t="inlineStr">
+      <c r="L64" t="inlineStr">
         <is>
           <t>KARENANDREAISAIS1999@GMAIL.COM</t>
         </is>
       </c>
-      <c r="M58" t="inlineStr">
+      <c r="M64" t="inlineStr">
         <is>
           <t>17-02-2026 14:45:48</t>
         </is>
       </c>
-      <c r="N58" t="inlineStr">
+      <c r="N64" t="inlineStr">
         <is>
           <t>Tarifas 2026 LE</t>
         </is>
       </c>
-      <c r="O58" t="inlineStr">
+      <c r="O64" t="inlineStr">
         <is>
           <t>No Forzoso</t>
         </is>
       </c>
-      <c r="P58" t="inlineStr">
+      <c r="P64" t="inlineStr">
         <is>
           <t>PLAN RECURRENTE PAGO INCIAL $1,449 LE</t>
         </is>
       </c>
-      <c r="Q58" t="inlineStr">
+      <c r="Q64" t="inlineStr">
         <is>
           <t>1449</t>
         </is>
       </c>
-      <c r="R58" t="inlineStr">
+      <c r="R64" t="inlineStr">
         <is>
           <t>17-02-2026 14:50:44</t>
         </is>
       </c>
-      <c r="S58" t="inlineStr">
+      <c r="S64" t="inlineStr">
         <is>
           <t>17-03-2026 23:59:59</t>
         </is>
       </c>
-      <c r="T58" t="inlineStr">
+      <c r="T64" t="inlineStr">
         <is>
           <t>17-02-2026 14:49:35</t>
         </is>
       </c>
-      <c r="U58" t="inlineStr">
+      <c r="U64" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V58" t="inlineStr">
+      <c r="V64" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="W58" t="inlineStr">
+      <c r="W64" t="inlineStr">
         <is>
           <t>Sucursal</t>
         </is>
       </c>
-      <c r="X58" t="inlineStr">
+      <c r="X64" t="inlineStr">
         <is>
           <t>26150522430060001816</t>
         </is>
       </c>
-      <c r="Y58" t="inlineStr"/>
-      <c r="Z58" t="inlineStr"/>
-      <c r="AA58" t="inlineStr">
+      <c r="Y64" t="inlineStr"/>
+      <c r="Z64" t="inlineStr"/>
+      <c r="AA64" t="inlineStr">
         <is>
           <t>1449</t>
         </is>
       </c>
-      <c r="AB58" t="inlineStr">
+      <c r="AB64" t="inlineStr">
         <is>
           <t>N/D</t>
         </is>
       </c>
-      <c r="AC58" t="inlineStr">
+      <c r="AC64" t="inlineStr">
         <is>
           <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>344807</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>22624</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>SAN LUIS</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>CRUZ GUADALUPE</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>LUGO</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>ROCHA</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>6532082764</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>AV NAYARIT 43 Y 44</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>01-01-2000</t>
+        </is>
+      </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>CRUZGLP01@LCLOUD.COM</t>
+        </is>
+      </c>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>18-02-2026 12:56:53</t>
+        </is>
+      </c>
+      <c r="N65" t="inlineStr">
+        <is>
+          <t>inscripcion promo 199</t>
+        </is>
+      </c>
+      <c r="O65" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>PROMO FEBRERO 12 MESES</t>
+        </is>
+      </c>
+      <c r="Q65" t="inlineStr">
+        <is>
+          <t>499</t>
+        </is>
+      </c>
+      <c r="R65" t="inlineStr">
+        <is>
+          <t>20-02-2026 10:30:09</t>
+        </is>
+      </c>
+      <c r="S65" t="inlineStr">
+        <is>
+          <t>20-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>20-02-2026 10:29:02</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X65" t="inlineStr">
+        <is>
+          <t>26150522523340001940</t>
+        </is>
+      </c>
+      <c r="Y65" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z65" t="inlineStr">
+        <is>
+          <t>GISSEL ANAHY REYES GERMAN</t>
+        </is>
+      </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>499</t>
+        </is>
+      </c>
+      <c r="AB65" t="inlineStr">
+        <is>
+          <t>Juan Pablo Romero Andrade</t>
+        </is>
+      </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>con rutina</t>
         </is>
       </c>
     </row>

--- a/data/rutinas/sucursales/Socios_con_y_sin_rutina__SAN LUIS.xlsx
+++ b/data/rutinas/sucursales/Socios_con_y_sin_rutina__SAN LUIS.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC65"/>
+  <dimension ref="A1:AC70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -578,12 +578,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>273095</t>
+          <t>119470</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>70597</t>
+          <t>17177</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -593,17 +593,17 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LUZ ANGELICA</t>
+          <t>ADILENE ANALY</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>MURILLO</t>
+          <t>HUERTA</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>SANCHEZ</t>
+          <t>ANGULO</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -613,12 +613,12 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>6531078647</t>
+          <t>6538490585</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>AV COLIMA Y 44</t>
+          <t>AV OAXACA D  27 Y 28</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -628,20 +628,24 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>02-06-2002</t>
+          <t>27-07-1989</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>MENDOZA_MURILLOO21@HOTMAIL.COM</t>
+          <t>ADY-27-60@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>11-01-2025 05:38:19</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr"/>
+          <t>30-08-2022 09:55:13</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>inscripcion promo 199</t>
+        </is>
+      </c>
       <c r="O2" t="inlineStr">
         <is>
           <t>Forzoso</t>
@@ -659,17 +663,17 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>13-02-2026 18:16:08</t>
+          <t>23-02-2026 14:40:10</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>13-03-2026 23:59:59</t>
+          <t>23-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>13-02-2026 18:12:25</t>
+          <t>23-02-2026 14:38:59</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -679,7 +683,7 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
@@ -689,7 +693,7 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>26150522327860001680</t>
+          <t>26150522582880002003</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr"/>
@@ -701,24 +705,24 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>Juan Pablo Romero Andrade</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>319145</t>
+          <t>273095</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>16642</t>
+          <t>70597</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -728,17 +732,17 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>CESAR BERNARDO</t>
+          <t>LUZ ANGELICA</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>ELIZONDO</t>
+          <t>MURILLO</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>RODRIGUEZ</t>
+          <t>SANCHEZ</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -748,39 +752,35 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>6862267616</t>
+          <t>6531078647</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>GUADALUPE VICTORIA Y 31</t>
+          <t>AV COLIMA Y 44</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>27-07-1992</t>
+          <t>02-06-2002</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>CESARBER27@HOTMAIL.COM</t>
+          <t>MENDOZA_MURILLOO21@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>16-10-2025 19:03:26</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>inscripcion promo 199</t>
-        </is>
-      </c>
+          <t>11-01-2025 05:38:19</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr">
         <is>
           <t>Forzoso</t>
@@ -798,17 +798,17 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>17-02-2026 10:45:09</t>
+          <t>13-02-2026 18:16:08</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>17-03-2026 23:59:59</t>
+          <t>13-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>17-02-2026 10:44:24</t>
+          <t>13-02-2026 18:12:25</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -818,7 +818,7 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
@@ -828,19 +828,11 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>26150522424240001807</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>GISSEL ANAHY REYES GERMAN</t>
-        </is>
-      </c>
+          <t>26150522327860001680</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr"/>
+      <c r="Z3" t="inlineStr"/>
       <c r="AA3" t="inlineStr">
         <is>
           <t>499</t>
@@ -848,7 +840,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>Juan Eduardo Torres Alcantar</t>
+          <t>Juan Pablo Romero Andrade</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -860,12 +852,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>317137</t>
+          <t>319145</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>14634</t>
+          <t>16642</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -875,17 +867,17 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>JOSE IGNACIO</t>
+          <t>CESAR BERNARDO</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>PARRA</t>
+          <t>ELIZONDO</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>JAQUEZ</t>
+          <t>RODRIGUEZ</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -895,12 +887,12 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>6531038638</t>
+          <t>6862267616</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>CALZADA AVIACION 104</t>
+          <t>GUADALUPE VICTORIA Y 31</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -910,20 +902,24 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>13-12-1975</t>
+          <t>27-07-1992</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>JOSEIGNACIOJOAN@GMAIL.COM</t>
+          <t>CESARBER27@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>03-10-2025 19:18:42</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr"/>
+          <t>16-10-2025 19:03:26</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>inscripcion promo 199</t>
+        </is>
+      </c>
       <c r="O4" t="inlineStr">
         <is>
           <t>Forzoso</t>
@@ -941,17 +937,17 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>13-02-2026 18:41:08</t>
+          <t>17-02-2026 10:45:09</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>13-03-2026 23:59:59</t>
+          <t>17-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>13-02-2026 18:39:22</t>
+          <t>17-02-2026 10:44:24</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -961,7 +957,7 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -971,7 +967,7 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>26150522328580001685</t>
+          <t>26150522424240001807</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
@@ -991,7 +987,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>Juan Pablo Romero Andrade</t>
+          <t>Juan Eduardo Torres Alcantar</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -1003,12 +999,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>34113</t>
+          <t>317137</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>32029</t>
+          <t>14634</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1018,17 +1014,17 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>YOVANY</t>
+          <t>JOSE IGNACIO</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>VALENZUELA</t>
+          <t>PARRA</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t xml:space="preserve">ALVARADO </t>
+          <t>JAQUEZ</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -1038,12 +1034,12 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>6531453465</t>
+          <t>6531038638</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>LEY DE ALFABETIZACION 9 Y 10</t>
+          <t>CALZADA AVIACION 104</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1053,17 +1049,17 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>30-12-1997</t>
+          <t>13-12-1975</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>YOVANYALVRADO@GMAIL.COM</t>
+          <t>JOSEIGNACIOJOAN@GMAIL.COM</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>29-06-2021 18:23:17</t>
+          <t>03-10-2025 19:18:42</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -1084,17 +1080,17 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>12-02-2026 05:24:56</t>
+          <t>13-02-2026 18:41:08</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>12-03-2026 23:59:59</t>
+          <t>13-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>12-02-2026 05:23:53</t>
+          <t>13-02-2026 18:39:22</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -1114,11 +1110,19 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>26150522281110001621</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr"/>
-      <c r="Z5" t="inlineStr"/>
+          <t>26150522328580001685</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>GISSEL ANAHY REYES GERMAN</t>
+        </is>
+      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>499</t>
@@ -1126,7 +1130,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>Juan Eduardo Torres Alcantar</t>
+          <t>Juan Pablo Romero Andrade</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -1138,12 +1142,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>109430</t>
+          <t>34113</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>7171</t>
+          <t>32029</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1153,17 +1157,17 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>GISELL</t>
+          <t>YOVANY</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>BARO</t>
+          <t>VALENZUELA</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>SOTO</t>
+          <t xml:space="preserve">ALVARADO </t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -1173,71 +1177,75 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>6531135478</t>
+          <t>6531453465</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>SAN LUIS</t>
+          <t>LEY DE ALFABETIZACION 9 Y 10</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>25-01-1999</t>
+          <t>30-12-1997</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>GISELBARO@HOTMAIL.COM</t>
+          <t>YOVANYALVRADO@GMAIL.COM</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>19-07-2022 07:14:06</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>Tarifas 2026 LE</t>
-        </is>
-      </c>
+          <t>29-06-2021 18:23:17</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>1 MES $899</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>17-02-2026 09:24:03</t>
+          <t>12-02-2026 05:24:56</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>17-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T6" t="inlineStr"/>
+          <t>12-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>12-02-2026 05:23:53</t>
+        </is>
+      </c>
       <c r="U6" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V6" t="inlineStr"/>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W6" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -1245,19 +1253,19 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>26150522422860001804</t>
+          <t>26150522281110001621</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr"/>
       <c r="Z6" t="inlineStr"/>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>Martin Ramiro Quiñonez Jauregui</t>
+          <t>Juan Eduardo Torres Alcantar</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -1269,12 +1277,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>330218</t>
+          <t>109430</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>15272</t>
+          <t>7171</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1284,17 +1292,17 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t xml:space="preserve">SILVIA </t>
+          <t>GISELL</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>ZAVALA</t>
+          <t>BARO</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>PACHECO</t>
+          <t>SOTO</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -1304,12 +1312,12 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>6531211789</t>
+          <t>6531135478</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>AV COAHUILA B Y C PESQUEIRA</t>
+          <t>SAN LUIS</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1319,60 +1327,56 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>15-02-1984</t>
+          <t>25-01-1999</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>AALER22398@GMAIL.COM</t>
+          <t>GISELBARO@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>24-12-2025 07:23:05</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr"/>
+          <t>19-07-2022 07:14:06</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>PLAN FAMILIA / AMIGOS X $499</t>
+          <t>1 MES $899</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>899</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>10-02-2026 05:56:10</t>
+          <t>17-02-2026 09:24:03</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>10-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T7" t="inlineStr">
-        <is>
-          <t>10-02-2026 05:55:08</t>
-        </is>
-      </c>
+          <t>17-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr"/>
       <c r="U7" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="V7" t="inlineStr"/>
       <c r="W7" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -1380,27 +1384,19 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>26150522222600001523</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>RAUL FELIX VAZQUEZ</t>
-        </is>
-      </c>
+          <t>26150522422860001804</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr"/>
+      <c r="Z7" t="inlineStr"/>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>899</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>Juan Eduardo Torres Alcantar</t>
+          <t>Martin Ramiro Quiñonez Jauregui</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
@@ -1412,12 +1408,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>339758</t>
+          <t>330218</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>17576</t>
+          <t>15272</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1427,17 +1423,17 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>ISABELLA</t>
+          <t xml:space="preserve">SILVIA </t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>ALARCON</t>
+          <t>ZAVALA</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>ACEVES</t>
+          <t>PACHECO</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -1447,10 +1443,14 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>6535382487</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>6531211789</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>AV COAHUILA B Y C PESQUEIRA</t>
+        </is>
+      </c>
       <c r="J8" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -1458,56 +1458,60 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>04-06-2010</t>
+          <t>15-02-1984</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>ALARCONISABELLA347@GMAIL.COM</t>
+          <t>AALER22398@GMAIL.COM</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>01-02-2026 10:00:33</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>Tarifas 2026 LE</t>
-        </is>
-      </c>
+          <t>24-12-2025 07:23:05</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>PLAN FAMILIA / AMIGOS X $499</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>01-02-2026 10:05:34</t>
+          <t>10-02-2026 05:56:10</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>01-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T8" t="inlineStr"/>
+          <t>10-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>10-02-2026 05:55:08</t>
+        </is>
+      </c>
       <c r="U8" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V8" t="inlineStr"/>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W8" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -1515,19 +1519,27 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>26150521988630001200</t>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr"/>
-      <c r="Z8" t="inlineStr"/>
+          <t>26150522222600001523</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>RAUL FELIX VAZQUEZ</t>
+        </is>
+      </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>Juan Pablo Romero Andrade</t>
+          <t>Juan Eduardo Torres Alcantar</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
@@ -1539,12 +1551,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>339777</t>
+          <t>339758</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>17595</t>
+          <t>17576</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1554,17 +1566,17 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>GISSEL LILIAN</t>
+          <t>ISABELLA</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>RODRIGUEZ</t>
+          <t>ALARCON</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>SILVA</t>
+          <t>ACEVES</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -1574,14 +1586,10 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>6531466820</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>MERIDA 1</t>
-        </is>
-      </c>
+          <t>6535382487</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -1589,17 +1597,17 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>02-09-1998</t>
+          <t>04-06-2010</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>GISSELSILVIA98@GMAIL.COM</t>
+          <t>ALARCONISABELLA347@GMAIL.COM</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>01-02-2026 10:50:32</t>
+          <t>01-02-2026 10:00:33</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1609,22 +1617,22 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>No Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>RECURRENTE $649 LE</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>01-02-2026 10:53:31</t>
+          <t>01-02-2026 10:05:34</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
@@ -1632,21 +1640,13 @@
           <t>01-03-2026 23:59:59</t>
         </is>
       </c>
-      <c r="T9" t="inlineStr">
-        <is>
-          <t>01-02-2026 10:52:55</t>
-        </is>
-      </c>
+      <c r="T9" t="inlineStr"/>
       <c r="U9" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="V9" t="inlineStr"/>
       <c r="W9" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -1654,14 +1654,14 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>26150521989600001201</t>
+          <t>26150521988630001200</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr"/>
       <c r="Z9" t="inlineStr"/>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -1678,12 +1678,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>277709</t>
+          <t>339777</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>75210</t>
+          <t>17595</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1693,17 +1693,17 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>ANGEL ALBERTO</t>
+          <t>GISSEL LILIAN</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>ACOSTA</t>
+          <t>RODRIGUEZ</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>RIVAS</t>
+          <t>SILVA</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -1713,63 +1713,67 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>6424832255</t>
+          <t>6531466820</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>CJON 5 DE MAYO 12 Y 13</t>
+          <t>MERIDA 1</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>06-03-1998</t>
+          <t>02-09-1998</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>ACOSTARIVS@GMAIL.COM</t>
+          <t>GISSELSILVIA98@GMAIL.COM</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>06-02-2025 18:37:15</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr"/>
+          <t>01-02-2026 10:50:32</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>No Forzoso</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>RECURRENTE $649 LE</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>649</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>13-02-2026 05:21:27</t>
+          <t>01-02-2026 10:53:31</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>14-03-2026 23:59:59</t>
+          <t>01-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>13-02-2026 05:19:56</t>
+          <t>01-02-2026 10:52:55</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
@@ -1779,7 +1783,7 @@
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W10" t="inlineStr">
@@ -1789,27 +1793,19 @@
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>26150522308700001658</t>
-        </is>
-      </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>RAUL FELIX VAZQUEZ</t>
-        </is>
-      </c>
+          <t>26150521989600001201</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr"/>
+      <c r="Z10" t="inlineStr"/>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>649</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>Juan Eduardo Torres Alcantar</t>
+          <t>Juan Pablo Romero Andrade</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
@@ -1948,12 +1944,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>339746</t>
+          <t>277709</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>17564</t>
+          <t>75210</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1963,17 +1959,17 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t xml:space="preserve">GRISEL </t>
+          <t>ANGEL ALBERTO</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>CUADRAS</t>
+          <t>ACOSTA</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>CUADRAS</t>
+          <t>RIVAS</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -1983,67 +1979,63 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>6531315370</t>
+          <t>6424832255</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>MEXICO B Y 28</t>
+          <t>CJON 5 DE MAYO 12 Y 13</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>17-02-1980</t>
+          <t>06-03-1998</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>CHACLAUDIA5@HOTMAIL.COM</t>
+          <t>ACOSTARIVS@GMAIL.COM</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>01-02-2026 09:25:23</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>Tarifas 2026 LE</t>
-        </is>
-      </c>
+          <t>06-02-2025 18:37:15</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
       <c r="O12" t="inlineStr">
         <is>
-          <t>No Forzoso</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>RECURRENTE $649 LE</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>03-02-2026 05:30:52</t>
+          <t>13-02-2026 05:21:27</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>03-03-2026 23:59:59</t>
+          <t>14-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>03-02-2026 05:30:25</t>
+          <t>13-02-2026 05:19:56</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
@@ -2053,7 +2045,7 @@
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W12" t="inlineStr">
@@ -2063,7 +2055,7 @@
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>26150522029990001268</t>
+          <t>26150522308700001658</t>
         </is>
       </c>
       <c r="Y12" t="inlineStr">
@@ -2073,17 +2065,17 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>GISSEL ANAHY REYES GERMAN</t>
+          <t>RAUL FELIX VAZQUEZ</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>Martin Ramiro Quiñonez Jauregui</t>
+          <t>Juan Eduardo Torres Alcantar</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
@@ -2095,12 +2087,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>340340</t>
+          <t>339746</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>18158</t>
+          <t>17564</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -2110,17 +2102,17 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>FATIMA</t>
+          <t xml:space="preserve">GRISEL </t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>SANCHEZ</t>
+          <t>CUADRAS</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>MEDINA</t>
+          <t>CUADRAS</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -2130,12 +2122,12 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>6531333103</t>
+          <t>6531315370</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>AV TORREON 39</t>
+          <t>MEXICO B Y 28</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -2145,17 +2137,17 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>27-08-2003</t>
+          <t>17-02-1980</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>FATIMASM2708@GMAIL.COM</t>
+          <t>CHACLAUDIA5@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>02-02-2026 18:15:23</t>
+          <t>01-02-2026 09:25:23</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
@@ -2165,32 +2157,32 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>No Forzoso</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES $549 LE</t>
+          <t>RECURRENTE $649 LE</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>649</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>02-02-2026 18:20:31</t>
+          <t>03-02-2026 05:30:52</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>02-03-2026 23:59:59</t>
+          <t>03-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>02-02-2026 18:19:16</t>
+          <t>03-02-2026 05:30:25</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
@@ -2210,19 +2202,27 @@
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>26150522020390001251</t>
-        </is>
-      </c>
-      <c r="Y13" t="inlineStr"/>
-      <c r="Z13" t="inlineStr"/>
+          <t>26150522029990001268</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>GISSEL ANAHY REYES GERMAN</t>
+        </is>
+      </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>649</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>Johan Osvaldo Beltran Quiros</t>
+          <t>Martin Ramiro Quiñonez Jauregui</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
@@ -2234,12 +2234,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>336709</t>
+          <t>340340</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>22435</t>
+          <t>18158</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -2249,17 +2249,17 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>MARIA FERNANDA</t>
+          <t>FATIMA</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>LAZALDE</t>
+          <t>SANCHEZ</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>ANDRADE</t>
+          <t>MEDINA</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -2269,12 +2269,12 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>6645697047</t>
+          <t>6531333103</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>C ADOLFO LOPEZ MATEOS 6413 C</t>
+          <t>AV TORREON 39</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -2284,20 +2284,24 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>21-01-2000</t>
+          <t>27-08-2003</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>FERGIE.LAZALDE@GMAIL.COM</t>
+          <t>FATIMASM2708@GMAIL.COM</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>21-01-2026 11:47:08</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr"/>
+          <t>02-02-2026 18:15:23</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
       <c r="O14" t="inlineStr">
         <is>
           <t>Forzoso</t>
@@ -2305,27 +2309,27 @@
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>DOMICILIADO 12 MESES $549 LE</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>11-02-2026 08:22:24</t>
+          <t>02-02-2026 18:20:31</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>11-03-2026 23:59:59</t>
+          <t>02-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>11-02-2026 08:21:44</t>
+          <t>02-02-2026 18:19:16</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
@@ -2335,7 +2339,7 @@
       </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W14" t="inlineStr">
@@ -2345,23 +2349,19 @@
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>26070522259520003153</t>
-        </is>
-      </c>
-      <c r="Y14" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
+          <t>26150522020390001251</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr"/>
       <c r="Z14" t="inlineStr"/>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>Jesus Alejandro  Partida Partida</t>
+          <t>Johan Osvaldo Beltran Quiros</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
@@ -2373,12 +2373,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>340602</t>
+          <t>336709</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>18420</t>
+          <t>22435</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -2388,87 +2388,95 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>DANTE EMILIANO</t>
+          <t>MARIA FERNANDA</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>GARCIA</t>
+          <t>LAZALDE</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>GOMEZ</t>
+          <t>ANDRADE</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>52</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>9228390416</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>6645697047</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>C ADOLFO LOPEZ MATEOS 6413 C</t>
+        </is>
+      </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>06-12-2010</t>
+          <t>21-01-2000</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>DANTE.GARCIA@INSTITUTOKINO.EDU.MX</t>
+          <t>FERGIE.LAZALDE@GMAIL.COM</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>03-02-2026 14:43:23</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>Tarifas 2026 LE</t>
-        </is>
-      </c>
+          <t>21-01-2026 11:47:08</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr"/>
       <c r="O15" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>03-02-2026 14:44:52</t>
+          <t>11-02-2026 08:22:24</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>03-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T15" t="inlineStr"/>
+          <t>11-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>11-02-2026 08:21:44</t>
+        </is>
+      </c>
       <c r="U15" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V15" t="inlineStr"/>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="W15" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -2476,19 +2484,23 @@
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>26150522041730001279</t>
-        </is>
-      </c>
-      <c r="Y15" t="inlineStr"/>
+          <t>26070522259520003153</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
       <c r="Z15" t="inlineStr"/>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>Juan Pablo Romero Andrade</t>
+          <t>Jesus Alejandro  Partida Partida</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
@@ -2500,12 +2512,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>340730</t>
+          <t>297488</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>18548</t>
+          <t>94986</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -2515,17 +2527,17 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>GUADALUPE SHEREZADA</t>
+          <t xml:space="preserve">BRENDA </t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>RAMIREZ</t>
+          <t>ROMAN</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>CORTEZ</t>
+          <t>IBARRA</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -2535,10 +2547,14 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>6531304693</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>6531125544</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>EMILIANO ZAPATA C Y COLOMBIA</t>
+        </is>
+      </c>
       <c r="J16" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -2546,56 +2562,64 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>02-07-2000</t>
+          <t>04-02-1984</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>BELLOBAINES.1982@GMAIL.COM</t>
+          <t>OKCHIQUITA4@GMAIL.COM</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>03-02-2026 17:27:01</t>
+          <t>09-06-2025 20:08:16</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>Tarifas 2026 LE</t>
+          <t>inscripcion promo 199</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>03-02-2026 17:32:11</t>
+          <t>19-02-2026 17:34:15</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>03-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T16" t="inlineStr"/>
+          <t>19-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>19-02-2026 17:33:15</t>
+        </is>
+      </c>
       <c r="U16" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V16" t="inlineStr"/>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W16" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -2603,36 +2627,40 @@
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>26150522049660001299</t>
-        </is>
-      </c>
-      <c r="Y16" t="inlineStr"/>
+          <t>26150522501710001922</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
       <c r="Z16" t="inlineStr"/>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>Juan Pablo Romero Andrade</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>297488</t>
+          <t>340602</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>94986</t>
+          <t>18420</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -2642,99 +2670,87 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t xml:space="preserve">BRENDA </t>
+          <t>DANTE EMILIANO</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>ROMAN</t>
+          <t>GARCIA</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>IBARRA</t>
+          <t>GOMEZ</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>6531125544</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>EMILIANO ZAPATA C Y COLOMBIA</t>
-        </is>
-      </c>
+          <t>9228390416</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>04-02-1984</t>
+          <t>06-12-2010</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>OKCHIQUITA4@GMAIL.COM</t>
+          <t>DANTE.GARCIA@INSTITUTOKINO.EDU.MX</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>09-06-2025 20:08:16</t>
+          <t>03-02-2026 14:43:23</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>inscripcion promo 199</t>
+          <t>Tarifas 2026 LE</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>19-02-2026 17:34:15</t>
+          <t>03-02-2026 14:44:52</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>19-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T17" t="inlineStr">
-        <is>
-          <t>19-02-2026 17:33:15</t>
-        </is>
-      </c>
+          <t>03-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr"/>
       <c r="U17" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V17" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="V17" t="inlineStr"/>
       <c r="W17" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -2742,40 +2758,36 @@
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>26150522501710001922</t>
-        </is>
-      </c>
-      <c r="Y17" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
+          <t>26150522041730001279</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr"/>
       <c r="Z17" t="inlineStr"/>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Juan Pablo Romero Andrade</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>341197</t>
+          <t>340730</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>19015</t>
+          <t>18548</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -2785,17 +2797,17 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>CARMEN</t>
+          <t>GUADALUPE SHEREZADA</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>ALICIA</t>
+          <t>RAMIREZ</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>GIL</t>
+          <t>CORTEZ</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -2805,14 +2817,10 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>6642049795</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>AV BENITO JUAREZ 24 Y 25</t>
-        </is>
-      </c>
+          <t>6531304693</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -2820,60 +2828,56 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>15-09-1947</t>
+          <t>02-07-2000</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>CARMEN1947@GMAIL.COM</t>
+          <t>BELLOBAINES.1982@GMAIL.COM</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>04-02-2026 21:10:39</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr"/>
+          <t>03-02-2026 17:27:01</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>11-02-2026 15:03:22</t>
+          <t>03-02-2026 17:32:11</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>11-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T18" t="inlineStr">
-        <is>
-          <t>11-02-2026 15:02:18</t>
-        </is>
-      </c>
+          <t>03-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr"/>
       <c r="U18" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V18" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="V18" t="inlineStr"/>
       <c r="W18" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -2881,27 +2885,19 @@
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>26150522265830001585</t>
-        </is>
-      </c>
-      <c r="Y18" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>GISSEL ANAHY REYES GERMAN</t>
-        </is>
-      </c>
+          <t>26150522049660001299</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr"/>
+      <c r="Z18" t="inlineStr"/>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>Juan Eduardo Torres Alcantar</t>
+          <t>Juan Pablo Romero Andrade</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
@@ -2913,12 +2909,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>325230</t>
+          <t>341197</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>22169</t>
+          <t>19015</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -2928,17 +2924,17 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t xml:space="preserve">GLORIA </t>
+          <t>CARMEN</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>SANTOS</t>
+          <t>ALICIA</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>PEREZ</t>
+          <t>GIL</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -2948,12 +2944,12 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>6531642345</t>
+          <t>6642049795</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>AV NUEVO LEON N9 Y 10</t>
+          <t>AV BENITO JUAREZ 24 Y 25</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -2963,24 +2959,20 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>09-08-1984</t>
+          <t>15-09-1947</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>PRICESASANTOS8409@GMAIL.COM</t>
+          <t>CARMEN1947@GMAIL.COM</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>25-11-2025 12:03:46</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>inscripcion promo 199</t>
-        </is>
-      </c>
+          <t>04-02-2026 21:10:39</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr"/>
       <c r="O19" t="inlineStr">
         <is>
           <t>Forzoso</t>
@@ -2998,17 +2990,17 @@
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>18-02-2026 18:24:56</t>
+          <t>11-02-2026 15:03:22</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>18-03-2026 23:59:59</t>
+          <t>11-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>18-02-2026 18:24:16</t>
+          <t>11-02-2026 15:02:18</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
@@ -3028,7 +3020,7 @@
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>26150522472400001881</t>
+          <t>26150522265830001585</t>
         </is>
       </c>
       <c r="Y19" t="inlineStr">
@@ -3048,7 +3040,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>Juan Pablo Romero Andrade</t>
+          <t>Juan Eduardo Torres Alcantar</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
@@ -3060,12 +3052,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>341991</t>
+          <t>325230</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>19809</t>
+          <t>22169</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -3075,17 +3067,17 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VICTOR HUGO</t>
+          <t xml:space="preserve">GLORIA </t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>SALAS</t>
+          <t>SANTOS</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>RODRIGUEZ</t>
+          <t>PEREZ</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -3095,32 +3087,32 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>6531130495</t>
+          <t>6531642345</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>SAN MARCOS</t>
+          <t>AV NUEVO LEON N9 Y 10</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>30-08-2001</t>
+          <t>09-08-1984</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>SALASRODRIGUEZVICTORHUGO@GMAIL.COM</t>
+          <t>PRICESASANTOS8409@GMAIL.COM</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>09-02-2026 05:08:33</t>
+          <t>25-11-2025 12:03:46</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
@@ -3145,17 +3137,17 @@
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>17-02-2026 16:21:53</t>
+          <t>18-02-2026 18:24:56</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>17-03-2026 23:59:59</t>
+          <t>18-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>17-02-2026 16:21:11</t>
+          <t>18-02-2026 18:24:16</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
@@ -3175,7 +3167,7 @@
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>26150522433690001818</t>
+          <t>26150522472400001881</t>
         </is>
       </c>
       <c r="Y20" t="inlineStr">
@@ -3185,7 +3177,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>RAUL FELIX VAZQUEZ</t>
+          <t>GISSEL ANAHY REYES GERMAN</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -3195,24 +3187,24 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Juan Pablo Romero Andrade</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>340152</t>
+          <t>341991</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>17970</t>
+          <t>19809</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -3222,17 +3214,17 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>MARTHA LIDIA</t>
+          <t>VICTOR HUGO</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t xml:space="preserve">DURAN </t>
+          <t>SALAS</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>CUEN</t>
+          <t>RODRIGUEZ</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -3242,12 +3234,12 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>6531218668</t>
+          <t>6531130495</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>PRIVADO ROFORMA</t>
+          <t>SAN MARCOS</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -3257,20 +3249,24 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>06-08-1960</t>
+          <t>30-08-2001</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>ROMERO.MARTHA50@ICLOUD.COM</t>
+          <t>SALASRODRIGUEZVICTORHUGO@GMAIL.COM</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>02-02-2026 13:57:36</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr"/>
+          <t>09-02-2026 05:08:33</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>inscripcion promo 199</t>
+        </is>
+      </c>
       <c r="O21" t="inlineStr">
         <is>
           <t>Forzoso</t>
@@ -3288,17 +3284,17 @@
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>02-02-2026 14:04:27</t>
+          <t>17-02-2026 16:21:53</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>02-03-2026 23:59:59</t>
+          <t>17-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>02-02-2026 14:03:30</t>
+          <t>17-02-2026 16:21:11</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
@@ -3308,7 +3304,7 @@
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W21" t="inlineStr">
@@ -3318,11 +3314,19 @@
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>26150522011860001229</t>
-        </is>
-      </c>
-      <c r="Y21" t="inlineStr"/>
-      <c r="Z21" t="inlineStr"/>
+          <t>26150522433690001818</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>RAUL FELIX VAZQUEZ</t>
+        </is>
+      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>499</t>
@@ -3330,12 +3334,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>Juan Pablo Romero Andrade</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
@@ -3759,12 +3763,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>342823</t>
+          <t>340805</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>20640</t>
+          <t>18623</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -3774,17 +3778,17 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>JESUS ABEL</t>
+          <t>RICARDO</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>VALERIO</t>
+          <t>TAPIA</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>LIMON</t>
+          <t>OLIVO</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -3794,12 +3798,12 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>6531665157</t>
+          <t>6531341539</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>CARRETERA DEL VALLE</t>
+          <t>AV GUERRERO 12</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -3809,20 +3813,24 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>23-07-2004</t>
+          <t>01-04-2000</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>VALERIOJESUS913@GMAIL.COM</t>
+          <t>RICARDITOTAPIA2129@GMAIL.COM</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>10-02-2026 19:05:03</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr"/>
+          <t>03-02-2026 19:10:40</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
       <c r="O25" t="inlineStr">
         <is>
           <t>Forzoso</t>
@@ -3830,27 +3838,27 @@
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>DOMICILIADO 12 MESES $549 LE</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>10-02-2026 19:09:25</t>
+          <t>03-02-2026 19:13:30</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>10-03-2026 23:59:59</t>
+          <t>03-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>10-02-2026 19:08:45</t>
+          <t>03-02-2026 19:12:47</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
@@ -3860,7 +3868,7 @@
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W25" t="inlineStr">
@@ -3870,19 +3878,19 @@
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>26150522245980001553</t>
+          <t>26150522055450001315</t>
         </is>
       </c>
       <c r="Y25" t="inlineStr"/>
       <c r="Z25" t="inlineStr"/>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>Johan Osvaldo Beltran Quiros</t>
+          <t>Martin Ramiro Quiñonez Jauregui</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
@@ -3894,12 +3902,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>340765</t>
+          <t>343341</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>18583</t>
+          <t>21158</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -3909,17 +3917,17 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VIVIANA</t>
+          <t>JUAN OMAR</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>ARVAYO</t>
+          <t>REYES</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>RASCON</t>
+          <t>RIVERA</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -3929,67 +3937,63 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>6531300005</t>
+          <t>6865976498</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t xml:space="preserve">AV COLIMA Y MATAMOROS </t>
+          <t>CJON NICARAGUA 31</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>03-01-1979</t>
+          <t>02-01-1992</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>VIVIARVAYO@GMAIL.COM</t>
+          <t>ELREYES023@GMAIL.COM</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>03-02-2026 18:01:17</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr">
-        <is>
-          <t>Tarifas 2026 LE</t>
-        </is>
-      </c>
+          <t>12-02-2026 17:35:55</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr"/>
       <c r="O26" t="inlineStr">
         <is>
-          <t>No Forzoso</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>PLAN RECURRENTE PAGO INCIAL $1,449 LE</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>1449</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>03-02-2026 18:16:20</t>
+          <t>14-02-2026 10:17:45</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
         <is>
-          <t>03-03-2026 23:59:59</t>
+          <t>14-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>03-02-2026 18:05:39</t>
+          <t>14-02-2026 10:17:11</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
@@ -3999,7 +4003,7 @@
       </c>
       <c r="V26" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W26" t="inlineStr">
@@ -4009,36 +4013,44 @@
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>26150522052430001305</t>
-        </is>
-      </c>
-      <c r="Y26" t="inlineStr"/>
-      <c r="Z26" t="inlineStr"/>
+          <t>26150522345630001701</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>GISSEL ANAHY REYES GERMAN</t>
+        </is>
+      </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>1449</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Juan Pablo Romero Andrade</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>340877</t>
+          <t>342823</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>18695</t>
+          <t>20640</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -4048,17 +4060,17 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>HECTOR ABRAHAM</t>
+          <t>JESUS ABEL</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>OJEDA</t>
+          <t>VALERIO</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>FRANCO</t>
+          <t>LIMON</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -4068,12 +4080,12 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>6532437111</t>
+          <t>6531665157</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>DALIAS 18 Y 19</t>
+          <t>CARRETERA DEL VALLE</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -4083,24 +4095,20 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>08-01-2005</t>
+          <t>23-07-2004</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>ABRAHAM30510@GMAIL.COM</t>
+          <t>VALERIOJESUS913@GMAIL.COM</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>04-02-2026 07:26:12</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr">
-        <is>
-          <t>Tarifas 2026 LE</t>
-        </is>
-      </c>
+          <t>10-02-2026 19:05:03</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr"/>
       <c r="O27" t="inlineStr">
         <is>
           <t>Forzoso</t>
@@ -4108,27 +4116,27 @@
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES $549 LE</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>04-02-2026 07:29:18</t>
+          <t>10-02-2026 19:09:25</t>
         </is>
       </c>
       <c r="S27" t="inlineStr">
         <is>
-          <t>04-03-2026 23:59:59</t>
+          <t>10-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>04-02-2026 07:28:45</t>
+          <t>10-02-2026 19:08:45</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
@@ -4148,19 +4156,19 @@
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>26150522068240001330</t>
+          <t>26150522245980001553</t>
         </is>
       </c>
       <c r="Y27" t="inlineStr"/>
       <c r="Z27" t="inlineStr"/>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>Martin Ramiro Quiñonez Jauregui</t>
+          <t>Johan Osvaldo Beltran Quiros</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
@@ -4581,12 +4589,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>340805</t>
+          <t>340152</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>18623</t>
+          <t>17970</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -4596,17 +4604,17 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>RICARDO</t>
+          <t>MARTHA LIDIA</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>TAPIA</t>
+          <t xml:space="preserve">DURAN </t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>OLIVO</t>
+          <t>CUEN</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -4616,12 +4624,12 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>6531341539</t>
+          <t>6531218668</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>AV GUERRERO 12</t>
+          <t>PRIVADO ROFORMA</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -4631,24 +4639,20 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>01-04-2000</t>
+          <t>06-08-1960</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>RICARDITOTAPIA2129@GMAIL.COM</t>
+          <t>ROMERO.MARTHA50@ICLOUD.COM</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>03-02-2026 19:10:40</t>
-        </is>
-      </c>
-      <c r="N31" t="inlineStr">
-        <is>
-          <t>Tarifas 2026 LE</t>
-        </is>
-      </c>
+          <t>02-02-2026 13:57:36</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr"/>
       <c r="O31" t="inlineStr">
         <is>
           <t>Forzoso</t>
@@ -4656,27 +4660,27 @@
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES $549 LE</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>03-02-2026 19:13:30</t>
+          <t>02-02-2026 14:04:27</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
         <is>
-          <t>03-03-2026 23:59:59</t>
+          <t>02-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>03-02-2026 19:12:47</t>
+          <t>02-02-2026 14:03:30</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
@@ -4696,19 +4700,19 @@
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>26150522055450001315</t>
+          <t>26150522011860001229</t>
         </is>
       </c>
       <c r="Y31" t="inlineStr"/>
       <c r="Z31" t="inlineStr"/>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>Martin Ramiro Quiñonez Jauregui</t>
+          <t>Juan Pablo Romero Andrade</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
@@ -4720,12 +4724,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>342562</t>
+          <t>343637</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>20379</t>
+          <t>21454</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -4735,17 +4739,17 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>AZALEA ZENYACE</t>
+          <t>RICARDO FRANCISCO</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>MORENO</t>
+          <t>LEDESMA</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>CARRIZOZA</t>
+          <t>PEDROZA</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -4755,32 +4759,32 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>6531038421</t>
+          <t>6531121344</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>CJN CHIHUAHUA 23</t>
+          <t>EL CHEQUE 8 S/N</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>23-09-1994</t>
+          <t>07-01-2006</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>ZEN_YACE94LIVE@HOTMAIL.COM</t>
+          <t>RICARDOPZK200@GMAIL.COM</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>10-02-2026 09:19:09</t>
+          <t>14-02-2026 06:48:50</t>
         </is>
       </c>
       <c r="N32" t="inlineStr"/>
@@ -4801,17 +4805,17 @@
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>12-02-2026 18:37:07</t>
+          <t>14-02-2026 08:02:52</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>12-03-2026 23:59:59</t>
+          <t>15-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>12-02-2026 18:33:55</t>
+          <t>14-02-2026 08:01:46</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
@@ -4831,7 +4835,7 @@
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>26150522302860001640</t>
+          <t>26150522343510001694</t>
         </is>
       </c>
       <c r="Y32" t="inlineStr">
@@ -4851,7 +4855,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>Juan Pablo Romero Andrade</t>
+          <t>Johan Osvaldo Beltran Quiros</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
@@ -4863,12 +4867,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>343341</t>
+          <t>342867</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>21158</t>
+          <t>20684</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -4878,17 +4882,17 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>JUAN OMAR</t>
+          <t>MIGUEL ANGEL</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>REYES</t>
+          <t>AMEZCUA</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>RIVERA</t>
+          <t>TORRES</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -4898,12 +4902,12 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>6865976498</t>
+          <t>6674708281</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>CJON NICARAGUA 31</t>
+          <t>FLORES 22</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -4913,17 +4917,17 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>02-01-1992</t>
+          <t>21-11-1995</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>ELREYES023@GMAIL.COM</t>
+          <t>MIGUELAMEZCUA21@GMAIL.COM</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>12-02-2026 17:35:55</t>
+          <t>10-02-2026 20:37:24</t>
         </is>
       </c>
       <c r="N33" t="inlineStr"/>
@@ -4944,17 +4948,17 @@
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>14-02-2026 10:17:45</t>
+          <t>12-02-2026 20:00:11</t>
         </is>
       </c>
       <c r="S33" t="inlineStr">
         <is>
-          <t>14-03-2026 23:59:59</t>
+          <t>12-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>14-02-2026 10:17:11</t>
+          <t>12-02-2026 19:59:09</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
@@ -4964,7 +4968,7 @@
       </c>
       <c r="V33" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W33" t="inlineStr">
@@ -4974,7 +4978,7 @@
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>26150522345630001701</t>
+          <t>26150522305570001650</t>
         </is>
       </c>
       <c r="Y33" t="inlineStr">
@@ -4994,24 +4998,24 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>Juan Pablo Romero Andrade</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>341196</t>
+          <t>342562</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>19014</t>
+          <t>20379</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -5021,17 +5025,17 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>ESMERALDA</t>
+          <t>AZALEA ZENYACE</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>JAVALERA</t>
+          <t>MORENO</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>ALCANTAR</t>
+          <t>CARRIZOZA</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -5041,12 +5045,12 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>6531196345</t>
+          <t>6531038421</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>AV TABASCO 41</t>
+          <t>CJN CHIHUAHUA 23</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -5056,17 +5060,17 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>19-03-1975</t>
+          <t>23-09-1994</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>ESMERALDA.JAVALERA@HOTMAIL.COM</t>
+          <t>ZEN_YACE94LIVE@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>04-02-2026 21:09:01</t>
+          <t>10-02-2026 09:19:09</t>
         </is>
       </c>
       <c r="N34" t="inlineStr"/>
@@ -5087,17 +5091,17 @@
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>11-02-2026 15:06:43</t>
+          <t>12-02-2026 18:37:07</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
         <is>
-          <t>11-03-2026 23:59:59</t>
+          <t>12-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>11-02-2026 15:05:40</t>
+          <t>12-02-2026 18:33:55</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
@@ -5117,7 +5121,7 @@
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>26150522265920001586</t>
+          <t>26150522302860001640</t>
         </is>
       </c>
       <c r="Y34" t="inlineStr">
@@ -5127,7 +5131,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>GISSEL ANAHY REYES GERMAN</t>
+          <t>RAUL FELIX VAZQUEZ</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -5137,7 +5141,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>Juan Eduardo Torres Alcantar</t>
+          <t>Juan Pablo Romero Andrade</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
@@ -5149,12 +5153,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>341271</t>
+          <t>344062</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>19089</t>
+          <t>21879</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -5164,17 +5168,17 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NICOLLE</t>
+          <t>RAYMUNDO ISRAEL</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>BUSTAMANTE</t>
+          <t>LOPEZ</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>ELIZONDO</t>
+          <t>ARREOLA</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -5184,75 +5188,67 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>6381121777</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>LOS ADOBES</t>
-        </is>
-      </c>
+          <t>6442276514</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
       <c r="J35" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>15-12-1997</t>
+          <t>21-05-2010</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>NICOLLE.BUSTAMANTE@UABC.EDU.MX</t>
+          <t>RL25090288@BACHILLERESDESONORA.EDU.MX</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>05-02-2026 10:43:03</t>
-        </is>
-      </c>
-      <c r="N35" t="inlineStr"/>
+          <t>16-02-2026 13:12:33</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>11-02-2026 13:33:23</t>
+          <t>16-02-2026 13:13:37</t>
         </is>
       </c>
       <c r="S35" t="inlineStr">
         <is>
-          <t>11-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T35" t="inlineStr">
-        <is>
-          <t>11-02-2026 13:31:59</t>
-        </is>
-      </c>
+          <t>16-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T35" t="inlineStr"/>
       <c r="U35" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V35" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="V35" t="inlineStr"/>
       <c r="W35" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -5260,22 +5256,14 @@
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>26150522264110001579</t>
-        </is>
-      </c>
-      <c r="Y35" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>RAUL FELIX VAZQUEZ</t>
-        </is>
-      </c>
+          <t>26150522388250001746</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr"/>
+      <c r="Z35" t="inlineStr"/>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB35" t="inlineStr">
@@ -5292,12 +5280,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>343837</t>
+          <t>341196</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>21654</t>
+          <t>19014</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -5307,17 +5295,17 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>CLAUDIA GABRIELA</t>
+          <t>ESMERALDA</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>ROGEL</t>
+          <t>JAVALERA</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>SANDOVAL</t>
+          <t>ALCANTAR</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -5327,12 +5315,12 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>6532075902</t>
+          <t>6531196345</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>HUERTAS 7</t>
+          <t>AV TABASCO 41</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -5342,17 +5330,17 @@
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>09-12-1991</t>
+          <t>19-03-1975</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>ROGELCLAUDIA266@GMAIL.COM</t>
+          <t>ESMERALDA.JAVALERA@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>15-02-2026 12:34:47</t>
+          <t>04-02-2026 21:09:01</t>
         </is>
       </c>
       <c r="N36" t="inlineStr"/>
@@ -5373,17 +5361,17 @@
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>15-02-2026 12:38:45</t>
+          <t>11-02-2026 15:06:43</t>
         </is>
       </c>
       <c r="S36" t="inlineStr">
         <is>
-          <t>15-03-2026 23:59:59</t>
+          <t>11-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>15-02-2026 12:37:38</t>
+          <t>11-02-2026 15:05:40</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
@@ -5403,11 +5391,19 @@
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>26150522365800001718</t>
-        </is>
-      </c>
-      <c r="Y36" t="inlineStr"/>
-      <c r="Z36" t="inlineStr"/>
+          <t>26150522265920001586</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>GISSEL ANAHY REYES GERMAN</t>
+        </is>
+      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>499</t>
@@ -5415,7 +5411,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>Juan Pablo Romero Andrade</t>
+          <t>Juan Eduardo Torres Alcantar</t>
         </is>
       </c>
       <c r="AC36" t="inlineStr">
@@ -5427,12 +5423,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>342867</t>
+          <t>341271</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>20684</t>
+          <t>19089</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -5442,17 +5438,17 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>MIGUEL ANGEL</t>
+          <t>NICOLLE</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AMEZCUA</t>
+          <t>BUSTAMANTE</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>TORRES</t>
+          <t>ELIZONDO</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -5462,32 +5458,32 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>6674708281</t>
+          <t>6381121777</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>FLORES 22</t>
+          <t>LOS ADOBES</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>21-11-1995</t>
+          <t>15-12-1997</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>MIGUELAMEZCUA21@GMAIL.COM</t>
+          <t>NICOLLE.BUSTAMANTE@UABC.EDU.MX</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>10-02-2026 20:37:24</t>
+          <t>05-02-2026 10:43:03</t>
         </is>
       </c>
       <c r="N37" t="inlineStr"/>
@@ -5508,17 +5504,17 @@
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>12-02-2026 20:00:11</t>
+          <t>11-02-2026 13:33:23</t>
         </is>
       </c>
       <c r="S37" t="inlineStr">
         <is>
-          <t>12-03-2026 23:59:59</t>
+          <t>11-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>12-02-2026 19:59:09</t>
+          <t>11-02-2026 13:31:59</t>
         </is>
       </c>
       <c r="U37" t="inlineStr">
@@ -5528,7 +5524,7 @@
       </c>
       <c r="V37" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W37" t="inlineStr">
@@ -5538,7 +5534,7 @@
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>26150522305570001650</t>
+          <t>26150522264110001579</t>
         </is>
       </c>
       <c r="Y37" t="inlineStr">
@@ -5548,7 +5544,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>GISSEL ANAHY REYES GERMAN</t>
+          <t>RAUL FELIX VAZQUEZ</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -5558,24 +5554,24 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Juan Pablo Romero Andrade</t>
         </is>
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>340779</t>
+          <t>343837</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>18597</t>
+          <t>21654</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -5585,17 +5581,17 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>CLAUDIA ITZEL</t>
+          <t>CLAUDIA GABRIELA</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t xml:space="preserve">DE LA ROSA </t>
+          <t>ROGEL</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>SANCHEZ</t>
+          <t>SANDOVAL</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -5605,10 +5601,14 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>6642467640</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr"/>
+          <t>6532075902</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>HUERTAS 7</t>
+        </is>
+      </c>
       <c r="J38" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -5616,56 +5616,60 @@
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>21-11-1988</t>
+          <t>09-12-1991</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>ITZELT.DELAROSA@GMAIL.COM</t>
+          <t>ROGELCLAUDIA266@GMAIL.COM</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>03-02-2026 18:20:07</t>
-        </is>
-      </c>
-      <c r="N38" t="inlineStr">
-        <is>
-          <t>Tarifas 2026 LE</t>
-        </is>
-      </c>
+          <t>15-02-2026 12:34:47</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr"/>
       <c r="O38" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>14-02-2026 12:53:49</t>
+          <t>15-02-2026 12:38:45</t>
         </is>
       </c>
       <c r="S38" t="inlineStr">
         <is>
-          <t>14-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T38" t="inlineStr"/>
+          <t>15-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>15-02-2026 12:37:38</t>
+        </is>
+      </c>
       <c r="U38" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V38" t="inlineStr"/>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W38" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -5673,40 +5677,36 @@
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>26140522348900001443</t>
-        </is>
-      </c>
-      <c r="Y38" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
+          <t>26150522365800001718</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr"/>
       <c r="Z38" t="inlineStr"/>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Juan Pablo Romero Andrade</t>
         </is>
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>343637</t>
+          <t>340765</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>21454</t>
+          <t>18583</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -5716,17 +5716,17 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>RICARDO FRANCISCO</t>
+          <t>VIVIANA</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>LEDESMA</t>
+          <t>ARVAYO</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>PEDROZA</t>
+          <t>RASCON</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -5736,63 +5736,67 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>6531121344</t>
+          <t>6531300005</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>EL CHEQUE 8 S/N</t>
+          <t xml:space="preserve">AV COLIMA Y MATAMOROS </t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>07-01-2006</t>
+          <t>03-01-1979</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>RICARDOPZK200@GMAIL.COM</t>
+          <t>VIVIARVAYO@GMAIL.COM</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>14-02-2026 06:48:50</t>
-        </is>
-      </c>
-      <c r="N39" t="inlineStr"/>
+          <t>03-02-2026 18:01:17</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>No Forzoso</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>PLAN RECURRENTE PAGO INCIAL $1,449 LE</t>
         </is>
       </c>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>1449</t>
         </is>
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>14-02-2026 08:02:52</t>
+          <t>03-02-2026 18:16:20</t>
         </is>
       </c>
       <c r="S39" t="inlineStr">
         <is>
-          <t>15-03-2026 23:59:59</t>
+          <t>03-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T39" t="inlineStr">
         <is>
-          <t>14-02-2026 08:01:46</t>
+          <t>03-02-2026 18:05:39</t>
         </is>
       </c>
       <c r="U39" t="inlineStr">
@@ -5812,44 +5816,36 @@
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>26150522343510001694</t>
-        </is>
-      </c>
-      <c r="Y39" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z39" t="inlineStr">
-        <is>
-          <t>RAUL FELIX VAZQUEZ</t>
-        </is>
-      </c>
+          <t>26150522052430001305</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr"/>
+      <c r="Z39" t="inlineStr"/>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>1449</t>
         </is>
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>Johan Osvaldo Beltran Quiros</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>343954</t>
+          <t>340877</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>21771</t>
+          <t>18695</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -5859,17 +5855,17 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LOURDES</t>
+          <t>HECTOR ABRAHAM</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>LOPEZ</t>
+          <t>OJEDA</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>SANCHEZ</t>
+          <t>FRANCO</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -5879,37 +5875,37 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>6531035239</t>
+          <t>6532437111</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>C 5 DE MAYO SN</t>
+          <t>DALIAS 18 Y 19</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>10-01-1986</t>
+          <t>08-01-2005</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>LULISLOPEZ999@GMAIL.COM</t>
+          <t>ABRAHAM30510@GMAIL.COM</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>16-02-2026 07:40:00</t>
+          <t>04-02-2026 07:26:12</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>inscripcion promo 199</t>
+          <t>Tarifas 2026 LE</t>
         </is>
       </c>
       <c r="O40" t="inlineStr">
@@ -5919,27 +5915,27 @@
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>DOMICILIADO 12 MESES $549 LE</t>
         </is>
       </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>16-02-2026 07:43:57</t>
+          <t>04-02-2026 07:29:18</t>
         </is>
       </c>
       <c r="S40" t="inlineStr">
         <is>
-          <t>16-03-2026 23:59:59</t>
+          <t>04-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T40" t="inlineStr">
         <is>
-          <t>16-02-2026 07:43:12</t>
+          <t>04-02-2026 07:28:45</t>
         </is>
       </c>
       <c r="U40" t="inlineStr">
@@ -5959,19 +5955,19 @@
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>26150522379670001736</t>
+          <t>26150522068240001330</t>
         </is>
       </c>
       <c r="Y40" t="inlineStr"/>
       <c r="Z40" t="inlineStr"/>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>Juan Eduardo Torres Alcantar</t>
+          <t>Martin Ramiro Quiñonez Jauregui</t>
         </is>
       </c>
       <c r="AC40" t="inlineStr">
@@ -5983,12 +5979,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>344220</t>
+          <t>340779</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>22037</t>
+          <t>18597</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -5998,17 +5994,17 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>CAROLINA</t>
+          <t>CLAUDIA ITZEL</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>FERNANDEZ</t>
+          <t xml:space="preserve">DE LA ROSA </t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>GUTIERREZ</t>
+          <t>SANCHEZ</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -6018,14 +6014,10 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>6531610904</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>CJON COLIMA 17 Y 18</t>
-        </is>
-      </c>
+          <t>6642467640</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
       <c r="J41" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -6033,64 +6025,56 @@
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>21-01-2003</t>
+          <t>21-11-1988</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>LINA_FDZ@ICLOUD.COM</t>
+          <t>ITZELT.DELAROSA@GMAIL.COM</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>16-02-2026 17:36:28</t>
+          <t>03-02-2026 18:20:07</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>inscripcion promo 199</t>
+          <t>Tarifas 2026 LE</t>
         </is>
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>21-02-2026 06:49:41</t>
+          <t>14-02-2026 12:53:49</t>
         </is>
       </c>
       <c r="S41" t="inlineStr">
         <is>
-          <t>21-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T41" t="inlineStr">
-        <is>
-          <t>21-02-2026 06:48:42</t>
-        </is>
-      </c>
+          <t>14-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T41" t="inlineStr"/>
       <c r="U41" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V41" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="V41" t="inlineStr"/>
       <c r="W41" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -6098,14 +6082,18 @@
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>26150522547830001961</t>
-        </is>
-      </c>
-      <c r="Y41" t="inlineStr"/>
+          <t>26140522348900001443</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
       <c r="Z41" t="inlineStr"/>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB41" t="inlineStr">
@@ -6122,12 +6110,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>341212</t>
+          <t>344605</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>19030</t>
+          <t>22422</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -6137,87 +6125,99 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t xml:space="preserve">YAHIR </t>
+          <t>LIZET</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t xml:space="preserve">SALGADO </t>
+          <t>HERNANDEZ</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>COVARRUBIAS</t>
+          <t>MENDEZ</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>6531128435</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr"/>
+          <t>5412729355</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>JALAPA B 5</t>
+        </is>
+      </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>21-08-2004</t>
+          <t>06-06-1998</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>YAHIRSALGADO021@GMAIL.COM</t>
+          <t>ALONDRAML1998@GMAIL.COM</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>05-02-2026 05:58:43</t>
+          <t>17-02-2026 17:23:47</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>Tarifas 2026 LE</t>
+          <t>inscripcion promo 199</t>
         </is>
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>05-02-2026 06:04:50</t>
+          <t>17-02-2026 17:32:20</t>
         </is>
       </c>
       <c r="S42" t="inlineStr">
         <is>
-          <t>05-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T42" t="inlineStr"/>
+          <t>17-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>17-02-2026 17:31:40</t>
+        </is>
+      </c>
       <c r="U42" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V42" t="inlineStr"/>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W42" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -6225,36 +6225,36 @@
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>26150522098340001363</t>
+          <t>26150522437780001826</t>
         </is>
       </c>
       <c r="Y42" t="inlineStr"/>
       <c r="Z42" t="inlineStr"/>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>Juan Eduardo Torres Alcantar</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>344062</t>
+          <t>343954</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>21879</t>
+          <t>21771</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -6264,7 +6264,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>RAYMUNDO ISRAEL</t>
+          <t>LOURDES</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -6274,7 +6274,7 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>ARREOLA</t>
+          <t>SANCHEZ</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -6284,53 +6284,57 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>6442276514</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr"/>
+          <t>6531035239</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>C 5 DE MAYO SN</t>
+        </is>
+      </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>21-05-2010</t>
+          <t>10-01-1986</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>RL25090288@BACHILLERESDESONORA.EDU.MX</t>
+          <t>LULISLOPEZ999@GMAIL.COM</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>16-02-2026 13:12:33</t>
+          <t>16-02-2026 07:40:00</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>Tarifas 2026 LE</t>
+          <t>inscripcion promo 199</t>
         </is>
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R43" t="inlineStr">
         <is>
-          <t>16-02-2026 13:13:37</t>
+          <t>16-02-2026 07:43:57</t>
         </is>
       </c>
       <c r="S43" t="inlineStr">
@@ -6338,13 +6342,21 @@
           <t>16-03-2026 23:59:59</t>
         </is>
       </c>
-      <c r="T43" t="inlineStr"/>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>16-02-2026 07:43:12</t>
+        </is>
+      </c>
       <c r="U43" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V43" t="inlineStr"/>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W43" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -6352,19 +6364,19 @@
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>26150522388250001746</t>
+          <t>26150522379670001736</t>
         </is>
       </c>
       <c r="Y43" t="inlineStr"/>
       <c r="Z43" t="inlineStr"/>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>Juan Pablo Romero Andrade</t>
+          <t>Juan Eduardo Torres Alcantar</t>
         </is>
       </c>
       <c r="AC43" t="inlineStr">
@@ -6376,12 +6388,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>343947</t>
+          <t>341212</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>21764</t>
+          <t>19030</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -6391,17 +6403,17 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t xml:space="preserve">FABIOLA </t>
+          <t xml:space="preserve">YAHIR </t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>LUQUE</t>
+          <t xml:space="preserve">SALGADO </t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>LUQUE</t>
+          <t>COVARRUBIAS</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -6411,79 +6423,67 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>6531273238</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>AV CANADA Y 3RA</t>
-        </is>
-      </c>
+          <t>6531128435</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
       <c r="J44" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>05-04-1986</t>
+          <t>21-08-2004</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>FABIOLALUQUE26@GMAIL.COM</t>
+          <t>YAHIRSALGADO021@GMAIL.COM</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>16-02-2026 07:08:47</t>
+          <t>05-02-2026 05:58:43</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>inscripcion promo 199</t>
+          <t>Tarifas 2026 LE</t>
         </is>
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q44" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R44" t="inlineStr">
         <is>
-          <t>19-02-2026 07:17:57</t>
+          <t>05-02-2026 06:04:50</t>
         </is>
       </c>
       <c r="S44" t="inlineStr">
         <is>
-          <t>19-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T44" t="inlineStr">
-        <is>
-          <t>19-02-2026 07:16:55</t>
-        </is>
-      </c>
+          <t>05-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T44" t="inlineStr"/>
       <c r="U44" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V44" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="V44" t="inlineStr"/>
       <c r="W44" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -6491,27 +6491,19 @@
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>26150522487880001902</t>
-        </is>
-      </c>
-      <c r="Y44" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z44" t="inlineStr">
-        <is>
-          <t>RAUL FELIX VAZQUEZ</t>
-        </is>
-      </c>
+          <t>26150522098340001363</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr"/>
+      <c r="Z44" t="inlineStr"/>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>Martin Ramiro Quiñonez Jauregui</t>
+          <t>Juan Eduardo Torres Alcantar</t>
         </is>
       </c>
       <c r="AC44" t="inlineStr">
@@ -6523,12 +6515,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>341270</t>
+          <t>343947</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>19088</t>
+          <t>21764</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -6538,17 +6530,17 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>JUAN MANUEL</t>
+          <t xml:space="preserve">FABIOLA </t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>ALONZO</t>
+          <t>LUQUE</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>ARZATE</t>
+          <t>LUQUE</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -6558,35 +6550,39 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>6161093843</t>
+          <t>6531273238</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>FRACC ADOBES 75</t>
+          <t>AV CANADA Y 3RA</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>14-02-1995</t>
+          <t>05-04-1986</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>JUANM_1495@HOTMAIL.COM</t>
+          <t>FABIOLALUQUE26@GMAIL.COM</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>05-02-2026 10:41:41</t>
-        </is>
-      </c>
-      <c r="N45" t="inlineStr"/>
+          <t>16-02-2026 07:08:47</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>inscripcion promo 199</t>
+        </is>
+      </c>
       <c r="O45" t="inlineStr">
         <is>
           <t>Forzoso</t>
@@ -6604,17 +6600,17 @@
       </c>
       <c r="R45" t="inlineStr">
         <is>
-          <t>11-02-2026 13:27:47</t>
+          <t>19-02-2026 07:17:57</t>
         </is>
       </c>
       <c r="S45" t="inlineStr">
         <is>
-          <t>11-03-2026 23:59:59</t>
+          <t>19-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T45" t="inlineStr">
         <is>
-          <t>11-02-2026 13:26:38</t>
+          <t>19-02-2026 07:16:55</t>
         </is>
       </c>
       <c r="U45" t="inlineStr">
@@ -6624,7 +6620,7 @@
       </c>
       <c r="V45" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W45" t="inlineStr">
@@ -6634,7 +6630,7 @@
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>26150522264040001578</t>
+          <t>26150522487880001902</t>
         </is>
       </c>
       <c r="Y45" t="inlineStr">
@@ -6654,7 +6650,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>Juan Pablo Romero Andrade</t>
+          <t>Martin Ramiro Quiñonez Jauregui</t>
         </is>
       </c>
       <c r="AC45" t="inlineStr">
@@ -6666,12 +6662,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>344605</t>
+          <t>344220</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>22422</t>
+          <t>22037</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -6681,32 +6677,32 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LIZET</t>
+          <t>CAROLINA</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>HERNANDEZ</t>
+          <t>FERNANDEZ</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>MENDEZ</t>
+          <t>GUTIERREZ</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>52</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>5412729355</t>
+          <t>6531610904</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>JALAPA B 5</t>
+          <t>CJON COLIMA 17 Y 18</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -6716,17 +6712,17 @@
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>06-06-1998</t>
+          <t>21-01-2003</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>ALONDRAML1998@GMAIL.COM</t>
+          <t>LINA_FDZ@ICLOUD.COM</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>17-02-2026 17:23:47</t>
+          <t>16-02-2026 17:36:28</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
@@ -6751,17 +6747,17 @@
       </c>
       <c r="R46" t="inlineStr">
         <is>
-          <t>17-02-2026 17:32:20</t>
+          <t>21-02-2026 06:49:41</t>
         </is>
       </c>
       <c r="S46" t="inlineStr">
         <is>
-          <t>17-03-2026 23:59:59</t>
+          <t>21-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T46" t="inlineStr">
         <is>
-          <t>17-02-2026 17:31:40</t>
+          <t>21-02-2026 06:48:42</t>
         </is>
       </c>
       <c r="U46" t="inlineStr">
@@ -6771,7 +6767,7 @@
       </c>
       <c r="V46" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W46" t="inlineStr">
@@ -6781,7 +6777,7 @@
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>26150522437780001826</t>
+          <t>26150522547830001961</t>
         </is>
       </c>
       <c r="Y46" t="inlineStr"/>
@@ -6944,12 +6940,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>342261</t>
+          <t>341270</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>20079</t>
+          <t>19088</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -6959,17 +6955,17 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t xml:space="preserve">VICTORIA </t>
+          <t>JUAN MANUEL</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t xml:space="preserve">ZAVALA </t>
+          <t>ALONZO</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>BARRIENTOS</t>
+          <t>ARZATE</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -6979,39 +6975,35 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>6531231721</t>
+          <t>6161093843</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t xml:space="preserve">HACIENDA DE LA CRUZ </t>
+          <t>FRACC ADOBES 75</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>04-04-1996</t>
+          <t>14-02-1995</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>GUADALUPEZAVALAMERCADO@HOTMAIL.COM</t>
+          <t>JUANM_1495@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>09-02-2026 16:34:55</t>
-        </is>
-      </c>
-      <c r="N48" t="inlineStr">
-        <is>
-          <t>Tarifas 2026 LE</t>
-        </is>
-      </c>
+          <t>05-02-2026 10:41:41</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr"/>
       <c r="O48" t="inlineStr">
         <is>
           <t>Forzoso</t>
@@ -7019,27 +7011,27 @@
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES $549 LE</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q48" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R48" t="inlineStr">
         <is>
-          <t>09-02-2026 16:37:21</t>
+          <t>11-02-2026 13:27:47</t>
         </is>
       </c>
       <c r="S48" t="inlineStr">
         <is>
-          <t>09-03-2026 23:59:59</t>
+          <t>11-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T48" t="inlineStr">
         <is>
-          <t>09-02-2026 16:36:34</t>
+          <t>11-02-2026 13:26:38</t>
         </is>
       </c>
       <c r="U48" t="inlineStr">
@@ -7059,19 +7051,27 @@
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>26150522198880001489</t>
-        </is>
-      </c>
-      <c r="Y48" t="inlineStr"/>
-      <c r="Z48" t="inlineStr"/>
+          <t>26150522264040001578</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>RAUL FELIX VAZQUEZ</t>
+        </is>
+      </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>Johan Osvaldo Beltran Quiros</t>
+          <t>Juan Pablo Romero Andrade</t>
         </is>
       </c>
       <c r="AC48" t="inlineStr">
@@ -7083,12 +7083,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>342499</t>
+          <t>342261</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>20316</t>
+          <t>20079</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -7098,17 +7098,17 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>ALBERTO</t>
+          <t xml:space="preserve">VICTORIA </t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>VINIEGRA</t>
+          <t xml:space="preserve">ZAVALA </t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>BERMUDEZ</t>
+          <t>BARRIENTOS</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -7118,35 +7118,39 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>6532096000</t>
+          <t>6531231721</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>COLIMA C 26</t>
+          <t xml:space="preserve">HACIENDA DE LA CRUZ </t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>20-05-1981</t>
+          <t>04-04-1996</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>VIVESISTEMS@GMAIL.COM</t>
+          <t>GUADALUPEZAVALAMERCADO@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>09-02-2026 21:13:12</t>
-        </is>
-      </c>
-      <c r="N49" t="inlineStr"/>
+          <t>09-02-2026 16:34:55</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
       <c r="O49" t="inlineStr">
         <is>
           <t>Forzoso</t>
@@ -7154,27 +7158,27 @@
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>DOMICILIADO 12 MESES $549 LE</t>
         </is>
       </c>
       <c r="Q49" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R49" t="inlineStr">
         <is>
-          <t>11-02-2026 21:02:27</t>
+          <t>09-02-2026 16:37:21</t>
         </is>
       </c>
       <c r="S49" t="inlineStr">
         <is>
-          <t>11-03-2026 23:59:59</t>
+          <t>09-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T49" t="inlineStr">
         <is>
-          <t>11-02-2026 21:01:55</t>
+          <t>09-02-2026 16:36:34</t>
         </is>
       </c>
       <c r="U49" t="inlineStr">
@@ -7184,7 +7188,7 @@
       </c>
       <c r="V49" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W49" t="inlineStr">
@@ -7194,27 +7198,19 @@
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>26150522279160001614</t>
-        </is>
-      </c>
-      <c r="Y49" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z49" t="inlineStr">
-        <is>
-          <t>GISSEL ANAHY REYES GERMAN</t>
-        </is>
-      </c>
+          <t>26150522198880001489</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr"/>
+      <c r="Z49" t="inlineStr"/>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>Juan Pablo Romero Andrade</t>
+          <t>Johan Osvaldo Beltran Quiros</t>
         </is>
       </c>
       <c r="AC49" t="inlineStr">
@@ -7226,12 +7222,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>342548</t>
+          <t>345080</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>20365</t>
+          <t>87245</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -7241,17 +7237,17 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>CECILIA GUADALUPE</t>
+          <t>LIZBETH</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>CORRAL</t>
+          <t>MARTINEZ</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>MEDINA</t>
+          <t>MEJIA</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -7261,14 +7257,10 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>6621711231</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>JUAREZ Y 20</t>
-        </is>
-      </c>
+          <t>6532094330</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
       <c r="J50" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -7276,17 +7268,17 @@
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>06-08-1998</t>
+          <t>01-04-2009</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>CECIGPE98@GMAIL.COM</t>
+          <t>LIZBETHMARTINEZMEJIAMX@GMAIL.COM</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>10-02-2026 08:25:29</t>
+          <t>19-02-2026 14:44:45</t>
         </is>
       </c>
       <c r="N50" t="inlineStr">
@@ -7296,44 +7288,36 @@
       </c>
       <c r="O50" t="inlineStr">
         <is>
-          <t>No Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>RECURRENTE $649 LE</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q50" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R50" t="inlineStr">
         <is>
-          <t>10-02-2026 08:31:37</t>
+          <t>19-02-2026 14:46:32</t>
         </is>
       </c>
       <c r="S50" t="inlineStr">
         <is>
-          <t>10-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T50" t="inlineStr">
-        <is>
-          <t>10-02-2026 08:30:41</t>
-        </is>
-      </c>
+          <t>19-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T50" t="inlineStr"/>
       <c r="U50" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V50" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="V50" t="inlineStr"/>
       <c r="W50" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -7341,36 +7325,36 @@
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>26150522225760001528</t>
+          <t>26150522495630001914</t>
         </is>
       </c>
       <c r="Y50" t="inlineStr"/>
       <c r="Z50" t="inlineStr"/>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>Juan Eduardo Torres Alcantar</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>345080</t>
+          <t>342512</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>87245</t>
+          <t>20329</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -7380,17 +7364,17 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LIZBETH</t>
+          <t>JOSE RICARDO</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>MARTINEZ</t>
+          <t>GARCIA</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>MEJIA</t>
+          <t>ANGULO</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -7400,28 +7384,32 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>6532094330</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr"/>
+          <t>6531217599</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>CJON HIDALGO Y 47</t>
+        </is>
+      </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>01-04-2009</t>
+          <t>03-04-1976</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>LIZBETHMARTINEZMEJIAMX@GMAIL.COM</t>
+          <t>RRICARDOGARCIA34@ICLOUD.COM</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>19-02-2026 14:44:45</t>
+          <t>10-02-2026 05:34:48</t>
         </is>
       </c>
       <c r="N51" t="inlineStr">
@@ -7431,36 +7419,44 @@
       </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>No Forzoso</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>RECURRENTE $649 LE</t>
         </is>
       </c>
       <c r="Q51" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>649</t>
         </is>
       </c>
       <c r="R51" t="inlineStr">
         <is>
-          <t>19-02-2026 14:46:32</t>
+          <t>11-02-2026 06:33:27</t>
         </is>
       </c>
       <c r="S51" t="inlineStr">
         <is>
-          <t>19-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T51" t="inlineStr"/>
+          <t>11-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>11-02-2026 06:32:18</t>
+        </is>
+      </c>
       <c r="U51" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V51" t="inlineStr"/>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W51" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -7468,36 +7464,44 @@
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>26150522495630001914</t>
-        </is>
-      </c>
-      <c r="Y51" t="inlineStr"/>
-      <c r="Z51" t="inlineStr"/>
+          <t>26150522257790001574</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>RAUL FELIX VAZQUEZ</t>
+        </is>
+      </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>649</t>
         </is>
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Juan Eduardo Torres Alcantar</t>
         </is>
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>342512</t>
+          <t>344190</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>20329</t>
+          <t>22007</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -7507,7 +7511,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>JOSE RICARDO</t>
+          <t xml:space="preserve">SEBASTIAN </t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -7517,7 +7521,7 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>ANGULO</t>
+          <t>GUERRERO</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -7527,14 +7531,10 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>6531217599</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>CJON HIDALGO Y 47</t>
-        </is>
-      </c>
+          <t>6531058427</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
       <c r="J52" t="inlineStr">
         <is>
           <t>Masculino</t>
@@ -7542,17 +7542,17 @@
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>03-04-1976</t>
+          <t>21-10-2009</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>RRICARDOGARCIA34@ICLOUD.COM</t>
+          <t>MONKEEX424@GMAIL.COM</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>10-02-2026 05:34:48</t>
+          <t>16-02-2026 17:04:57</t>
         </is>
       </c>
       <c r="N52" t="inlineStr">
@@ -7562,44 +7562,36 @@
       </c>
       <c r="O52" t="inlineStr">
         <is>
-          <t>No Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>RECURRENTE $649 LE</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q52" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R52" t="inlineStr">
         <is>
-          <t>11-02-2026 06:33:27</t>
+          <t>18-02-2026 17:05:10</t>
         </is>
       </c>
       <c r="S52" t="inlineStr">
         <is>
-          <t>11-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T52" t="inlineStr">
-        <is>
-          <t>11-02-2026 06:32:18</t>
-        </is>
-      </c>
+          <t>18-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T52" t="inlineStr"/>
       <c r="U52" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V52" t="inlineStr">
-        <is>
           <t>1</t>
         </is>
       </c>
+      <c r="V52" t="inlineStr"/>
       <c r="W52" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -7607,7 +7599,7 @@
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>26150522257790001574</t>
+          <t>26150522468100001872</t>
         </is>
       </c>
       <c r="Y52" t="inlineStr">
@@ -7617,17 +7609,17 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>RAUL FELIX VAZQUEZ</t>
+          <t>GISSEL ANAHY REYES GERMAN</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>Juan Eduardo Torres Alcantar</t>
+          <t>Juan Pablo Romero Andrade</t>
         </is>
       </c>
       <c r="AC52" t="inlineStr">
@@ -7639,12 +7631,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>344190</t>
+          <t>345697</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>22007</t>
+          <t>87862</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -7654,17 +7646,17 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t xml:space="preserve">SEBASTIAN </t>
+          <t xml:space="preserve">EMMANUEL </t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>GARCIA</t>
+          <t>SUAREZ</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>GUERRERO</t>
+          <t>QUIROGA</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -7674,7 +7666,7 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>6531058427</t>
+          <t>6531748406</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -7685,22 +7677,22 @@
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>21-10-2009</t>
+          <t>05-05-2007</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>MONKEEX424@GMAIL.COM</t>
+          <t>JUANEMANUEL.S.Q@GMAIL.COM</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>16-02-2026 17:04:57</t>
+          <t>23-02-2026 10:30:42</t>
         </is>
       </c>
       <c r="N53" t="inlineStr">
         <is>
-          <t>Tarifas 2026 LE</t>
+          <t>convenio 300</t>
         </is>
       </c>
       <c r="O53" t="inlineStr">
@@ -7720,12 +7712,12 @@
       </c>
       <c r="R53" t="inlineStr">
         <is>
-          <t>18-02-2026 17:05:10</t>
+          <t>23-02-2026 10:34:37</t>
         </is>
       </c>
       <c r="S53" t="inlineStr">
         <is>
-          <t>18-03-2026 23:59:59</t>
+          <t>23-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T53" t="inlineStr"/>
@@ -7742,19 +7734,11 @@
       </c>
       <c r="X53" t="inlineStr">
         <is>
-          <t>26150522468100001872</t>
-        </is>
-      </c>
-      <c r="Y53" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z53" t="inlineStr">
-        <is>
-          <t>GISSEL ANAHY REYES GERMAN</t>
-        </is>
-      </c>
+          <t>26150522576190001992</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr"/>
+      <c r="Z53" t="inlineStr"/>
       <c r="AA53" t="inlineStr">
         <is>
           <t>549</t>
@@ -7774,12 +7758,12 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>342846</t>
+          <t>344844</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>20663</t>
+          <t>22661</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -7789,17 +7773,17 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>CARLOS JULIAN</t>
+          <t>LEONEL</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>NUÑEZ</t>
+          <t>CARRILLO</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>ROMERO</t>
+          <t>ENRIQUEZ</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
@@ -7809,75 +7793,67 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>6531308246</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>TORREON 4 Y 5</t>
-        </is>
-      </c>
+          <t>4494668367</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
       <c r="J54" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>29-08-2000</t>
+          <t>27-01-2010</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>EJNR2E@GMAIL.COM</t>
+          <t>CARRILLO12346@GMAIL.COM</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>10-02-2026 19:39:03</t>
-        </is>
-      </c>
-      <c r="N54" t="inlineStr"/>
+          <t>18-02-2026 15:41:40</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>convenio 300</t>
+        </is>
+      </c>
       <c r="O54" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q54" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R54" t="inlineStr">
         <is>
-          <t>11-02-2026 19:15:15</t>
+          <t>23-02-2026 16:40:49</t>
         </is>
       </c>
       <c r="S54" t="inlineStr">
         <is>
-          <t>11-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T54" t="inlineStr">
-        <is>
-          <t>11-02-2026 19:14:37</t>
-        </is>
-      </c>
+          <t>23-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T54" t="inlineStr"/>
       <c r="U54" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V54" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="V54" t="inlineStr"/>
       <c r="W54" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -7885,7 +7861,7 @@
       </c>
       <c r="X54" t="inlineStr">
         <is>
-          <t>26150522276380001607</t>
+          <t>26150522587950002017</t>
         </is>
       </c>
       <c r="Y54" t="inlineStr">
@@ -7900,29 +7876,29 @@
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>Juan Pablo Romero Andrade</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>342849</t>
+          <t>342828</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>20666</t>
+          <t>20645</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -7932,17 +7908,17 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t xml:space="preserve">PAOLA </t>
+          <t>NUBIA GUADALUPE</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>ALONSO</t>
+          <t>SOLARES</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>MANRIQUEZ</t>
+          <t>ARVIZU</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
@@ -7952,12 +7928,12 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>6535395572</t>
+          <t>6531665151</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>CJN KINO 33</t>
+          <t>CARRETERA DEL VALLE</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
@@ -7967,17 +7943,17 @@
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>13-12-1999</t>
+          <t>27-09-2002</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>PAOLAALONSOMGZ@GMAIL.COM</t>
+          <t>NUBIAG3@ICLOUD.COM</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>10-02-2026 19:41:46</t>
+          <t>10-02-2026 19:11:57</t>
         </is>
       </c>
       <c r="N55" t="inlineStr"/>
@@ -7998,17 +7974,17 @@
       </c>
       <c r="R55" t="inlineStr">
         <is>
-          <t>11-02-2026 19:11:46</t>
+          <t>10-02-2026 19:16:21</t>
         </is>
       </c>
       <c r="S55" t="inlineStr">
         <is>
-          <t>11-03-2026 23:59:59</t>
+          <t>10-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T55" t="inlineStr">
         <is>
-          <t>11-02-2026 19:10:56</t>
+          <t>10-02-2026 19:15:42</t>
         </is>
       </c>
       <c r="U55" t="inlineStr">
@@ -8028,19 +8004,11 @@
       </c>
       <c r="X55" t="inlineStr">
         <is>
-          <t>26150522276280001606</t>
-        </is>
-      </c>
-      <c r="Y55" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z55" t="inlineStr">
-        <is>
-          <t>GISSEL ANAHY REYES GERMAN</t>
-        </is>
-      </c>
+          <t>26150522246290001554</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr"/>
+      <c r="Z55" t="inlineStr"/>
       <c r="AA55" t="inlineStr">
         <is>
           <t>499</t>
@@ -8048,7 +8016,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>Juan Pablo Romero Andrade</t>
+          <t>Johan Osvaldo Beltran Quiros</t>
         </is>
       </c>
       <c r="AC55" t="inlineStr">
@@ -8060,12 +8028,12 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>342828</t>
+          <t>344649</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>20645</t>
+          <t>22466</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -8075,17 +8043,17 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NUBIA GUADALUPE</t>
+          <t>ROSA MARIA</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>SOLARES</t>
+          <t>VALADES</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>ARVIZU</t>
+          <t>SARMIENTO</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
@@ -8095,12 +8063,12 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>6531665151</t>
+          <t>6864265235</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>CARRETERA DEL VALLE</t>
+          <t>AV JACARANDAS 19</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
@@ -8110,20 +8078,24 @@
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>27-09-2002</t>
+          <t>26-10-1989</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>NUBIAG3@ICLOUD.COM</t>
+          <t>GENERICO@GAMIL.COM</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>10-02-2026 19:11:57</t>
-        </is>
-      </c>
-      <c r="N56" t="inlineStr"/>
+          <t>17-02-2026 18:13:05</t>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>inscripcion promo 199</t>
+        </is>
+      </c>
       <c r="O56" t="inlineStr">
         <is>
           <t>Forzoso</t>
@@ -8141,17 +8113,17 @@
       </c>
       <c r="R56" t="inlineStr">
         <is>
-          <t>10-02-2026 19:16:21</t>
+          <t>18-02-2026 19:06:17</t>
         </is>
       </c>
       <c r="S56" t="inlineStr">
         <is>
-          <t>10-03-2026 23:59:59</t>
+          <t>18-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T56" t="inlineStr">
         <is>
-          <t>10-02-2026 19:15:42</t>
+          <t>18-02-2026 19:05:40</t>
         </is>
       </c>
       <c r="U56" t="inlineStr">
@@ -8171,11 +8143,19 @@
       </c>
       <c r="X56" t="inlineStr">
         <is>
-          <t>26150522246290001554</t>
-        </is>
-      </c>
-      <c r="Y56" t="inlineStr"/>
-      <c r="Z56" t="inlineStr"/>
+          <t>26150522474170001890</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z56" t="inlineStr">
+        <is>
+          <t>GISSEL ANAHY REYES GERMAN</t>
+        </is>
+      </c>
       <c r="AA56" t="inlineStr">
         <is>
           <t>499</t>
@@ -8183,24 +8163,24 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>Johan Osvaldo Beltran Quiros</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>344649</t>
+          <t>342499</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>22466</t>
+          <t>20316</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -8210,17 +8190,17 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>ROSA MARIA</t>
+          <t>ALBERTO</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>VALADES</t>
+          <t>VINIEGRA</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>SARMIENTO</t>
+          <t>BERMUDEZ</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -8230,39 +8210,35 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>6864265235</t>
+          <t>6532096000</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>AV JACARANDAS 19</t>
+          <t>COLIMA C 26</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>26-10-1989</t>
+          <t>20-05-1981</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>GENERICO@GAMIL.COM</t>
+          <t>VIVESISTEMS@GMAIL.COM</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>17-02-2026 18:13:05</t>
-        </is>
-      </c>
-      <c r="N57" t="inlineStr">
-        <is>
-          <t>inscripcion promo 199</t>
-        </is>
-      </c>
+          <t>09-02-2026 21:13:12</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr"/>
       <c r="O57" t="inlineStr">
         <is>
           <t>Forzoso</t>
@@ -8280,17 +8256,17 @@
       </c>
       <c r="R57" t="inlineStr">
         <is>
-          <t>18-02-2026 19:06:17</t>
+          <t>11-02-2026 21:02:27</t>
         </is>
       </c>
       <c r="S57" t="inlineStr">
         <is>
-          <t>18-03-2026 23:59:59</t>
+          <t>11-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T57" t="inlineStr">
         <is>
-          <t>18-02-2026 19:05:40</t>
+          <t>11-02-2026 21:01:55</t>
         </is>
       </c>
       <c r="U57" t="inlineStr">
@@ -8310,7 +8286,7 @@
       </c>
       <c r="X57" t="inlineStr">
         <is>
-          <t>26150522474170001890</t>
+          <t>26150522279160001614</t>
         </is>
       </c>
       <c r="Y57" t="inlineStr">
@@ -8330,24 +8306,24 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Juan Pablo Romero Andrade</t>
         </is>
       </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>342866</t>
+          <t>342548</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>20683</t>
+          <t>20365</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -8357,95 +8333,99 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>IAN AXEL</t>
+          <t>CECILIA GUADALUPE</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>SANDOVAL</t>
+          <t>CORRAL</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>TORRES</t>
+          <t>MEDINA</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>6621711231</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>JUAREZ Y 20</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>06-08-1998</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>CECIGPE98@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>10-02-2026 08:25:29</t>
+        </is>
+      </c>
+      <c r="N58" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
+      <c r="O58" t="inlineStr">
+        <is>
+          <t>No Forzoso</t>
+        </is>
+      </c>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>RECURRENTE $649 LE</t>
+        </is>
+      </c>
+      <c r="Q58" t="inlineStr">
+        <is>
+          <t>649</t>
+        </is>
+      </c>
+      <c r="R58" t="inlineStr">
+        <is>
+          <t>10-02-2026 08:31:37</t>
+        </is>
+      </c>
+      <c r="S58" t="inlineStr">
+        <is>
+          <t>10-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>10-02-2026 08:30:41</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="H58" t="inlineStr">
-        <is>
-          <t>9285501740</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>COLIMA C 26</t>
-        </is>
-      </c>
-      <c r="J58" t="inlineStr">
-        <is>
-          <t>Masculino</t>
-        </is>
-      </c>
-      <c r="K58" t="inlineStr">
-        <is>
-          <t>30-08-2010</t>
-        </is>
-      </c>
-      <c r="L58" t="inlineStr">
-        <is>
-          <t>IAN.SANDOVALTO@GMAIL.COM</t>
-        </is>
-      </c>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>10-02-2026 20:35:22</t>
-        </is>
-      </c>
-      <c r="N58" t="inlineStr"/>
-      <c r="O58" t="inlineStr">
-        <is>
-          <t>Forzoso</t>
-        </is>
-      </c>
-      <c r="P58" t="inlineStr">
-        <is>
-          <t>PROMO FEBRERO 12 MESES</t>
-        </is>
-      </c>
-      <c r="Q58" t="inlineStr">
-        <is>
-          <t>499</t>
-        </is>
-      </c>
-      <c r="R58" t="inlineStr">
-        <is>
-          <t>11-02-2026 21:04:30</t>
-        </is>
-      </c>
-      <c r="S58" t="inlineStr">
-        <is>
-          <t>11-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T58" t="inlineStr">
-        <is>
-          <t>11-02-2026 21:03:57</t>
-        </is>
-      </c>
-      <c r="U58" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V58" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="W58" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -8453,27 +8433,19 @@
       </c>
       <c r="X58" t="inlineStr">
         <is>
-          <t>26150522279200001615</t>
-        </is>
-      </c>
-      <c r="Y58" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z58" t="inlineStr">
-        <is>
-          <t>GISSEL ANAHY REYES GERMAN</t>
-        </is>
-      </c>
+          <t>26150522225760001528</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr"/>
+      <c r="Z58" t="inlineStr"/>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>649</t>
         </is>
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>Juan Pablo Romero Andrade</t>
+          <t>Juan Eduardo Torres Alcantar</t>
         </is>
       </c>
       <c r="AC58" t="inlineStr">
@@ -8485,12 +8457,12 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>343958</t>
+          <t>342846</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>21775</t>
+          <t>20663</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -8500,17 +8472,17 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>ELIZABETH</t>
+          <t>CARLOS JULIAN</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>FLORES</t>
+          <t>NUÑEZ</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>HERAS</t>
+          <t>ROMERO</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
@@ -8520,12 +8492,12 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>6531288733</t>
+          <t>6531308246</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>CJON FLORES Y C 16 SN</t>
+          <t>TORREON 4 Y 5</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
@@ -8535,52 +8507,48 @@
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>03-02-1988</t>
+          <t>29-08-2000</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>VICTORIALLAMAS2000@GMEIL.COM</t>
+          <t>EJNR2E@GMAIL.COM</t>
         </is>
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>16-02-2026 07:59:39</t>
-        </is>
-      </c>
-      <c r="N59" t="inlineStr">
-        <is>
-          <t>Tarifas 2026 LE</t>
-        </is>
-      </c>
+          <t>10-02-2026 19:39:03</t>
+        </is>
+      </c>
+      <c r="N59" t="inlineStr"/>
       <c r="O59" t="inlineStr">
         <is>
-          <t>No Forzoso</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>RECURRENTE $649 LE</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q59" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R59" t="inlineStr">
         <is>
-          <t>16-02-2026 08:07:18</t>
+          <t>11-02-2026 19:15:15</t>
         </is>
       </c>
       <c r="S59" t="inlineStr">
         <is>
-          <t>16-03-2026 23:59:59</t>
+          <t>11-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T59" t="inlineStr">
         <is>
-          <t>16-02-2026 08:06:23</t>
+          <t>11-02-2026 19:14:37</t>
         </is>
       </c>
       <c r="U59" t="inlineStr">
@@ -8600,36 +8568,44 @@
       </c>
       <c r="X59" t="inlineStr">
         <is>
-          <t>26150522380380001737</t>
-        </is>
-      </c>
-      <c r="Y59" t="inlineStr"/>
-      <c r="Z59" t="inlineStr"/>
+          <t>26150522276380001607</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z59" t="inlineStr">
+        <is>
+          <t>GISSEL ANAHY REYES GERMAN</t>
+        </is>
+      </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Juan Pablo Romero Andrade</t>
         </is>
       </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>343531</t>
+          <t>342849</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>21348</t>
+          <t>20666</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -8639,17 +8615,17 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>URIEL IGNACIO</t>
+          <t xml:space="preserve">PAOLA </t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>SID</t>
+          <t>ALONSO</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>AREVALO</t>
+          <t>MANRIQUEZ</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
@@ -8659,32 +8635,32 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>6531071848</t>
+          <t>6535395572</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>FELIX CONTRERAS 44</t>
+          <t>CJN KINO 33</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>02-06-2005</t>
+          <t>13-12-1999</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>URIELIGNACIOSIDDAVERALO@GMAIL.COM</t>
+          <t>PAOLAALONSOMGZ@GMAIL.COM</t>
         </is>
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>13-02-2026 16:28:37</t>
+          <t>10-02-2026 19:41:46</t>
         </is>
       </c>
       <c r="N60" t="inlineStr"/>
@@ -8705,17 +8681,17 @@
       </c>
       <c r="R60" t="inlineStr">
         <is>
-          <t>13-02-2026 16:34:53</t>
+          <t>11-02-2026 19:11:46</t>
         </is>
       </c>
       <c r="S60" t="inlineStr">
         <is>
-          <t>13-03-2026 23:59:59</t>
+          <t>11-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T60" t="inlineStr">
         <is>
-          <t>13-02-2026 16:34:13</t>
+          <t>11-02-2026 19:10:56</t>
         </is>
       </c>
       <c r="U60" t="inlineStr">
@@ -8735,11 +8711,19 @@
       </c>
       <c r="X60" t="inlineStr">
         <is>
-          <t>26150522324410001674</t>
-        </is>
-      </c>
-      <c r="Y60" t="inlineStr"/>
-      <c r="Z60" t="inlineStr"/>
+          <t>26150522276280001606</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z60" t="inlineStr">
+        <is>
+          <t>GISSEL ANAHY REYES GERMAN</t>
+        </is>
+      </c>
       <c r="AA60" t="inlineStr">
         <is>
           <t>499</t>
@@ -8759,12 +8743,12 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>343813</t>
+          <t>343958</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>21630</t>
+          <t>21775</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -8774,17 +8758,17 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>YOCELIN DEL CARMEN</t>
+          <t>ELIZABETH</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>LOPEZ</t>
+          <t>FLORES</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>VALENZUELA</t>
+          <t>HERAS</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
@@ -8794,12 +8778,12 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>6531305359</t>
+          <t>6531288733</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>AV CARRANZA 36</t>
+          <t>CJON FLORES Y C 16 SN</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
@@ -8809,48 +8793,52 @@
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>16-07-1999</t>
+          <t>03-02-1988</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>YOCELINLOPEZ490@GMAIL.COM</t>
+          <t>VICTORIALLAMAS2000@GMEIL.COM</t>
         </is>
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>15-02-2026 11:25:12</t>
-        </is>
-      </c>
-      <c r="N61" t="inlineStr"/>
+          <t>16-02-2026 07:59:39</t>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
       <c r="O61" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>No Forzoso</t>
         </is>
       </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>RECURRENTE $649 LE</t>
         </is>
       </c>
       <c r="Q61" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>649</t>
         </is>
       </c>
       <c r="R61" t="inlineStr">
         <is>
-          <t>15-02-2026 11:31:12</t>
+          <t>16-02-2026 08:07:18</t>
         </is>
       </c>
       <c r="S61" t="inlineStr">
         <is>
-          <t>15-03-2026 23:59:59</t>
+          <t>16-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T61" t="inlineStr">
         <is>
-          <t>15-02-2026 11:29:38</t>
+          <t>16-02-2026 08:06:23</t>
         </is>
       </c>
       <c r="U61" t="inlineStr">
@@ -8870,36 +8858,36 @@
       </c>
       <c r="X61" t="inlineStr">
         <is>
-          <t>26150522364500001715</t>
+          <t>26150522380380001737</t>
         </is>
       </c>
       <c r="Y61" t="inlineStr"/>
       <c r="Z61" t="inlineStr"/>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>649</t>
         </is>
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>Juan Pablo Romero Andrade</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC61" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>344583</t>
+          <t>345830</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>22400</t>
+          <t>87995</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -8909,17 +8897,17 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t xml:space="preserve">CARLOS </t>
+          <t>MARIA GUADALUPE</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>ACOSTA</t>
+          <t>HEREDIA</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>SANTOS</t>
+          <t>HERRERA</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
@@ -8929,32 +8917,32 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>6531202025</t>
+          <t>6531742310</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>AV NUEVO LEON 9</t>
+          <t>CANADA B Y SAN ALBERTO</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>04-03-2005</t>
+          <t>22-03-1976</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>TZELI9535@GMAIL.COM</t>
+          <t>HEREDIAHERRERA76@GMAIL.COM</t>
         </is>
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>17-02-2026 16:50:12</t>
+          <t>23-02-2026 15:19:36</t>
         </is>
       </c>
       <c r="N62" t="inlineStr">
@@ -8979,17 +8967,17 @@
       </c>
       <c r="R62" t="inlineStr">
         <is>
-          <t>19-02-2026 17:11:32</t>
+          <t>23-02-2026 15:23:45</t>
         </is>
       </c>
       <c r="S62" t="inlineStr">
         <is>
-          <t>19-03-2026 23:59:59</t>
+          <t>23-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T62" t="inlineStr">
         <is>
-          <t>19-02-2026 17:10:51</t>
+          <t>23-02-2026 15:23:09</t>
         </is>
       </c>
       <c r="U62" t="inlineStr">
@@ -9009,19 +8997,11 @@
       </c>
       <c r="X62" t="inlineStr">
         <is>
-          <t>26150522500690001919</t>
-        </is>
-      </c>
-      <c r="Y62" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z62" t="inlineStr">
-        <is>
-          <t>GISSEL ANAHY REYES GERMAN</t>
-        </is>
-      </c>
+          <t>26150522584530002009</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr"/>
+      <c r="Z62" t="inlineStr"/>
       <c r="AA62" t="inlineStr">
         <is>
           <t>499</t>
@@ -9029,24 +9009,24 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>Johan Osvaldo Beltran Quiros</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC62" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>345101</t>
+          <t>342866</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>87266</t>
+          <t>20683</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -9056,87 +9036,95 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>CAMILA</t>
+          <t>IAN AXEL</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>VASQUEZ</t>
+          <t>SANDOVAL</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>LOPEZ</t>
+          <t>TORRES</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>6531040237</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr"/>
+          <t>9285501740</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>COLIMA C 26</t>
+        </is>
+      </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>08-10-2007</t>
+          <t>30-08-2010</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>VASQUEZLOPEZCAMILA@GMAIL.COM</t>
+          <t>IAN.SANDOVALTO@GMAIL.COM</t>
         </is>
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>19-02-2026 15:31:29</t>
-        </is>
-      </c>
-      <c r="N63" t="inlineStr">
-        <is>
-          <t>Tarifas 2026 LE</t>
-        </is>
-      </c>
+          <t>10-02-2026 20:35:22</t>
+        </is>
+      </c>
+      <c r="N63" t="inlineStr"/>
       <c r="O63" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P63" t="inlineStr">
         <is>
-          <t>3 MESES $1,899</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q63" t="inlineStr">
         <is>
-          <t>633</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R63" t="inlineStr">
         <is>
-          <t>19-02-2026 15:34:34</t>
+          <t>11-02-2026 21:04:30</t>
         </is>
       </c>
       <c r="S63" t="inlineStr">
         <is>
-          <t>19-05-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T63" t="inlineStr"/>
+          <t>11-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>11-02-2026 21:03:57</t>
+        </is>
+      </c>
       <c r="U63" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="V63" t="inlineStr"/>
       <c r="W63" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -9144,19 +9132,27 @@
       </c>
       <c r="X63" t="inlineStr">
         <is>
-          <t>26150522497060001917</t>
-        </is>
-      </c>
-      <c r="Y63" t="inlineStr"/>
-      <c r="Z63" t="inlineStr"/>
+          <t>26150522279200001615</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z63" t="inlineStr">
+        <is>
+          <t>GISSEL ANAHY REYES GERMAN</t>
+        </is>
+      </c>
       <c r="AA63" t="inlineStr">
         <is>
-          <t>1899</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>Johan Osvaldo Beltran Quiros</t>
+          <t>Juan Pablo Romero Andrade</t>
         </is>
       </c>
       <c r="AC63" t="inlineStr">
@@ -9168,12 +9164,12 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>344507</t>
+          <t>343531</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>22324</t>
+          <t>21348</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -9183,17 +9179,17 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>KAREN ANDREA</t>
+          <t>URIEL IGNACIO</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>ISAIS</t>
+          <t>SID</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>QUILES</t>
+          <t>AREVALO</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
@@ -9203,67 +9199,63 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>6531517509</t>
+          <t>6531071848</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>AV PUEBLA 1RA</t>
+          <t>FELIX CONTRERAS 44</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>12-02-1999</t>
+          <t>02-06-2005</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>KARENANDREAISAIS1999@GMAIL.COM</t>
+          <t>URIELIGNACIOSIDDAVERALO@GMAIL.COM</t>
         </is>
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>17-02-2026 14:45:48</t>
-        </is>
-      </c>
-      <c r="N64" t="inlineStr">
-        <is>
-          <t>Tarifas 2026 LE</t>
-        </is>
-      </c>
+          <t>13-02-2026 16:28:37</t>
+        </is>
+      </c>
+      <c r="N64" t="inlineStr"/>
       <c r="O64" t="inlineStr">
         <is>
-          <t>No Forzoso</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>PLAN RECURRENTE PAGO INCIAL $1,449 LE</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q64" t="inlineStr">
         <is>
-          <t>1449</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R64" t="inlineStr">
         <is>
-          <t>17-02-2026 14:50:44</t>
+          <t>13-02-2026 16:34:53</t>
         </is>
       </c>
       <c r="S64" t="inlineStr">
         <is>
-          <t>17-03-2026 23:59:59</t>
+          <t>13-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T64" t="inlineStr">
         <is>
-          <t>17-02-2026 14:49:35</t>
+          <t>13-02-2026 16:34:13</t>
         </is>
       </c>
       <c r="U64" t="inlineStr">
@@ -9283,169 +9275,844 @@
       </c>
       <c r="X64" t="inlineStr">
         <is>
-          <t>26150522430060001816</t>
+          <t>26150522324410001674</t>
         </is>
       </c>
       <c r="Y64" t="inlineStr"/>
       <c r="Z64" t="inlineStr"/>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>1449</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Juan Pablo Romero Andrade</t>
         </is>
       </c>
       <c r="AC64" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
+          <t>343813</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>21630</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>SAN LUIS</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>YOCELIN DEL CARMEN</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>LOPEZ</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>VALENZUELA</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>6531305359</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>AV CARRANZA 36</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>16-07-1999</t>
+        </is>
+      </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>YOCELINLOPEZ490@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>15-02-2026 11:25:12</t>
+        </is>
+      </c>
+      <c r="N65" t="inlineStr"/>
+      <c r="O65" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>PROMO FEBRERO 12 MESES</t>
+        </is>
+      </c>
+      <c r="Q65" t="inlineStr">
+        <is>
+          <t>499</t>
+        </is>
+      </c>
+      <c r="R65" t="inlineStr">
+        <is>
+          <t>15-02-2026 11:31:12</t>
+        </is>
+      </c>
+      <c r="S65" t="inlineStr">
+        <is>
+          <t>15-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>15-02-2026 11:29:38</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X65" t="inlineStr">
+        <is>
+          <t>26150522364500001715</t>
+        </is>
+      </c>
+      <c r="Y65" t="inlineStr"/>
+      <c r="Z65" t="inlineStr"/>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>499</t>
+        </is>
+      </c>
+      <c r="AB65" t="inlineStr">
+        <is>
+          <t>Juan Pablo Romero Andrade</t>
+        </is>
+      </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>345101</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>87266</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>SAN LUIS</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>CAMILA</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>VASQUEZ</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>LOPEZ</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>6531040237</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>08-10-2007</t>
+        </is>
+      </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>VASQUEZLOPEZCAMILA@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>19-02-2026 15:31:29</t>
+        </is>
+      </c>
+      <c r="N66" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
+      <c r="O66" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>3 MESES $1,899</t>
+        </is>
+      </c>
+      <c r="Q66" t="inlineStr">
+        <is>
+          <t>633</t>
+        </is>
+      </c>
+      <c r="R66" t="inlineStr">
+        <is>
+          <t>19-02-2026 15:34:34</t>
+        </is>
+      </c>
+      <c r="S66" t="inlineStr">
+        <is>
+          <t>19-05-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T66" t="inlineStr"/>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr"/>
+      <c r="W66" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X66" t="inlineStr">
+        <is>
+          <t>26150522497060001917</t>
+        </is>
+      </c>
+      <c r="Y66" t="inlineStr"/>
+      <c r="Z66" t="inlineStr"/>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>1899</t>
+        </is>
+      </c>
+      <c r="AB66" t="inlineStr">
+        <is>
+          <t>Johan Osvaldo Beltran Quiros</t>
+        </is>
+      </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>345985</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>88150</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>SAN LUIS</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>LUZ</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>MENESES</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>MENESES</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>6531109304</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>28-02-2010</t>
+        </is>
+      </c>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>LUZMENESES2810@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>23-02-2026 18:29:05</t>
+        </is>
+      </c>
+      <c r="N67" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
+      <c r="O67" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>1 MES $899</t>
+        </is>
+      </c>
+      <c r="Q67" t="inlineStr">
+        <is>
+          <t>899</t>
+        </is>
+      </c>
+      <c r="R67" t="inlineStr">
+        <is>
+          <t>23-02-2026 18:30:15</t>
+        </is>
+      </c>
+      <c r="S67" t="inlineStr">
+        <is>
+          <t>23-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T67" t="inlineStr"/>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr"/>
+      <c r="W67" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X67" t="inlineStr">
+        <is>
+          <t>26150522595820002029</t>
+        </is>
+      </c>
+      <c r="Y67" t="inlineStr"/>
+      <c r="Z67" t="inlineStr"/>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>899</t>
+        </is>
+      </c>
+      <c r="AB67" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>344583</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>22400</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>SAN LUIS</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CARLOS </t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>ACOSTA</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>SANTOS</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>6531202025</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>AV NUEVO LEON 9</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>04-03-2005</t>
+        </is>
+      </c>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>TZELI9535@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>17-02-2026 16:50:12</t>
+        </is>
+      </c>
+      <c r="N68" t="inlineStr">
+        <is>
+          <t>inscripcion promo 199</t>
+        </is>
+      </c>
+      <c r="O68" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>PROMO FEBRERO 12 MESES</t>
+        </is>
+      </c>
+      <c r="Q68" t="inlineStr">
+        <is>
+          <t>499</t>
+        </is>
+      </c>
+      <c r="R68" t="inlineStr">
+        <is>
+          <t>19-02-2026 17:11:32</t>
+        </is>
+      </c>
+      <c r="S68" t="inlineStr">
+        <is>
+          <t>19-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>19-02-2026 17:10:51</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W68" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X68" t="inlineStr">
+        <is>
+          <t>26150522500690001919</t>
+        </is>
+      </c>
+      <c r="Y68" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z68" t="inlineStr">
+        <is>
+          <t>GISSEL ANAHY REYES GERMAN</t>
+        </is>
+      </c>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>499</t>
+        </is>
+      </c>
+      <c r="AB68" t="inlineStr">
+        <is>
+          <t>Johan Osvaldo Beltran Quiros</t>
+        </is>
+      </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>344507</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>22324</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>SAN LUIS</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>KAREN ANDREA</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>ISAIS</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>QUILES</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>6531517509</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>AV PUEBLA 1RA</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>12-02-1999</t>
+        </is>
+      </c>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>KARENANDREAISAIS1999@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>17-02-2026 14:45:48</t>
+        </is>
+      </c>
+      <c r="N69" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
+      <c r="O69" t="inlineStr">
+        <is>
+          <t>No Forzoso</t>
+        </is>
+      </c>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>PLAN RECURRENTE PAGO INCIAL $1,449 LE</t>
+        </is>
+      </c>
+      <c r="Q69" t="inlineStr">
+        <is>
+          <t>1449</t>
+        </is>
+      </c>
+      <c r="R69" t="inlineStr">
+        <is>
+          <t>17-02-2026 14:50:44</t>
+        </is>
+      </c>
+      <c r="S69" t="inlineStr">
+        <is>
+          <t>17-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>17-02-2026 14:49:35</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W69" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X69" t="inlineStr">
+        <is>
+          <t>26150522430060001816</t>
+        </is>
+      </c>
+      <c r="Y69" t="inlineStr"/>
+      <c r="Z69" t="inlineStr"/>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>1449</t>
+        </is>
+      </c>
+      <c r="AB69" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
           <t>344807</t>
         </is>
       </c>
-      <c r="B65" t="inlineStr">
+      <c r="B70" t="inlineStr">
         <is>
           <t>22624</t>
         </is>
       </c>
-      <c r="C65" t="inlineStr">
+      <c r="C70" t="inlineStr">
         <is>
           <t>SAN LUIS</t>
         </is>
       </c>
-      <c r="D65" t="inlineStr">
+      <c r="D70" t="inlineStr">
         <is>
           <t>CRUZ GUADALUPE</t>
         </is>
       </c>
-      <c r="E65" t="inlineStr">
+      <c r="E70" t="inlineStr">
         <is>
           <t>LUGO</t>
         </is>
       </c>
-      <c r="F65" t="inlineStr">
+      <c r="F70" t="inlineStr">
         <is>
           <t>ROCHA</t>
         </is>
       </c>
-      <c r="G65" t="inlineStr">
+      <c r="G70" t="inlineStr">
         <is>
           <t>52</t>
         </is>
       </c>
-      <c r="H65" t="inlineStr">
+      <c r="H70" t="inlineStr">
         <is>
           <t>6532082764</t>
         </is>
       </c>
-      <c r="I65" t="inlineStr">
+      <c r="I70" t="inlineStr">
         <is>
           <t>AV NAYARIT 43 Y 44</t>
         </is>
       </c>
-      <c r="J65" t="inlineStr">
+      <c r="J70" t="inlineStr">
         <is>
           <t>Femenino</t>
         </is>
       </c>
-      <c r="K65" t="inlineStr">
+      <c r="K70" t="inlineStr">
         <is>
           <t>01-01-2000</t>
         </is>
       </c>
-      <c r="L65" t="inlineStr">
+      <c r="L70" t="inlineStr">
         <is>
           <t>CRUZGLP01@LCLOUD.COM</t>
         </is>
       </c>
-      <c r="M65" t="inlineStr">
+      <c r="M70" t="inlineStr">
         <is>
           <t>18-02-2026 12:56:53</t>
         </is>
       </c>
-      <c r="N65" t="inlineStr">
+      <c r="N70" t="inlineStr">
         <is>
           <t>inscripcion promo 199</t>
         </is>
       </c>
-      <c r="O65" t="inlineStr">
+      <c r="O70" t="inlineStr">
         <is>
           <t>Forzoso</t>
         </is>
       </c>
-      <c r="P65" t="inlineStr">
+      <c r="P70" t="inlineStr">
         <is>
           <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
-      <c r="Q65" t="inlineStr">
+      <c r="Q70" t="inlineStr">
         <is>
           <t>499</t>
         </is>
       </c>
-      <c r="R65" t="inlineStr">
+      <c r="R70" t="inlineStr">
         <is>
           <t>20-02-2026 10:30:09</t>
         </is>
       </c>
-      <c r="S65" t="inlineStr">
+      <c r="S70" t="inlineStr">
         <is>
           <t>20-03-2026 23:59:59</t>
         </is>
       </c>
-      <c r="T65" t="inlineStr">
+      <c r="T70" t="inlineStr">
         <is>
           <t>20-02-2026 10:29:02</t>
         </is>
       </c>
-      <c r="U65" t="inlineStr">
+      <c r="U70" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V65" t="inlineStr">
+      <c r="V70" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="W65" t="inlineStr">
+      <c r="W70" t="inlineStr">
         <is>
           <t>Sucursal</t>
         </is>
       </c>
-      <c r="X65" t="inlineStr">
+      <c r="X70" t="inlineStr">
         <is>
           <t>26150522523340001940</t>
         </is>
       </c>
-      <c r="Y65" t="inlineStr">
+      <c r="Y70" t="inlineStr">
         <is>
           <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
         </is>
       </c>
-      <c r="Z65" t="inlineStr">
+      <c r="Z70" t="inlineStr">
         <is>
           <t>GISSEL ANAHY REYES GERMAN</t>
         </is>
       </c>
-      <c r="AA65" t="inlineStr">
+      <c r="AA70" t="inlineStr">
         <is>
           <t>499</t>
         </is>
       </c>
-      <c r="AB65" t="inlineStr">
+      <c r="AB70" t="inlineStr">
         <is>
           <t>Juan Pablo Romero Andrade</t>
         </is>
       </c>
-      <c r="AC65" t="inlineStr">
+      <c r="AC70" t="inlineStr">
         <is>
           <t>con rutina</t>
         </is>

--- a/data/rutinas/sucursales/Socios_con_y_sin_rutina__SAN LUIS.xlsx
+++ b/data/rutinas/sucursales/Socios_con_y_sin_rutina__SAN LUIS.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC70"/>
+  <dimension ref="A1:AC76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -717,12 +717,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>273095</t>
+          <t>277709</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>70597</t>
+          <t>75210</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -732,17 +732,17 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LUZ ANGELICA</t>
+          <t>ANGEL ALBERTO</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>MURILLO</t>
+          <t>ACOSTA</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>SANCHEZ</t>
+          <t>RIVAS</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -752,32 +752,32 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>6531078647</t>
+          <t>6424832255</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>AV COLIMA Y 44</t>
+          <t>CJON 5 DE MAYO 12 Y 13</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>02-06-2002</t>
+          <t>06-03-1998</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>MENDOZA_MURILLOO21@HOTMAIL.COM</t>
+          <t>ACOSTARIVS@GMAIL.COM</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>11-01-2025 05:38:19</t>
+          <t>06-02-2025 18:37:15</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -798,17 +798,17 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>13-02-2026 18:16:08</t>
+          <t>13-02-2026 05:21:27</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>13-03-2026 23:59:59</t>
+          <t>14-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>13-02-2026 18:12:25</t>
+          <t>13-02-2026 05:19:56</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -818,7 +818,7 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
@@ -828,11 +828,19 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>26150522327860001680</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr"/>
-      <c r="Z3" t="inlineStr"/>
+          <t>26150522308700001658</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>RAUL FELIX VAZQUEZ</t>
+        </is>
+      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>499</t>
@@ -840,7 +848,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>Juan Pablo Romero Andrade</t>
+          <t>Juan Eduardo Torres Alcantar</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -852,12 +860,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>319145</t>
+          <t>273095</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>16642</t>
+          <t>70597</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -867,17 +875,17 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>CESAR BERNARDO</t>
+          <t>LUZ ANGELICA</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>ELIZONDO</t>
+          <t>MURILLO</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>RODRIGUEZ</t>
+          <t>SANCHEZ</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -887,39 +895,35 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>6862267616</t>
+          <t>6531078647</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>GUADALUPE VICTORIA Y 31</t>
+          <t>AV COLIMA Y 44</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>27-07-1992</t>
+          <t>02-06-2002</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>CESARBER27@HOTMAIL.COM</t>
+          <t>MENDOZA_MURILLOO21@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>16-10-2025 19:03:26</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>inscripcion promo 199</t>
-        </is>
-      </c>
+          <t>11-01-2025 05:38:19</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr">
         <is>
           <t>Forzoso</t>
@@ -937,17 +941,17 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>17-02-2026 10:45:09</t>
+          <t>13-02-2026 18:16:08</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>17-03-2026 23:59:59</t>
+          <t>13-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>17-02-2026 10:44:24</t>
+          <t>13-02-2026 18:12:25</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -957,7 +961,7 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -967,19 +971,11 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>26150522424240001807</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>GISSEL ANAHY REYES GERMAN</t>
-        </is>
-      </c>
+          <t>26150522327860001680</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr"/>
+      <c r="Z4" t="inlineStr"/>
       <c r="AA4" t="inlineStr">
         <is>
           <t>499</t>
@@ -987,7 +983,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>Juan Eduardo Torres Alcantar</t>
+          <t>Juan Pablo Romero Andrade</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -999,12 +995,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>317137</t>
+          <t>34113</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>14634</t>
+          <t>32029</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1014,17 +1010,17 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>JOSE IGNACIO</t>
+          <t>YOVANY</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>PARRA</t>
+          <t>VALENZUELA</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>JAQUEZ</t>
+          <t xml:space="preserve">ALVARADO </t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -1034,12 +1030,12 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>6531038638</t>
+          <t>6531453465</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>CALZADA AVIACION 104</t>
+          <t>LEY DE ALFABETIZACION 9 Y 10</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1049,17 +1045,17 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>13-12-1975</t>
+          <t>30-12-1997</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>JOSEIGNACIOJOAN@GMAIL.COM</t>
+          <t>YOVANYALVRADO@GMAIL.COM</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>03-10-2025 19:18:42</t>
+          <t>29-06-2021 18:23:17</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -1080,17 +1076,17 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>13-02-2026 18:41:08</t>
+          <t>12-02-2026 05:24:56</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>13-03-2026 23:59:59</t>
+          <t>12-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>13-02-2026 18:39:22</t>
+          <t>12-02-2026 05:23:53</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -1110,19 +1106,11 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>26150522328580001685</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>GISSEL ANAHY REYES GERMAN</t>
-        </is>
-      </c>
+          <t>26150522281110001621</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr"/>
+      <c r="Z5" t="inlineStr"/>
       <c r="AA5" t="inlineStr">
         <is>
           <t>499</t>
@@ -1130,7 +1118,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>Juan Pablo Romero Andrade</t>
+          <t>Juan Eduardo Torres Alcantar</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -1142,12 +1130,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>34113</t>
+          <t>109430</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>32029</t>
+          <t>7171</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1157,17 +1145,17 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>YOVANY</t>
+          <t>GISELL</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>VALENZUELA</t>
+          <t>BARO</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t xml:space="preserve">ALVARADO </t>
+          <t>SOTO</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -1177,75 +1165,71 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>6531453465</t>
+          <t>6531135478</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>LEY DE ALFABETIZACION 9 Y 10</t>
+          <t>SAN LUIS</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>30-12-1997</t>
+          <t>25-01-1999</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>YOVANYALVRADO@GMAIL.COM</t>
+          <t>GISELBARO@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>29-06-2021 18:23:17</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr"/>
+          <t>19-07-2022 07:14:06</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>1 MES $899</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>899</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>12-02-2026 05:24:56</t>
+          <t>17-02-2026 09:24:03</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>12-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t>12-02-2026 05:23:53</t>
-        </is>
-      </c>
+          <t>17-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr"/>
       <c r="U6" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="V6" t="inlineStr"/>
       <c r="W6" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -1253,19 +1237,19 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>26150522281110001621</t>
+          <t>26150522422860001804</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr"/>
       <c r="Z6" t="inlineStr"/>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>899</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>Juan Eduardo Torres Alcantar</t>
+          <t>Martin Ramiro Quiñonez Jauregui</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -1277,12 +1261,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>109430</t>
+          <t>317137</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>7171</t>
+          <t>14634</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1292,17 +1276,17 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>GISELL</t>
+          <t>JOSE IGNACIO</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>BARO</t>
+          <t>PARRA</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>SOTO</t>
+          <t>JAQUEZ</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -1312,71 +1296,75 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>6531135478</t>
+          <t>6531038638</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>SAN LUIS</t>
+          <t>CALZADA AVIACION 104</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>25-01-1999</t>
+          <t>13-12-1975</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>GISELBARO@HOTMAIL.COM</t>
+          <t>JOSEIGNACIOJOAN@GMAIL.COM</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>19-07-2022 07:14:06</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>Tarifas 2026 LE</t>
-        </is>
-      </c>
+          <t>03-10-2025 19:18:42</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>1 MES $899</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>17-02-2026 09:24:03</t>
+          <t>13-02-2026 18:41:08</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>17-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T7" t="inlineStr"/>
+          <t>13-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>13-02-2026 18:39:22</t>
+        </is>
+      </c>
       <c r="U7" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V7" t="inlineStr"/>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W7" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -1384,19 +1372,27 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>26150522422860001804</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr"/>
-      <c r="Z7" t="inlineStr"/>
+          <t>26150522328580001685</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>GISSEL ANAHY REYES GERMAN</t>
+        </is>
+      </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>Martin Ramiro Quiñonez Jauregui</t>
+          <t>Juan Pablo Romero Andrade</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
@@ -1551,12 +1547,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>339758</t>
+          <t>340298</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>17576</t>
+          <t>18116</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1566,17 +1562,17 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>ISABELLA</t>
+          <t xml:space="preserve">DARIO </t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>ALARCON</t>
+          <t>GARCIA</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>ACEVES</t>
+          <t>GARCIA</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -1586,7 +1582,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>6535382487</t>
+          <t>6531617077</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1597,17 +1593,17 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>04-06-2010</t>
+          <t>14-03-1986</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>ALARCONISABELLA347@GMAIL.COM</t>
+          <t>DARIOGS1486@ICLOUD.COM</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>01-02-2026 10:00:33</t>
+          <t>02-02-2026 17:03:53</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1632,18 +1628,18 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>01-02-2026 10:05:34</t>
+          <t>02-02-2026 17:04:52</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>01-03-2026 23:59:59</t>
+          <t>02-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T9" t="inlineStr"/>
       <c r="U9" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="V9" t="inlineStr"/>
@@ -1654,7 +1650,7 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>26150521988630001200</t>
+          <t>26150522017940001237</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr"/>
@@ -1666,7 +1662,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>Juan Pablo Romero Andrade</t>
+          <t>Johan Osvaldo Beltran Quiros</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
@@ -1678,12 +1674,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>339777</t>
+          <t>319145</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>17595</t>
+          <t>16642</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1693,19 +1689,19 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>GISSEL LILIAN</t>
+          <t>CESAR BERNARDO</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
+          <t>ELIZONDO</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
           <t>RODRIGUEZ</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>SILVA</t>
-        </is>
-      </c>
       <c r="G10" t="inlineStr">
         <is>
           <t>52</t>
@@ -1713,67 +1709,67 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>6531466820</t>
+          <t>6862267616</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>MERIDA 1</t>
+          <t>GUADALUPE VICTORIA Y 31</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>02-09-1998</t>
+          <t>27-07-1992</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>GISSELSILVIA98@GMAIL.COM</t>
+          <t>CESARBER27@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>01-02-2026 10:50:32</t>
+          <t>16-10-2025 19:03:26</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>Tarifas 2026 LE</t>
+          <t>inscripcion promo 199</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>No Forzoso</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>RECURRENTE $649 LE</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>01-02-2026 10:53:31</t>
+          <t>17-02-2026 10:45:09</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>01-03-2026 23:59:59</t>
+          <t>17-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>01-02-2026 10:52:55</t>
+          <t>17-02-2026 10:44:24</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
@@ -1783,7 +1779,7 @@
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W10" t="inlineStr">
@@ -1793,19 +1789,27 @@
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>26150521989600001201</t>
-        </is>
-      </c>
-      <c r="Y10" t="inlineStr"/>
-      <c r="Z10" t="inlineStr"/>
+          <t>26150522424240001807</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>GISSEL ANAHY REYES GERMAN</t>
+        </is>
+      </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>Juan Pablo Romero Andrade</t>
+          <t>Juan Eduardo Torres Alcantar</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
@@ -1817,12 +1821,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>340298</t>
+          <t>339746</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>18116</t>
+          <t>17564</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1832,17 +1836,17 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t xml:space="preserve">DARIO </t>
+          <t xml:space="preserve">GRISEL </t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>GARCIA</t>
+          <t>CUADRAS</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>GARCIA</t>
+          <t>CUADRAS</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -1852,10 +1856,14 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>6531617077</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>6531315370</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>MEXICO B Y 28</t>
+        </is>
+      </c>
       <c r="J11" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -1863,17 +1871,17 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>14-03-1986</t>
+          <t>17-02-1980</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>DARIOGS1486@ICLOUD.COM</t>
+          <t>CHACLAUDIA5@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>02-02-2026 17:03:53</t>
+          <t>01-02-2026 09:25:23</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1883,36 +1891,44 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>No Forzoso</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>RECURRENTE $649 LE</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>649</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>02-02-2026 17:04:52</t>
+          <t>03-02-2026 05:30:52</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>02-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T11" t="inlineStr"/>
+          <t>03-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>03-02-2026 05:30:25</t>
+        </is>
+      </c>
       <c r="U11" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="V11" t="inlineStr"/>
       <c r="W11" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -1920,19 +1936,27 @@
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>26150522017940001237</t>
-        </is>
-      </c>
-      <c r="Y11" t="inlineStr"/>
-      <c r="Z11" t="inlineStr"/>
+          <t>26150522029990001268</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>GISSEL ANAHY REYES GERMAN</t>
+        </is>
+      </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>649</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>Johan Osvaldo Beltran Quiros</t>
+          <t>Martin Ramiro Quiñonez Jauregui</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
@@ -1944,12 +1968,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>277709</t>
+          <t>339758</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>75210</t>
+          <t>17576</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1959,17 +1983,17 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>ANGEL ALBERTO</t>
+          <t>ISABELLA</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>ACOSTA</t>
+          <t>ALARCON</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>RIVAS</t>
+          <t>ACEVES</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -1979,75 +2003,67 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>6424832255</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>CJON 5 DE MAYO 12 Y 13</t>
-        </is>
-      </c>
+          <t>6535382487</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>06-03-1998</t>
+          <t>04-06-2010</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>ACOSTARIVS@GMAIL.COM</t>
+          <t>ALARCONISABELLA347@GMAIL.COM</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>06-02-2025 18:37:15</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr"/>
+          <t>01-02-2026 10:00:33</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>13-02-2026 05:21:27</t>
+          <t>01-02-2026 10:05:34</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>14-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>13-02-2026 05:19:56</t>
-        </is>
-      </c>
+          <t>01-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr"/>
       <c r="U12" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V12" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="V12" t="inlineStr"/>
       <c r="W12" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -2055,27 +2071,19 @@
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>26150522308700001658</t>
-        </is>
-      </c>
-      <c r="Y12" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>RAUL FELIX VAZQUEZ</t>
-        </is>
-      </c>
+          <t>26150521988630001200</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr"/>
+      <c r="Z12" t="inlineStr"/>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>Juan Eduardo Torres Alcantar</t>
+          <t>Juan Pablo Romero Andrade</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
@@ -2087,12 +2095,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>339746</t>
+          <t>339777</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>17564</t>
+          <t>17595</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -2102,17 +2110,17 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t xml:space="preserve">GRISEL </t>
+          <t>GISSEL LILIAN</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>CUADRAS</t>
+          <t>RODRIGUEZ</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>CUADRAS</t>
+          <t>SILVA</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -2122,12 +2130,12 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>6531315370</t>
+          <t>6531466820</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>MEXICO B Y 28</t>
+          <t>MERIDA 1</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -2137,17 +2145,17 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>17-02-1980</t>
+          <t>02-09-1998</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>CHACLAUDIA5@HOTMAIL.COM</t>
+          <t>GISSELSILVIA98@GMAIL.COM</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>01-02-2026 09:25:23</t>
+          <t>01-02-2026 10:50:32</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
@@ -2172,17 +2180,17 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>03-02-2026 05:30:52</t>
+          <t>01-02-2026 10:53:31</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>03-03-2026 23:59:59</t>
+          <t>01-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>03-02-2026 05:30:25</t>
+          <t>01-02-2026 10:52:55</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
@@ -2202,19 +2210,11 @@
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>26150522029990001268</t>
-        </is>
-      </c>
-      <c r="Y13" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>GISSEL ANAHY REYES GERMAN</t>
-        </is>
-      </c>
+          <t>26150521989600001201</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr"/>
+      <c r="Z13" t="inlineStr"/>
       <c r="AA13" t="inlineStr">
         <is>
           <t>649</t>
@@ -2222,7 +2222,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>Martin Ramiro Quiñonez Jauregui</t>
+          <t>Juan Pablo Romero Andrade</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
@@ -2234,12 +2234,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>340340</t>
+          <t>297488</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>18158</t>
+          <t>94986</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -2249,17 +2249,17 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>FATIMA</t>
+          <t xml:space="preserve">BRENDA </t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>SANCHEZ</t>
+          <t>ROMAN</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>MEDINA</t>
+          <t>IBARRA</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -2269,12 +2269,12 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>6531333103</t>
+          <t>6531125544</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>AV TORREON 39</t>
+          <t>EMILIANO ZAPATA C Y COLOMBIA</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -2284,22 +2284,22 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>27-08-2003</t>
+          <t>04-02-1984</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>FATIMASM2708@GMAIL.COM</t>
+          <t>OKCHIQUITA4@GMAIL.COM</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>02-02-2026 18:15:23</t>
+          <t>09-06-2025 20:08:16</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>Tarifas 2026 LE</t>
+          <t>inscripcion promo 199</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
@@ -2309,27 +2309,27 @@
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES $549 LE</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>02-02-2026 18:20:31</t>
+          <t>19-02-2026 17:34:15</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>02-03-2026 23:59:59</t>
+          <t>19-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>02-02-2026 18:19:16</t>
+          <t>19-02-2026 17:33:15</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
@@ -2349,36 +2349,40 @@
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>26150522020390001251</t>
-        </is>
-      </c>
-      <c r="Y14" t="inlineStr"/>
+          <t>26150522501710001922</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
       <c r="Z14" t="inlineStr"/>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>Johan Osvaldo Beltran Quiros</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>336709</t>
+          <t>340602</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>22435</t>
+          <t>18420</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -2388,95 +2392,87 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>MARIA FERNANDA</t>
+          <t>DANTE EMILIANO</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>LAZALDE</t>
+          <t>GARCIA</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>ANDRADE</t>
+          <t>GOMEZ</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>6645697047</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>C ADOLFO LOPEZ MATEOS 6413 C</t>
-        </is>
-      </c>
+          <t>9228390416</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>21-01-2000</t>
+          <t>06-12-2010</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>FERGIE.LAZALDE@GMAIL.COM</t>
+          <t>DANTE.GARCIA@INSTITUTOKINO.EDU.MX</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>21-01-2026 11:47:08</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr"/>
+          <t>03-02-2026 14:43:23</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>11-02-2026 08:22:24</t>
+          <t>03-02-2026 14:44:52</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>11-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T15" t="inlineStr">
-        <is>
-          <t>11-02-2026 08:21:44</t>
-        </is>
-      </c>
+          <t>03-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr"/>
       <c r="U15" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V15" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="V15" t="inlineStr"/>
       <c r="W15" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -2484,23 +2480,19 @@
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>26070522259520003153</t>
-        </is>
-      </c>
-      <c r="Y15" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
+          <t>26150522041730001279</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr"/>
       <c r="Z15" t="inlineStr"/>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>Jesus Alejandro  Partida Partida</t>
+          <t>Juan Pablo Romero Andrade</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
@@ -2512,12 +2504,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>297488</t>
+          <t>340730</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>94986</t>
+          <t>18548</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -2527,17 +2519,17 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t xml:space="preserve">BRENDA </t>
+          <t>GUADALUPE SHEREZADA</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>ROMAN</t>
+          <t>RAMIREZ</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>IBARRA</t>
+          <t>CORTEZ</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -2547,14 +2539,10 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>6531125544</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>EMILIANO ZAPATA C Y COLOMBIA</t>
-        </is>
-      </c>
+          <t>6531304693</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -2562,64 +2550,56 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>04-02-1984</t>
+          <t>02-07-2000</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>OKCHIQUITA4@GMAIL.COM</t>
+          <t>BELLOBAINES.1982@GMAIL.COM</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>09-06-2025 20:08:16</t>
+          <t>03-02-2026 17:27:01</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>inscripcion promo 199</t>
+          <t>Tarifas 2026 LE</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>19-02-2026 17:34:15</t>
+          <t>03-02-2026 17:32:11</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>19-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T16" t="inlineStr">
-        <is>
-          <t>19-02-2026 17:33:15</t>
-        </is>
-      </c>
+          <t>03-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr"/>
       <c r="U16" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V16" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="V16" t="inlineStr"/>
       <c r="W16" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -2627,40 +2607,36 @@
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>26150522501710001922</t>
-        </is>
-      </c>
-      <c r="Y16" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
+          <t>26150522049660001299</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr"/>
       <c r="Z16" t="inlineStr"/>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Juan Pablo Romero Andrade</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>340602</t>
+          <t>340340</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>18420</t>
+          <t>18158</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -2670,87 +2646,99 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>DANTE EMILIANO</t>
+          <t>FATIMA</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>GARCIA</t>
+          <t>SANCHEZ</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>GOMEZ</t>
+          <t>MEDINA</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>6531333103</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>AV TORREON 39</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>27-08-2003</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>FATIMASM2708@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>02-02-2026 18:15:23</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>DOMICILIADO 12 MESES $549 LE</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>02-02-2026 18:20:31</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>02-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>02-02-2026 18:19:16</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>9228390416</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>Masculino</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>06-12-2010</t>
-        </is>
-      </c>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>DANTE.GARCIA@INSTITUTOKINO.EDU.MX</t>
-        </is>
-      </c>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>03-02-2026 14:43:23</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>Tarifas 2026 LE</t>
-        </is>
-      </c>
-      <c r="O17" t="inlineStr">
-        <is>
-          <t>Sin contrato</t>
-        </is>
-      </c>
-      <c r="P17" t="inlineStr">
-        <is>
-          <t>CONVENIOS $549</t>
-        </is>
-      </c>
-      <c r="Q17" t="inlineStr">
-        <is>
-          <t>549</t>
-        </is>
-      </c>
-      <c r="R17" t="inlineStr">
-        <is>
-          <t>03-02-2026 14:44:52</t>
-        </is>
-      </c>
-      <c r="S17" t="inlineStr">
-        <is>
-          <t>03-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T17" t="inlineStr"/>
-      <c r="U17" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V17" t="inlineStr"/>
       <c r="W17" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -2758,7 +2746,7 @@
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>26150522041730001279</t>
+          <t>26150522020390001251</t>
         </is>
       </c>
       <c r="Y17" t="inlineStr"/>
@@ -2770,7 +2758,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>Juan Pablo Romero Andrade</t>
+          <t>Johan Osvaldo Beltran Quiros</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
@@ -2782,12 +2770,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>340730</t>
+          <t>325230</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>18548</t>
+          <t>22169</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -2797,17 +2785,17 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>GUADALUPE SHEREZADA</t>
+          <t xml:space="preserve">GLORIA </t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>RAMIREZ</t>
+          <t>SANTOS</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>CORTEZ</t>
+          <t>PEREZ</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -2817,10 +2805,14 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>6531304693</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>6531642345</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>AV NUEVO LEON N9 Y 10</t>
+        </is>
+      </c>
       <c r="J18" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -2828,56 +2820,64 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>02-07-2000</t>
+          <t>09-08-1984</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>BELLOBAINES.1982@GMAIL.COM</t>
+          <t>PRICESASANTOS8409@GMAIL.COM</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>03-02-2026 17:27:01</t>
+          <t>25-11-2025 12:03:46</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>Tarifas 2026 LE</t>
+          <t>inscripcion promo 199</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>03-02-2026 17:32:11</t>
+          <t>18-02-2026 18:24:56</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>03-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T18" t="inlineStr"/>
+          <t>18-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>18-02-2026 18:24:16</t>
+        </is>
+      </c>
       <c r="U18" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V18" t="inlineStr"/>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W18" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -2885,14 +2885,22 @@
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>26150522049660001299</t>
-        </is>
-      </c>
-      <c r="Y18" t="inlineStr"/>
-      <c r="Z18" t="inlineStr"/>
+          <t>26150522472400001881</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>GISSEL ANAHY REYES GERMAN</t>
+        </is>
+      </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
@@ -3052,12 +3060,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>325230</t>
+          <t>341991</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>22169</t>
+          <t>19809</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -3067,17 +3075,17 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t xml:space="preserve">GLORIA </t>
+          <t>VICTOR HUGO</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>SANTOS</t>
+          <t>SALAS</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>PEREZ</t>
+          <t>RODRIGUEZ</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -3087,32 +3095,32 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>6531642345</t>
+          <t>6531130495</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>AV NUEVO LEON N9 Y 10</t>
+          <t>SAN MARCOS</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>09-08-1984</t>
+          <t>30-08-2001</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>PRICESASANTOS8409@GMAIL.COM</t>
+          <t>SALASRODRIGUEZVICTORHUGO@GMAIL.COM</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>25-11-2025 12:03:46</t>
+          <t>09-02-2026 05:08:33</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
@@ -3137,17 +3145,17 @@
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>18-02-2026 18:24:56</t>
+          <t>17-02-2026 16:21:53</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>18-03-2026 23:59:59</t>
+          <t>17-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>18-02-2026 18:24:16</t>
+          <t>17-02-2026 16:21:11</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
@@ -3167,7 +3175,7 @@
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>26150522472400001881</t>
+          <t>26150522433690001818</t>
         </is>
       </c>
       <c r="Y20" t="inlineStr">
@@ -3177,7 +3185,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>GISSEL ANAHY REYES GERMAN</t>
+          <t>RAUL FELIX VAZQUEZ</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -3187,24 +3195,24 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>Juan Pablo Romero Andrade</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>341991</t>
+          <t>336709</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>19809</t>
+          <t>22435</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -3214,17 +3222,17 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VICTOR HUGO</t>
+          <t>MARIA FERNANDA</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>SALAS</t>
+          <t>LAZALDE</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>RODRIGUEZ</t>
+          <t>ANDRADE</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -3234,39 +3242,35 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>6531130495</t>
+          <t>6645697047</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>SAN MARCOS</t>
+          <t>C ADOLFO LOPEZ MATEOS 6413 C</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>30-08-2001</t>
+          <t>21-01-2000</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>SALASRODRIGUEZVICTORHUGO@GMAIL.COM</t>
+          <t>FERGIE.LAZALDE@GMAIL.COM</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>09-02-2026 05:08:33</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr">
-        <is>
-          <t>inscripcion promo 199</t>
-        </is>
-      </c>
+          <t>21-01-2026 11:47:08</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr"/>
       <c r="O21" t="inlineStr">
         <is>
           <t>Forzoso</t>
@@ -3284,17 +3288,17 @@
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>17-02-2026 16:21:53</t>
+          <t>11-02-2026 08:22:24</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>17-03-2026 23:59:59</t>
+          <t>11-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>17-02-2026 16:21:11</t>
+          <t>11-02-2026 08:21:44</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
@@ -3304,7 +3308,7 @@
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W21" t="inlineStr">
@@ -3314,7 +3318,7 @@
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>26150522433690001818</t>
+          <t>26070522259520003153</t>
         </is>
       </c>
       <c r="Y21" t="inlineStr">
@@ -3322,11 +3326,7 @@
           <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
         </is>
       </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>RAUL FELIX VAZQUEZ</t>
-        </is>
-      </c>
+      <c r="Z21" t="inlineStr"/>
       <c r="AA21" t="inlineStr">
         <is>
           <t>499</t>
@@ -3334,12 +3334,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Jesus Alejandro  Partida Partida</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
@@ -3624,12 +3624,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>339854</t>
+          <t>343341</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>17672</t>
+          <t>21158</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -3639,17 +3639,17 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>DIEGO ARMANDO</t>
+          <t>JUAN OMAR</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>MEDINA</t>
+          <t>REYES</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>PIEDRA</t>
+          <t>RIVERA</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -3659,12 +3659,12 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>6531658872</t>
+          <t>6865976498</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>REVOLUCION Y 40</t>
+          <t>CJON NICARAGUA 31</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -3674,52 +3674,48 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>06-03-1989</t>
+          <t>02-01-1992</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>DIEGO.MEDINA@YAHOO.COM</t>
+          <t>ELREYES023@GMAIL.COM</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>02-02-2026 05:44:27</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr">
-        <is>
-          <t>Tarifas 2026 LE</t>
-        </is>
-      </c>
+          <t>12-02-2026 17:35:55</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr"/>
       <c r="O24" t="inlineStr">
         <is>
-          <t>No Forzoso</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>PLAN FAMILIAR RECURRENTE $999</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>999</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>02-02-2026 05:46:51</t>
+          <t>14-02-2026 10:17:45</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>02-03-2026 23:59:59</t>
+          <t>14-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>02-02-2026 05:45:55</t>
+          <t>14-02-2026 10:17:11</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
@@ -3739,36 +3735,44 @@
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>26150521997870001209</t>
-        </is>
-      </c>
-      <c r="Y24" t="inlineStr"/>
-      <c r="Z24" t="inlineStr"/>
+          <t>26150522345630001701</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>GISSEL ANAHY REYES GERMAN</t>
+        </is>
+      </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>999</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Juan Pablo Romero Andrade</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>340805</t>
+          <t>342823</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>18623</t>
+          <t>20640</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -3778,17 +3782,17 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>RICARDO</t>
+          <t>JESUS ABEL</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>TAPIA</t>
+          <t>VALERIO</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>OLIVO</t>
+          <t>LIMON</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -3798,12 +3802,12 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>6531341539</t>
+          <t>6531665157</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>AV GUERRERO 12</t>
+          <t>CARRETERA DEL VALLE</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -3813,24 +3817,20 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>01-04-2000</t>
+          <t>23-07-2004</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>RICARDITOTAPIA2129@GMAIL.COM</t>
+          <t>VALERIOJESUS913@GMAIL.COM</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>03-02-2026 19:10:40</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr">
-        <is>
-          <t>Tarifas 2026 LE</t>
-        </is>
-      </c>
+          <t>10-02-2026 19:05:03</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr"/>
       <c r="O25" t="inlineStr">
         <is>
           <t>Forzoso</t>
@@ -3838,27 +3838,27 @@
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES $549 LE</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>03-02-2026 19:13:30</t>
+          <t>10-02-2026 19:09:25</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>03-03-2026 23:59:59</t>
+          <t>10-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>03-02-2026 19:12:47</t>
+          <t>10-02-2026 19:08:45</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
@@ -3868,7 +3868,7 @@
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W25" t="inlineStr">
@@ -3878,19 +3878,19 @@
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>26150522055450001315</t>
+          <t>26150522245980001553</t>
         </is>
       </c>
       <c r="Y25" t="inlineStr"/>
       <c r="Z25" t="inlineStr"/>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>Martin Ramiro Quiñonez Jauregui</t>
+          <t>Johan Osvaldo Beltran Quiros</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
@@ -3902,12 +3902,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>343341</t>
+          <t>343637</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>21158</t>
+          <t>21454</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -3917,17 +3917,17 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>JUAN OMAR</t>
+          <t>RICARDO FRANCISCO</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>REYES</t>
+          <t>LEDESMA</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>RIVERA</t>
+          <t>PEDROZA</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -3937,12 +3937,12 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>6865976498</t>
+          <t>6531121344</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>CJON NICARAGUA 31</t>
+          <t>EL CHEQUE 8 S/N</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -3952,17 +3952,17 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>02-01-1992</t>
+          <t>07-01-2006</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>ELREYES023@GMAIL.COM</t>
+          <t>RICARDOPZK200@GMAIL.COM</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>12-02-2026 17:35:55</t>
+          <t>14-02-2026 06:48:50</t>
         </is>
       </c>
       <c r="N26" t="inlineStr"/>
@@ -3983,17 +3983,17 @@
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>14-02-2026 10:17:45</t>
+          <t>14-02-2026 08:02:52</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
         <is>
-          <t>14-03-2026 23:59:59</t>
+          <t>15-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>14-02-2026 10:17:11</t>
+          <t>14-02-2026 08:01:46</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
@@ -4003,7 +4003,7 @@
       </c>
       <c r="V26" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W26" t="inlineStr">
@@ -4013,7 +4013,7 @@
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>26150522345630001701</t>
+          <t>26150522343510001694</t>
         </is>
       </c>
       <c r="Y26" t="inlineStr">
@@ -4023,7 +4023,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>GISSEL ANAHY REYES GERMAN</t>
+          <t>RAUL FELIX VAZQUEZ</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -4033,7 +4033,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>Juan Pablo Romero Andrade</t>
+          <t>Johan Osvaldo Beltran Quiros</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
@@ -4045,12 +4045,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>342823</t>
+          <t>339854</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>20640</t>
+          <t>17672</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -4060,17 +4060,17 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>JESUS ABEL</t>
+          <t>DIEGO ARMANDO</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>VALERIO</t>
+          <t>MEDINA</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>LIMON</t>
+          <t>PIEDRA</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -4080,12 +4080,12 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>6531665157</t>
+          <t>6531658872</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>CARRETERA DEL VALLE</t>
+          <t>REVOLUCION Y 40</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -4095,48 +4095,52 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>23-07-2004</t>
+          <t>06-03-1989</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>VALERIOJESUS913@GMAIL.COM</t>
+          <t>DIEGO.MEDINA@YAHOO.COM</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>10-02-2026 19:05:03</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr"/>
+          <t>02-02-2026 05:44:27</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>No Forzoso</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>PLAN FAMILIAR RECURRENTE $999</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>999</t>
         </is>
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>10-02-2026 19:09:25</t>
+          <t>02-02-2026 05:46:51</t>
         </is>
       </c>
       <c r="S27" t="inlineStr">
         <is>
-          <t>10-03-2026 23:59:59</t>
+          <t>02-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>10-02-2026 19:08:45</t>
+          <t>02-02-2026 05:45:55</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
@@ -4146,7 +4150,7 @@
       </c>
       <c r="V27" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W27" t="inlineStr">
@@ -4156,36 +4160,36 @@
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>26150522245980001553</t>
+          <t>26150521997870001209</t>
         </is>
       </c>
       <c r="Y27" t="inlineStr"/>
       <c r="Z27" t="inlineStr"/>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>999</t>
         </is>
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>Johan Osvaldo Beltran Quiros</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>342742</t>
+          <t>340152</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>20559</t>
+          <t>17970</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -4195,17 +4199,17 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>KARINA</t>
+          <t>MARTHA LIDIA</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>QUILES</t>
+          <t xml:space="preserve">DURAN </t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>CAMACHO</t>
+          <t>CUEN</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -4215,32 +4219,32 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>6531163674</t>
+          <t>6531218668</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>AV PUEBLA 1RA Y HERMOSILLO</t>
+          <t>PRIVADO ROFORMA</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>22-02-1975</t>
+          <t>06-08-1960</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>KARINAAQUILESC1975@GMAIL.COM</t>
+          <t>ROMERO.MARTHA50@ICLOUD.COM</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>10-02-2026 17:14:23</t>
+          <t>02-02-2026 13:57:36</t>
         </is>
       </c>
       <c r="N28" t="inlineStr"/>
@@ -4261,17 +4265,17 @@
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>10-02-2026 17:19:39</t>
+          <t>02-02-2026 14:04:27</t>
         </is>
       </c>
       <c r="S28" t="inlineStr">
         <is>
-          <t>10-03-2026 23:59:59</t>
+          <t>02-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>10-02-2026 17:18:56</t>
+          <t>02-02-2026 14:03:30</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
@@ -4291,7 +4295,7 @@
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>26150522239320001545</t>
+          <t>26150522011860001229</t>
         </is>
       </c>
       <c r="Y28" t="inlineStr"/>
@@ -4303,7 +4307,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>Martin Ramiro Quiñonez Jauregui</t>
+          <t>Juan Pablo Romero Andrade</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
@@ -4315,12 +4319,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>340160</t>
+          <t>342562</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>17978</t>
+          <t>20379</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -4330,52 +4334,52 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>ALEJANDRO</t>
+          <t>AZALEA ZENYACE</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>ROMERO</t>
+          <t>MORENO</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>GARCIA</t>
+          <t>CARRIZOZA</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>52</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>2099007353</t>
+          <t>6531038421</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>PRIVADA REFORMA</t>
+          <t>CJN CHIHUAHUA 23</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>27-03-1957</t>
+          <t>23-09-1994</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>ALEX57ROMERO@GMAIL.COM</t>
+          <t>ZEN_YACE94LIVE@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>02-02-2026 14:07:14</t>
+          <t>10-02-2026 09:19:09</t>
         </is>
       </c>
       <c r="N29" t="inlineStr"/>
@@ -4396,17 +4400,17 @@
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>02-02-2026 14:09:30</t>
+          <t>12-02-2026 18:37:07</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>02-03-2026 23:59:59</t>
+          <t>12-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>02-02-2026 14:08:43</t>
+          <t>12-02-2026 18:33:55</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
@@ -4416,7 +4420,7 @@
       </c>
       <c r="V29" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W29" t="inlineStr">
@@ -4426,11 +4430,19 @@
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>26150522012090001230</t>
-        </is>
-      </c>
-      <c r="Y29" t="inlineStr"/>
-      <c r="Z29" t="inlineStr"/>
+          <t>26150522302860001640</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>RAUL FELIX VAZQUEZ</t>
+        </is>
+      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>499</t>
@@ -4450,12 +4462,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>340247</t>
+          <t>340805</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>18065</t>
+          <t>18623</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -4465,17 +4477,17 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LESLIE CLARETH</t>
+          <t>RICARDO</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>VEGA</t>
+          <t>TAPIA</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>QUEVEDO</t>
+          <t>OLIVO</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -4485,32 +4497,32 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>6531329411</t>
+          <t>6531341539</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>AV NAYARIT 21</t>
+          <t>AV GUERRERO 12</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>18-08-2006</t>
+          <t>01-04-2000</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>VEGA.LESLIE.3E@GMAIL.COM</t>
+          <t>RICARDITOTAPIA2129@GMAIL.COM</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>02-02-2026 16:08:34</t>
+          <t>03-02-2026 19:10:40</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
@@ -4535,17 +4547,17 @@
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>02-02-2026 16:43:55</t>
+          <t>03-02-2026 19:13:30</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>02-03-2026 23:59:59</t>
+          <t>03-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>02-02-2026 16:12:35</t>
+          <t>03-02-2026 19:12:47</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
@@ -4555,7 +4567,7 @@
       </c>
       <c r="V30" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W30" t="inlineStr">
@@ -4565,7 +4577,7 @@
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>26150522017110001235</t>
+          <t>26150522055450001315</t>
         </is>
       </c>
       <c r="Y30" t="inlineStr"/>
@@ -4577,7 +4589,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>Juan Eduardo Torres Alcantar</t>
+          <t>Martin Ramiro Quiñonez Jauregui</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
@@ -4589,12 +4601,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>340152</t>
+          <t>344062</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>17970</t>
+          <t>21879</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -4604,17 +4616,17 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>MARTHA LIDIA</t>
+          <t>RAYMUNDO ISRAEL</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t xml:space="preserve">DURAN </t>
+          <t>LOPEZ</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>CUEN</t>
+          <t>ARREOLA</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -4624,14 +4636,10 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>6531218668</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>PRIVADO ROFORMA</t>
-        </is>
-      </c>
+          <t>6442276514</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
       <c r="J31" t="inlineStr">
         <is>
           <t>Masculino</t>
@@ -4639,60 +4647,56 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>06-08-1960</t>
+          <t>21-05-2010</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>ROMERO.MARTHA50@ICLOUD.COM</t>
+          <t>RL25090288@BACHILLERESDESONORA.EDU.MX</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>02-02-2026 13:57:36</t>
-        </is>
-      </c>
-      <c r="N31" t="inlineStr"/>
+          <t>16-02-2026 13:12:33</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>02-02-2026 14:04:27</t>
+          <t>16-02-2026 13:13:37</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
         <is>
-          <t>02-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T31" t="inlineStr">
-        <is>
-          <t>02-02-2026 14:03:30</t>
-        </is>
-      </c>
+          <t>16-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T31" t="inlineStr"/>
       <c r="U31" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V31" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="V31" t="inlineStr"/>
       <c r="W31" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -4700,14 +4704,14 @@
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>26150522011860001229</t>
+          <t>26150522388250001746</t>
         </is>
       </c>
       <c r="Y31" t="inlineStr"/>
       <c r="Z31" t="inlineStr"/>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr">
@@ -4724,12 +4728,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>343637</t>
+          <t>340160</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>21454</t>
+          <t>17978</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -4739,32 +4743,32 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>RICARDO FRANCISCO</t>
+          <t>ALEJANDRO</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>LEDESMA</t>
+          <t>ROMERO</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>PEDROZA</t>
+          <t>GARCIA</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>6531121344</t>
+          <t>2099007353</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>EL CHEQUE 8 S/N</t>
+          <t>PRIVADA REFORMA</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -4774,17 +4778,17 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>07-01-2006</t>
+          <t>27-03-1957</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>RICARDOPZK200@GMAIL.COM</t>
+          <t>ALEX57ROMERO@GMAIL.COM</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>14-02-2026 06:48:50</t>
+          <t>02-02-2026 14:07:14</t>
         </is>
       </c>
       <c r="N32" t="inlineStr"/>
@@ -4805,17 +4809,17 @@
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>14-02-2026 08:02:52</t>
+          <t>02-02-2026 14:09:30</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>15-03-2026 23:59:59</t>
+          <t>02-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>14-02-2026 08:01:46</t>
+          <t>02-02-2026 14:08:43</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
@@ -4825,7 +4829,7 @@
       </c>
       <c r="V32" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W32" t="inlineStr">
@@ -4835,19 +4839,11 @@
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>26150522343510001694</t>
-        </is>
-      </c>
-      <c r="Y32" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>RAUL FELIX VAZQUEZ</t>
-        </is>
-      </c>
+          <t>26150522012090001230</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr"/>
+      <c r="Z32" t="inlineStr"/>
       <c r="AA32" t="inlineStr">
         <is>
           <t>499</t>
@@ -4855,7 +4851,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>Johan Osvaldo Beltran Quiros</t>
+          <t>Juan Pablo Romero Andrade</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
@@ -4867,12 +4863,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>342867</t>
+          <t>340247</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>20684</t>
+          <t>18065</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -4882,17 +4878,17 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>MIGUEL ANGEL</t>
+          <t>LESLIE CLARETH</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AMEZCUA</t>
+          <t>VEGA</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>TORRES</t>
+          <t>QUEVEDO</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -4902,35 +4898,39 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>6674708281</t>
+          <t>6531329411</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>FLORES 22</t>
+          <t>AV NAYARIT 21</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>21-11-1995</t>
+          <t>18-08-2006</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>MIGUELAMEZCUA21@GMAIL.COM</t>
+          <t>VEGA.LESLIE.3E@GMAIL.COM</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>10-02-2026 20:37:24</t>
-        </is>
-      </c>
-      <c r="N33" t="inlineStr"/>
+          <t>02-02-2026 16:08:34</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
       <c r="O33" t="inlineStr">
         <is>
           <t>Forzoso</t>
@@ -4938,27 +4938,27 @@
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>DOMICILIADO 12 MESES $549 LE</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>12-02-2026 20:00:11</t>
+          <t>02-02-2026 16:43:55</t>
         </is>
       </c>
       <c r="S33" t="inlineStr">
         <is>
-          <t>12-03-2026 23:59:59</t>
+          <t>02-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>12-02-2026 19:59:09</t>
+          <t>02-02-2026 16:12:35</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
@@ -4978,44 +4978,36 @@
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>26150522305570001650</t>
-        </is>
-      </c>
-      <c r="Y33" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>GISSEL ANAHY REYES GERMAN</t>
-        </is>
-      </c>
+          <t>26150522017110001235</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr"/>
+      <c r="Z33" t="inlineStr"/>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Juan Eduardo Torres Alcantar</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>342562</t>
+          <t>341196</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>20379</t>
+          <t>19014</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -5025,17 +5017,17 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>AZALEA ZENYACE</t>
+          <t>ESMERALDA</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>MORENO</t>
+          <t>JAVALERA</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>CARRIZOZA</t>
+          <t>ALCANTAR</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -5045,12 +5037,12 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>6531038421</t>
+          <t>6531196345</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>CJN CHIHUAHUA 23</t>
+          <t>AV TABASCO 41</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -5060,17 +5052,17 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>23-09-1994</t>
+          <t>19-03-1975</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>ZEN_YACE94LIVE@HOTMAIL.COM</t>
+          <t>ESMERALDA.JAVALERA@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>10-02-2026 09:19:09</t>
+          <t>04-02-2026 21:09:01</t>
         </is>
       </c>
       <c r="N34" t="inlineStr"/>
@@ -5091,17 +5083,17 @@
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>12-02-2026 18:37:07</t>
+          <t>11-02-2026 15:06:43</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
         <is>
-          <t>12-03-2026 23:59:59</t>
+          <t>11-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>12-02-2026 18:33:55</t>
+          <t>11-02-2026 15:05:40</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
@@ -5121,7 +5113,7 @@
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>26150522302860001640</t>
+          <t>26150522265920001586</t>
         </is>
       </c>
       <c r="Y34" t="inlineStr">
@@ -5131,7 +5123,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>RAUL FELIX VAZQUEZ</t>
+          <t>GISSEL ANAHY REYES GERMAN</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -5141,7 +5133,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>Juan Pablo Romero Andrade</t>
+          <t>Juan Eduardo Torres Alcantar</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
@@ -5153,12 +5145,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>344062</t>
+          <t>341271</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>21879</t>
+          <t>19089</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -5168,17 +5160,17 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>RAYMUNDO ISRAEL</t>
+          <t>NICOLLE</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>LOPEZ</t>
+          <t>BUSTAMANTE</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>ARREOLA</t>
+          <t>ELIZONDO</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -5188,67 +5180,75 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>6442276514</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
+          <t>6381121777</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>LOS ADOBES</t>
+        </is>
+      </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>21-05-2010</t>
+          <t>15-12-1997</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>RL25090288@BACHILLERESDESONORA.EDU.MX</t>
+          <t>NICOLLE.BUSTAMANTE@UABC.EDU.MX</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>16-02-2026 13:12:33</t>
-        </is>
-      </c>
-      <c r="N35" t="inlineStr">
-        <is>
-          <t>Tarifas 2026 LE</t>
-        </is>
-      </c>
+          <t>05-02-2026 10:43:03</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr"/>
       <c r="O35" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>16-02-2026 13:13:37</t>
+          <t>11-02-2026 13:33:23</t>
         </is>
       </c>
       <c r="S35" t="inlineStr">
         <is>
-          <t>16-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T35" t="inlineStr"/>
+          <t>11-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>11-02-2026 13:31:59</t>
+        </is>
+      </c>
       <c r="U35" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V35" t="inlineStr"/>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="W35" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -5256,14 +5256,22 @@
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>26150522388250001746</t>
-        </is>
-      </c>
-      <c r="Y35" t="inlineStr"/>
-      <c r="Z35" t="inlineStr"/>
+          <t>26150522264110001579</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>RAUL FELIX VAZQUEZ</t>
+        </is>
+      </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB35" t="inlineStr">
@@ -5280,12 +5288,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>341196</t>
+          <t>344605</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>19014</t>
+          <t>22422</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -5295,32 +5303,32 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>ESMERALDA</t>
+          <t>LIZET</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>JAVALERA</t>
+          <t>HERNANDEZ</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>ALCANTAR</t>
+          <t>MENDEZ</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>6531196345</t>
+          <t>5412729355</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>AV TABASCO 41</t>
+          <t>JALAPA B 5</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -5330,20 +5338,24 @@
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>19-03-1975</t>
+          <t>06-06-1998</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>ESMERALDA.JAVALERA@HOTMAIL.COM</t>
+          <t>ALONDRAML1998@GMAIL.COM</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>04-02-2026 21:09:01</t>
-        </is>
-      </c>
-      <c r="N36" t="inlineStr"/>
+          <t>17-02-2026 17:23:47</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>inscripcion promo 199</t>
+        </is>
+      </c>
       <c r="O36" t="inlineStr">
         <is>
           <t>Forzoso</t>
@@ -5361,17 +5373,17 @@
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>11-02-2026 15:06:43</t>
+          <t>17-02-2026 17:32:20</t>
         </is>
       </c>
       <c r="S36" t="inlineStr">
         <is>
-          <t>11-03-2026 23:59:59</t>
+          <t>17-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>11-02-2026 15:05:40</t>
+          <t>17-02-2026 17:31:40</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
@@ -5391,19 +5403,11 @@
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>26150522265920001586</t>
-        </is>
-      </c>
-      <c r="Y36" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z36" t="inlineStr">
-        <is>
-          <t>GISSEL ANAHY REYES GERMAN</t>
-        </is>
-      </c>
+          <t>26150522437780001826</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr"/>
+      <c r="Z36" t="inlineStr"/>
       <c r="AA36" t="inlineStr">
         <is>
           <t>499</t>
@@ -5411,24 +5415,24 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>Juan Eduardo Torres Alcantar</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>341271</t>
+          <t>340765</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>19089</t>
+          <t>18583</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -5438,17 +5442,17 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NICOLLE</t>
+          <t>VIVIANA</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>BUSTAMANTE</t>
+          <t>ARVAYO</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>ELIZONDO</t>
+          <t>RASCON</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -5458,12 +5462,12 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>6381121777</t>
+          <t>6531300005</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>LOS ADOBES</t>
+          <t xml:space="preserve">AV COLIMA Y MATAMOROS </t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -5473,48 +5477,52 @@
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>15-12-1997</t>
+          <t>03-01-1979</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>NICOLLE.BUSTAMANTE@UABC.EDU.MX</t>
+          <t>VIVIARVAYO@GMAIL.COM</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>05-02-2026 10:43:03</t>
-        </is>
-      </c>
-      <c r="N37" t="inlineStr"/>
+          <t>03-02-2026 18:01:17</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>No Forzoso</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>PLAN RECURRENTE PAGO INCIAL $1,449 LE</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>1449</t>
         </is>
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>11-02-2026 13:33:23</t>
+          <t>03-02-2026 18:16:20</t>
         </is>
       </c>
       <c r="S37" t="inlineStr">
         <is>
-          <t>11-03-2026 23:59:59</t>
+          <t>03-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>11-02-2026 13:31:59</t>
+          <t>03-02-2026 18:05:39</t>
         </is>
       </c>
       <c r="U37" t="inlineStr">
@@ -5524,7 +5532,7 @@
       </c>
       <c r="V37" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W37" t="inlineStr">
@@ -5534,44 +5542,36 @@
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>26150522264110001579</t>
-        </is>
-      </c>
-      <c r="Y37" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>RAUL FELIX VAZQUEZ</t>
-        </is>
-      </c>
+          <t>26150522052430001305</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr"/>
+      <c r="Z37" t="inlineStr"/>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>1449</t>
         </is>
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>Juan Pablo Romero Andrade</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>343837</t>
+          <t>340877</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>21654</t>
+          <t>18695</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -5581,17 +5581,17 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>CLAUDIA GABRIELA</t>
+          <t>HECTOR ABRAHAM</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>ROGEL</t>
+          <t>OJEDA</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>SANDOVAL</t>
+          <t>FRANCO</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -5601,35 +5601,39 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>6532075902</t>
+          <t>6532437111</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>HUERTAS 7</t>
+          <t>DALIAS 18 Y 19</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>09-12-1991</t>
+          <t>08-01-2005</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>ROGELCLAUDIA266@GMAIL.COM</t>
+          <t>ABRAHAM30510@GMAIL.COM</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>15-02-2026 12:34:47</t>
-        </is>
-      </c>
-      <c r="N38" t="inlineStr"/>
+          <t>04-02-2026 07:26:12</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
       <c r="O38" t="inlineStr">
         <is>
           <t>Forzoso</t>
@@ -5637,27 +5641,27 @@
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>DOMICILIADO 12 MESES $549 LE</t>
         </is>
       </c>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>15-02-2026 12:38:45</t>
+          <t>04-02-2026 07:29:18</t>
         </is>
       </c>
       <c r="S38" t="inlineStr">
         <is>
-          <t>15-03-2026 23:59:59</t>
+          <t>04-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T38" t="inlineStr">
         <is>
-          <t>15-02-2026 12:37:38</t>
+          <t>04-02-2026 07:28:45</t>
         </is>
       </c>
       <c r="U38" t="inlineStr">
@@ -5677,19 +5681,19 @@
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>26150522365800001718</t>
+          <t>26150522068240001330</t>
         </is>
       </c>
       <c r="Y38" t="inlineStr"/>
       <c r="Z38" t="inlineStr"/>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>Juan Pablo Romero Andrade</t>
+          <t>Martin Ramiro Quiñonez Jauregui</t>
         </is>
       </c>
       <c r="AC38" t="inlineStr">
@@ -5701,12 +5705,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>340765</t>
+          <t>342742</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>18583</t>
+          <t>20559</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -5716,17 +5720,17 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VIVIANA</t>
+          <t>KARINA</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>ARVAYO</t>
+          <t>QUILES</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>RASCON</t>
+          <t>CAMACHO</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -5736,12 +5740,12 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>6531300005</t>
+          <t>6531163674</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t xml:space="preserve">AV COLIMA Y MATAMOROS </t>
+          <t>AV PUEBLA 1RA Y HERMOSILLO</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -5751,52 +5755,48 @@
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>03-01-1979</t>
+          <t>22-02-1975</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>VIVIARVAYO@GMAIL.COM</t>
+          <t>KARINAAQUILESC1975@GMAIL.COM</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>03-02-2026 18:01:17</t>
-        </is>
-      </c>
-      <c r="N39" t="inlineStr">
-        <is>
-          <t>Tarifas 2026 LE</t>
-        </is>
-      </c>
+          <t>10-02-2026 17:14:23</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr"/>
       <c r="O39" t="inlineStr">
         <is>
-          <t>No Forzoso</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>PLAN RECURRENTE PAGO INCIAL $1,449 LE</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>1449</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>03-02-2026 18:16:20</t>
+          <t>10-02-2026 17:19:39</t>
         </is>
       </c>
       <c r="S39" t="inlineStr">
         <is>
-          <t>03-03-2026 23:59:59</t>
+          <t>10-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T39" t="inlineStr">
         <is>
-          <t>03-02-2026 18:05:39</t>
+          <t>10-02-2026 17:18:56</t>
         </is>
       </c>
       <c r="U39" t="inlineStr">
@@ -5806,7 +5806,7 @@
       </c>
       <c r="V39" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W39" t="inlineStr">
@@ -5816,36 +5816,36 @@
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>26150522052430001305</t>
+          <t>26150522239320001545</t>
         </is>
       </c>
       <c r="Y39" t="inlineStr"/>
       <c r="Z39" t="inlineStr"/>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>1449</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Martin Ramiro Quiñonez Jauregui</t>
         </is>
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>340877</t>
+          <t>343837</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>18695</t>
+          <t>21654</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -5855,17 +5855,17 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>HECTOR ABRAHAM</t>
+          <t>CLAUDIA GABRIELA</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>OJEDA</t>
+          <t>ROGEL</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>FRANCO</t>
+          <t>SANDOVAL</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -5875,39 +5875,35 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>6532437111</t>
+          <t>6532075902</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>DALIAS 18 Y 19</t>
+          <t>HUERTAS 7</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>08-01-2005</t>
+          <t>09-12-1991</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>ABRAHAM30510@GMAIL.COM</t>
+          <t>ROGELCLAUDIA266@GMAIL.COM</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>04-02-2026 07:26:12</t>
-        </is>
-      </c>
-      <c r="N40" t="inlineStr">
-        <is>
-          <t>Tarifas 2026 LE</t>
-        </is>
-      </c>
+          <t>15-02-2026 12:34:47</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr"/>
       <c r="O40" t="inlineStr">
         <is>
           <t>Forzoso</t>
@@ -5915,27 +5911,27 @@
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES $549 LE</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>04-02-2026 07:29:18</t>
+          <t>15-02-2026 12:38:45</t>
         </is>
       </c>
       <c r="S40" t="inlineStr">
         <is>
-          <t>04-03-2026 23:59:59</t>
+          <t>15-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T40" t="inlineStr">
         <is>
-          <t>04-02-2026 07:28:45</t>
+          <t>15-02-2026 12:37:38</t>
         </is>
       </c>
       <c r="U40" t="inlineStr">
@@ -5955,19 +5951,19 @@
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>26150522068240001330</t>
+          <t>26150522365800001718</t>
         </is>
       </c>
       <c r="Y40" t="inlineStr"/>
       <c r="Z40" t="inlineStr"/>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>Martin Ramiro Quiñonez Jauregui</t>
+          <t>Juan Pablo Romero Andrade</t>
         </is>
       </c>
       <c r="AC40" t="inlineStr">
@@ -5979,12 +5975,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>340779</t>
+          <t>343954</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>18597</t>
+          <t>21771</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -5994,12 +5990,12 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>CLAUDIA ITZEL</t>
+          <t>LOURDES</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t xml:space="preserve">DE LA ROSA </t>
+          <t>LOPEZ</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -6014,10 +6010,14 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>6642467640</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr"/>
+          <t>6531035239</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>C 5 DE MAYO SN</t>
+        </is>
+      </c>
       <c r="J41" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -6025,56 +6025,64 @@
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>21-11-1988</t>
+          <t>10-01-1986</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>ITZELT.DELAROSA@GMAIL.COM</t>
+          <t>LULISLOPEZ999@GMAIL.COM</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>03-02-2026 18:20:07</t>
+          <t>16-02-2026 07:40:00</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>Tarifas 2026 LE</t>
+          <t>inscripcion promo 199</t>
         </is>
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>14-02-2026 12:53:49</t>
+          <t>16-02-2026 07:43:57</t>
         </is>
       </c>
       <c r="S41" t="inlineStr">
         <is>
-          <t>14-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T41" t="inlineStr"/>
+          <t>16-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>16-02-2026 07:43:12</t>
+        </is>
+      </c>
       <c r="U41" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V41" t="inlineStr"/>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W41" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -6082,40 +6090,36 @@
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>26140522348900001443</t>
-        </is>
-      </c>
-      <c r="Y41" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
+          <t>26150522379670001736</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr"/>
       <c r="Z41" t="inlineStr"/>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Juan Eduardo Torres Alcantar</t>
         </is>
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>344605</t>
+          <t>340779</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>22422</t>
+          <t>18597</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -6125,34 +6129,30 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LIZET</t>
+          <t>CLAUDIA ITZEL</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>HERNANDEZ</t>
+          <t xml:space="preserve">DE LA ROSA </t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>MENDEZ</t>
+          <t>SANCHEZ</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>52</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>5412729355</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>JALAPA B 5</t>
-        </is>
-      </c>
+          <t>6642467640</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
       <c r="J42" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -6160,64 +6160,56 @@
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>06-06-1998</t>
+          <t>21-11-1988</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>ALONDRAML1998@GMAIL.COM</t>
+          <t>ITZELT.DELAROSA@GMAIL.COM</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>17-02-2026 17:23:47</t>
+          <t>03-02-2026 18:20:07</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>inscripcion promo 199</t>
+          <t>Tarifas 2026 LE</t>
         </is>
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>17-02-2026 17:32:20</t>
+          <t>14-02-2026 12:53:49</t>
         </is>
       </c>
       <c r="S42" t="inlineStr">
         <is>
-          <t>17-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T42" t="inlineStr">
-        <is>
-          <t>17-02-2026 17:31:40</t>
-        </is>
-      </c>
+          <t>14-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T42" t="inlineStr"/>
       <c r="U42" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V42" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="V42" t="inlineStr"/>
       <c r="W42" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -6225,14 +6217,18 @@
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>26150522437780001826</t>
-        </is>
-      </c>
-      <c r="Y42" t="inlineStr"/>
+          <t>26140522348900001443</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
       <c r="Z42" t="inlineStr"/>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB42" t="inlineStr">
@@ -6249,12 +6245,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>343954</t>
+          <t>344220</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>21771</t>
+          <t>22037</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -6264,17 +6260,17 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LOURDES</t>
+          <t>CAROLINA</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>LOPEZ</t>
+          <t>FERNANDEZ</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>SANCHEZ</t>
+          <t>GUTIERREZ</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -6284,12 +6280,12 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>6531035239</t>
+          <t>6531610904</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>C 5 DE MAYO SN</t>
+          <t>CJON COLIMA 17 Y 18</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -6299,17 +6295,17 @@
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>10-01-1986</t>
+          <t>21-01-2003</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>LULISLOPEZ999@GMAIL.COM</t>
+          <t>LINA_FDZ@ICLOUD.COM</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>16-02-2026 07:40:00</t>
+          <t>16-02-2026 17:36:28</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
@@ -6334,17 +6330,17 @@
       </c>
       <c r="R43" t="inlineStr">
         <is>
-          <t>16-02-2026 07:43:57</t>
+          <t>21-02-2026 06:49:41</t>
         </is>
       </c>
       <c r="S43" t="inlineStr">
         <is>
-          <t>16-03-2026 23:59:59</t>
+          <t>21-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T43" t="inlineStr">
         <is>
-          <t>16-02-2026 07:43:12</t>
+          <t>21-02-2026 06:48:42</t>
         </is>
       </c>
       <c r="U43" t="inlineStr">
@@ -6354,7 +6350,7 @@
       </c>
       <c r="V43" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W43" t="inlineStr">
@@ -6364,7 +6360,7 @@
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>26150522379670001736</t>
+          <t>26150522547830001961</t>
         </is>
       </c>
       <c r="Y43" t="inlineStr"/>
@@ -6376,12 +6372,12 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>Juan Eduardo Torres Alcantar</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
@@ -6515,12 +6511,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>343947</t>
+          <t>341270</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>21764</t>
+          <t>19088</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -6530,17 +6526,17 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t xml:space="preserve">FABIOLA </t>
+          <t>JUAN MANUEL</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>LUQUE</t>
+          <t>ALONZO</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>LUQUE</t>
+          <t>ARZATE</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -6550,39 +6546,35 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>6531273238</t>
+          <t>6161093843</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>AV CANADA Y 3RA</t>
+          <t>FRACC ADOBES 75</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>05-04-1986</t>
+          <t>14-02-1995</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>FABIOLALUQUE26@GMAIL.COM</t>
+          <t>JUANM_1495@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>16-02-2026 07:08:47</t>
-        </is>
-      </c>
-      <c r="N45" t="inlineStr">
-        <is>
-          <t>inscripcion promo 199</t>
-        </is>
-      </c>
+          <t>05-02-2026 10:41:41</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr"/>
       <c r="O45" t="inlineStr">
         <is>
           <t>Forzoso</t>
@@ -6600,17 +6592,17 @@
       </c>
       <c r="R45" t="inlineStr">
         <is>
-          <t>19-02-2026 07:17:57</t>
+          <t>11-02-2026 13:27:47</t>
         </is>
       </c>
       <c r="S45" t="inlineStr">
         <is>
-          <t>19-03-2026 23:59:59</t>
+          <t>11-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T45" t="inlineStr">
         <is>
-          <t>19-02-2026 07:16:55</t>
+          <t>11-02-2026 13:26:38</t>
         </is>
       </c>
       <c r="U45" t="inlineStr">
@@ -6620,7 +6612,7 @@
       </c>
       <c r="V45" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W45" t="inlineStr">
@@ -6630,7 +6622,7 @@
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>26150522487880001902</t>
+          <t>26150522264040001578</t>
         </is>
       </c>
       <c r="Y45" t="inlineStr">
@@ -6650,7 +6642,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>Martin Ramiro Quiñonez Jauregui</t>
+          <t>Juan Pablo Romero Andrade</t>
         </is>
       </c>
       <c r="AC45" t="inlineStr">
@@ -6662,12 +6654,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>344220</t>
+          <t>344190</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>22037</t>
+          <t>22007</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -6677,17 +6669,17 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>CAROLINA</t>
+          <t xml:space="preserve">SEBASTIAN </t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>FERNANDEZ</t>
+          <t>GARCIA</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>GUTIERREZ</t>
+          <t>GUERRERO</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -6697,79 +6689,67 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>6531610904</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>CJON COLIMA 17 Y 18</t>
-        </is>
-      </c>
+          <t>6531058427</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
       <c r="J46" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>21-01-2003</t>
+          <t>21-10-2009</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>LINA_FDZ@ICLOUD.COM</t>
+          <t>MONKEEX424@GMAIL.COM</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>16-02-2026 17:36:28</t>
+          <t>16-02-2026 17:04:57</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>inscripcion promo 199</t>
+          <t>Tarifas 2026 LE</t>
         </is>
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q46" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R46" t="inlineStr">
         <is>
-          <t>21-02-2026 06:49:41</t>
+          <t>18-02-2026 17:05:10</t>
         </is>
       </c>
       <c r="S46" t="inlineStr">
         <is>
-          <t>21-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T46" t="inlineStr">
-        <is>
-          <t>21-02-2026 06:48:42</t>
-        </is>
-      </c>
+          <t>18-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T46" t="inlineStr"/>
       <c r="U46" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V46" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr"/>
       <c r="W46" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -6777,24 +6757,32 @@
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>26150522547830001961</t>
-        </is>
-      </c>
-      <c r="Y46" t="inlineStr"/>
-      <c r="Z46" t="inlineStr"/>
+          <t>26150522468100001872</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>GISSEL ANAHY REYES GERMAN</t>
+        </is>
+      </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Juan Pablo Romero Andrade</t>
         </is>
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
@@ -6940,12 +6928,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>341270</t>
+          <t>342261</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>19088</t>
+          <t>20079</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -6955,17 +6943,17 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>JUAN MANUEL</t>
+          <t xml:space="preserve">VICTORIA </t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>ALONZO</t>
+          <t xml:space="preserve">ZAVALA </t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>ARZATE</t>
+          <t>BARRIENTOS</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -6975,35 +6963,39 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>6161093843</t>
+          <t>6531231721</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>FRACC ADOBES 75</t>
+          <t xml:space="preserve">HACIENDA DE LA CRUZ </t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>14-02-1995</t>
+          <t>04-04-1996</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>JUANM_1495@HOTMAIL.COM</t>
+          <t>GUADALUPEZAVALAMERCADO@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>05-02-2026 10:41:41</t>
-        </is>
-      </c>
-      <c r="N48" t="inlineStr"/>
+          <t>09-02-2026 16:34:55</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
       <c r="O48" t="inlineStr">
         <is>
           <t>Forzoso</t>
@@ -7011,27 +7003,27 @@
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>DOMICILIADO 12 MESES $549 LE</t>
         </is>
       </c>
       <c r="Q48" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R48" t="inlineStr">
         <is>
-          <t>11-02-2026 13:27:47</t>
+          <t>09-02-2026 16:37:21</t>
         </is>
       </c>
       <c r="S48" t="inlineStr">
         <is>
-          <t>11-03-2026 23:59:59</t>
+          <t>09-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T48" t="inlineStr">
         <is>
-          <t>11-02-2026 13:26:38</t>
+          <t>09-02-2026 16:36:34</t>
         </is>
       </c>
       <c r="U48" t="inlineStr">
@@ -7051,27 +7043,19 @@
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>26150522264040001578</t>
-        </is>
-      </c>
-      <c r="Y48" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z48" t="inlineStr">
-        <is>
-          <t>RAUL FELIX VAZQUEZ</t>
-        </is>
-      </c>
+          <t>26150522198880001489</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr"/>
+      <c r="Z48" t="inlineStr"/>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>Juan Pablo Romero Andrade</t>
+          <t>Johan Osvaldo Beltran Quiros</t>
         </is>
       </c>
       <c r="AC48" t="inlineStr">
@@ -7083,12 +7067,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>342261</t>
+          <t>344649</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>20079</t>
+          <t>22466</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -7098,17 +7082,17 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t xml:space="preserve">VICTORIA </t>
+          <t>ROSA MARIA</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t xml:space="preserve">ZAVALA </t>
+          <t>VALADES</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>BARRIENTOS</t>
+          <t>SARMIENTO</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -7118,12 +7102,12 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>6531231721</t>
+          <t>6864265235</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t xml:space="preserve">HACIENDA DE LA CRUZ </t>
+          <t>AV JACARANDAS 19</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -7133,22 +7117,22 @@
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>04-04-1996</t>
+          <t>26-10-1989</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>GUADALUPEZAVALAMERCADO@HOTMAIL.COM</t>
+          <t>GENERICO@GAMIL.COM</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>09-02-2026 16:34:55</t>
+          <t>17-02-2026 18:13:05</t>
         </is>
       </c>
       <c r="N49" t="inlineStr">
         <is>
-          <t>Tarifas 2026 LE</t>
+          <t>inscripcion promo 199</t>
         </is>
       </c>
       <c r="O49" t="inlineStr">
@@ -7158,27 +7142,27 @@
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES $549 LE</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q49" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R49" t="inlineStr">
         <is>
-          <t>09-02-2026 16:37:21</t>
+          <t>18-02-2026 19:06:17</t>
         </is>
       </c>
       <c r="S49" t="inlineStr">
         <is>
-          <t>09-03-2026 23:59:59</t>
+          <t>18-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T49" t="inlineStr">
         <is>
-          <t>09-02-2026 16:36:34</t>
+          <t>18-02-2026 19:05:40</t>
         </is>
       </c>
       <c r="U49" t="inlineStr">
@@ -7188,7 +7172,7 @@
       </c>
       <c r="V49" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W49" t="inlineStr">
@@ -7198,36 +7182,44 @@
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>26150522198880001489</t>
-        </is>
-      </c>
-      <c r="Y49" t="inlineStr"/>
-      <c r="Z49" t="inlineStr"/>
+          <t>26150522474170001890</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>GISSEL ANAHY REYES GERMAN</t>
+        </is>
+      </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>Johan Osvaldo Beltran Quiros</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>345080</t>
+          <t>342512</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>87245</t>
+          <t>20329</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -7237,17 +7229,17 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LIZBETH</t>
+          <t>JOSE RICARDO</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>MARTINEZ</t>
+          <t>GARCIA</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>MEJIA</t>
+          <t>ANGULO</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -7257,28 +7249,32 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>6532094330</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr"/>
+          <t>6531217599</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>CJON HIDALGO Y 47</t>
+        </is>
+      </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>01-04-2009</t>
+          <t>03-04-1976</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>LIZBETHMARTINEZMEJIAMX@GMAIL.COM</t>
+          <t>RRICARDOGARCIA34@ICLOUD.COM</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>19-02-2026 14:44:45</t>
+          <t>10-02-2026 05:34:48</t>
         </is>
       </c>
       <c r="N50" t="inlineStr">
@@ -7288,36 +7284,44 @@
       </c>
       <c r="O50" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>No Forzoso</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>RECURRENTE $649 LE</t>
         </is>
       </c>
       <c r="Q50" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>649</t>
         </is>
       </c>
       <c r="R50" t="inlineStr">
         <is>
-          <t>19-02-2026 14:46:32</t>
+          <t>11-02-2026 06:33:27</t>
         </is>
       </c>
       <c r="S50" t="inlineStr">
         <is>
-          <t>19-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T50" t="inlineStr"/>
+          <t>11-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>11-02-2026 06:32:18</t>
+        </is>
+      </c>
       <c r="U50" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V50" t="inlineStr"/>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W50" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -7325,36 +7329,44 @@
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>26150522495630001914</t>
-        </is>
-      </c>
-      <c r="Y50" t="inlineStr"/>
-      <c r="Z50" t="inlineStr"/>
+          <t>26150522257790001574</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>RAUL FELIX VAZQUEZ</t>
+        </is>
+      </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>649</t>
         </is>
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Juan Eduardo Torres Alcantar</t>
         </is>
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>342512</t>
+          <t>345080</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>20329</t>
+          <t>87245</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -7364,17 +7376,17 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>JOSE RICARDO</t>
+          <t>LIZBETH</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>GARCIA</t>
+          <t>MARTINEZ</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>ANGULO</t>
+          <t>MEJIA</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -7384,32 +7396,28 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>6531217599</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>CJON HIDALGO Y 47</t>
-        </is>
-      </c>
+          <t>6532094330</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
       <c r="J51" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>03-04-1976</t>
+          <t>01-04-2009</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>RRICARDOGARCIA34@ICLOUD.COM</t>
+          <t>LIZBETHMARTINEZMEJIAMX@GMAIL.COM</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>10-02-2026 05:34:48</t>
+          <t>19-02-2026 14:44:45</t>
         </is>
       </c>
       <c r="N51" t="inlineStr">
@@ -7419,44 +7427,36 @@
       </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t>No Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>RECURRENTE $649 LE</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q51" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R51" t="inlineStr">
         <is>
-          <t>11-02-2026 06:33:27</t>
+          <t>19-02-2026 14:46:32</t>
         </is>
       </c>
       <c r="S51" t="inlineStr">
         <is>
-          <t>11-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T51" t="inlineStr">
-        <is>
-          <t>11-02-2026 06:32:18</t>
-        </is>
-      </c>
+          <t>19-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T51" t="inlineStr"/>
       <c r="U51" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V51" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="V51" t="inlineStr"/>
       <c r="W51" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -7464,44 +7464,36 @@
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>26150522257790001574</t>
-        </is>
-      </c>
-      <c r="Y51" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z51" t="inlineStr">
-        <is>
-          <t>RAUL FELIX VAZQUEZ</t>
-        </is>
-      </c>
+          <t>26150522495630001914</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr"/>
+      <c r="Z51" t="inlineStr"/>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>Juan Eduardo Torres Alcantar</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>344190</t>
+          <t>342867</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>22007</t>
+          <t>20684</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -7511,17 +7503,17 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t xml:space="preserve">SEBASTIAN </t>
+          <t>MIGUEL ANGEL</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>GARCIA</t>
+          <t>AMEZCUA</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>GUERRERO</t>
+          <t>TORRES</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -7531,10 +7523,14 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>6531058427</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr"/>
+          <t>6674708281</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>FLORES 22</t>
+        </is>
+      </c>
       <c r="J52" t="inlineStr">
         <is>
           <t>Masculino</t>
@@ -7542,56 +7538,60 @@
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>21-10-2009</t>
+          <t>21-11-1995</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>MONKEEX424@GMAIL.COM</t>
+          <t>MIGUELAMEZCUA21@GMAIL.COM</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>16-02-2026 17:04:57</t>
-        </is>
-      </c>
-      <c r="N52" t="inlineStr">
-        <is>
-          <t>Tarifas 2026 LE</t>
-        </is>
-      </c>
+          <t>10-02-2026 20:37:24</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr"/>
       <c r="O52" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q52" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R52" t="inlineStr">
         <is>
-          <t>18-02-2026 17:05:10</t>
+          <t>12-02-2026 20:00:11</t>
         </is>
       </c>
       <c r="S52" t="inlineStr">
         <is>
-          <t>18-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T52" t="inlineStr"/>
+          <t>12-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>12-02-2026 19:59:09</t>
+        </is>
+      </c>
       <c r="U52" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="V52" t="inlineStr"/>
       <c r="W52" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -7599,7 +7599,7 @@
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>26150522468100001872</t>
+          <t>26150522305570001650</t>
         </is>
       </c>
       <c r="Y52" t="inlineStr">
@@ -7614,29 +7614,29 @@
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>Juan Pablo Romero Andrade</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>345697</t>
+          <t>344860</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>87862</t>
+          <t>22677</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -7646,17 +7646,17 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t xml:space="preserve">EMMANUEL </t>
+          <t>JUAN RAMIRO</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>SUAREZ</t>
+          <t>MELENDEZ</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>QUIROGA</t>
+          <t>AMAYA</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -7666,10 +7666,14 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>6531748406</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr"/>
+          <t>6531152328</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>CANADA Y 3RA</t>
+        </is>
+      </c>
       <c r="J53" t="inlineStr">
         <is>
           <t>Masculino</t>
@@ -7677,56 +7681,64 @@
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>05-05-2007</t>
+          <t>20-11-1998</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>JUANEMANUEL.S.Q@GMAIL.COM</t>
+          <t>AMAYAJUAN0102@GMAIL.COM</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>23-02-2026 10:30:42</t>
+          <t>18-02-2026 16:29:06</t>
         </is>
       </c>
       <c r="N53" t="inlineStr">
         <is>
-          <t>convenio 300</t>
+          <t>inscripcion promo 199</t>
         </is>
       </c>
       <c r="O53" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q53" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R53" t="inlineStr">
         <is>
-          <t>23-02-2026 10:34:37</t>
+          <t>25-02-2026 17:38:16</t>
         </is>
       </c>
       <c r="S53" t="inlineStr">
         <is>
-          <t>23-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T53" t="inlineStr"/>
+          <t>25-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>25-02-2026 17:37:43</t>
+        </is>
+      </c>
       <c r="U53" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="V53" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="W53" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -7734,36 +7746,44 @@
       </c>
       <c r="X53" t="inlineStr">
         <is>
-          <t>26150522576190001992</t>
-        </is>
-      </c>
-      <c r="Y53" t="inlineStr"/>
-      <c r="Z53" t="inlineStr"/>
+          <t>26150522660740002115</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>GISSEL ANAHY REYES GERMAN</t>
+        </is>
+      </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Juan Pablo Romero Andrade</t>
         </is>
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>344844</t>
+          <t>342828</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>22661</t>
+          <t>20645</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -7773,17 +7793,17 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LEONEL</t>
+          <t>NUBIA GUADALUPE</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>CARRILLO</t>
+          <t>SOLARES</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>ENRIQUEZ</t>
+          <t>ARVIZU</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
@@ -7793,67 +7813,75 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>4494668367</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr"/>
+          <t>6531665151</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>CARRETERA DEL VALLE</t>
+        </is>
+      </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>27-01-2010</t>
+          <t>27-09-2002</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>CARRILLO12346@GMAIL.COM</t>
+          <t>NUBIAG3@ICLOUD.COM</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>18-02-2026 15:41:40</t>
-        </is>
-      </c>
-      <c r="N54" t="inlineStr">
-        <is>
-          <t>convenio 300</t>
-        </is>
-      </c>
+          <t>10-02-2026 19:11:57</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr"/>
       <c r="O54" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q54" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R54" t="inlineStr">
         <is>
-          <t>23-02-2026 16:40:49</t>
+          <t>10-02-2026 19:16:21</t>
         </is>
       </c>
       <c r="S54" t="inlineStr">
         <is>
-          <t>23-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T54" t="inlineStr"/>
+          <t>10-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>10-02-2026 19:15:42</t>
+        </is>
+      </c>
       <c r="U54" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V54" t="inlineStr"/>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W54" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -7861,44 +7889,36 @@
       </c>
       <c r="X54" t="inlineStr">
         <is>
-          <t>26150522587950002017</t>
-        </is>
-      </c>
-      <c r="Y54" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z54" t="inlineStr">
-        <is>
-          <t>GISSEL ANAHY REYES GERMAN</t>
-        </is>
-      </c>
+          <t>26150522246290001554</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr"/>
+      <c r="Z54" t="inlineStr"/>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Johan Osvaldo Beltran Quiros</t>
         </is>
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>342828</t>
+          <t>342499</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>20645</t>
+          <t>20316</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -7908,17 +7928,17 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NUBIA GUADALUPE</t>
+          <t>ALBERTO</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>SOLARES</t>
+          <t>VINIEGRA</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>ARVIZU</t>
+          <t>BERMUDEZ</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
@@ -7928,32 +7948,32 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>6531665151</t>
+          <t>6532096000</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>CARRETERA DEL VALLE</t>
+          <t>COLIMA C 26</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>27-09-2002</t>
+          <t>20-05-1981</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>NUBIAG3@ICLOUD.COM</t>
+          <t>VIVESISTEMS@GMAIL.COM</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>10-02-2026 19:11:57</t>
+          <t>09-02-2026 21:13:12</t>
         </is>
       </c>
       <c r="N55" t="inlineStr"/>
@@ -7974,17 +7994,17 @@
       </c>
       <c r="R55" t="inlineStr">
         <is>
-          <t>10-02-2026 19:16:21</t>
+          <t>11-02-2026 21:02:27</t>
         </is>
       </c>
       <c r="S55" t="inlineStr">
         <is>
-          <t>10-03-2026 23:59:59</t>
+          <t>11-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T55" t="inlineStr">
         <is>
-          <t>10-02-2026 19:15:42</t>
+          <t>11-02-2026 21:01:55</t>
         </is>
       </c>
       <c r="U55" t="inlineStr">
@@ -8004,11 +8024,19 @@
       </c>
       <c r="X55" t="inlineStr">
         <is>
-          <t>26150522246290001554</t>
-        </is>
-      </c>
-      <c r="Y55" t="inlineStr"/>
-      <c r="Z55" t="inlineStr"/>
+          <t>26150522279160001614</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z55" t="inlineStr">
+        <is>
+          <t>GISSEL ANAHY REYES GERMAN</t>
+        </is>
+      </c>
       <c r="AA55" t="inlineStr">
         <is>
           <t>499</t>
@@ -8016,7 +8044,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>Johan Osvaldo Beltran Quiros</t>
+          <t>Juan Pablo Romero Andrade</t>
         </is>
       </c>
       <c r="AC55" t="inlineStr">
@@ -8028,12 +8056,12 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>344649</t>
+          <t>342548</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>22466</t>
+          <t>20365</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -8043,17 +8071,17 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>ROSA MARIA</t>
+          <t>CECILIA GUADALUPE</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>VALADES</t>
+          <t>CORRAL</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>SARMIENTO</t>
+          <t>MEDINA</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
@@ -8063,12 +8091,12 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>6864265235</t>
+          <t>6621711231</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>AV JACARANDAS 19</t>
+          <t>JUAREZ Y 20</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
@@ -8078,52 +8106,52 @@
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>26-10-1989</t>
+          <t>06-08-1998</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>GENERICO@GAMIL.COM</t>
+          <t>CECIGPE98@GMAIL.COM</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>17-02-2026 18:13:05</t>
+          <t>10-02-2026 08:25:29</t>
         </is>
       </c>
       <c r="N56" t="inlineStr">
         <is>
-          <t>inscripcion promo 199</t>
+          <t>Tarifas 2026 LE</t>
         </is>
       </c>
       <c r="O56" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>No Forzoso</t>
         </is>
       </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>RECURRENTE $649 LE</t>
         </is>
       </c>
       <c r="Q56" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>649</t>
         </is>
       </c>
       <c r="R56" t="inlineStr">
         <is>
-          <t>18-02-2026 19:06:17</t>
+          <t>10-02-2026 08:31:37</t>
         </is>
       </c>
       <c r="S56" t="inlineStr">
         <is>
-          <t>18-03-2026 23:59:59</t>
+          <t>10-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T56" t="inlineStr">
         <is>
-          <t>18-02-2026 19:05:40</t>
+          <t>10-02-2026 08:30:41</t>
         </is>
       </c>
       <c r="U56" t="inlineStr">
@@ -8143,44 +8171,36 @@
       </c>
       <c r="X56" t="inlineStr">
         <is>
-          <t>26150522474170001890</t>
-        </is>
-      </c>
-      <c r="Y56" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z56" t="inlineStr">
-        <is>
-          <t>GISSEL ANAHY REYES GERMAN</t>
-        </is>
-      </c>
+          <t>26150522225760001528</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr"/>
+      <c r="Z56" t="inlineStr"/>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>649</t>
         </is>
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Juan Eduardo Torres Alcantar</t>
         </is>
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>342499</t>
+          <t>342846</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>20316</t>
+          <t>20663</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -8190,17 +8210,17 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>ALBERTO</t>
+          <t>CARLOS JULIAN</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>VINIEGRA</t>
+          <t>NUÑEZ</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>BERMUDEZ</t>
+          <t>ROMERO</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -8210,32 +8230,32 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>6532096000</t>
+          <t>6531308246</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>COLIMA C 26</t>
+          <t>TORREON 4 Y 5</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>20-05-1981</t>
+          <t>29-08-2000</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>VIVESISTEMS@GMAIL.COM</t>
+          <t>EJNR2E@GMAIL.COM</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>09-02-2026 21:13:12</t>
+          <t>10-02-2026 19:39:03</t>
         </is>
       </c>
       <c r="N57" t="inlineStr"/>
@@ -8256,7 +8276,7 @@
       </c>
       <c r="R57" t="inlineStr">
         <is>
-          <t>11-02-2026 21:02:27</t>
+          <t>11-02-2026 19:15:15</t>
         </is>
       </c>
       <c r="S57" t="inlineStr">
@@ -8266,7 +8286,7 @@
       </c>
       <c r="T57" t="inlineStr">
         <is>
-          <t>11-02-2026 21:01:55</t>
+          <t>11-02-2026 19:14:37</t>
         </is>
       </c>
       <c r="U57" t="inlineStr">
@@ -8286,7 +8306,7 @@
       </c>
       <c r="X57" t="inlineStr">
         <is>
-          <t>26150522279160001614</t>
+          <t>26150522276380001607</t>
         </is>
       </c>
       <c r="Y57" t="inlineStr">
@@ -8318,12 +8338,12 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>342548</t>
+          <t>342849</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>20365</t>
+          <t>20666</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -8333,17 +8353,17 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>CECILIA GUADALUPE</t>
+          <t xml:space="preserve">PAOLA </t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>CORRAL</t>
+          <t>ALONSO</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>MEDINA</t>
+          <t>MANRIQUEZ</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
@@ -8353,12 +8373,12 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>6621711231</t>
+          <t>6535395572</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>JUAREZ Y 20</t>
+          <t>CJN KINO 33</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
@@ -8368,52 +8388,48 @@
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>06-08-1998</t>
+          <t>13-12-1999</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>CECIGPE98@GMAIL.COM</t>
+          <t>PAOLAALONSOMGZ@GMAIL.COM</t>
         </is>
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>10-02-2026 08:25:29</t>
-        </is>
-      </c>
-      <c r="N58" t="inlineStr">
-        <is>
-          <t>Tarifas 2026 LE</t>
-        </is>
-      </c>
+          <t>10-02-2026 19:41:46</t>
+        </is>
+      </c>
+      <c r="N58" t="inlineStr"/>
       <c r="O58" t="inlineStr">
         <is>
-          <t>No Forzoso</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>RECURRENTE $649 LE</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q58" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R58" t="inlineStr">
         <is>
-          <t>10-02-2026 08:31:37</t>
+          <t>11-02-2026 19:11:46</t>
         </is>
       </c>
       <c r="S58" t="inlineStr">
         <is>
-          <t>10-03-2026 23:59:59</t>
+          <t>11-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T58" t="inlineStr">
         <is>
-          <t>10-02-2026 08:30:41</t>
+          <t>11-02-2026 19:10:56</t>
         </is>
       </c>
       <c r="U58" t="inlineStr">
@@ -8433,19 +8449,27 @@
       </c>
       <c r="X58" t="inlineStr">
         <is>
-          <t>26150522225760001528</t>
-        </is>
-      </c>
-      <c r="Y58" t="inlineStr"/>
-      <c r="Z58" t="inlineStr"/>
+          <t>26150522276280001606</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z58" t="inlineStr">
+        <is>
+          <t>GISSEL ANAHY REYES GERMAN</t>
+        </is>
+      </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>Juan Eduardo Torres Alcantar</t>
+          <t>Juan Pablo Romero Andrade</t>
         </is>
       </c>
       <c r="AC58" t="inlineStr">
@@ -8457,12 +8481,12 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>342846</t>
+          <t>344844</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>20663</t>
+          <t>22661</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -8472,17 +8496,17 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>CARLOS JULIAN</t>
+          <t>LEONEL</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>NUÑEZ</t>
+          <t>CARRILLO</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>ROMERO</t>
+          <t>ENRIQUEZ</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
@@ -8492,75 +8516,67 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>6531308246</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>TORREON 4 Y 5</t>
-        </is>
-      </c>
+          <t>4494668367</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
       <c r="J59" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>29-08-2000</t>
+          <t>27-01-2010</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>EJNR2E@GMAIL.COM</t>
+          <t>CARRILLO12346@GMAIL.COM</t>
         </is>
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>10-02-2026 19:39:03</t>
-        </is>
-      </c>
-      <c r="N59" t="inlineStr"/>
+          <t>18-02-2026 15:41:40</t>
+        </is>
+      </c>
+      <c r="N59" t="inlineStr">
+        <is>
+          <t>convenio 300</t>
+        </is>
+      </c>
       <c r="O59" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q59" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R59" t="inlineStr">
         <is>
-          <t>11-02-2026 19:15:15</t>
+          <t>23-02-2026 16:40:49</t>
         </is>
       </c>
       <c r="S59" t="inlineStr">
         <is>
-          <t>11-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T59" t="inlineStr">
-        <is>
-          <t>11-02-2026 19:14:37</t>
-        </is>
-      </c>
+          <t>23-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T59" t="inlineStr"/>
       <c r="U59" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V59" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="V59" t="inlineStr"/>
       <c r="W59" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -8568,7 +8584,7 @@
       </c>
       <c r="X59" t="inlineStr">
         <is>
-          <t>26150522276380001607</t>
+          <t>26150522587950002017</t>
         </is>
       </c>
       <c r="Y59" t="inlineStr">
@@ -8583,29 +8599,29 @@
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>Juan Pablo Romero Andrade</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>342849</t>
+          <t>346596</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>20666</t>
+          <t>88761</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -8615,17 +8631,17 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t xml:space="preserve">PAOLA </t>
+          <t>BRAYAN FEDERICO</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>ALONSO</t>
+          <t>GARCIA</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>MANRIQUEZ</t>
+          <t>GONZALEZ</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
@@ -8635,35 +8651,39 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>6535395572</t>
+          <t>6861229499</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>CJN KINO 33</t>
+          <t>CAMELIAS B 26 Y 27</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>13-12-1999</t>
+          <t>05-09-2004</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>PAOLAALONSOMGZ@GMAIL.COM</t>
+          <t>BRAYANFEDERICOGARCIAGONZALEZ@GMAIL.COM</t>
         </is>
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>10-02-2026 19:41:46</t>
-        </is>
-      </c>
-      <c r="N60" t="inlineStr"/>
+          <t>25-02-2026 19:36:04</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>inscripcion promo 199</t>
+        </is>
+      </c>
       <c r="O60" t="inlineStr">
         <is>
           <t>Forzoso</t>
@@ -8681,17 +8701,17 @@
       </c>
       <c r="R60" t="inlineStr">
         <is>
-          <t>11-02-2026 19:11:46</t>
+          <t>25-02-2026 19:37:35</t>
         </is>
       </c>
       <c r="S60" t="inlineStr">
         <is>
-          <t>11-03-2026 23:59:59</t>
+          <t>25-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T60" t="inlineStr">
         <is>
-          <t>11-02-2026 19:10:56</t>
+          <t>25-02-2026 19:37:02</t>
         </is>
       </c>
       <c r="U60" t="inlineStr">
@@ -8711,19 +8731,11 @@
       </c>
       <c r="X60" t="inlineStr">
         <is>
-          <t>26150522276280001606</t>
-        </is>
-      </c>
-      <c r="Y60" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z60" t="inlineStr">
-        <is>
-          <t>GISSEL ANAHY REYES GERMAN</t>
-        </is>
-      </c>
+          <t>26150522666520002129</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr"/>
+      <c r="Z60" t="inlineStr"/>
       <c r="AA60" t="inlineStr">
         <is>
           <t>499</t>
@@ -8731,24 +8743,24 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>Juan Pablo Romero Andrade</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC60" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>343958</t>
+          <t>346597</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>21775</t>
+          <t>88762</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -8758,32 +8770,32 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>ELIZABETH</t>
+          <t>FLOR MAYTTE</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>FLORES</t>
+          <t>HERNANDEZ</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>HERAS</t>
+          <t>ORTIZ</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>6531288733</t>
+          <t>9285501292</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>CJON FLORES Y C 16 SN</t>
+          <t>ESCALONIAS Y 26</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
@@ -8793,52 +8805,52 @@
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>03-02-1988</t>
+          <t>27-07-2005</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>VICTORIALLAMAS2000@GMEIL.COM</t>
+          <t>FLORANTIZ05@GMAIL.COM</t>
         </is>
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>16-02-2026 07:59:39</t>
+          <t>25-02-2026 19:39:33</t>
         </is>
       </c>
       <c r="N61" t="inlineStr">
         <is>
-          <t>Tarifas 2026 LE</t>
+          <t>inscripcion promo 199</t>
         </is>
       </c>
       <c r="O61" t="inlineStr">
         <is>
-          <t>No Forzoso</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>RECURRENTE $649 LE</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q61" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R61" t="inlineStr">
         <is>
-          <t>16-02-2026 08:07:18</t>
+          <t>25-02-2026 19:44:17</t>
         </is>
       </c>
       <c r="S61" t="inlineStr">
         <is>
-          <t>16-03-2026 23:59:59</t>
+          <t>25-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T61" t="inlineStr">
         <is>
-          <t>16-02-2026 08:06:23</t>
+          <t>25-02-2026 19:43:32</t>
         </is>
       </c>
       <c r="U61" t="inlineStr">
@@ -8858,14 +8870,14 @@
       </c>
       <c r="X61" t="inlineStr">
         <is>
-          <t>26150522380380001737</t>
+          <t>26150522666760002130</t>
         </is>
       </c>
       <c r="Y61" t="inlineStr"/>
       <c r="Z61" t="inlineStr"/>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB61" t="inlineStr">
@@ -9009,12 +9021,12 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Juan Pablo Romero Andrade</t>
         </is>
       </c>
       <c r="AC62" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
@@ -9164,12 +9176,12 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>343531</t>
+          <t>343947</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>21348</t>
+          <t>21764</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -9179,17 +9191,17 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>URIEL IGNACIO</t>
+          <t xml:space="preserve">FABIOLA </t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>SID</t>
+          <t>LUQUE</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>AREVALO</t>
+          <t>LUQUE</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
@@ -9199,35 +9211,39 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>6531071848</t>
+          <t>6531273238</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>FELIX CONTRERAS 44</t>
+          <t>AV CANADA Y 3RA</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>02-06-2005</t>
+          <t>05-04-1986</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>URIELIGNACIOSIDDAVERALO@GMAIL.COM</t>
+          <t>FABIOLALUQUE26@GMAIL.COM</t>
         </is>
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>13-02-2026 16:28:37</t>
-        </is>
-      </c>
-      <c r="N64" t="inlineStr"/>
+          <t>16-02-2026 07:08:47</t>
+        </is>
+      </c>
+      <c r="N64" t="inlineStr">
+        <is>
+          <t>inscripcion promo 199</t>
+        </is>
+      </c>
       <c r="O64" t="inlineStr">
         <is>
           <t>Forzoso</t>
@@ -9245,17 +9261,17 @@
       </c>
       <c r="R64" t="inlineStr">
         <is>
-          <t>13-02-2026 16:34:53</t>
+          <t>19-02-2026 07:17:57</t>
         </is>
       </c>
       <c r="S64" t="inlineStr">
         <is>
-          <t>13-03-2026 23:59:59</t>
+          <t>19-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T64" t="inlineStr">
         <is>
-          <t>13-02-2026 16:34:13</t>
+          <t>19-02-2026 07:16:55</t>
         </is>
       </c>
       <c r="U64" t="inlineStr">
@@ -9275,11 +9291,19 @@
       </c>
       <c r="X64" t="inlineStr">
         <is>
-          <t>26150522324410001674</t>
-        </is>
-      </c>
-      <c r="Y64" t="inlineStr"/>
-      <c r="Z64" t="inlineStr"/>
+          <t>26150522487880001902</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z64" t="inlineStr">
+        <is>
+          <t>RAUL FELIX VAZQUEZ</t>
+        </is>
+      </c>
       <c r="AA64" t="inlineStr">
         <is>
           <t>499</t>
@@ -9287,7 +9311,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>Juan Pablo Romero Andrade</t>
+          <t>Martin Ramiro Quiñonez Jauregui</t>
         </is>
       </c>
       <c r="AC64" t="inlineStr">
@@ -9299,12 +9323,12 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>343813</t>
+          <t>343958</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>21630</t>
+          <t>21775</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -9314,17 +9338,17 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>YOCELIN DEL CARMEN</t>
+          <t>ELIZABETH</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>LOPEZ</t>
+          <t>FLORES</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>VALENZUELA</t>
+          <t>HERAS</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
@@ -9334,12 +9358,12 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>6531305359</t>
+          <t>6531288733</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>AV CARRANZA 36</t>
+          <t>CJON FLORES Y C 16 SN</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
@@ -9349,48 +9373,52 @@
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>16-07-1999</t>
+          <t>03-02-1988</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>YOCELINLOPEZ490@GMAIL.COM</t>
+          <t>VICTORIALLAMAS2000@GMEIL.COM</t>
         </is>
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>15-02-2026 11:25:12</t>
-        </is>
-      </c>
-      <c r="N65" t="inlineStr"/>
+          <t>16-02-2026 07:59:39</t>
+        </is>
+      </c>
+      <c r="N65" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
       <c r="O65" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>No Forzoso</t>
         </is>
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>RECURRENTE $649 LE</t>
         </is>
       </c>
       <c r="Q65" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>649</t>
         </is>
       </c>
       <c r="R65" t="inlineStr">
         <is>
-          <t>15-02-2026 11:31:12</t>
+          <t>16-02-2026 08:07:18</t>
         </is>
       </c>
       <c r="S65" t="inlineStr">
         <is>
-          <t>15-03-2026 23:59:59</t>
+          <t>16-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T65" t="inlineStr">
         <is>
-          <t>15-02-2026 11:29:38</t>
+          <t>16-02-2026 08:06:23</t>
         </is>
       </c>
       <c r="U65" t="inlineStr">
@@ -9410,36 +9438,36 @@
       </c>
       <c r="X65" t="inlineStr">
         <is>
-          <t>26150522364500001715</t>
+          <t>26150522380380001737</t>
         </is>
       </c>
       <c r="Y65" t="inlineStr"/>
       <c r="Z65" t="inlineStr"/>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>649</t>
         </is>
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>Juan Pablo Romero Andrade</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC65" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>345101</t>
+          <t>343531</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>87266</t>
+          <t>21348</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -9449,17 +9477,17 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>CAMILA</t>
+          <t>URIEL IGNACIO</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>VASQUEZ</t>
+          <t>SID</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>LOPEZ</t>
+          <t>AREVALO</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
@@ -9469,67 +9497,75 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>6531040237</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr"/>
+          <t>6531071848</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>FELIX CONTRERAS 44</t>
+        </is>
+      </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>08-10-2007</t>
+          <t>02-06-2005</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>VASQUEZLOPEZCAMILA@GMAIL.COM</t>
+          <t>URIELIGNACIOSIDDAVERALO@GMAIL.COM</t>
         </is>
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>19-02-2026 15:31:29</t>
-        </is>
-      </c>
-      <c r="N66" t="inlineStr">
-        <is>
-          <t>Tarifas 2026 LE</t>
-        </is>
-      </c>
+          <t>13-02-2026 16:28:37</t>
+        </is>
+      </c>
+      <c r="N66" t="inlineStr"/>
       <c r="O66" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>3 MESES $1,899</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q66" t="inlineStr">
         <is>
-          <t>633</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R66" t="inlineStr">
         <is>
-          <t>19-02-2026 15:34:34</t>
+          <t>13-02-2026 16:34:53</t>
         </is>
       </c>
       <c r="S66" t="inlineStr">
         <is>
-          <t>19-05-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T66" t="inlineStr"/>
+          <t>13-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>13-02-2026 16:34:13</t>
+        </is>
+      </c>
       <c r="U66" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="V66" t="inlineStr"/>
       <c r="W66" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -9537,19 +9573,19 @@
       </c>
       <c r="X66" t="inlineStr">
         <is>
-          <t>26150522497060001917</t>
+          <t>26150522324410001674</t>
         </is>
       </c>
       <c r="Y66" t="inlineStr"/>
       <c r="Z66" t="inlineStr"/>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>1899</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>Johan Osvaldo Beltran Quiros</t>
+          <t>Juan Pablo Romero Andrade</t>
         </is>
       </c>
       <c r="AC66" t="inlineStr">
@@ -9561,12 +9597,12 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>345985</t>
+          <t>343813</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>88150</t>
+          <t>21630</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -9576,17 +9612,17 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LUZ</t>
+          <t>YOCELIN DEL CARMEN</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>MENESES</t>
+          <t>LOPEZ</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>MENESES</t>
+          <t>VALENZUELA</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
@@ -9596,10 +9632,14 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>6531109304</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr"/>
+          <t>6531305359</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>AV CARRANZA 36</t>
+        </is>
+      </c>
       <c r="J67" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -9607,56 +9647,60 @@
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>28-02-2010</t>
+          <t>16-07-1999</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>LUZMENESES2810@GMAIL.COM</t>
+          <t>YOCELINLOPEZ490@GMAIL.COM</t>
         </is>
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>23-02-2026 18:29:05</t>
-        </is>
-      </c>
-      <c r="N67" t="inlineStr">
-        <is>
-          <t>Tarifas 2026 LE</t>
-        </is>
-      </c>
+          <t>15-02-2026 11:25:12</t>
+        </is>
+      </c>
+      <c r="N67" t="inlineStr"/>
       <c r="O67" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>1 MES $899</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q67" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R67" t="inlineStr">
         <is>
-          <t>23-02-2026 18:30:15</t>
+          <t>15-02-2026 11:31:12</t>
         </is>
       </c>
       <c r="S67" t="inlineStr">
         <is>
-          <t>23-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T67" t="inlineStr"/>
+          <t>15-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>15-02-2026 11:29:38</t>
+        </is>
+      </c>
       <c r="U67" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="V67" t="inlineStr"/>
       <c r="W67" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -9664,36 +9708,36 @@
       </c>
       <c r="X67" t="inlineStr">
         <is>
-          <t>26150522595820002029</t>
+          <t>26150522364500001715</t>
         </is>
       </c>
       <c r="Y67" t="inlineStr"/>
       <c r="Z67" t="inlineStr"/>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Juan Pablo Romero Andrade</t>
         </is>
       </c>
       <c r="AC67" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>344583</t>
+          <t>345101</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>22400</t>
+          <t>87266</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -9703,17 +9747,17 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t xml:space="preserve">CARLOS </t>
+          <t>CAMILA</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>ACOSTA</t>
+          <t>VASQUEZ</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>SANTOS</t>
+          <t>LOPEZ</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
@@ -9723,79 +9767,67 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>6531202025</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr">
-        <is>
-          <t>AV NUEVO LEON 9</t>
-        </is>
-      </c>
+          <t>6531040237</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
       <c r="J68" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>04-03-2005</t>
+          <t>08-10-2007</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>TZELI9535@GMAIL.COM</t>
+          <t>VASQUEZLOPEZCAMILA@GMAIL.COM</t>
         </is>
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>17-02-2026 16:50:12</t>
+          <t>19-02-2026 15:31:29</t>
         </is>
       </c>
       <c r="N68" t="inlineStr">
         <is>
-          <t>inscripcion promo 199</t>
+          <t>Tarifas 2026 LE</t>
         </is>
       </c>
       <c r="O68" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>3 MESES $1,899</t>
         </is>
       </c>
       <c r="Q68" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>633</t>
         </is>
       </c>
       <c r="R68" t="inlineStr">
         <is>
-          <t>19-02-2026 17:11:32</t>
+          <t>19-02-2026 15:34:34</t>
         </is>
       </c>
       <c r="S68" t="inlineStr">
         <is>
-          <t>19-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T68" t="inlineStr">
-        <is>
-          <t>19-02-2026 17:10:51</t>
-        </is>
-      </c>
+          <t>19-05-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T68" t="inlineStr"/>
       <c r="U68" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V68" t="inlineStr">
-        <is>
           <t>1</t>
         </is>
       </c>
+      <c r="V68" t="inlineStr"/>
       <c r="W68" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -9803,22 +9835,14 @@
       </c>
       <c r="X68" t="inlineStr">
         <is>
-          <t>26150522500690001919</t>
-        </is>
-      </c>
-      <c r="Y68" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z68" t="inlineStr">
-        <is>
-          <t>GISSEL ANAHY REYES GERMAN</t>
-        </is>
-      </c>
+          <t>26150522497060001917</t>
+        </is>
+      </c>
+      <c r="Y68" t="inlineStr"/>
+      <c r="Z68" t="inlineStr"/>
       <c r="AA68" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>1899</t>
         </is>
       </c>
       <c r="AB68" t="inlineStr">
@@ -9835,12 +9859,12 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>344507</t>
+          <t>344583</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>22324</t>
+          <t>22400</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -9850,17 +9874,17 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>KAREN ANDREA</t>
+          <t xml:space="preserve">CARLOS </t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>ISAIS</t>
+          <t>ACOSTA</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>QUILES</t>
+          <t>SANTOS</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
@@ -9870,67 +9894,67 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>6531517509</t>
+          <t>6531202025</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>AV PUEBLA 1RA</t>
+          <t>AV NUEVO LEON 9</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>12-02-1999</t>
+          <t>04-03-2005</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>KARENANDREAISAIS1999@GMAIL.COM</t>
+          <t>TZELI9535@GMAIL.COM</t>
         </is>
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>17-02-2026 14:45:48</t>
+          <t>17-02-2026 16:50:12</t>
         </is>
       </c>
       <c r="N69" t="inlineStr">
         <is>
-          <t>Tarifas 2026 LE</t>
+          <t>inscripcion promo 199</t>
         </is>
       </c>
       <c r="O69" t="inlineStr">
         <is>
-          <t>No Forzoso</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P69" t="inlineStr">
         <is>
-          <t>PLAN RECURRENTE PAGO INCIAL $1,449 LE</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q69" t="inlineStr">
         <is>
-          <t>1449</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R69" t="inlineStr">
         <is>
-          <t>17-02-2026 14:50:44</t>
+          <t>19-02-2026 17:11:32</t>
         </is>
       </c>
       <c r="S69" t="inlineStr">
         <is>
-          <t>17-03-2026 23:59:59</t>
+          <t>19-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T69" t="inlineStr">
         <is>
-          <t>17-02-2026 14:49:35</t>
+          <t>19-02-2026 17:10:51</t>
         </is>
       </c>
       <c r="U69" t="inlineStr">
@@ -9950,171 +9974,981 @@
       </c>
       <c r="X69" t="inlineStr">
         <is>
-          <t>26150522430060001816</t>
-        </is>
-      </c>
-      <c r="Y69" t="inlineStr"/>
-      <c r="Z69" t="inlineStr"/>
+          <t>26150522500690001919</t>
+        </is>
+      </c>
+      <c r="Y69" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z69" t="inlineStr">
+        <is>
+          <t>GISSEL ANAHY REYES GERMAN</t>
+        </is>
+      </c>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>1449</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Johan Osvaldo Beltran Quiros</t>
         </is>
       </c>
       <c r="AC69" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
+          <t>345697</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>87862</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>SAN LUIS</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EMMANUEL </t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>SUAREZ</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>QUIROGA</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>6531748406</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>05-05-2007</t>
+        </is>
+      </c>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>JUANEMANUEL.S.Q@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>23-02-2026 10:30:42</t>
+        </is>
+      </c>
+      <c r="N70" t="inlineStr">
+        <is>
+          <t>convenio 300</t>
+        </is>
+      </c>
+      <c r="O70" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>CONVENIOS $549</t>
+        </is>
+      </c>
+      <c r="Q70" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R70" t="inlineStr">
+        <is>
+          <t>23-02-2026 10:34:37</t>
+        </is>
+      </c>
+      <c r="S70" t="inlineStr">
+        <is>
+          <t>23-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T70" t="inlineStr"/>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr"/>
+      <c r="W70" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X70" t="inlineStr">
+        <is>
+          <t>26150522576190001992</t>
+        </is>
+      </c>
+      <c r="Y70" t="inlineStr"/>
+      <c r="Z70" t="inlineStr"/>
+      <c r="AA70" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB70" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC70" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>345808</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>87973</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>SAN LUIS</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t xml:space="preserve">JESUS MANUEL </t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GARCIA </t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>MONTAÑO</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>6531557014</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr"/>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>25-12-1981</t>
+        </is>
+      </c>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>CHUMA0292@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>23-02-2026 14:45:30</t>
+        </is>
+      </c>
+      <c r="N71" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
+      <c r="O71" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>1 MES $899</t>
+        </is>
+      </c>
+      <c r="Q71" t="inlineStr">
+        <is>
+          <t>899</t>
+        </is>
+      </c>
+      <c r="R71" t="inlineStr">
+        <is>
+          <t>25-02-2026 14:28:08</t>
+        </is>
+      </c>
+      <c r="S71" t="inlineStr">
+        <is>
+          <t>25-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T71" t="inlineStr"/>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr"/>
+      <c r="W71" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X71" t="inlineStr">
+        <is>
+          <t>26150522653580002100</t>
+        </is>
+      </c>
+      <c r="Y71" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z71" t="inlineStr">
+        <is>
+          <t>GISSEL ANAHY REYES GERMAN</t>
+        </is>
+      </c>
+      <c r="AA71" t="inlineStr">
+        <is>
+          <t>899</t>
+        </is>
+      </c>
+      <c r="AB71" t="inlineStr">
+        <is>
+          <t>Juan Pablo Romero Andrade</t>
+        </is>
+      </c>
+      <c r="AC71" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>345926</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>88091</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>SAN LUIS</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>PAOLA STEPHANY</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>ROBLES</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>OLIVARRIA</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>6531333751</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr"/>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>06-06-1988</t>
+        </is>
+      </c>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>PAOLAS.ROBLES@OUTLOOK.COM</t>
+        </is>
+      </c>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>23-02-2026 17:33:51</t>
+        </is>
+      </c>
+      <c r="N72" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
+      <c r="O72" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>1 MES $899</t>
+        </is>
+      </c>
+      <c r="Q72" t="inlineStr">
+        <is>
+          <t>899</t>
+        </is>
+      </c>
+      <c r="R72" t="inlineStr">
+        <is>
+          <t>25-02-2026 17:32:24</t>
+        </is>
+      </c>
+      <c r="S72" t="inlineStr">
+        <is>
+          <t>25-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T72" t="inlineStr"/>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V72" t="inlineStr"/>
+      <c r="W72" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X72" t="inlineStr">
+        <is>
+          <t>26150522660500002114</t>
+        </is>
+      </c>
+      <c r="Y72" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z72" t="inlineStr">
+        <is>
+          <t>MANUEL DIAZ RECEPCION</t>
+        </is>
+      </c>
+      <c r="AA72" t="inlineStr">
+        <is>
+          <t>899</t>
+        </is>
+      </c>
+      <c r="AB72" t="inlineStr">
+        <is>
+          <t>Juan Pablo Romero Andrade</t>
+        </is>
+      </c>
+      <c r="AC72" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>345985</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>88150</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>SAN LUIS</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>LUZ</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>MENESES</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>MENESES</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>6531109304</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr"/>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>28-02-2010</t>
+        </is>
+      </c>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>LUZMENESES2810@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>23-02-2026 18:29:05</t>
+        </is>
+      </c>
+      <c r="N73" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
+      <c r="O73" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>1 MES $899</t>
+        </is>
+      </c>
+      <c r="Q73" t="inlineStr">
+        <is>
+          <t>899</t>
+        </is>
+      </c>
+      <c r="R73" t="inlineStr">
+        <is>
+          <t>23-02-2026 18:30:15</t>
+        </is>
+      </c>
+      <c r="S73" t="inlineStr">
+        <is>
+          <t>23-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T73" t="inlineStr"/>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V73" t="inlineStr"/>
+      <c r="W73" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X73" t="inlineStr">
+        <is>
+          <t>26150522595820002029</t>
+        </is>
+      </c>
+      <c r="Y73" t="inlineStr"/>
+      <c r="Z73" t="inlineStr"/>
+      <c r="AA73" t="inlineStr">
+        <is>
+          <t>899</t>
+        </is>
+      </c>
+      <c r="AB73" t="inlineStr">
+        <is>
+          <t>Juan Pablo Romero Andrade</t>
+        </is>
+      </c>
+      <c r="AC73" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>344507</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>22324</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>SAN LUIS</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>KAREN ANDREA</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>ISAIS</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>QUILES</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>6531517509</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>AV PUEBLA 1RA</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>12-02-1999</t>
+        </is>
+      </c>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>KARENANDREAISAIS1999@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>17-02-2026 14:45:48</t>
+        </is>
+      </c>
+      <c r="N74" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
+      <c r="O74" t="inlineStr">
+        <is>
+          <t>No Forzoso</t>
+        </is>
+      </c>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>PLAN RECURRENTE PAGO INCIAL $1,449 LE</t>
+        </is>
+      </c>
+      <c r="Q74" t="inlineStr">
+        <is>
+          <t>1449</t>
+        </is>
+      </c>
+      <c r="R74" t="inlineStr">
+        <is>
+          <t>17-02-2026 14:50:44</t>
+        </is>
+      </c>
+      <c r="S74" t="inlineStr">
+        <is>
+          <t>17-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>17-02-2026 14:49:35</t>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V74" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W74" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X74" t="inlineStr">
+        <is>
+          <t>26150522430060001816</t>
+        </is>
+      </c>
+      <c r="Y74" t="inlineStr"/>
+      <c r="Z74" t="inlineStr"/>
+      <c r="AA74" t="inlineStr">
+        <is>
+          <t>1449</t>
+        </is>
+      </c>
+      <c r="AB74" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC74" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
           <t>344807</t>
         </is>
       </c>
-      <c r="B70" t="inlineStr">
+      <c r="B75" t="inlineStr">
         <is>
           <t>22624</t>
         </is>
       </c>
-      <c r="C70" t="inlineStr">
+      <c r="C75" t="inlineStr">
         <is>
           <t>SAN LUIS</t>
         </is>
       </c>
-      <c r="D70" t="inlineStr">
+      <c r="D75" t="inlineStr">
         <is>
           <t>CRUZ GUADALUPE</t>
         </is>
       </c>
-      <c r="E70" t="inlineStr">
+      <c r="E75" t="inlineStr">
         <is>
           <t>LUGO</t>
         </is>
       </c>
-      <c r="F70" t="inlineStr">
+      <c r="F75" t="inlineStr">
         <is>
           <t>ROCHA</t>
         </is>
       </c>
-      <c r="G70" t="inlineStr">
+      <c r="G75" t="inlineStr">
         <is>
           <t>52</t>
         </is>
       </c>
-      <c r="H70" t="inlineStr">
+      <c r="H75" t="inlineStr">
         <is>
           <t>6532082764</t>
         </is>
       </c>
-      <c r="I70" t="inlineStr">
+      <c r="I75" t="inlineStr">
         <is>
           <t>AV NAYARIT 43 Y 44</t>
         </is>
       </c>
-      <c r="J70" t="inlineStr">
+      <c r="J75" t="inlineStr">
         <is>
           <t>Femenino</t>
         </is>
       </c>
-      <c r="K70" t="inlineStr">
+      <c r="K75" t="inlineStr">
         <is>
           <t>01-01-2000</t>
         </is>
       </c>
-      <c r="L70" t="inlineStr">
+      <c r="L75" t="inlineStr">
         <is>
           <t>CRUZGLP01@LCLOUD.COM</t>
         </is>
       </c>
-      <c r="M70" t="inlineStr">
+      <c r="M75" t="inlineStr">
         <is>
           <t>18-02-2026 12:56:53</t>
         </is>
       </c>
-      <c r="N70" t="inlineStr">
+      <c r="N75" t="inlineStr">
         <is>
           <t>inscripcion promo 199</t>
         </is>
       </c>
-      <c r="O70" t="inlineStr">
+      <c r="O75" t="inlineStr">
         <is>
           <t>Forzoso</t>
         </is>
       </c>
-      <c r="P70" t="inlineStr">
+      <c r="P75" t="inlineStr">
         <is>
           <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
-      <c r="Q70" t="inlineStr">
+      <c r="Q75" t="inlineStr">
         <is>
           <t>499</t>
         </is>
       </c>
-      <c r="R70" t="inlineStr">
+      <c r="R75" t="inlineStr">
         <is>
           <t>20-02-2026 10:30:09</t>
         </is>
       </c>
-      <c r="S70" t="inlineStr">
+      <c r="S75" t="inlineStr">
         <is>
           <t>20-03-2026 23:59:59</t>
         </is>
       </c>
-      <c r="T70" t="inlineStr">
+      <c r="T75" t="inlineStr">
         <is>
           <t>20-02-2026 10:29:02</t>
         </is>
       </c>
-      <c r="U70" t="inlineStr">
+      <c r="U75" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V70" t="inlineStr">
+      <c r="V75" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="W70" t="inlineStr">
+      <c r="W75" t="inlineStr">
         <is>
           <t>Sucursal</t>
         </is>
       </c>
-      <c r="X70" t="inlineStr">
+      <c r="X75" t="inlineStr">
         <is>
           <t>26150522523340001940</t>
         </is>
       </c>
-      <c r="Y70" t="inlineStr">
+      <c r="Y75" t="inlineStr">
         <is>
           <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
         </is>
       </c>
-      <c r="Z70" t="inlineStr">
+      <c r="Z75" t="inlineStr">
         <is>
           <t>GISSEL ANAHY REYES GERMAN</t>
         </is>
       </c>
-      <c r="AA70" t="inlineStr">
+      <c r="AA75" t="inlineStr">
         <is>
           <t>499</t>
         </is>
       </c>
-      <c r="AB70" t="inlineStr">
+      <c r="AB75" t="inlineStr">
         <is>
           <t>Juan Pablo Romero Andrade</t>
         </is>
       </c>
-      <c r="AC70" t="inlineStr">
+      <c r="AC75" t="inlineStr">
         <is>
           <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>346592</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>88757</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>SAN LUIS</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>BRISSA KAROLINA</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>HERNANDEZ</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>ORTIZ</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>9289752311</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>ESCALONIAS  26</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>14-10-2009</t>
+        </is>
+      </c>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>BHERNANDEZ140905@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>25-02-2026 19:28:40</t>
+        </is>
+      </c>
+      <c r="N76" t="inlineStr">
+        <is>
+          <t>inscripcion promo 199</t>
+        </is>
+      </c>
+      <c r="O76" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>PROMO FEBRERO 12 MESES</t>
+        </is>
+      </c>
+      <c r="Q76" t="inlineStr">
+        <is>
+          <t>499</t>
+        </is>
+      </c>
+      <c r="R76" t="inlineStr">
+        <is>
+          <t>25-02-2026 19:33:11</t>
+        </is>
+      </c>
+      <c r="S76" t="inlineStr">
+        <is>
+          <t>25-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>25-02-2026 19:32:36</t>
+        </is>
+      </c>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V76" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W76" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X76" t="inlineStr">
+        <is>
+          <t>26150522666320002128</t>
+        </is>
+      </c>
+      <c r="Y76" t="inlineStr"/>
+      <c r="Z76" t="inlineStr"/>
+      <c r="AA76" t="inlineStr">
+        <is>
+          <t>499</t>
+        </is>
+      </c>
+      <c r="AB76" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC76" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>

--- a/data/rutinas/sucursales/Socios_con_y_sin_rutina__SAN LUIS.xlsx
+++ b/data/rutinas/sucursales/Socios_con_y_sin_rutina__SAN LUIS.xlsx
@@ -1968,12 +1968,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>340602</t>
+          <t>297488</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>18420</t>
+          <t>94986</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1983,87 +1983,99 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>DANTE EMILIANO</t>
+          <t xml:space="preserve">BRENDA </t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>GARCIA</t>
+          <t>ROMAN</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>GOMEZ</t>
+          <t>IBARRA</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>6531125544</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>EMILIANO ZAPATA C Y COLOMBIA</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>04-02-1984</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>OKCHIQUITA4@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>09-06-2025 20:08:16</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>inscripcion promo 199</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>PROMO FEBRERO 12 MESES</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>499</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>19-02-2026 17:34:15</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>19-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>19-02-2026 17:33:15</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>9228390416</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>Masculino</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>06-12-2010</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>DANTE.GARCIA@INSTITUTOKINO.EDU.MX</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>03-02-2026 14:43:23</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>Tarifas 2026 LE</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>Sin contrato</t>
-        </is>
-      </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>CONVENIOS $549</t>
-        </is>
-      </c>
-      <c r="Q12" t="inlineStr">
-        <is>
-          <t>549</t>
-        </is>
-      </c>
-      <c r="R12" t="inlineStr">
-        <is>
-          <t>03-02-2026 14:44:52</t>
-        </is>
-      </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>03-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T12" t="inlineStr"/>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V12" t="inlineStr"/>
       <c r="W12" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -2071,36 +2083,40 @@
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>26150522041730001279</t>
-        </is>
-      </c>
-      <c r="Y12" t="inlineStr"/>
+          <t>26150522501710001922</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
       <c r="Z12" t="inlineStr"/>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>Juan Pablo Romero Andrade</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>340730</t>
+          <t>340602</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>18548</t>
+          <t>18420</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -2110,48 +2126,48 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>GUADALUPE SHEREZADA</t>
+          <t>DANTE EMILIANO</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>RAMIREZ</t>
+          <t>GARCIA</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>CORTEZ</t>
+          <t>GOMEZ</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>6531304693</t>
+          <t>9228390416</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>02-07-2000</t>
+          <t>06-12-2010</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>BELLOBAINES.1982@GMAIL.COM</t>
+          <t>DANTE.GARCIA@INSTITUTOKINO.EDU.MX</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>03-02-2026 17:27:01</t>
+          <t>03-02-2026 14:43:23</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
@@ -2176,7 +2192,7 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>03-02-2026 17:32:11</t>
+          <t>03-02-2026 14:44:52</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
@@ -2198,7 +2214,7 @@
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>26150522049660001299</t>
+          <t>26150522041730001279</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr"/>
@@ -2222,12 +2238,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>297488</t>
+          <t>340730</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>94986</t>
+          <t>18548</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -2237,17 +2253,17 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t xml:space="preserve">BRENDA </t>
+          <t>GUADALUPE SHEREZADA</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>ROMAN</t>
+          <t>RAMIREZ</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>IBARRA</t>
+          <t>CORTEZ</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -2257,14 +2273,10 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>6531125544</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>EMILIANO ZAPATA C Y COLOMBIA</t>
-        </is>
-      </c>
+          <t>6531304693</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -2272,64 +2284,56 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>04-02-1984</t>
+          <t>02-07-2000</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>OKCHIQUITA4@GMAIL.COM</t>
+          <t>BELLOBAINES.1982@GMAIL.COM</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>09-06-2025 20:08:16</t>
+          <t>03-02-2026 17:27:01</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>inscripcion promo 199</t>
+          <t>Tarifas 2026 LE</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>19-02-2026 17:34:15</t>
+          <t>03-02-2026 17:32:11</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>19-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T14" t="inlineStr">
-        <is>
-          <t>19-02-2026 17:33:15</t>
-        </is>
-      </c>
+          <t>03-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr"/>
       <c r="U14" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="V14" t="inlineStr"/>
       <c r="W14" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -2337,40 +2341,36 @@
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>26150522501710001922</t>
-        </is>
-      </c>
-      <c r="Y14" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
+          <t>26150522049660001299</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr"/>
       <c r="Z14" t="inlineStr"/>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Juan Pablo Romero Andrade</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>339758</t>
+          <t>340947</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>17576</t>
+          <t>18765</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -2380,17 +2380,17 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>ISABELLA</t>
+          <t>ARMANDO</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>ALARCON</t>
+          <t>LOPEZ</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>ACEVES</t>
+          <t>GARCIA</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -2400,67 +2400,79 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>6535382487</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>6461858748</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SAN ISIDRO </t>
+        </is>
+      </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>04-06-2010</t>
+          <t>12-08-1991</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>ALARCONISABELLA347@GMAIL.COM</t>
+          <t>ARMANDO.ADMISION@GMAIL.COM</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>01-02-2026 10:00:33</t>
+          <t>04-02-2026 11:47:04</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>Tarifas 2026 LE</t>
+          <t>inscripcion promo 199</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>01-02-2026 10:05:34</t>
+          <t>27-02-2026 17:32:27</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>01-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T15" t="inlineStr"/>
+          <t>27-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>27-02-2026 17:32:04</t>
+        </is>
+      </c>
       <c r="U15" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V15" t="inlineStr"/>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="W15" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -2468,36 +2480,44 @@
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>26150521988630001200</t>
-        </is>
-      </c>
-      <c r="Y15" t="inlineStr"/>
-      <c r="Z15" t="inlineStr"/>
+          <t>26080522720790003421</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>DANIA XIMENA  PERALTA PIÑUELAS</t>
+        </is>
+      </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>Juan Pablo Romero Andrade</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>339777</t>
+          <t>339758</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>17595</t>
+          <t>17576</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -2507,17 +2527,17 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>GISSEL LILIAN</t>
+          <t>ISABELLA</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>RODRIGUEZ</t>
+          <t>ALARCON</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>SILVA</t>
+          <t>ACEVES</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -2527,14 +2547,10 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>6531466820</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>MERIDA 1</t>
-        </is>
-      </c>
+          <t>6535382487</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -2542,17 +2558,17 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>02-09-1998</t>
+          <t>04-06-2010</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>GISSELSILVIA98@GMAIL.COM</t>
+          <t>ALARCONISABELLA347@GMAIL.COM</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>01-02-2026 10:50:32</t>
+          <t>01-02-2026 10:00:33</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
@@ -2562,22 +2578,22 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>No Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>RECURRENTE $649 LE</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>01-02-2026 10:53:31</t>
+          <t>01-02-2026 10:05:34</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
@@ -2585,21 +2601,13 @@
           <t>01-03-2026 23:59:59</t>
         </is>
       </c>
-      <c r="T16" t="inlineStr">
-        <is>
-          <t>01-02-2026 10:52:55</t>
-        </is>
-      </c>
+      <c r="T16" t="inlineStr"/>
       <c r="U16" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V16" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="V16" t="inlineStr"/>
       <c r="W16" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -2607,14 +2615,14 @@
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>26150521989600001201</t>
+          <t>26150521988630001200</t>
         </is>
       </c>
       <c r="Y16" t="inlineStr"/>
       <c r="Z16" t="inlineStr"/>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
@@ -2631,12 +2639,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>340947</t>
+          <t>339777</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>18765</t>
+          <t>17595</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -2646,17 +2654,17 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>ARMANDO</t>
+          <t>GISSEL LILIAN</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>LOPEZ</t>
+          <t>RODRIGUEZ</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>GARCIA</t>
+          <t>SILVA</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -2666,67 +2674,67 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>6461858748</t>
+          <t>6531466820</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAN ISIDRO </t>
+          <t>MERIDA 1</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>12-08-1991</t>
+          <t>02-09-1998</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>ARMANDO.ADMISION@GMAIL.COM</t>
+          <t>GISSELSILVIA98@GMAIL.COM</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>04-02-2026 11:47:04</t>
+          <t>01-02-2026 10:50:32</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>inscripcion promo 199</t>
+          <t>Tarifas 2026 LE</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>No Forzoso</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>RECURRENTE $649 LE</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>649</t>
         </is>
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>27-02-2026 17:32:27</t>
+          <t>01-02-2026 10:53:31</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>27-03-2026 23:59:59</t>
+          <t>01-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>27-02-2026 17:32:04</t>
+          <t>01-02-2026 10:52:55</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
@@ -2736,7 +2744,7 @@
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W17" t="inlineStr">
@@ -2746,44 +2754,36 @@
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>26080522720790003421</t>
-        </is>
-      </c>
-      <c r="Y17" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>DANIA XIMENA  PERALTA PIÑUELAS</t>
-        </is>
-      </c>
+          <t>26150521989600001201</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr"/>
+      <c r="Z17" t="inlineStr"/>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>649</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Juan Pablo Romero Andrade</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>340340</t>
+          <t>325230</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>18158</t>
+          <t>22169</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -2793,17 +2793,17 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>FATIMA</t>
+          <t xml:space="preserve">GLORIA </t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>SANCHEZ</t>
+          <t>SANTOS</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>MEDINA</t>
+          <t>PEREZ</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -2813,12 +2813,12 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>6531333103</t>
+          <t>6531642345</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>AV TORREON 39</t>
+          <t>AV NUEVO LEON N9 Y 10</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -2828,22 +2828,22 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>27-08-2003</t>
+          <t>09-08-1984</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>FATIMASM2708@GMAIL.COM</t>
+          <t>PRICESASANTOS8409@GMAIL.COM</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>02-02-2026 18:15:23</t>
+          <t>25-11-2025 12:03:46</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>Tarifas 2026 LE</t>
+          <t>inscripcion promo 199</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
@@ -2853,27 +2853,27 @@
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES $549 LE</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>02-02-2026 18:20:31</t>
+          <t>18-02-2026 18:24:56</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>02-03-2026 23:59:59</t>
+          <t>18-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>02-02-2026 18:19:16</t>
+          <t>18-02-2026 18:24:16</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
@@ -2893,19 +2893,27 @@
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>26150522020390001251</t>
-        </is>
-      </c>
-      <c r="Y18" t="inlineStr"/>
-      <c r="Z18" t="inlineStr"/>
+          <t>26150522472400001881</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>GISSEL ANAHY REYES GERMAN</t>
+        </is>
+      </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>Johan Osvaldo Beltran Quiros</t>
+          <t>Juan Pablo Romero Andrade</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
@@ -2917,12 +2925,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>325230</t>
+          <t>340340</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>22169</t>
+          <t>18158</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -2932,17 +2940,17 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t xml:space="preserve">GLORIA </t>
+          <t>FATIMA</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>SANTOS</t>
+          <t>SANCHEZ</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>PEREZ</t>
+          <t>MEDINA</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -2952,12 +2960,12 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>6531642345</t>
+          <t>6531333103</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>AV NUEVO LEON N9 Y 10</t>
+          <t>AV TORREON 39</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -2967,22 +2975,22 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>09-08-1984</t>
+          <t>27-08-2003</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>PRICESASANTOS8409@GMAIL.COM</t>
+          <t>FATIMASM2708@GMAIL.COM</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>25-11-2025 12:03:46</t>
+          <t>02-02-2026 18:15:23</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>inscripcion promo 199</t>
+          <t>Tarifas 2026 LE</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
@@ -2992,27 +3000,27 @@
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>DOMICILIADO 12 MESES $549 LE</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>18-02-2026 18:24:56</t>
+          <t>02-02-2026 18:20:31</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>18-03-2026 23:59:59</t>
+          <t>02-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>18-02-2026 18:24:16</t>
+          <t>02-02-2026 18:19:16</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
@@ -3032,27 +3040,19 @@
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>26150522472400001881</t>
-        </is>
-      </c>
-      <c r="Y19" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>GISSEL ANAHY REYES GERMAN</t>
-        </is>
-      </c>
+          <t>26150522020390001251</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr"/>
+      <c r="Z19" t="inlineStr"/>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>Juan Pablo Romero Andrade</t>
+          <t>Johan Osvaldo Beltran Quiros</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
@@ -3481,12 +3481,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>342823</t>
+          <t>339854</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>20640</t>
+          <t>17672</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -3496,17 +3496,17 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>JESUS ABEL</t>
+          <t>DIEGO ARMANDO</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>VALERIO</t>
+          <t>MEDINA</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>LIMON</t>
+          <t>PIEDRA</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -3516,12 +3516,12 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>6531665157</t>
+          <t>6531658872</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>CARRETERA DEL VALLE</t>
+          <t>REVOLUCION Y 40</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -3531,48 +3531,52 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>23-07-2004</t>
+          <t>06-03-1989</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>VALERIOJESUS913@GMAIL.COM</t>
+          <t>DIEGO.MEDINA@YAHOO.COM</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>10-02-2026 19:05:03</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr"/>
+          <t>02-02-2026 05:44:27</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>No Forzoso</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>PLAN FAMILIAR RECURRENTE $999</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>999</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>10-02-2026 19:09:25</t>
+          <t>02-02-2026 05:46:51</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>10-03-2026 23:59:59</t>
+          <t>02-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>10-02-2026 19:08:45</t>
+          <t>02-02-2026 05:45:55</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
@@ -3582,7 +3586,7 @@
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W23" t="inlineStr">
@@ -3592,36 +3596,36 @@
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>26150522245980001553</t>
+          <t>26150521997870001209</t>
         </is>
       </c>
       <c r="Y23" t="inlineStr"/>
       <c r="Z23" t="inlineStr"/>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>999</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>Johan Osvaldo Beltran Quiros</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>341197</t>
+          <t>342823</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>19015</t>
+          <t>20640</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -3631,17 +3635,17 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>CARMEN</t>
+          <t>JESUS ABEL</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>ALICIA</t>
+          <t>VALERIO</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>GIL</t>
+          <t>LIMON</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -3651,32 +3655,32 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>6642049795</t>
+          <t>6531665157</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>AV BENITO JUAREZ 24 Y 25</t>
+          <t>CARRETERA DEL VALLE</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>15-09-1947</t>
+          <t>23-07-2004</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>CARMEN1947@GMAIL.COM</t>
+          <t>VALERIOJESUS913@GMAIL.COM</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>04-02-2026 21:10:39</t>
+          <t>10-02-2026 19:05:03</t>
         </is>
       </c>
       <c r="N24" t="inlineStr"/>
@@ -3697,17 +3701,17 @@
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>11-02-2026 15:03:22</t>
+          <t>10-02-2026 19:09:25</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>11-03-2026 23:59:59</t>
+          <t>10-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>11-02-2026 15:02:18</t>
+          <t>10-02-2026 19:08:45</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
@@ -3727,19 +3731,11 @@
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>26150522265830001585</t>
-        </is>
-      </c>
-      <c r="Y24" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>GISSEL ANAHY REYES GERMAN</t>
-        </is>
-      </c>
+          <t>26150522245980001553</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr"/>
+      <c r="Z24" t="inlineStr"/>
       <c r="AA24" t="inlineStr">
         <is>
           <t>499</t>
@@ -3747,7 +3743,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>Juan Eduardo Torres Alcantar</t>
+          <t>Johan Osvaldo Beltran Quiros</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
@@ -3759,12 +3755,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>339854</t>
+          <t>341197</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>17672</t>
+          <t>19015</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -3774,17 +3770,17 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>DIEGO ARMANDO</t>
+          <t>CARMEN</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>MEDINA</t>
+          <t>ALICIA</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>PIEDRA</t>
+          <t>GIL</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -3794,67 +3790,63 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>6531658872</t>
+          <t>6642049795</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>REVOLUCION Y 40</t>
+          <t>AV BENITO JUAREZ 24 Y 25</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>06-03-1989</t>
+          <t>15-09-1947</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>DIEGO.MEDINA@YAHOO.COM</t>
+          <t>CARMEN1947@GMAIL.COM</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>02-02-2026 05:44:27</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr">
-        <is>
-          <t>Tarifas 2026 LE</t>
-        </is>
-      </c>
+          <t>04-02-2026 21:10:39</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr"/>
       <c r="O25" t="inlineStr">
         <is>
-          <t>No Forzoso</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>PLAN FAMILIAR RECURRENTE $999</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>999</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>02-02-2026 05:46:51</t>
+          <t>11-02-2026 15:03:22</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>02-03-2026 23:59:59</t>
+          <t>11-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>02-02-2026 05:45:55</t>
+          <t>11-02-2026 15:02:18</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
@@ -3864,7 +3856,7 @@
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W25" t="inlineStr">
@@ -3874,36 +3866,44 @@
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>26150521997870001209</t>
-        </is>
-      </c>
-      <c r="Y25" t="inlineStr"/>
-      <c r="Z25" t="inlineStr"/>
+          <t>26150522265830001585</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>GISSEL ANAHY REYES GERMAN</t>
+        </is>
+      </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>999</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Juan Eduardo Torres Alcantar</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>340152</t>
+          <t>343341</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>17970</t>
+          <t>21158</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -3913,17 +3913,17 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>MARTHA LIDIA</t>
+          <t>JUAN OMAR</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t xml:space="preserve">DURAN </t>
+          <t>REYES</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>CUEN</t>
+          <t>RIVERA</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -3933,12 +3933,12 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>6531218668</t>
+          <t>6865976498</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>PRIVADO ROFORMA</t>
+          <t>CJON NICARAGUA 31</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -3948,17 +3948,17 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>06-08-1960</t>
+          <t>02-01-1992</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>ROMERO.MARTHA50@ICLOUD.COM</t>
+          <t>ELREYES023@GMAIL.COM</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>02-02-2026 13:57:36</t>
+          <t>12-02-2026 17:35:55</t>
         </is>
       </c>
       <c r="N26" t="inlineStr"/>
@@ -3979,17 +3979,17 @@
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>02-02-2026 14:04:27</t>
+          <t>14-02-2026 10:17:45</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
         <is>
-          <t>02-03-2026 23:59:59</t>
+          <t>14-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>02-02-2026 14:03:30</t>
+          <t>14-02-2026 10:17:11</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
@@ -4009,11 +4009,19 @@
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>26150522011860001229</t>
-        </is>
-      </c>
-      <c r="Y26" t="inlineStr"/>
-      <c r="Z26" t="inlineStr"/>
+          <t>26150522345630001701</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>GISSEL ANAHY REYES GERMAN</t>
+        </is>
+      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>499</t>
@@ -4033,12 +4041,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>343341</t>
+          <t>340152</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>21158</t>
+          <t>17970</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -4048,17 +4056,17 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>JUAN OMAR</t>
+          <t>MARTHA LIDIA</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>REYES</t>
+          <t xml:space="preserve">DURAN </t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>RIVERA</t>
+          <t>CUEN</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -4068,12 +4076,12 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>6865976498</t>
+          <t>6531218668</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>CJON NICARAGUA 31</t>
+          <t>PRIVADO ROFORMA</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -4083,17 +4091,17 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>02-01-1992</t>
+          <t>06-08-1960</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>ELREYES023@GMAIL.COM</t>
+          <t>ROMERO.MARTHA50@ICLOUD.COM</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>12-02-2026 17:35:55</t>
+          <t>02-02-2026 13:57:36</t>
         </is>
       </c>
       <c r="N27" t="inlineStr"/>
@@ -4114,17 +4122,17 @@
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>14-02-2026 10:17:45</t>
+          <t>02-02-2026 14:04:27</t>
         </is>
       </c>
       <c r="S27" t="inlineStr">
         <is>
-          <t>14-03-2026 23:59:59</t>
+          <t>02-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>14-02-2026 10:17:11</t>
+          <t>02-02-2026 14:03:30</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
@@ -4144,19 +4152,11 @@
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>26150522345630001701</t>
-        </is>
-      </c>
-      <c r="Y27" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>GISSEL ANAHY REYES GERMAN</t>
-        </is>
-      </c>
+          <t>26150522011860001229</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr"/>
+      <c r="Z27" t="inlineStr"/>
       <c r="AA27" t="inlineStr">
         <is>
           <t>499</t>
@@ -4454,12 +4454,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>340247</t>
+          <t>340805</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>18065</t>
+          <t>18623</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -4469,17 +4469,17 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LESLIE CLARETH</t>
+          <t>RICARDO</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>VEGA</t>
+          <t>TAPIA</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>QUEVEDO</t>
+          <t>OLIVO</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -4489,32 +4489,32 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>6531329411</t>
+          <t>6531341539</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>AV NAYARIT 21</t>
+          <t>AV GUERRERO 12</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>18-08-2006</t>
+          <t>01-04-2000</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>VEGA.LESLIE.3E@GMAIL.COM</t>
+          <t>RICARDITOTAPIA2129@GMAIL.COM</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>02-02-2026 16:08:34</t>
+          <t>03-02-2026 19:10:40</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
@@ -4539,17 +4539,17 @@
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>02-02-2026 16:43:55</t>
+          <t>03-02-2026 19:13:30</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>02-03-2026 23:59:59</t>
+          <t>03-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>02-02-2026 16:12:35</t>
+          <t>03-02-2026 19:12:47</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
@@ -4559,7 +4559,7 @@
       </c>
       <c r="V30" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W30" t="inlineStr">
@@ -4569,7 +4569,7 @@
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>26150522017110001235</t>
+          <t>26150522055450001315</t>
         </is>
       </c>
       <c r="Y30" t="inlineStr"/>
@@ -4581,7 +4581,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>Juan Eduardo Torres Alcantar</t>
+          <t>Martin Ramiro Quiñonez Jauregui</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
@@ -4593,12 +4593,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>340805</t>
+          <t>340247</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>18623</t>
+          <t>18065</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -4608,17 +4608,17 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>RICARDO</t>
+          <t>LESLIE CLARETH</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>TAPIA</t>
+          <t>VEGA</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>OLIVO</t>
+          <t>QUEVEDO</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -4628,32 +4628,32 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>6531341539</t>
+          <t>6531329411</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>AV GUERRERO 12</t>
+          <t>AV NAYARIT 21</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>01-04-2000</t>
+          <t>18-08-2006</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>RICARDITOTAPIA2129@GMAIL.COM</t>
+          <t>VEGA.LESLIE.3E@GMAIL.COM</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>03-02-2026 19:10:40</t>
+          <t>02-02-2026 16:08:34</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
@@ -4678,17 +4678,17 @@
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>03-02-2026 19:13:30</t>
+          <t>02-02-2026 16:43:55</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
         <is>
-          <t>03-03-2026 23:59:59</t>
+          <t>02-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>03-02-2026 19:12:47</t>
+          <t>02-02-2026 16:12:35</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
@@ -4698,7 +4698,7 @@
       </c>
       <c r="V31" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W31" t="inlineStr">
@@ -4708,7 +4708,7 @@
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>26150522055450001315</t>
+          <t>26150522017110001235</t>
         </is>
       </c>
       <c r="Y31" t="inlineStr"/>
@@ -4720,7 +4720,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>Martin Ramiro Quiñonez Jauregui</t>
+          <t>Juan Eduardo Torres Alcantar</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
@@ -4732,12 +4732,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>340765</t>
+          <t>344062</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>18583</t>
+          <t>21879</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -4747,17 +4747,17 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VIVIANA</t>
+          <t>RAYMUNDO ISRAEL</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>ARVAYO</t>
+          <t>LOPEZ</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>RASCON</t>
+          <t>ARREOLA</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -4767,32 +4767,28 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>6531300005</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t xml:space="preserve">AV COLIMA Y MATAMOROS </t>
-        </is>
-      </c>
+          <t>6442276514</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
       <c r="J32" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>03-01-1979</t>
+          <t>21-05-2010</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>VIVIARVAYO@GMAIL.COM</t>
+          <t>RL25090288@BACHILLERESDESONORA.EDU.MX</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>03-02-2026 18:01:17</t>
+          <t>16-02-2026 13:12:33</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
@@ -4802,44 +4798,36 @@
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>No Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>PLAN RECURRENTE PAGO INCIAL $1,449 LE</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>1449</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>03-02-2026 18:16:20</t>
+          <t>16-02-2026 13:13:37</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>03-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T32" t="inlineStr">
-        <is>
-          <t>03-02-2026 18:05:39</t>
-        </is>
-      </c>
+          <t>16-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T32" t="inlineStr"/>
       <c r="U32" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V32" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="V32" t="inlineStr"/>
       <c r="W32" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -4847,36 +4835,36 @@
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>26150522052430001305</t>
+          <t>26150522388250001746</t>
         </is>
       </c>
       <c r="Y32" t="inlineStr"/>
       <c r="Z32" t="inlineStr"/>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>1449</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Juan Pablo Romero Andrade</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>340877</t>
+          <t>341196</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>18695</t>
+          <t>19014</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -4886,17 +4874,17 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>HECTOR ABRAHAM</t>
+          <t>ESMERALDA</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>OJEDA</t>
+          <t>JAVALERA</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>FRANCO</t>
+          <t>ALCANTAR</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -4906,39 +4894,35 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>6532437111</t>
+          <t>6531196345</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>DALIAS 18 Y 19</t>
+          <t>AV TABASCO 41</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>08-01-2005</t>
+          <t>19-03-1975</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>ABRAHAM30510@GMAIL.COM</t>
+          <t>ESMERALDA.JAVALERA@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>04-02-2026 07:26:12</t>
-        </is>
-      </c>
-      <c r="N33" t="inlineStr">
-        <is>
-          <t>Tarifas 2026 LE</t>
-        </is>
-      </c>
+          <t>04-02-2026 21:09:01</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr"/>
       <c r="O33" t="inlineStr">
         <is>
           <t>Forzoso</t>
@@ -4946,27 +4930,27 @@
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES $549 LE</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>04-02-2026 07:29:18</t>
+          <t>11-02-2026 15:06:43</t>
         </is>
       </c>
       <c r="S33" t="inlineStr">
         <is>
-          <t>04-03-2026 23:59:59</t>
+          <t>11-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>04-02-2026 07:28:45</t>
+          <t>11-02-2026 15:05:40</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
@@ -4986,19 +4970,27 @@
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>26150522068240001330</t>
-        </is>
-      </c>
-      <c r="Y33" t="inlineStr"/>
-      <c r="Z33" t="inlineStr"/>
+          <t>26150522265920001586</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>GISSEL ANAHY REYES GERMAN</t>
+        </is>
+      </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>Martin Ramiro Quiñonez Jauregui</t>
+          <t>Juan Eduardo Torres Alcantar</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
@@ -5010,12 +5002,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>344062</t>
+          <t>341271</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>21879</t>
+          <t>19089</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -5025,17 +5017,17 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>RAYMUNDO ISRAEL</t>
+          <t>NICOLLE</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>LOPEZ</t>
+          <t>BUSTAMANTE</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>ARREOLA</t>
+          <t>ELIZONDO</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -5045,67 +5037,75 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>6442276514</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
+          <t>6381121777</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>LOS ADOBES</t>
+        </is>
+      </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>21-05-2010</t>
+          <t>15-12-1997</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>RL25090288@BACHILLERESDESONORA.EDU.MX</t>
+          <t>NICOLLE.BUSTAMANTE@UABC.EDU.MX</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>16-02-2026 13:12:33</t>
-        </is>
-      </c>
-      <c r="N34" t="inlineStr">
-        <is>
-          <t>Tarifas 2026 LE</t>
-        </is>
-      </c>
+          <t>05-02-2026 10:43:03</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr"/>
       <c r="O34" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>16-02-2026 13:13:37</t>
+          <t>11-02-2026 13:33:23</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
         <is>
-          <t>16-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T34" t="inlineStr"/>
+          <t>11-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>11-02-2026 13:31:59</t>
+        </is>
+      </c>
       <c r="U34" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V34" t="inlineStr"/>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="W34" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -5113,14 +5113,22 @@
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>26150522388250001746</t>
-        </is>
-      </c>
-      <c r="Y34" t="inlineStr"/>
-      <c r="Z34" t="inlineStr"/>
+          <t>26150522264110001579</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>RAUL FELIX VAZQUEZ</t>
+        </is>
+      </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB34" t="inlineStr">
@@ -5137,12 +5145,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>343837</t>
+          <t>340765</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>21654</t>
+          <t>18583</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -5152,17 +5160,17 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>CLAUDIA GABRIELA</t>
+          <t>VIVIANA</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>ROGEL</t>
+          <t>ARVAYO</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>SANDOVAL</t>
+          <t>RASCON</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -5172,12 +5180,12 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>6532075902</t>
+          <t>6531300005</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>HUERTAS 7</t>
+          <t xml:space="preserve">AV COLIMA Y MATAMOROS </t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -5187,48 +5195,52 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>09-12-1991</t>
+          <t>03-01-1979</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>ROGELCLAUDIA266@GMAIL.COM</t>
+          <t>VIVIARVAYO@GMAIL.COM</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>15-02-2026 12:34:47</t>
-        </is>
-      </c>
-      <c r="N35" t="inlineStr"/>
+          <t>03-02-2026 18:01:17</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>No Forzoso</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>PLAN RECURRENTE PAGO INCIAL $1,449 LE</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>1449</t>
         </is>
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>15-02-2026 12:38:45</t>
+          <t>03-02-2026 18:16:20</t>
         </is>
       </c>
       <c r="S35" t="inlineStr">
         <is>
-          <t>15-03-2026 23:59:59</t>
+          <t>03-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>15-02-2026 12:37:38</t>
+          <t>03-02-2026 18:05:39</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
@@ -5248,36 +5260,36 @@
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>26150522365800001718</t>
+          <t>26150522052430001305</t>
         </is>
       </c>
       <c r="Y35" t="inlineStr"/>
       <c r="Z35" t="inlineStr"/>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>1449</t>
         </is>
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>Juan Pablo Romero Andrade</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>341196</t>
+          <t>340877</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>19014</t>
+          <t>18695</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -5287,17 +5299,17 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>ESMERALDA</t>
+          <t>HECTOR ABRAHAM</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>JAVALERA</t>
+          <t>OJEDA</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>ALCANTAR</t>
+          <t>FRANCO</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -5307,35 +5319,39 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>6531196345</t>
+          <t>6532437111</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>AV TABASCO 41</t>
+          <t>DALIAS 18 Y 19</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>19-03-1975</t>
+          <t>08-01-2005</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>ESMERALDA.JAVALERA@HOTMAIL.COM</t>
+          <t>ABRAHAM30510@GMAIL.COM</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>04-02-2026 21:09:01</t>
-        </is>
-      </c>
-      <c r="N36" t="inlineStr"/>
+          <t>04-02-2026 07:26:12</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
       <c r="O36" t="inlineStr">
         <is>
           <t>Forzoso</t>
@@ -5343,27 +5359,27 @@
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>DOMICILIADO 12 MESES $549 LE</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>11-02-2026 15:06:43</t>
+          <t>04-02-2026 07:29:18</t>
         </is>
       </c>
       <c r="S36" t="inlineStr">
         <is>
-          <t>11-03-2026 23:59:59</t>
+          <t>04-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>11-02-2026 15:05:40</t>
+          <t>04-02-2026 07:28:45</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
@@ -5383,27 +5399,19 @@
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>26150522265920001586</t>
-        </is>
-      </c>
-      <c r="Y36" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z36" t="inlineStr">
-        <is>
-          <t>GISSEL ANAHY REYES GERMAN</t>
-        </is>
-      </c>
+          <t>26150522068240001330</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr"/>
+      <c r="Z36" t="inlineStr"/>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>Juan Eduardo Torres Alcantar</t>
+          <t>Martin Ramiro Quiñonez Jauregui</t>
         </is>
       </c>
       <c r="AC36" t="inlineStr">
@@ -5415,12 +5423,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>341271</t>
+          <t>343837</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>19089</t>
+          <t>21654</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -5430,17 +5438,17 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NICOLLE</t>
+          <t>CLAUDIA GABRIELA</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>BUSTAMANTE</t>
+          <t>ROGEL</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>ELIZONDO</t>
+          <t>SANDOVAL</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -5450,12 +5458,12 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>6381121777</t>
+          <t>6532075902</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>LOS ADOBES</t>
+          <t>HUERTAS 7</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -5465,17 +5473,17 @@
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>15-12-1997</t>
+          <t>09-12-1991</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>NICOLLE.BUSTAMANTE@UABC.EDU.MX</t>
+          <t>ROGELCLAUDIA266@GMAIL.COM</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>05-02-2026 10:43:03</t>
+          <t>15-02-2026 12:34:47</t>
         </is>
       </c>
       <c r="N37" t="inlineStr"/>
@@ -5496,17 +5504,17 @@
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>11-02-2026 13:33:23</t>
+          <t>15-02-2026 12:38:45</t>
         </is>
       </c>
       <c r="S37" t="inlineStr">
         <is>
-          <t>11-03-2026 23:59:59</t>
+          <t>15-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>11-02-2026 13:31:59</t>
+          <t>15-02-2026 12:37:38</t>
         </is>
       </c>
       <c r="U37" t="inlineStr">
@@ -5516,7 +5524,7 @@
       </c>
       <c r="V37" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W37" t="inlineStr">
@@ -5526,19 +5534,11 @@
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>26150522264110001579</t>
-        </is>
-      </c>
-      <c r="Y37" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>RAUL FELIX VAZQUEZ</t>
-        </is>
-      </c>
+          <t>26150522365800001718</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr"/>
+      <c r="Z37" t="inlineStr"/>
       <c r="AA37" t="inlineStr">
         <is>
           <t>499</t>
@@ -5844,12 +5844,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>340779</t>
+          <t>343954</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>18597</t>
+          <t>21771</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -5859,12 +5859,12 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>CLAUDIA ITZEL</t>
+          <t>LOURDES</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t xml:space="preserve">DE LA ROSA </t>
+          <t>LOPEZ</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -5879,10 +5879,14 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>6642467640</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr"/>
+          <t>6531035239</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>C 5 DE MAYO SN</t>
+        </is>
+      </c>
       <c r="J40" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -5890,56 +5894,64 @@
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>21-11-1988</t>
+          <t>10-01-1986</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>ITZELT.DELAROSA@GMAIL.COM</t>
+          <t>LULISLOPEZ999@GMAIL.COM</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>03-02-2026 18:20:07</t>
+          <t>16-02-2026 07:40:00</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>Tarifas 2026 LE</t>
+          <t>inscripcion promo 199</t>
         </is>
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>14-02-2026 12:53:49</t>
+          <t>16-02-2026 07:43:57</t>
         </is>
       </c>
       <c r="S40" t="inlineStr">
         <is>
-          <t>14-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T40" t="inlineStr"/>
+          <t>16-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>16-02-2026 07:43:12</t>
+        </is>
+      </c>
       <c r="U40" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V40" t="inlineStr"/>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W40" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -5947,40 +5959,36 @@
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>26140522348900001443</t>
-        </is>
-      </c>
-      <c r="Y40" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
+          <t>26150522379670001736</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr"/>
       <c r="Z40" t="inlineStr"/>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Juan Eduardo Torres Alcantar</t>
         </is>
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>343954</t>
+          <t>344220</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>21771</t>
+          <t>22037</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -5990,17 +5998,17 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LOURDES</t>
+          <t>CAROLINA</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>LOPEZ</t>
+          <t>FERNANDEZ</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>SANCHEZ</t>
+          <t>GUTIERREZ</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -6010,12 +6018,12 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>6531035239</t>
+          <t>6531610904</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>C 5 DE MAYO SN</t>
+          <t>CJON COLIMA 17 Y 18</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -6025,17 +6033,17 @@
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>10-01-1986</t>
+          <t>21-01-2003</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>LULISLOPEZ999@GMAIL.COM</t>
+          <t>LINA_FDZ@ICLOUD.COM</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>16-02-2026 07:40:00</t>
+          <t>16-02-2026 17:36:28</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
@@ -6060,17 +6068,17 @@
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>16-02-2026 07:43:57</t>
+          <t>21-02-2026 06:49:41</t>
         </is>
       </c>
       <c r="S41" t="inlineStr">
         <is>
-          <t>16-03-2026 23:59:59</t>
+          <t>21-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t>16-02-2026 07:43:12</t>
+          <t>21-02-2026 06:48:42</t>
         </is>
       </c>
       <c r="U41" t="inlineStr">
@@ -6080,7 +6088,7 @@
       </c>
       <c r="V41" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W41" t="inlineStr">
@@ -6090,7 +6098,7 @@
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>26150522379670001736</t>
+          <t>26150522547830001961</t>
         </is>
       </c>
       <c r="Y41" t="inlineStr"/>
@@ -6102,24 +6110,24 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>Juan Eduardo Torres Alcantar</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>344220</t>
+          <t>340779</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>22037</t>
+          <t>18597</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -6129,17 +6137,17 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>CAROLINA</t>
+          <t>CLAUDIA ITZEL</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>FERNANDEZ</t>
+          <t xml:space="preserve">DE LA ROSA </t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>GUTIERREZ</t>
+          <t>SANCHEZ</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -6149,14 +6157,10 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>6531610904</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>CJON COLIMA 17 Y 18</t>
-        </is>
-      </c>
+          <t>6642467640</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
       <c r="J42" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -6164,64 +6168,56 @@
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>21-01-2003</t>
+          <t>21-11-1988</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>LINA_FDZ@ICLOUD.COM</t>
+          <t>ITZELT.DELAROSA@GMAIL.COM</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>16-02-2026 17:36:28</t>
+          <t>03-02-2026 18:20:07</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>inscripcion promo 199</t>
+          <t>Tarifas 2026 LE</t>
         </is>
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>21-02-2026 06:49:41</t>
+          <t>14-02-2026 12:53:49</t>
         </is>
       </c>
       <c r="S42" t="inlineStr">
         <is>
-          <t>21-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T42" t="inlineStr">
-        <is>
-          <t>21-02-2026 06:48:42</t>
-        </is>
-      </c>
+          <t>14-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T42" t="inlineStr"/>
       <c r="U42" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V42" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="V42" t="inlineStr"/>
       <c r="W42" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -6229,14 +6225,18 @@
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>26150522547830001961</t>
-        </is>
-      </c>
-      <c r="Y42" t="inlineStr"/>
+          <t>26140522348900001443</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
       <c r="Z42" t="inlineStr"/>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB42" t="inlineStr">
@@ -6658,12 +6658,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>342562</t>
+          <t>342245</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>20379</t>
+          <t>20063</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -6673,17 +6673,17 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>AZALEA ZENYACE</t>
+          <t>MANUEL ANTONIO</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>MORENO</t>
+          <t xml:space="preserve">RUIZ </t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>CARRIZOZA</t>
+          <t>SILVA</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -6693,63 +6693,67 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>6531038421</t>
+          <t>6863042514</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>CJN CHIHUAHUA 23</t>
+          <t>CJN SAN JUAN Y SAN LUIS</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>23-09-1994</t>
+          <t>09-10-1991</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>ZEN_YACE94LIVE@HOTMAIL.COM</t>
+          <t>MANUELANTONIOSILVARUIZ@GMAIL.COM</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>10-02-2026 09:19:09</t>
-        </is>
-      </c>
-      <c r="N46" t="inlineStr"/>
+          <t>09-02-2026 16:10:49</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>No Forzoso</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>RECURRENTE $649 LE</t>
         </is>
       </c>
       <c r="Q46" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>649</t>
         </is>
       </c>
       <c r="R46" t="inlineStr">
         <is>
-          <t>12-02-2026 18:37:07</t>
+          <t>09-02-2026 16:12:25</t>
         </is>
       </c>
       <c r="S46" t="inlineStr">
         <is>
-          <t>12-03-2026 23:59:59</t>
+          <t>09-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T46" t="inlineStr">
         <is>
-          <t>12-02-2026 18:33:55</t>
+          <t>09-02-2026 16:11:51</t>
         </is>
       </c>
       <c r="U46" t="inlineStr">
@@ -6759,7 +6763,7 @@
       </c>
       <c r="V46" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W46" t="inlineStr">
@@ -6769,27 +6773,19 @@
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>26150522302860001640</t>
-        </is>
-      </c>
-      <c r="Y46" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z46" t="inlineStr">
-        <is>
-          <t>RAUL FELIX VAZQUEZ</t>
-        </is>
-      </c>
+          <t>26150522197240001486</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr"/>
+      <c r="Z46" t="inlineStr"/>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>649</t>
         </is>
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>Juan Pablo Romero Andrade</t>
+          <t>Johan Osvaldo Beltran Quiros</t>
         </is>
       </c>
       <c r="AC46" t="inlineStr">
@@ -6801,12 +6797,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>342245</t>
+          <t>342261</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>20063</t>
+          <t>20079</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -6816,17 +6812,17 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>MANUEL ANTONIO</t>
+          <t xml:space="preserve">VICTORIA </t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t xml:space="preserve">RUIZ </t>
+          <t xml:space="preserve">ZAVALA </t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>SILVA</t>
+          <t>BARRIENTOS</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -6836,32 +6832,32 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>6863042514</t>
+          <t>6531231721</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>CJN SAN JUAN Y SAN LUIS</t>
+          <t xml:space="preserve">HACIENDA DE LA CRUZ </t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>09-10-1991</t>
+          <t>04-04-1996</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>MANUELANTONIOSILVARUIZ@GMAIL.COM</t>
+          <t>GUADALUPEZAVALAMERCADO@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>09-02-2026 16:10:49</t>
+          <t>09-02-2026 16:34:55</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
@@ -6871,22 +6867,22 @@
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>No Forzoso</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>RECURRENTE $649 LE</t>
+          <t>DOMICILIADO 12 MESES $549 LE</t>
         </is>
       </c>
       <c r="Q47" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R47" t="inlineStr">
         <is>
-          <t>09-02-2026 16:12:25</t>
+          <t>09-02-2026 16:37:21</t>
         </is>
       </c>
       <c r="S47" t="inlineStr">
@@ -6896,7 +6892,7 @@
       </c>
       <c r="T47" t="inlineStr">
         <is>
-          <t>09-02-2026 16:11:51</t>
+          <t>09-02-2026 16:36:34</t>
         </is>
       </c>
       <c r="U47" t="inlineStr">
@@ -6916,14 +6912,14 @@
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>26150522197240001486</t>
+          <t>26150522198880001489</t>
         </is>
       </c>
       <c r="Y47" t="inlineStr"/>
       <c r="Z47" t="inlineStr"/>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB47" t="inlineStr">
@@ -6940,12 +6936,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>342261</t>
+          <t>342562</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>20079</t>
+          <t>20379</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -6955,17 +6951,17 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t xml:space="preserve">VICTORIA </t>
+          <t>AZALEA ZENYACE</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t xml:space="preserve">ZAVALA </t>
+          <t>MORENO</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>BARRIENTOS</t>
+          <t>CARRIZOZA</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -6975,12 +6971,12 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>6531231721</t>
+          <t>6531038421</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t xml:space="preserve">HACIENDA DE LA CRUZ </t>
+          <t>CJN CHIHUAHUA 23</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -6990,24 +6986,20 @@
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>04-04-1996</t>
+          <t>23-09-1994</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>GUADALUPEZAVALAMERCADO@HOTMAIL.COM</t>
+          <t>ZEN_YACE94LIVE@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>09-02-2026 16:34:55</t>
-        </is>
-      </c>
-      <c r="N48" t="inlineStr">
-        <is>
-          <t>Tarifas 2026 LE</t>
-        </is>
-      </c>
+          <t>10-02-2026 09:19:09</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr"/>
       <c r="O48" t="inlineStr">
         <is>
           <t>Forzoso</t>
@@ -7015,27 +7007,27 @@
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES $549 LE</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q48" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R48" t="inlineStr">
         <is>
-          <t>09-02-2026 16:37:21</t>
+          <t>12-02-2026 18:37:07</t>
         </is>
       </c>
       <c r="S48" t="inlineStr">
         <is>
-          <t>09-03-2026 23:59:59</t>
+          <t>12-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T48" t="inlineStr">
         <is>
-          <t>09-02-2026 16:36:34</t>
+          <t>12-02-2026 18:33:55</t>
         </is>
       </c>
       <c r="U48" t="inlineStr">
@@ -7045,7 +7037,7 @@
       </c>
       <c r="V48" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W48" t="inlineStr">
@@ -7055,19 +7047,27 @@
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>26150522198880001489</t>
-        </is>
-      </c>
-      <c r="Y48" t="inlineStr"/>
-      <c r="Z48" t="inlineStr"/>
+          <t>26150522302860001640</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>RAUL FELIX VAZQUEZ</t>
+        </is>
+      </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>Johan Osvaldo Beltran Quiros</t>
+          <t>Juan Pablo Romero Andrade</t>
         </is>
       </c>
       <c r="AC48" t="inlineStr">
@@ -7488,12 +7488,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>342867</t>
+          <t>342512</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>20684</t>
+          <t>20329</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -7503,17 +7503,17 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>MIGUEL ANGEL</t>
+          <t>JOSE RICARDO</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AMEZCUA</t>
+          <t>GARCIA</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>TORRES</t>
+          <t>ANGULO</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -7523,12 +7523,12 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>6674708281</t>
+          <t>6531217599</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>FLORES 22</t>
+          <t>CJON HIDALGO Y 47</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
@@ -7538,48 +7538,52 @@
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>21-11-1995</t>
+          <t>03-04-1976</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>MIGUELAMEZCUA21@GMAIL.COM</t>
+          <t>RRICARDOGARCIA34@ICLOUD.COM</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>10-02-2026 20:37:24</t>
-        </is>
-      </c>
-      <c r="N52" t="inlineStr"/>
+          <t>10-02-2026 05:34:48</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
       <c r="O52" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>No Forzoso</t>
         </is>
       </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>RECURRENTE $649 LE</t>
         </is>
       </c>
       <c r="Q52" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>649</t>
         </is>
       </c>
       <c r="R52" t="inlineStr">
         <is>
-          <t>12-02-2026 20:00:11</t>
+          <t>11-02-2026 06:33:27</t>
         </is>
       </c>
       <c r="S52" t="inlineStr">
         <is>
-          <t>12-03-2026 23:59:59</t>
+          <t>11-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T52" t="inlineStr">
         <is>
-          <t>12-02-2026 19:59:09</t>
+          <t>11-02-2026 06:32:18</t>
         </is>
       </c>
       <c r="U52" t="inlineStr">
@@ -7599,7 +7603,7 @@
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>26150522305570001650</t>
+          <t>26150522257790001574</t>
         </is>
       </c>
       <c r="Y52" t="inlineStr">
@@ -7609,34 +7613,34 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>GISSEL ANAHY REYES GERMAN</t>
+          <t>RAUL FELIX VAZQUEZ</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>649</t>
         </is>
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Juan Eduardo Torres Alcantar</t>
         </is>
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>342846</t>
+          <t>342828</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>20663</t>
+          <t>20645</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -7646,17 +7650,17 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>CARLOS JULIAN</t>
+          <t>NUBIA GUADALUPE</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>NUÑEZ</t>
+          <t>SOLARES</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>ROMERO</t>
+          <t>ARVIZU</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -7666,12 +7670,12 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>6531308246</t>
+          <t>6531665151</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>TORREON 4 Y 5</t>
+          <t>CARRETERA DEL VALLE</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
@@ -7681,17 +7685,17 @@
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>29-08-2000</t>
+          <t>27-09-2002</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>EJNR2E@GMAIL.COM</t>
+          <t>NUBIAG3@ICLOUD.COM</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>10-02-2026 19:39:03</t>
+          <t>10-02-2026 19:11:57</t>
         </is>
       </c>
       <c r="N53" t="inlineStr"/>
@@ -7712,17 +7716,17 @@
       </c>
       <c r="R53" t="inlineStr">
         <is>
-          <t>11-02-2026 19:15:15</t>
+          <t>10-02-2026 19:16:21</t>
         </is>
       </c>
       <c r="S53" t="inlineStr">
         <is>
-          <t>11-03-2026 23:59:59</t>
+          <t>10-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T53" t="inlineStr">
         <is>
-          <t>11-02-2026 19:14:37</t>
+          <t>10-02-2026 19:15:42</t>
         </is>
       </c>
       <c r="U53" t="inlineStr">
@@ -7742,19 +7746,11 @@
       </c>
       <c r="X53" t="inlineStr">
         <is>
-          <t>26150522276380001607</t>
-        </is>
-      </c>
-      <c r="Y53" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z53" t="inlineStr">
-        <is>
-          <t>GISSEL ANAHY REYES GERMAN</t>
-        </is>
-      </c>
+          <t>26150522246290001554</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr"/>
+      <c r="Z53" t="inlineStr"/>
       <c r="AA53" t="inlineStr">
         <is>
           <t>499</t>
@@ -7762,7 +7758,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>Juan Pablo Romero Andrade</t>
+          <t>Johan Osvaldo Beltran Quiros</t>
         </is>
       </c>
       <c r="AC53" t="inlineStr">
@@ -7774,12 +7770,12 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>342512</t>
+          <t>342867</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>20329</t>
+          <t>20684</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -7789,17 +7785,17 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>JOSE RICARDO</t>
+          <t>MIGUEL ANGEL</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>GARCIA</t>
+          <t>AMEZCUA</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>ANGULO</t>
+          <t>TORRES</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
@@ -7809,12 +7805,12 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>6531217599</t>
+          <t>6674708281</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>CJON HIDALGO Y 47</t>
+          <t>FLORES 22</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
@@ -7824,52 +7820,48 @@
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>03-04-1976</t>
+          <t>21-11-1995</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>RRICARDOGARCIA34@ICLOUD.COM</t>
+          <t>MIGUELAMEZCUA21@GMAIL.COM</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>10-02-2026 05:34:48</t>
-        </is>
-      </c>
-      <c r="N54" t="inlineStr">
-        <is>
-          <t>Tarifas 2026 LE</t>
-        </is>
-      </c>
+          <t>10-02-2026 20:37:24</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr"/>
       <c r="O54" t="inlineStr">
         <is>
-          <t>No Forzoso</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>RECURRENTE $649 LE</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q54" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R54" t="inlineStr">
         <is>
-          <t>11-02-2026 06:33:27</t>
+          <t>12-02-2026 20:00:11</t>
         </is>
       </c>
       <c r="S54" t="inlineStr">
         <is>
-          <t>11-03-2026 23:59:59</t>
+          <t>12-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T54" t="inlineStr">
         <is>
-          <t>11-02-2026 06:32:18</t>
+          <t>12-02-2026 19:59:09</t>
         </is>
       </c>
       <c r="U54" t="inlineStr">
@@ -7889,7 +7881,7 @@
       </c>
       <c r="X54" t="inlineStr">
         <is>
-          <t>26150522257790001574</t>
+          <t>26150522305570001650</t>
         </is>
       </c>
       <c r="Y54" t="inlineStr">
@@ -7899,34 +7891,34 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>RAUL FELIX VAZQUEZ</t>
+          <t>GISSEL ANAHY REYES GERMAN</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>Juan Eduardo Torres Alcantar</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>342828</t>
+          <t>342846</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>20645</t>
+          <t>20663</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -7936,17 +7928,17 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NUBIA GUADALUPE</t>
+          <t>CARLOS JULIAN</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>SOLARES</t>
+          <t>NUÑEZ</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>ARVIZU</t>
+          <t>ROMERO</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
@@ -7956,12 +7948,12 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>6531665151</t>
+          <t>6531308246</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>CARRETERA DEL VALLE</t>
+          <t>TORREON 4 Y 5</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
@@ -7971,17 +7963,17 @@
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>27-09-2002</t>
+          <t>29-08-2000</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>NUBIAG3@ICLOUD.COM</t>
+          <t>EJNR2E@GMAIL.COM</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>10-02-2026 19:11:57</t>
+          <t>10-02-2026 19:39:03</t>
         </is>
       </c>
       <c r="N55" t="inlineStr"/>
@@ -8002,17 +7994,17 @@
       </c>
       <c r="R55" t="inlineStr">
         <is>
-          <t>10-02-2026 19:16:21</t>
+          <t>11-02-2026 19:15:15</t>
         </is>
       </c>
       <c r="S55" t="inlineStr">
         <is>
-          <t>10-03-2026 23:59:59</t>
+          <t>11-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T55" t="inlineStr">
         <is>
-          <t>10-02-2026 19:15:42</t>
+          <t>11-02-2026 19:14:37</t>
         </is>
       </c>
       <c r="U55" t="inlineStr">
@@ -8032,11 +8024,19 @@
       </c>
       <c r="X55" t="inlineStr">
         <is>
-          <t>26150522246290001554</t>
-        </is>
-      </c>
-      <c r="Y55" t="inlineStr"/>
-      <c r="Z55" t="inlineStr"/>
+          <t>26150522276380001607</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z55" t="inlineStr">
+        <is>
+          <t>GISSEL ANAHY REYES GERMAN</t>
+        </is>
+      </c>
       <c r="AA55" t="inlineStr">
         <is>
           <t>499</t>
@@ -8044,7 +8044,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>Johan Osvaldo Beltran Quiros</t>
+          <t>Juan Pablo Romero Andrade</t>
         </is>
       </c>
       <c r="AC55" t="inlineStr">
@@ -8759,12 +8759,12 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>343947</t>
+          <t>344190</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>21764</t>
+          <t>22007</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -8774,17 +8774,17 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t xml:space="preserve">FABIOLA </t>
+          <t xml:space="preserve">SEBASTIAN </t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>LUQUE</t>
+          <t>GARCIA</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>LUQUE</t>
+          <t>GUERRERO</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
@@ -8794,79 +8794,67 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>6531273238</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t>AV CANADA Y 3RA</t>
-        </is>
-      </c>
+          <t>6531058427</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
       <c r="J61" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>05-04-1986</t>
+          <t>21-10-2009</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>FABIOLALUQUE26@GMAIL.COM</t>
+          <t>MONKEEX424@GMAIL.COM</t>
         </is>
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>16-02-2026 07:08:47</t>
+          <t>16-02-2026 17:04:57</t>
         </is>
       </c>
       <c r="N61" t="inlineStr">
         <is>
-          <t>inscripcion promo 199</t>
+          <t>Tarifas 2026 LE</t>
         </is>
       </c>
       <c r="O61" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q61" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R61" t="inlineStr">
         <is>
-          <t>19-02-2026 07:17:57</t>
+          <t>18-02-2026 17:05:10</t>
         </is>
       </c>
       <c r="S61" t="inlineStr">
         <is>
-          <t>19-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T61" t="inlineStr">
-        <is>
-          <t>19-02-2026 07:16:55</t>
-        </is>
-      </c>
+          <t>18-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T61" t="inlineStr"/>
       <c r="U61" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V61" t="inlineStr">
-        <is>
           <t>1</t>
         </is>
       </c>
+      <c r="V61" t="inlineStr"/>
       <c r="W61" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -8874,7 +8862,7 @@
       </c>
       <c r="X61" t="inlineStr">
         <is>
-          <t>26150522487880001902</t>
+          <t>26150522468100001872</t>
         </is>
       </c>
       <c r="Y61" t="inlineStr">
@@ -8884,17 +8872,17 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>RAUL FELIX VAZQUEZ</t>
+          <t>GISSEL ANAHY REYES GERMAN</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>Martin Ramiro Quiñonez Jauregui</t>
+          <t>Juan Pablo Romero Andrade</t>
         </is>
       </c>
       <c r="AC61" t="inlineStr">
@@ -8906,12 +8894,12 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>344190</t>
+          <t>343947</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>22007</t>
+          <t>21764</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -8921,17 +8909,17 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t xml:space="preserve">SEBASTIAN </t>
+          <t xml:space="preserve">FABIOLA </t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>GARCIA</t>
+          <t>LUQUE</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>GUERRERO</t>
+          <t>LUQUE</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
@@ -8941,67 +8929,79 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>6531058427</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr"/>
+          <t>6531273238</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>AV CANADA Y 3RA</t>
+        </is>
+      </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>21-10-2009</t>
+          <t>05-04-1986</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>MONKEEX424@GMAIL.COM</t>
+          <t>FABIOLALUQUE26@GMAIL.COM</t>
         </is>
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>16-02-2026 17:04:57</t>
+          <t>16-02-2026 07:08:47</t>
         </is>
       </c>
       <c r="N62" t="inlineStr">
         <is>
-          <t>Tarifas 2026 LE</t>
+          <t>inscripcion promo 199</t>
         </is>
       </c>
       <c r="O62" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q62" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R62" t="inlineStr">
         <is>
-          <t>18-02-2026 17:05:10</t>
+          <t>19-02-2026 07:17:57</t>
         </is>
       </c>
       <c r="S62" t="inlineStr">
         <is>
-          <t>18-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T62" t="inlineStr"/>
+          <t>19-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>19-02-2026 07:16:55</t>
+        </is>
+      </c>
       <c r="U62" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="V62" t="inlineStr"/>
       <c r="W62" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -9009,7 +9009,7 @@
       </c>
       <c r="X62" t="inlineStr">
         <is>
-          <t>26150522468100001872</t>
+          <t>26150522487880001902</t>
         </is>
       </c>
       <c r="Y62" t="inlineStr">
@@ -9019,17 +9019,17 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>GISSEL ANAHY REYES GERMAN</t>
+          <t>RAUL FELIX VAZQUEZ</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>Juan Pablo Romero Andrade</t>
+          <t>Martin Ramiro Quiñonez Jauregui</t>
         </is>
       </c>
       <c r="AC62" t="inlineStr">
@@ -9041,12 +9041,12 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>343531</t>
+          <t>344649</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>21348</t>
+          <t>22466</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -9056,17 +9056,17 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>URIEL IGNACIO</t>
+          <t>ROSA MARIA</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>SID</t>
+          <t>VALADES</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>AREVALO</t>
+          <t>SARMIENTO</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
@@ -9076,35 +9076,39 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>6531071848</t>
+          <t>6864265235</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>FELIX CONTRERAS 44</t>
+          <t>AV JACARANDAS 19</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>02-06-2005</t>
+          <t>26-10-1989</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>URIELIGNACIOSIDDAVERALO@GMAIL.COM</t>
+          <t>GENERICO@GAMIL.COM</t>
         </is>
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>13-02-2026 16:28:37</t>
-        </is>
-      </c>
-      <c r="N63" t="inlineStr"/>
+          <t>17-02-2026 18:13:05</t>
+        </is>
+      </c>
+      <c r="N63" t="inlineStr">
+        <is>
+          <t>inscripcion promo 199</t>
+        </is>
+      </c>
       <c r="O63" t="inlineStr">
         <is>
           <t>Forzoso</t>
@@ -9122,17 +9126,17 @@
       </c>
       <c r="R63" t="inlineStr">
         <is>
-          <t>13-02-2026 16:34:53</t>
+          <t>18-02-2026 19:06:17</t>
         </is>
       </c>
       <c r="S63" t="inlineStr">
         <is>
-          <t>13-03-2026 23:59:59</t>
+          <t>18-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T63" t="inlineStr">
         <is>
-          <t>13-02-2026 16:34:13</t>
+          <t>18-02-2026 19:05:40</t>
         </is>
       </c>
       <c r="U63" t="inlineStr">
@@ -9152,11 +9156,19 @@
       </c>
       <c r="X63" t="inlineStr">
         <is>
-          <t>26150522324410001674</t>
-        </is>
-      </c>
-      <c r="Y63" t="inlineStr"/>
-      <c r="Z63" t="inlineStr"/>
+          <t>26150522474170001890</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z63" t="inlineStr">
+        <is>
+          <t>GISSEL ANAHY REYES GERMAN</t>
+        </is>
+      </c>
       <c r="AA63" t="inlineStr">
         <is>
           <t>499</t>
@@ -9176,12 +9188,12 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>344844</t>
+          <t>343531</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>22661</t>
+          <t>21348</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -9191,17 +9203,17 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LEONEL</t>
+          <t>URIEL IGNACIO</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>CARRILLO</t>
+          <t>SID</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>ENRIQUEZ</t>
+          <t>AREVALO</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
@@ -9211,10 +9223,14 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>4494668367</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr"/>
+          <t>6531071848</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>FELIX CONTRERAS 44</t>
+        </is>
+      </c>
       <c r="J64" t="inlineStr">
         <is>
           <t>Masculino</t>
@@ -9222,56 +9238,60 @@
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>27-01-2010</t>
+          <t>02-06-2005</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>CARRILLO12346@GMAIL.COM</t>
+          <t>URIELIGNACIOSIDDAVERALO@GMAIL.COM</t>
         </is>
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>18-02-2026 15:41:40</t>
-        </is>
-      </c>
-      <c r="N64" t="inlineStr">
-        <is>
-          <t>convenio 300</t>
-        </is>
-      </c>
+          <t>13-02-2026 16:28:37</t>
+        </is>
+      </c>
+      <c r="N64" t="inlineStr"/>
       <c r="O64" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q64" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R64" t="inlineStr">
         <is>
-          <t>23-02-2026 16:40:49</t>
+          <t>13-02-2026 16:34:53</t>
         </is>
       </c>
       <c r="S64" t="inlineStr">
         <is>
-          <t>23-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T64" t="inlineStr"/>
+          <t>13-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>13-02-2026 16:34:13</t>
+        </is>
+      </c>
       <c r="U64" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V64" t="inlineStr"/>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W64" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -9279,44 +9299,36 @@
       </c>
       <c r="X64" t="inlineStr">
         <is>
-          <t>26150522587950002017</t>
-        </is>
-      </c>
-      <c r="Y64" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z64" t="inlineStr">
-        <is>
-          <t>GISSEL ANAHY REYES GERMAN</t>
-        </is>
-      </c>
+          <t>26150522324410001674</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr"/>
+      <c r="Z64" t="inlineStr"/>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Juan Pablo Romero Andrade</t>
         </is>
       </c>
       <c r="AC64" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>343813</t>
+          <t>345101</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>21630</t>
+          <t>87266</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -9326,19 +9338,19 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>YOCELIN DEL CARMEN</t>
+          <t>CAMILA</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
+          <t>VASQUEZ</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
           <t>LOPEZ</t>
         </is>
       </c>
-      <c r="F65" t="inlineStr">
-        <is>
-          <t>VALENZUELA</t>
-        </is>
-      </c>
       <c r="G65" t="inlineStr">
         <is>
           <t>52</t>
@@ -9346,14 +9358,10 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>6531305359</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr">
-        <is>
-          <t>AV CARRANZA 36</t>
-        </is>
-      </c>
+          <t>6531040237</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
       <c r="J65" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -9361,60 +9369,56 @@
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>16-07-1999</t>
+          <t>08-10-2007</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>YOCELINLOPEZ490@GMAIL.COM</t>
+          <t>VASQUEZLOPEZCAMILA@GMAIL.COM</t>
         </is>
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>15-02-2026 11:25:12</t>
-        </is>
-      </c>
-      <c r="N65" t="inlineStr"/>
+          <t>19-02-2026 15:31:29</t>
+        </is>
+      </c>
+      <c r="N65" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
       <c r="O65" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>3 MESES $1,899</t>
         </is>
       </c>
       <c r="Q65" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>633</t>
         </is>
       </c>
       <c r="R65" t="inlineStr">
         <is>
-          <t>15-02-2026 11:31:12</t>
+          <t>19-02-2026 15:34:34</t>
         </is>
       </c>
       <c r="S65" t="inlineStr">
         <is>
-          <t>15-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T65" t="inlineStr">
-        <is>
-          <t>15-02-2026 11:29:38</t>
-        </is>
-      </c>
+          <t>19-05-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T65" t="inlineStr"/>
       <c r="U65" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V65" t="inlineStr">
-        <is>
           <t>1</t>
         </is>
       </c>
+      <c r="V65" t="inlineStr"/>
       <c r="W65" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -9422,19 +9426,19 @@
       </c>
       <c r="X65" t="inlineStr">
         <is>
-          <t>26150522364500001715</t>
+          <t>26150522497060001917</t>
         </is>
       </c>
       <c r="Y65" t="inlineStr"/>
       <c r="Z65" t="inlineStr"/>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>1899</t>
         </is>
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>Juan Pablo Romero Andrade</t>
+          <t>Johan Osvaldo Beltran Quiros</t>
         </is>
       </c>
       <c r="AC65" t="inlineStr">
@@ -9446,12 +9450,12 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>344649</t>
+          <t>344860</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>22466</t>
+          <t>22677</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -9461,17 +9465,17 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>ROSA MARIA</t>
+          <t>JUAN RAMIRO</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>VALADES</t>
+          <t>MELENDEZ</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>SARMIENTO</t>
+          <t>AMAYA</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
@@ -9481,32 +9485,32 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>6864265235</t>
+          <t>6531152328</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>AV JACARANDAS 19</t>
+          <t>CANADA Y 3RA</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>26-10-1989</t>
+          <t>20-11-1998</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>GENERICO@GAMIL.COM</t>
+          <t>AMAYAJUAN0102@GMAIL.COM</t>
         </is>
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>17-02-2026 18:13:05</t>
+          <t>18-02-2026 16:29:06</t>
         </is>
       </c>
       <c r="N66" t="inlineStr">
@@ -9531,17 +9535,17 @@
       </c>
       <c r="R66" t="inlineStr">
         <is>
-          <t>18-02-2026 19:06:17</t>
+          <t>25-02-2026 17:38:16</t>
         </is>
       </c>
       <c r="S66" t="inlineStr">
         <is>
-          <t>18-03-2026 23:59:59</t>
+          <t>25-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T66" t="inlineStr">
         <is>
-          <t>18-02-2026 19:05:40</t>
+          <t>25-02-2026 17:37:43</t>
         </is>
       </c>
       <c r="U66" t="inlineStr">
@@ -9551,7 +9555,7 @@
       </c>
       <c r="V66" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W66" t="inlineStr">
@@ -9561,7 +9565,7 @@
       </c>
       <c r="X66" t="inlineStr">
         <is>
-          <t>26150522474170001890</t>
+          <t>26150522660740002115</t>
         </is>
       </c>
       <c r="Y66" t="inlineStr">
@@ -9593,12 +9597,12 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>344583</t>
+          <t>343813</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>22400</t>
+          <t>21630</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -9608,17 +9612,17 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t xml:space="preserve">CARLOS </t>
+          <t>YOCELIN DEL CARMEN</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>ACOSTA</t>
+          <t>LOPEZ</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>SANTOS</t>
+          <t>VALENZUELA</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
@@ -9628,39 +9632,35 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>6531202025</t>
+          <t>6531305359</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>AV NUEVO LEON 9</t>
+          <t>AV CARRANZA 36</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>04-03-2005</t>
+          <t>16-07-1999</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>TZELI9535@GMAIL.COM</t>
+          <t>YOCELINLOPEZ490@GMAIL.COM</t>
         </is>
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>17-02-2026 16:50:12</t>
-        </is>
-      </c>
-      <c r="N67" t="inlineStr">
-        <is>
-          <t>inscripcion promo 199</t>
-        </is>
-      </c>
+          <t>15-02-2026 11:25:12</t>
+        </is>
+      </c>
+      <c r="N67" t="inlineStr"/>
       <c r="O67" t="inlineStr">
         <is>
           <t>Forzoso</t>
@@ -9678,17 +9678,17 @@
       </c>
       <c r="R67" t="inlineStr">
         <is>
-          <t>19-02-2026 17:11:32</t>
+          <t>15-02-2026 11:31:12</t>
         </is>
       </c>
       <c r="S67" t="inlineStr">
         <is>
-          <t>19-03-2026 23:59:59</t>
+          <t>15-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T67" t="inlineStr">
         <is>
-          <t>19-02-2026 17:10:51</t>
+          <t>15-02-2026 11:29:38</t>
         </is>
       </c>
       <c r="U67" t="inlineStr">
@@ -9708,19 +9708,11 @@
       </c>
       <c r="X67" t="inlineStr">
         <is>
-          <t>26150522500690001919</t>
-        </is>
-      </c>
-      <c r="Y67" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z67" t="inlineStr">
-        <is>
-          <t>GISSEL ANAHY REYES GERMAN</t>
-        </is>
-      </c>
+          <t>26150522364500001715</t>
+        </is>
+      </c>
+      <c r="Y67" t="inlineStr"/>
+      <c r="Z67" t="inlineStr"/>
       <c r="AA67" t="inlineStr">
         <is>
           <t>499</t>
@@ -9728,7 +9720,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>Johan Osvaldo Beltran Quiros</t>
+          <t>Juan Pablo Romero Andrade</t>
         </is>
       </c>
       <c r="AC67" t="inlineStr">
@@ -9740,12 +9732,12 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>344860</t>
+          <t>344844</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>22677</t>
+          <t>22661</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -9755,17 +9747,17 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>JUAN RAMIRO</t>
+          <t>LEONEL</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>MELENDEZ</t>
+          <t>CARRILLO</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>AMAYA</t>
+          <t>ENRIQUEZ</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
@@ -9775,14 +9767,10 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>6531152328</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr">
-        <is>
-          <t>CANADA Y 3RA</t>
-        </is>
-      </c>
+          <t>4494668367</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
       <c r="J68" t="inlineStr">
         <is>
           <t>Masculino</t>
@@ -9790,64 +9778,56 @@
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>20-11-1998</t>
+          <t>27-01-2010</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>AMAYAJUAN0102@GMAIL.COM</t>
+          <t>CARRILLO12346@GMAIL.COM</t>
         </is>
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>18-02-2026 16:29:06</t>
+          <t>18-02-2026 15:41:40</t>
         </is>
       </c>
       <c r="N68" t="inlineStr">
         <is>
-          <t>inscripcion promo 199</t>
+          <t>convenio 300</t>
         </is>
       </c>
       <c r="O68" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q68" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R68" t="inlineStr">
         <is>
-          <t>25-02-2026 17:38:16</t>
+          <t>23-02-2026 16:40:49</t>
         </is>
       </c>
       <c r="S68" t="inlineStr">
         <is>
-          <t>25-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T68" t="inlineStr">
-        <is>
-          <t>25-02-2026 17:37:43</t>
-        </is>
-      </c>
+          <t>23-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T68" t="inlineStr"/>
       <c r="U68" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V68" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="V68" t="inlineStr"/>
       <c r="W68" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -9855,7 +9835,7 @@
       </c>
       <c r="X68" t="inlineStr">
         <is>
-          <t>26150522660740002115</t>
+          <t>26150522587950002017</t>
         </is>
       </c>
       <c r="Y68" t="inlineStr">
@@ -9870,29 +9850,29 @@
       </c>
       <c r="AA68" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>Juan Pablo Romero Andrade</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC68" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>345101</t>
+          <t>344583</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>87266</t>
+          <t>22400</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -9902,17 +9882,17 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>CAMILA</t>
+          <t xml:space="preserve">CARLOS </t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>VASQUEZ</t>
+          <t>ACOSTA</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>LOPEZ</t>
+          <t>SANTOS</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
@@ -9922,67 +9902,79 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>6531040237</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr"/>
+          <t>6531202025</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>AV NUEVO LEON 9</t>
+        </is>
+      </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>08-10-2007</t>
+          <t>04-03-2005</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>VASQUEZLOPEZCAMILA@GMAIL.COM</t>
+          <t>TZELI9535@GMAIL.COM</t>
         </is>
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>19-02-2026 15:31:29</t>
+          <t>17-02-2026 16:50:12</t>
         </is>
       </c>
       <c r="N69" t="inlineStr">
         <is>
-          <t>Tarifas 2026 LE</t>
+          <t>inscripcion promo 199</t>
         </is>
       </c>
       <c r="O69" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P69" t="inlineStr">
         <is>
-          <t>3 MESES $1,899</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q69" t="inlineStr">
         <is>
-          <t>633</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R69" t="inlineStr">
         <is>
-          <t>19-02-2026 15:34:34</t>
+          <t>19-02-2026 17:11:32</t>
         </is>
       </c>
       <c r="S69" t="inlineStr">
         <is>
-          <t>19-05-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T69" t="inlineStr"/>
+          <t>19-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>19-02-2026 17:10:51</t>
+        </is>
+      </c>
       <c r="U69" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="V69" t="inlineStr"/>
       <c r="W69" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -9990,14 +9982,22 @@
       </c>
       <c r="X69" t="inlineStr">
         <is>
-          <t>26150522497060001917</t>
-        </is>
-      </c>
-      <c r="Y69" t="inlineStr"/>
-      <c r="Z69" t="inlineStr"/>
+          <t>26150522500690001919</t>
+        </is>
+      </c>
+      <c r="Y69" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z69" t="inlineStr">
+        <is>
+          <t>GISSEL ANAHY REYES GERMAN</t>
+        </is>
+      </c>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>1899</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB69" t="inlineStr">
@@ -10014,12 +10014,12 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>344507</t>
+          <t>345808</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>22324</t>
+          <t>87973</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -10029,17 +10029,17 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>KAREN ANDREA</t>
+          <t xml:space="preserve">JESUS MANUEL </t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>ISAIS</t>
+          <t xml:space="preserve">GARCIA </t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>QUILES</t>
+          <t>MONTAÑO</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
@@ -10049,32 +10049,28 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>6531517509</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr">
-        <is>
-          <t>AV PUEBLA 1RA</t>
-        </is>
-      </c>
+          <t>6531557014</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
       <c r="J70" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>12-02-1999</t>
+          <t>25-12-1981</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>KARENANDREAISAIS1999@GMAIL.COM</t>
+          <t>CHUMA0292@GMAIL.COM</t>
         </is>
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t>17-02-2026 14:45:48</t>
+          <t>23-02-2026 14:45:30</t>
         </is>
       </c>
       <c r="N70" t="inlineStr">
@@ -10084,44 +10080,36 @@
       </c>
       <c r="O70" t="inlineStr">
         <is>
-          <t>No Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>PLAN RECURRENTE PAGO INCIAL $1,449 LE</t>
+          <t>1 MES $899</t>
         </is>
       </c>
       <c r="Q70" t="inlineStr">
         <is>
-          <t>1449</t>
+          <t>899</t>
         </is>
       </c>
       <c r="R70" t="inlineStr">
         <is>
-          <t>17-02-2026 14:50:44</t>
+          <t>25-02-2026 14:28:08</t>
         </is>
       </c>
       <c r="S70" t="inlineStr">
         <is>
-          <t>17-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T70" t="inlineStr">
-        <is>
-          <t>17-02-2026 14:49:35</t>
-        </is>
-      </c>
+          <t>25-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T70" t="inlineStr"/>
       <c r="U70" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V70" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="V70" t="inlineStr"/>
       <c r="W70" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -10129,36 +10117,44 @@
       </c>
       <c r="X70" t="inlineStr">
         <is>
-          <t>26150522430060001816</t>
-        </is>
-      </c>
-      <c r="Y70" t="inlineStr"/>
-      <c r="Z70" t="inlineStr"/>
+          <t>26150522653580002100</t>
+        </is>
+      </c>
+      <c r="Y70" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z70" t="inlineStr">
+        <is>
+          <t>GISSEL ANAHY REYES GERMAN</t>
+        </is>
+      </c>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>1449</t>
+          <t>899</t>
         </is>
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Juan Pablo Romero Andrade</t>
         </is>
       </c>
       <c r="AC70" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>345808</t>
+          <t>345926</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>87973</t>
+          <t>88091</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -10168,17 +10164,17 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t xml:space="preserve">JESUS MANUEL </t>
+          <t>PAOLA STEPHANY</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t xml:space="preserve">GARCIA </t>
+          <t>ROBLES</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>MONTAÑO</t>
+          <t>OLIVARRIA</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
@@ -10188,28 +10184,28 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>6531557014</t>
+          <t>6531333751</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
       <c r="J71" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>25-12-1981</t>
+          <t>06-06-1988</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>CHUMA0292@GMAIL.COM</t>
+          <t>PAOLAS.ROBLES@OUTLOOK.COM</t>
         </is>
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t>23-02-2026 14:45:30</t>
+          <t>23-02-2026 17:33:51</t>
         </is>
       </c>
       <c r="N71" t="inlineStr">
@@ -10234,7 +10230,7 @@
       </c>
       <c r="R71" t="inlineStr">
         <is>
-          <t>25-02-2026 14:28:08</t>
+          <t>25-02-2026 17:32:24</t>
         </is>
       </c>
       <c r="S71" t="inlineStr">
@@ -10256,7 +10252,7 @@
       </c>
       <c r="X71" t="inlineStr">
         <is>
-          <t>26150522653580002100</t>
+          <t>26150522660500002114</t>
         </is>
       </c>
       <c r="Y71" t="inlineStr">
@@ -10266,7 +10262,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>GISSEL ANAHY REYES GERMAN</t>
+          <t>MANUEL DIAZ RECEPCION</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -10288,12 +10284,12 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>345926</t>
+          <t>345985</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>88091</t>
+          <t>88150</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -10303,17 +10299,17 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>PAOLA STEPHANY</t>
+          <t>LUZ</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>ROBLES</t>
+          <t>MENESES</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>OLIVARRIA</t>
+          <t>MENESES</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
@@ -10323,7 +10319,7 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>6531333751</t>
+          <t>6531109304</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -10334,17 +10330,17 @@
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>06-06-1988</t>
+          <t>28-02-2010</t>
         </is>
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>PAOLAS.ROBLES@OUTLOOK.COM</t>
+          <t>LUZMENESES2810@GMAIL.COM</t>
         </is>
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>23-02-2026 17:33:51</t>
+          <t>23-02-2026 18:29:05</t>
         </is>
       </c>
       <c r="N72" t="inlineStr">
@@ -10369,18 +10365,18 @@
       </c>
       <c r="R72" t="inlineStr">
         <is>
-          <t>25-02-2026 17:32:24</t>
+          <t>23-02-2026 18:30:15</t>
         </is>
       </c>
       <c r="S72" t="inlineStr">
         <is>
-          <t>25-03-2026 23:59:59</t>
+          <t>23-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T72" t="inlineStr"/>
       <c r="U72" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="V72" t="inlineStr"/>
@@ -10391,19 +10387,11 @@
       </c>
       <c r="X72" t="inlineStr">
         <is>
-          <t>26150522660500002114</t>
-        </is>
-      </c>
-      <c r="Y72" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z72" t="inlineStr">
-        <is>
-          <t>MANUEL DIAZ RECEPCION</t>
-        </is>
-      </c>
+          <t>26150522595820002029</t>
+        </is>
+      </c>
+      <c r="Y72" t="inlineStr"/>
+      <c r="Z72" t="inlineStr"/>
       <c r="AA72" t="inlineStr">
         <is>
           <t>899</t>
@@ -10423,12 +10411,12 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>345697</t>
+          <t>345830</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>87862</t>
+          <t>87995</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -10438,17 +10426,17 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t xml:space="preserve">EMMANUEL </t>
+          <t>MARIA GUADALUPE</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>SUAREZ</t>
+          <t>HEREDIA</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>QUIROGA</t>
+          <t>HERRERA</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
@@ -10458,53 +10446,57 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>6531748406</t>
-        </is>
-      </c>
-      <c r="I73" t="inlineStr"/>
+          <t>6531742310</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>CANADA B Y SAN ALBERTO</t>
+        </is>
+      </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>05-05-2007</t>
+          <t>22-03-1976</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>JUANEMANUEL.S.Q@GMAIL.COM</t>
+          <t>HEREDIAHERRERA76@GMAIL.COM</t>
         </is>
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t>23-02-2026 10:30:42</t>
+          <t>23-02-2026 15:19:36</t>
         </is>
       </c>
       <c r="N73" t="inlineStr">
         <is>
-          <t>convenio 300</t>
+          <t>inscripcion promo 199</t>
         </is>
       </c>
       <c r="O73" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q73" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R73" t="inlineStr">
         <is>
-          <t>23-02-2026 10:34:37</t>
+          <t>23-02-2026 15:23:45</t>
         </is>
       </c>
       <c r="S73" t="inlineStr">
@@ -10512,13 +10504,21 @@
           <t>23-03-2026 23:59:59</t>
         </is>
       </c>
-      <c r="T73" t="inlineStr"/>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>23-02-2026 15:23:09</t>
+        </is>
+      </c>
       <c r="U73" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V73" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="V73" t="inlineStr"/>
       <c r="W73" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -10526,36 +10526,36 @@
       </c>
       <c r="X73" t="inlineStr">
         <is>
-          <t>26150522576190001992</t>
+          <t>26150522584530002009</t>
         </is>
       </c>
       <c r="Y73" t="inlineStr"/>
       <c r="Z73" t="inlineStr"/>
       <c r="AA73" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Juan Pablo Romero Andrade</t>
         </is>
       </c>
       <c r="AC73" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>345830</t>
+          <t>344507</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>87995</t>
+          <t>22324</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -10565,17 +10565,17 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>MARIA GUADALUPE</t>
+          <t>KAREN ANDREA</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>HEREDIA</t>
+          <t>ISAIS</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>HERRERA</t>
+          <t>QUILES</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
@@ -10585,12 +10585,12 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>6531742310</t>
+          <t>6531517509</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>CANADA B Y SAN ALBERTO</t>
+          <t>AV PUEBLA 1RA</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
@@ -10600,52 +10600,52 @@
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>22-03-1976</t>
+          <t>12-02-1999</t>
         </is>
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>HEREDIAHERRERA76@GMAIL.COM</t>
+          <t>KARENANDREAISAIS1999@GMAIL.COM</t>
         </is>
       </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t>23-02-2026 15:19:36</t>
+          <t>17-02-2026 14:45:48</t>
         </is>
       </c>
       <c r="N74" t="inlineStr">
         <is>
-          <t>inscripcion promo 199</t>
+          <t>Tarifas 2026 LE</t>
         </is>
       </c>
       <c r="O74" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>No Forzoso</t>
         </is>
       </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>PLAN RECURRENTE PAGO INCIAL $1,449 LE</t>
         </is>
       </c>
       <c r="Q74" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>1449</t>
         </is>
       </c>
       <c r="R74" t="inlineStr">
         <is>
-          <t>23-02-2026 15:23:45</t>
+          <t>17-02-2026 14:50:44</t>
         </is>
       </c>
       <c r="S74" t="inlineStr">
         <is>
-          <t>23-03-2026 23:59:59</t>
+          <t>17-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T74" t="inlineStr">
         <is>
-          <t>23-02-2026 15:23:09</t>
+          <t>17-02-2026 14:49:35</t>
         </is>
       </c>
       <c r="U74" t="inlineStr">
@@ -10665,36 +10665,36 @@
       </c>
       <c r="X74" t="inlineStr">
         <is>
-          <t>26150522584530002009</t>
+          <t>26150522430060001816</t>
         </is>
       </c>
       <c r="Y74" t="inlineStr"/>
       <c r="Z74" t="inlineStr"/>
       <c r="AA74" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>1449</t>
         </is>
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>Juan Pablo Romero Andrade</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC74" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>344807</t>
+          <t>345697</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>22624</t>
+          <t>87862</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -10704,17 +10704,17 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>CRUZ GUADALUPE</t>
+          <t xml:space="preserve">EMMANUEL </t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>LUGO</t>
+          <t>SUAREZ</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>ROCHA</t>
+          <t>QUIROGA</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
@@ -10724,79 +10724,67 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>6532082764</t>
-        </is>
-      </c>
-      <c r="I75" t="inlineStr">
-        <is>
-          <t>AV NAYARIT 43 Y 44</t>
-        </is>
-      </c>
+          <t>6531748406</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr"/>
       <c r="J75" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>01-01-2000</t>
+          <t>05-05-2007</t>
         </is>
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>CRUZGLP01@LCLOUD.COM</t>
+          <t>JUANEMANUEL.S.Q@GMAIL.COM</t>
         </is>
       </c>
       <c r="M75" t="inlineStr">
         <is>
-          <t>18-02-2026 12:56:53</t>
+          <t>23-02-2026 10:30:42</t>
         </is>
       </c>
       <c r="N75" t="inlineStr">
         <is>
-          <t>inscripcion promo 199</t>
+          <t>convenio 300</t>
         </is>
       </c>
       <c r="O75" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q75" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R75" t="inlineStr">
         <is>
-          <t>20-02-2026 10:30:09</t>
+          <t>23-02-2026 10:34:37</t>
         </is>
       </c>
       <c r="S75" t="inlineStr">
         <is>
-          <t>20-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T75" t="inlineStr">
-        <is>
-          <t>20-02-2026 10:29:02</t>
-        </is>
-      </c>
+          <t>23-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T75" t="inlineStr"/>
       <c r="U75" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V75" t="inlineStr">
-        <is>
           <t>1</t>
         </is>
       </c>
+      <c r="V75" t="inlineStr"/>
       <c r="W75" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -10804,44 +10792,36 @@
       </c>
       <c r="X75" t="inlineStr">
         <is>
-          <t>26150522523340001940</t>
-        </is>
-      </c>
-      <c r="Y75" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z75" t="inlineStr">
-        <is>
-          <t>GISSEL ANAHY REYES GERMAN</t>
-        </is>
-      </c>
+          <t>26150522576190001992</t>
+        </is>
+      </c>
+      <c r="Y75" t="inlineStr"/>
+      <c r="Z75" t="inlineStr"/>
       <c r="AA75" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>Juan Pablo Romero Andrade</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC75" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>345985</t>
+          <t>346907</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>88150</t>
+          <t>89072</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -10851,17 +10831,17 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>LUZ</t>
+          <t>ABIGAIL</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>MENESES</t>
+          <t>LOPEZ</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>MENESES</t>
+          <t>VALENZUELA</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
@@ -10871,10 +10851,14 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>6531109304</t>
-        </is>
-      </c>
-      <c r="I76" t="inlineStr"/>
+          <t>6535385654</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>AV SONORA 46 Y 47</t>
+        </is>
+      </c>
       <c r="J76" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -10882,56 +10866,64 @@
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>28-02-2010</t>
+          <t>25-06-2003</t>
         </is>
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>LUZMENESES2810@GMAIL.COM</t>
+          <t>ALV252003@GMAIL.COM</t>
         </is>
       </c>
       <c r="M76" t="inlineStr">
         <is>
-          <t>23-02-2026 18:29:05</t>
+          <t>27-02-2026 10:45:30</t>
         </is>
       </c>
       <c r="N76" t="inlineStr">
         <is>
-          <t>Tarifas 2026 LE</t>
+          <t>inscripcion promo 199</t>
         </is>
       </c>
       <c r="O76" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>1 MES $899</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q76" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R76" t="inlineStr">
         <is>
-          <t>23-02-2026 18:30:15</t>
+          <t>27-02-2026 10:47:55</t>
         </is>
       </c>
       <c r="S76" t="inlineStr">
         <is>
-          <t>23-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T76" t="inlineStr"/>
+          <t>27-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>27-02-2026 10:46:55</t>
+        </is>
+      </c>
       <c r="U76" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V76" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="V76" t="inlineStr"/>
       <c r="W76" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -10939,36 +10931,36 @@
       </c>
       <c r="X76" t="inlineStr">
         <is>
-          <t>26150522595820002029</t>
+          <t>26150522708890002174</t>
         </is>
       </c>
       <c r="Y76" t="inlineStr"/>
       <c r="Z76" t="inlineStr"/>
       <c r="AA76" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>Juan Pablo Romero Andrade</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC76" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>346907</t>
+          <t>344807</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>89072</t>
+          <t>22624</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -10978,17 +10970,17 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>ABIGAIL</t>
+          <t>CRUZ GUADALUPE</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>LOPEZ</t>
+          <t>LUGO</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>VALENZUELA</t>
+          <t>ROCHA</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
@@ -10998,12 +10990,12 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>6535385654</t>
+          <t>6532082764</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>AV SONORA 46 Y 47</t>
+          <t>AV NAYARIT 43 Y 44</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
@@ -11013,17 +11005,17 @@
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>25-06-2003</t>
+          <t>01-01-2000</t>
         </is>
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>ALV252003@GMAIL.COM</t>
+          <t>CRUZGLP01@LCLOUD.COM</t>
         </is>
       </c>
       <c r="M77" t="inlineStr">
         <is>
-          <t>27-02-2026 10:45:30</t>
+          <t>18-02-2026 12:56:53</t>
         </is>
       </c>
       <c r="N77" t="inlineStr">
@@ -11048,17 +11040,17 @@
       </c>
       <c r="R77" t="inlineStr">
         <is>
-          <t>27-02-2026 10:47:55</t>
+          <t>20-02-2026 10:30:09</t>
         </is>
       </c>
       <c r="S77" t="inlineStr">
         <is>
-          <t>27-03-2026 23:59:59</t>
+          <t>20-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T77" t="inlineStr">
         <is>
-          <t>27-02-2026 10:46:55</t>
+          <t>20-02-2026 10:29:02</t>
         </is>
       </c>
       <c r="U77" t="inlineStr">
@@ -11078,11 +11070,19 @@
       </c>
       <c r="X77" t="inlineStr">
         <is>
-          <t>26150522708890002174</t>
-        </is>
-      </c>
-      <c r="Y77" t="inlineStr"/>
-      <c r="Z77" t="inlineStr"/>
+          <t>26150522523340001940</t>
+        </is>
+      </c>
+      <c r="Y77" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z77" t="inlineStr">
+        <is>
+          <t>GISSEL ANAHY REYES GERMAN</t>
+        </is>
+      </c>
       <c r="AA77" t="inlineStr">
         <is>
           <t>499</t>
@@ -11090,12 +11090,12 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Juan Pablo Romero Andrade</t>
         </is>
       </c>
       <c r="AC77" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>

--- a/data/rutinas/sucursales/Socios_con_y_sin_rutina__SAN LUIS.xlsx
+++ b/data/rutinas/sucursales/Socios_con_y_sin_rutina__SAN LUIS.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC5"/>
+  <dimension ref="A1:AC8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -987,12 +987,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>347775</t>
+          <t>348010</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>89940</t>
+          <t>90175</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1002,17 +1002,17 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>KAREN PAOLA</t>
+          <t>ISRAEL</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>DUARTE</t>
+          <t>VALDEZ</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>RODRIGUEZ</t>
+          <t>ALVARADO</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -1022,33 +1022,33 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>6531128069</t>
+          <t>6531174824</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>22-12-1996</t>
+          <t>12-12-1996</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>PAO.DUARTE.ROD@GMAIL.COM</t>
+          <t>ISRAELVALDEZ647@GMAIL.COM</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>02-03-2026 17:55:45</t>
+          <t>03-03-2026 11:23:55</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>convenio 300</t>
+          <t>Tarifas 2026 LE</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -1058,28 +1058,28 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>1 MES $899</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>899</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>02-03-2026 17:58:23</t>
+          <t>03-03-2026 11:25:21</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>02-04-2026 23:59:59</t>
+          <t>03-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T5" t="inlineStr"/>
       <c r="U5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="V5" t="inlineStr"/>
@@ -1090,24 +1090,429 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>26150522809500002290</t>
+          <t>26150522837480002335</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr"/>
       <c r="Z5" t="inlineStr"/>
       <c r="AA5" t="inlineStr">
         <is>
+          <t>899</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>348143</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>90308</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>SAN LUIS</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>JAQUELINE</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>OZUNA</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>CASTRO</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>6531299473</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>CJON MORELOS Y JUAREZ</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>05-04-1999</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>OZUNA052024@OUTLOOK.COM</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>03-03-2026 17:02:29</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>Inscripcion $150</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
           <t>549</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>03-03-2026 17:05:49</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>03-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>03-03-2026 17:05:17</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>26150522849130002352</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr"/>
+      <c r="Z6" t="inlineStr"/>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>Juan Pablo Romero Andrade</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>347775</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>89940</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>SAN LUIS</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>KAREN PAOLA</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>DUARTE</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>RODRIGUEZ</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>6531128069</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>22-12-1996</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>PAO.DUARTE.ROD@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>02-03-2026 17:55:45</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>convenio 300</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>CONVENIOS $549</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>02-03-2026 17:58:23</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>02-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr"/>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr"/>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>26150522809500002290</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr"/>
+      <c r="Z7" t="inlineStr"/>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
         <is>
           <t>N/D</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
+      <c r="AC7" t="inlineStr">
         <is>
           <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>347998</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>90163</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>SAN LUIS</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>DAHENA DARLENE</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>VEGA</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>MONTIZO</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>6531111880</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>AV CARRANZA 29 Y 30</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>04-06-1992</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>SUPERVICION.FRUTAL@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>03-03-2026 10:11:47</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>Inscripcion $150</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>03-03-2026 10:21:09</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>03-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>03-03-2026 10:20:10</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>26150522836290002334</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr"/>
+      <c r="Z8" t="inlineStr"/>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>Juan Eduardo Torres Alcantar</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>con rutina</t>
         </is>
       </c>
     </row>

--- a/data/rutinas/sucursales/Socios_con_y_sin_rutina__SAN LUIS.xlsx
+++ b/data/rutinas/sucursales/Socios_con_y_sin_rutina__SAN LUIS.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC8"/>
+  <dimension ref="A1:AC13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -860,12 +860,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>347479</t>
+          <t>335330</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>89644</t>
+          <t>24555</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -875,17 +875,17 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">LISA </t>
+          <t>DIEGO</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>FLORES</t>
+          <t>VAZQUEZ</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>YESCAS</t>
+          <t>CELIS</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -895,33 +895,33 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>6531711682</t>
+          <t>6531649951</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>26-10-1975</t>
+          <t>12-09-2007</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>VYBRASILISA@GMAIL.COM</t>
+          <t>DIEGOVAZQUEZ1209@GMAIL.COM</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>02-03-2026 10:01:44</t>
+          <t>16-01-2026 14:12:31</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>Tarifas 2026 LE</t>
+          <t>convenio 300</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -931,28 +931,28 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>3 MESES $1,899</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>633</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>02-03-2026 10:03:52</t>
+          <t>04-03-2026 18:45:03</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>02-06-2026 23:59:59</t>
+          <t>04-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T4" t="inlineStr"/>
       <c r="U4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="V4" t="inlineStr"/>
@@ -963,36 +963,44 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>26150522787060002251</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr"/>
-      <c r="Z4" t="inlineStr"/>
+          <t>26150522895500002404</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>RAUL FELIX VAZQUEZ</t>
+        </is>
+      </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>1899</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>Juan Eduardo Torres Alcantar</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>348010</t>
+          <t>347389</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>90175</t>
+          <t>89554</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1002,17 +1010,17 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>ISRAEL</t>
+          <t>MARTIN</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>VALDEZ</t>
+          <t>LIRA</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>ALVARADO</t>
+          <t>SORIA</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -1022,10 +1030,14 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>6531174824</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>6531197369</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>CJON LAZARO CARDENAS 41 Y42</t>
+        </is>
+      </c>
       <c r="J5" t="inlineStr">
         <is>
           <t>Masculino</t>
@@ -1033,56 +1045,64 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>12-12-1996</t>
+          <t>25-05-1974</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>ISRAELVALDEZ647@GMAIL.COM</t>
+          <t>AUTOELECTRICOGDL1977@GMAIL.COM</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>03-03-2026 11:23:55</t>
+          <t>02-03-2026 05:39:01</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>Tarifas 2026 LE</t>
+          <t>Inscripcion $150</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>1 MES $899</t>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>03-03-2026 11:25:21</t>
+          <t>05-03-2026 05:22:25</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>03-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T5" t="inlineStr"/>
+          <t>05-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>05-03-2026 05:21:13</t>
+        </is>
+      </c>
       <c r="U5" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="V5" t="inlineStr"/>
       <c r="W5" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -1090,14 +1110,22 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>26150522837480002335</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr"/>
-      <c r="Z5" t="inlineStr"/>
+          <t>26150522901950002416</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>RAUL FELIX VAZQUEZ</t>
+        </is>
+      </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -1114,12 +1142,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>348143</t>
+          <t>346790</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>90308</t>
+          <t>88955</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1129,99 +1157,87 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>JAQUELINE</t>
+          <t>ABRAHAM</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>OZUNA</t>
+          <t>QUINTERO</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>CASTRO</t>
+          <t>QUINTERO</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>6531299473</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>CJON MORELOS Y JUAREZ</t>
-        </is>
-      </c>
+          <t>8315665944</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>05-04-1999</t>
+          <t>17-05-1993</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>OZUNA052024@OUTLOOK.COM</t>
+          <t>ABRAHAMQUINT66@GMAIL.COM</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>03-03-2026 17:02:29</t>
+          <t>26-02-2026 17:53:31</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>Inscripcion $150</t>
+          <t>Tarifas 2026 LE</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+          <t>1 MES $899</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>899</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>03-03-2026 17:05:49</t>
+          <t>04-03-2026 18:31:38</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>03-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t>03-03-2026 17:05:17</t>
-        </is>
-      </c>
+          <t>04-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr"/>
       <c r="U6" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="V6" t="inlineStr"/>
       <c r="W6" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -1229,36 +1245,44 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>26150522849130002352</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr"/>
-      <c r="Z6" t="inlineStr"/>
+          <t>26150522894600002401</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>GISSEL ANAHY REYES GERMAN</t>
+        </is>
+      </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>899</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>Juan Pablo Romero Andrade</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>347775</t>
+          <t>347762</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>89940</t>
+          <t>89927</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1268,17 +1292,17 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>KAREN PAOLA</t>
+          <t>ROMAN ISAAC</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>DUARTE</t>
+          <t xml:space="preserve">GOMEZ </t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>RODRIGUEZ</t>
+          <t>COTA</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -1288,28 +1312,28 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>6531128069</t>
+          <t>6221718560</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>22-12-1996</t>
+          <t>07-02-1989</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>PAO.DUARTE.ROD@GMAIL.COM</t>
+          <t>ROMANG89@LIVE.COM.MX</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>02-03-2026 17:55:45</t>
+          <t>02-03-2026 17:42:58</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -1334,12 +1358,12 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>02-03-2026 17:58:23</t>
+          <t>04-03-2026 17:39:25</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>02-04-2026 23:59:59</t>
+          <t>04-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T7" t="inlineStr"/>
@@ -1356,11 +1380,19 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>26150522809500002290</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr"/>
-      <c r="Z7" t="inlineStr"/>
+          <t>26150522891430002392</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>GISSEL ANAHY REYES GERMAN</t>
+        </is>
+      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>549</t>
@@ -1368,24 +1400,24 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Johan Osvaldo Beltran Quiros</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>347998</t>
+          <t>347479</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>90163</t>
+          <t>89644</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1395,17 +1427,17 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>DAHENA DARLENE</t>
+          <t xml:space="preserve">LISA </t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>VEGA</t>
+          <t>FLORES</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>MONTIZO</t>
+          <t>YESCAS</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -1415,14 +1447,10 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>6531111880</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>AV CARRANZA 29 Y 30</t>
-        </is>
-      </c>
+          <t>6531711682</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -1430,64 +1458,56 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>04-06-1992</t>
+          <t>26-10-1975</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>SUPERVICION.FRUTAL@GMAIL.COM</t>
+          <t>VYBRASILISA@GMAIL.COM</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>03-03-2026 10:11:47</t>
+          <t>02-03-2026 10:01:44</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>Inscripcion $150</t>
+          <t>Tarifas 2026 LE</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+          <t>3 MESES $1,899</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>633</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>03-03-2026 10:21:09</t>
+          <t>02-03-2026 10:03:52</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>03-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T8" t="inlineStr">
-        <is>
-          <t>03-03-2026 10:20:10</t>
-        </is>
-      </c>
+          <t>02-06-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr"/>
       <c r="U8" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V8" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr"/>
       <c r="W8" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -1495,22 +1515,701 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>26150522836290002334</t>
+          <t>26150522787060002251</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr"/>
       <c r="Z8" t="inlineStr"/>
       <c r="AA8" t="inlineStr">
         <is>
+          <t>1899</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>Juan Eduardo Torres Alcantar</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>347775</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>89940</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>SAN LUIS</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>KAREN PAOLA</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>DUARTE</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>RODRIGUEZ</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>6531128069</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>22-12-1996</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>PAO.DUARTE.ROD@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>02-03-2026 17:55:45</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>convenio 300</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>CONVENIOS $549</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
           <t>549</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>02-03-2026 17:58:23</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>02-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr"/>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr"/>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>26150522809500002290</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr"/>
+      <c r="Z9" t="inlineStr"/>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>348010</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>90175</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>SAN LUIS</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>ISRAEL</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>VALDEZ</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>ALVARADO</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>6531174824</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>12-12-1996</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>ISRAELVALDEZ647@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>03-03-2026 11:23:55</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>1 MES $899</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>899</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>03-03-2026 11:25:21</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>03-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr"/>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr"/>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>26150522837480002335</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr"/>
+      <c r="Z10" t="inlineStr"/>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>899</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>347867</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>90032</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>SAN LUIS</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>ADRIANA</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>ESQUER</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>TERAN</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>6865432785</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>OBREGON Y 20</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>04-12-1969</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>AET89@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>02-03-2026 19:24:40</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>Inscripcion $150</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>04-03-2026 18:23:35</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>04-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>04-03-2026 18:22:20</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>26150522894140002400</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>GISSEL ANAHY REYES GERMAN</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>Johan Osvaldo Beltran Quiros</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>347998</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>90163</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>SAN LUIS</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>DAHENA DARLENE</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>VEGA</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>MONTIZO</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>6531111880</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>AV CARRANZA 29 Y 30</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>04-06-1992</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>SUPERVICION.FRUTAL@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>03-03-2026 10:11:47</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>Inscripcion $150</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>03-03-2026 10:21:09</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>03-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>03-03-2026 10:20:10</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>26150522836290002334</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr"/>
+      <c r="Z12" t="inlineStr"/>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
         <is>
           <t>Juan Eduardo Torres Alcantar</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>348143</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>90308</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>SAN LUIS</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>JAQUELINE</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>OZUNA</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>CASTRO</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>6531299473</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>CJON MORELOS Y JUAREZ</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>05-04-1999</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>OZUNA052024@OUTLOOK.COM</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>03-03-2026 17:02:29</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>Inscripcion $150</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>03-03-2026 17:05:49</t>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>03-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>03-03-2026 17:05:17</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>26150522849130002352</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr"/>
+      <c r="Z13" t="inlineStr"/>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>Juan Pablo Romero Andrade</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
         <is>
           <t>con rutina</t>
         </is>

--- a/data/rutinas/sucursales/Socios_con_y_sin_rutina__SAN LUIS.xlsx
+++ b/data/rutinas/sucursales/Socios_con_y_sin_rutina__SAN LUIS.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC13"/>
+  <dimension ref="A1:AC15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -578,12 +578,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>346761</t>
+          <t>335330</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>88926</t>
+          <t>24555</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -593,17 +593,17 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">JOSE LUIS </t>
+          <t>DIEGO</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>RAMIREZ</t>
+          <t>VAZQUEZ</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>SANCHEZ</t>
+          <t>CELIS</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -613,14 +613,10 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>6531068319</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>CJON 5 DE MAYO 3302</t>
-        </is>
-      </c>
+          <t>6531649951</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr">
         <is>
           <t>Masculino</t>
@@ -628,32 +624,32 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>17-03-1993</t>
+          <t>12-09-2007</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>JR555204@GMAIL.COM</t>
+          <t>DIEGOVAZQUEZ1209@GMAIL.COM</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>26-02-2026 17:00:06</t>
+          <t>16-01-2026 14:12:31</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>Inscripcion $150</t>
+          <t>convenio 300</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
@@ -663,29 +659,21 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>02-03-2026 18:43:58</t>
+          <t>04-03-2026 18:45:03</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>02-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T2" t="inlineStr">
-        <is>
-          <t>02-03-2026 18:43:08</t>
-        </is>
-      </c>
+          <t>03-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr"/>
       <c r="U2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="V2" t="inlineStr"/>
       <c r="W2" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -693,7 +681,7 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>26150522813580002301</t>
+          <t>26150522895500002404</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -703,7 +691,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>GISSEL ANAHY REYES GERMAN</t>
+          <t>RAUL FELIX VAZQUEZ</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -811,7 +799,7 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>02-04-2026 23:59:59</t>
+          <t>01-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T3" t="inlineStr"/>
@@ -860,12 +848,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>335330</t>
+          <t>346761</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>24555</t>
+          <t>88926</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -875,17 +863,17 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>DIEGO</t>
+          <t xml:space="preserve">JOSE LUIS </t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>VAZQUEZ</t>
+          <t>RAMIREZ</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>CELIS</t>
+          <t>SANCHEZ</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -895,10 +883,14 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>6531649951</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>6531068319</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>CJON 5 DE MAYO 3302</t>
+        </is>
+      </c>
       <c r="J4" t="inlineStr">
         <is>
           <t>Masculino</t>
@@ -906,32 +898,32 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>12-09-2007</t>
+          <t>17-03-1993</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>DIEGOVAZQUEZ1209@GMAIL.COM</t>
+          <t>JR555204@GMAIL.COM</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>16-01-2026 14:12:31</t>
+          <t>26-02-2026 17:00:06</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>convenio 300</t>
+          <t>Inscripcion $150</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
@@ -941,21 +933,29 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>04-03-2026 18:45:03</t>
+          <t>02-03-2026 18:43:58</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>04-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T4" t="inlineStr"/>
+          <t>01-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>02-03-2026 18:43:08</t>
+        </is>
+      </c>
       <c r="U4" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V4" t="inlineStr"/>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W4" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -963,7 +963,7 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>26150522895500002404</t>
+          <t>26150522813580002301</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
@@ -973,7 +973,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>RAUL FELIX VAZQUEZ</t>
+          <t>GISSEL ANAHY REYES GERMAN</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1085,7 +1085,7 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>05-04-2026 23:59:59</t>
+          <t>04-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1228,7 +1228,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>04-04-2026 23:59:59</t>
+          <t>03-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T6" t="inlineStr"/>
@@ -1277,12 +1277,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>347762</t>
+          <t>347867</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>89927</t>
+          <t>90032</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1292,17 +1292,17 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>ROMAN ISAAC</t>
+          <t>ADRIANA</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t xml:space="preserve">GOMEZ </t>
+          <t>ESQUER</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>COTA</t>
+          <t>TERAN</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -1312,43 +1312,47 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>6221718560</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>6865432785</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>OBREGON Y 20</t>
+        </is>
+      </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>07-02-1989</t>
+          <t>04-12-1969</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>ROMANG89@LIVE.COM.MX</t>
+          <t>AET89@GMAIL.COM</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>02-03-2026 17:42:58</t>
+          <t>02-03-2026 19:24:40</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>convenio 300</t>
+          <t>Inscripcion $150</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
@@ -1358,21 +1362,29 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>04-03-2026 17:39:25</t>
+          <t>04-03-2026 18:23:35</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>04-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T7" t="inlineStr"/>
+          <t>03-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>04-03-2026 18:22:20</t>
+        </is>
+      </c>
       <c r="U7" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V7" t="inlineStr"/>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="W7" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -1380,7 +1392,7 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>26150522891430002392</t>
+          <t>26150522894140002400</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
@@ -1412,12 +1424,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>347479</t>
+          <t>347775</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>89644</t>
+          <t>89940</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1427,17 +1439,17 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t xml:space="preserve">LISA </t>
+          <t>KAREN PAOLA</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>FLORES</t>
+          <t>DUARTE</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>YESCAS</t>
+          <t>RODRIGUEZ</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -1447,7 +1459,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>6531711682</t>
+          <t>6531128069</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1458,22 +1470,22 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>26-10-1975</t>
+          <t>22-12-1996</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>VYBRASILISA@GMAIL.COM</t>
+          <t>PAO.DUARTE.ROD@GMAIL.COM</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>02-03-2026 10:01:44</t>
+          <t>02-03-2026 17:55:45</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>Tarifas 2026 LE</t>
+          <t>convenio 300</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -1483,28 +1495,28 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>3 MESES $1,899</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>633</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>02-03-2026 10:03:52</t>
+          <t>02-03-2026 17:58:23</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>02-06-2026 23:59:59</t>
+          <t>01-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T8" t="inlineStr"/>
       <c r="U8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="V8" t="inlineStr"/>
@@ -1515,36 +1527,36 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>26150522787060002251</t>
+          <t>26150522809500002290</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr"/>
       <c r="Z8" t="inlineStr"/>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>1899</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>Juan Eduardo Torres Alcantar</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>347775</t>
+          <t>347762</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>89940</t>
+          <t>89927</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1554,17 +1566,17 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>KAREN PAOLA</t>
+          <t>ROMAN ISAAC</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>DUARTE</t>
+          <t xml:space="preserve">GOMEZ </t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>RODRIGUEZ</t>
+          <t>COTA</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -1574,28 +1586,28 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>6531128069</t>
+          <t>6221718560</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>22-12-1996</t>
+          <t>07-02-1989</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>PAO.DUARTE.ROD@GMAIL.COM</t>
+          <t>ROMANG89@LIVE.COM.MX</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>02-03-2026 17:55:45</t>
+          <t>02-03-2026 17:42:58</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1620,12 +1632,12 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>02-03-2026 17:58:23</t>
+          <t>04-03-2026 17:39:25</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>02-04-2026 23:59:59</t>
+          <t>03-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T9" t="inlineStr"/>
@@ -1642,11 +1654,19 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>26150522809500002290</t>
-        </is>
-      </c>
-      <c r="Y9" t="inlineStr"/>
-      <c r="Z9" t="inlineStr"/>
+          <t>26150522891430002392</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>GISSEL ANAHY REYES GERMAN</t>
+        </is>
+      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>549</t>
@@ -1654,24 +1674,24 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Johan Osvaldo Beltran Quiros</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>348010</t>
+          <t>347479</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>90175</t>
+          <t>89644</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1681,17 +1701,17 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>ISRAEL</t>
+          <t xml:space="preserve">LISA </t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>VALDEZ</t>
+          <t>FLORES</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>ALVARADO</t>
+          <t>YESCAS</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -1701,28 +1721,28 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>6531174824</t>
+          <t>6531711682</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>12-12-1996</t>
+          <t>26-10-1975</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>ISRAELVALDEZ647@GMAIL.COM</t>
+          <t>VYBRASILISA@GMAIL.COM</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>03-03-2026 11:23:55</t>
+          <t>02-03-2026 10:01:44</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1737,22 +1757,22 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>1 MES $899</t>
+          <t>3 MESES $1,899</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>633</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>03-03-2026 11:25:21</t>
+          <t>02-03-2026 10:03:52</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>03-04-2026 23:59:59</t>
+          <t>01-06-2026 23:59:59</t>
         </is>
       </c>
       <c r="T10" t="inlineStr"/>
@@ -1769,36 +1789,36 @@
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>26150522837480002335</t>
+          <t>26150522787060002251</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr"/>
       <c r="Z10" t="inlineStr"/>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>1899</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Juan Eduardo Torres Alcantar</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>347867</t>
+          <t>347998</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>90032</t>
+          <t>90163</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1808,17 +1828,17 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>ADRIANA</t>
+          <t>DAHENA DARLENE</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>ESQUER</t>
+          <t>VEGA</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>TERAN</t>
+          <t>MONTIZO</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -1828,12 +1848,12 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>6865432785</t>
+          <t>6531111880</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>OBREGON Y 20</t>
+          <t>AV CARRANZA 29 Y 30</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1843,17 +1863,17 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>04-12-1969</t>
+          <t>04-06-1992</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>AET89@GMAIL.COM</t>
+          <t>SUPERVICION.FRUTAL@GMAIL.COM</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>02-03-2026 19:24:40</t>
+          <t>03-03-2026 10:11:47</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1878,17 +1898,17 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>04-03-2026 18:23:35</t>
+          <t>03-03-2026 10:21:09</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>04-04-2026 23:59:59</t>
+          <t>02-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>04-03-2026 18:22:20</t>
+          <t>03-03-2026 10:20:10</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
@@ -1908,19 +1928,11 @@
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>26150522894140002400</t>
-        </is>
-      </c>
-      <c r="Y11" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>GISSEL ANAHY REYES GERMAN</t>
-        </is>
-      </c>
+          <t>26150522836290002334</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr"/>
+      <c r="Z11" t="inlineStr"/>
       <c r="AA11" t="inlineStr">
         <is>
           <t>549</t>
@@ -1928,7 +1940,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>Johan Osvaldo Beltran Quiros</t>
+          <t>Juan Eduardo Torres Alcantar</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
@@ -1940,12 +1952,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>347998</t>
+          <t>348010</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>90163</t>
+          <t>90175</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1955,17 +1967,17 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>DAHENA DARLENE</t>
+          <t>ISRAEL</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>VEGA</t>
+          <t>VALDEZ</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>MONTIZO</t>
+          <t>ALVARADO</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -1975,79 +1987,67 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>6531111880</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>AV CARRANZA 29 Y 30</t>
-        </is>
-      </c>
+          <t>6531174824</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>04-06-1992</t>
+          <t>12-12-1996</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>SUPERVICION.FRUTAL@GMAIL.COM</t>
+          <t>ISRAELVALDEZ647@GMAIL.COM</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>03-03-2026 10:11:47</t>
+          <t>03-03-2026 11:23:55</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>Inscripcion $150</t>
+          <t>Tarifas 2026 LE</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+          <t>1 MES $899</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>899</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>03-03-2026 10:21:09</t>
+          <t>03-03-2026 11:25:21</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>03-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>03-03-2026 10:20:10</t>
-        </is>
-      </c>
+          <t>02-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr"/>
       <c r="U12" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V12" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr"/>
       <c r="W12" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -2055,24 +2055,24 @@
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>26150522836290002334</t>
+          <t>26150522837480002335</t>
         </is>
       </c>
       <c r="Y12" t="inlineStr"/>
       <c r="Z12" t="inlineStr"/>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>899</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>Juan Eduardo Torres Alcantar</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
@@ -2169,7 +2169,7 @@
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>03-04-2026 23:59:59</t>
+          <t>02-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T13" t="inlineStr">
@@ -2212,6 +2212,272 @@
       <c r="AC13" t="inlineStr">
         <is>
           <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>348842</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>91007</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>SAN LUIS</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>EZAU</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>RODRIGUEZ</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>SOTELO</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>6531755736</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>CJON QUINTANA ROO 4 Y 5</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>20-11-1995</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>EZAURODRIGUEZ814@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>06-03-2026 07:40:32</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>Inscripcion $150</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>06-03-2026 08:13:26</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>05-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>06-03-2026 07:54:34</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>26150522944300002450</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr"/>
+      <c r="Z14" t="inlineStr"/>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>349000</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>91165</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>SAN LUIS</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>FELIPE ANTONIO</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>DAVILA</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>PELON</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>6535343327</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>14-05-1953</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>SOLMARI22@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>06-03-2026 17:33:34</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>convenio 300</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>CONVENIOS $549</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>06-03-2026 17:35:50</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>05-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr"/>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr"/>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>26150522956910002465</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr"/>
+      <c r="Z15" t="inlineStr"/>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>

--- a/data/rutinas/sucursales/Socios_con_y_sin_rutina__SAN LUIS.xlsx
+++ b/data/rutinas/sucursales/Socios_con_y_sin_rutina__SAN LUIS.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC15"/>
+  <dimension ref="A1:AC36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -578,12 +578,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>335330</t>
+          <t>324734</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>24555</t>
+          <t>21673</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -593,63 +593,67 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>DIEGO</t>
+          <t xml:space="preserve">JESSICA </t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>VAZQUEZ</t>
+          <t>HERNANDEZ</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>CELIS</t>
+          <t>MORA</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>6531649951</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>9282915246</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>CJN JALISCO 2 Y 3</t>
+        </is>
+      </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>12-09-2007</t>
+          <t>22-11-1994</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>DIEGOVAZQUEZ1209@GMAIL.COM</t>
+          <t>AYORAWDY123@GMAIL.COM</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>16-01-2026 14:12:31</t>
+          <t>22-11-2025 08:37:32</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>convenio 300</t>
+          <t>Inscripcion $150</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
@@ -659,21 +663,29 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>04-03-2026 18:45:03</t>
+          <t>10-03-2026 15:11:19</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>03-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T2" t="inlineStr"/>
+          <t>09-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>10-03-2026 15:09:42</t>
+        </is>
+      </c>
       <c r="U2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr"/>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W2" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -681,7 +693,7 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>26150522895500002404</t>
+          <t>26150523054390002580</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -713,12 +725,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>342269</t>
+          <t>335330</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>20087</t>
+          <t>24555</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -728,53 +740,53 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>CHRISTOPHER</t>
+          <t>DIEGO</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t xml:space="preserve">VEGA </t>
+          <t>VAZQUEZ</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>FAJARDO</t>
+          <t>CELIS</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>52</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>9285090770</t>
+          <t>6531649951</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>08-04-2007</t>
+          <t>12-09-2007</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>VEGACHRISTOPHER752@GMAIL.COM</t>
+          <t>DIEGOVAZQUEZ1209@GMAIL.COM</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>09-02-2026 16:39:45</t>
+          <t>16-01-2026 14:12:31</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>Tarifas 2026 LE</t>
+          <t>convenio 300</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -784,28 +796,28 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>1 MES $899</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>02-03-2026 16:36:46</t>
+          <t>04-03-2026 18:45:03</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>01-04-2026 23:59:59</t>
+          <t>03-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T3" t="inlineStr"/>
       <c r="U3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="V3" t="inlineStr"/>
@@ -816,7 +828,7 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>26150522802210002275</t>
+          <t>26150522895500002404</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -826,12 +838,12 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>GISSEL ANAHY REYES GERMAN</t>
+          <t>RAUL FELIX VAZQUEZ</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -848,12 +860,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>346761</t>
+          <t>317637</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>88926</t>
+          <t>15134</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -863,17 +875,17 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">JOSE LUIS </t>
+          <t xml:space="preserve">OSCAR RAUL </t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>RAMIREZ</t>
+          <t>ARIZONA</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>SANCHEZ</t>
+          <t>RIVAS</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -883,32 +895,32 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>6531068319</t>
+          <t>6531608695</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>CJON 5 DE MAYO 3302</t>
+          <t>CJN COLIMA 40 Y 41</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>17-03-1993</t>
+          <t>26-09-1988</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>JR555204@GMAIL.COM</t>
+          <t>OSCAR.RA27@GMAIL.COM</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>26-02-2026 17:00:06</t>
+          <t>07-10-2025 09:09:30</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -933,17 +945,17 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>02-03-2026 18:43:58</t>
+          <t>12-03-2026 14:25:09</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>01-04-2026 23:59:59</t>
+          <t>11-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>02-03-2026 18:43:08</t>
+          <t>12-03-2026 14:24:06</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -963,7 +975,7 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>26150522813580002301</t>
+          <t>26150523123370002679</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
@@ -973,7 +985,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>GISSEL ANAHY REYES GERMAN</t>
+          <t>PERLA YANIRA MANZO VILLA</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -995,12 +1007,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>347389</t>
+          <t>342269</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>89554</t>
+          <t>20087</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1010,99 +1022,87 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>MARTIN</t>
+          <t>CHRISTOPHER</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>LIRA</t>
+          <t xml:space="preserve">VEGA </t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>SORIA</t>
+          <t>FAJARDO</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>6531197369</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>CJON LAZARO CARDENAS 41 Y42</t>
-        </is>
-      </c>
+          <t>9285090770</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>25-05-1974</t>
+          <t>08-04-2007</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>AUTOELECTRICOGDL1977@GMAIL.COM</t>
+          <t>VEGACHRISTOPHER752@GMAIL.COM</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>02-03-2026 05:39:01</t>
+          <t>09-02-2026 16:39:45</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>Inscripcion $150</t>
+          <t>Tarifas 2026 LE</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+          <t>1 MES $899</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>899</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>05-03-2026 05:22:25</t>
+          <t>02-03-2026 16:36:46</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>04-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>05-03-2026 05:21:13</t>
-        </is>
-      </c>
+          <t>01-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr"/>
       <c r="U5" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V5" t="inlineStr">
-        <is>
           <t>1</t>
         </is>
       </c>
+      <c r="V5" t="inlineStr"/>
       <c r="W5" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -1110,7 +1110,7 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>26150522901950002416</t>
+          <t>26150522802210002275</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
@@ -1120,34 +1120,34 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>RAUL FELIX VAZQUEZ</t>
+          <t>GISSEL ANAHY REYES GERMAN</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>899</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Johan Osvaldo Beltran Quiros</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>346790</t>
+          <t>346761</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>88955</t>
+          <t>88926</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1157,87 +1157,99 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>ABRAHAM</t>
+          <t xml:space="preserve">JOSE LUIS </t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>QUINTERO</t>
+          <t>RAMIREZ</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>QUINTERO</t>
+          <t>SANCHEZ</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>6531068319</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>CJON 5 DE MAYO 3302</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>17-03-1993</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>JR555204@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>26-02-2026 17:00:06</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>Inscripcion $150</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>02-03-2026 18:43:58</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>01-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>02-03-2026 18:43:08</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>8315665944</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>Masculino</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>17-05-1993</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>ABRAHAMQUINT66@GMAIL.COM</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>26-02-2026 17:53:31</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>Tarifas 2026 LE</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>Sin contrato</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>1 MES $899</t>
-        </is>
-      </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>899</t>
-        </is>
-      </c>
-      <c r="R6" t="inlineStr">
-        <is>
-          <t>04-03-2026 18:31:38</t>
-        </is>
-      </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>03-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T6" t="inlineStr"/>
-      <c r="U6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V6" t="inlineStr"/>
       <c r="W6" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -1245,7 +1257,7 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>26150522894600002401</t>
+          <t>26150522813580002301</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
@@ -1260,7 +1272,7 @@
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -1277,12 +1289,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>347867</t>
+          <t>347389</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>90032</t>
+          <t>89554</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1292,17 +1304,17 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>ADRIANA</t>
+          <t>MARTIN</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>ESQUER</t>
+          <t>LIRA</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>TERAN</t>
+          <t>SORIA</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -1312,32 +1324,32 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>6865432785</t>
+          <t>6531197369</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>OBREGON Y 20</t>
+          <t>CJON LAZARO CARDENAS 41 Y42</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>04-12-1969</t>
+          <t>25-05-1974</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>AET89@GMAIL.COM</t>
+          <t>AUTOELECTRICOGDL1977@GMAIL.COM</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>02-03-2026 19:24:40</t>
+          <t>02-03-2026 05:39:01</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -1362,17 +1374,17 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>04-03-2026 18:23:35</t>
+          <t>05-03-2026 05:22:25</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>03-04-2026 23:59:59</t>
+          <t>04-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>04-03-2026 18:22:20</t>
+          <t>05-03-2026 05:21:13</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
@@ -1382,7 +1394,7 @@
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -1392,7 +1404,7 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>26150522894140002400</t>
+          <t>26150522901950002416</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
@@ -1402,7 +1414,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>GISSEL ANAHY REYES GERMAN</t>
+          <t>RAUL FELIX VAZQUEZ</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1412,24 +1424,24 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>Johan Osvaldo Beltran Quiros</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>347775</t>
+          <t>346790</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>89940</t>
+          <t>88955</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1439,53 +1451,53 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>KAREN PAOLA</t>
+          <t>ABRAHAM</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>DUARTE</t>
+          <t>QUINTERO</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>RODRIGUEZ</t>
+          <t>QUINTERO</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>6531128069</t>
+          <t>8315665944</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>22-12-1996</t>
+          <t>17-05-1993</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>PAO.DUARTE.ROD@GMAIL.COM</t>
+          <t>ABRAHAMQUINT66@GMAIL.COM</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>02-03-2026 17:55:45</t>
+          <t>26-02-2026 17:53:31</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>convenio 300</t>
+          <t>Tarifas 2026 LE</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -1495,22 +1507,22 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>1 MES $899</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>899</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>02-03-2026 17:58:23</t>
+          <t>04-03-2026 18:31:38</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>01-04-2026 23:59:59</t>
+          <t>03-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T8" t="inlineStr"/>
@@ -1527,36 +1539,44 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>26150522809500002290</t>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr"/>
-      <c r="Z8" t="inlineStr"/>
+          <t>26150522894600002401</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>GISSEL ANAHY REYES GERMAN</t>
+        </is>
+      </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>899</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Johan Osvaldo Beltran Quiros</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>347762</t>
+          <t>347479</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>89927</t>
+          <t>89644</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1566,17 +1586,17 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>ROMAN ISAAC</t>
+          <t xml:space="preserve">LISA </t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t xml:space="preserve">GOMEZ </t>
+          <t>FLORES</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>COTA</t>
+          <t>YESCAS</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -1586,33 +1606,33 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>6221718560</t>
+          <t>6531711682</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>07-02-1989</t>
+          <t>26-10-1975</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>ROMANG89@LIVE.COM.MX</t>
+          <t>VYBRASILISA@GMAIL.COM</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>02-03-2026 17:42:58</t>
+          <t>02-03-2026 10:01:44</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>convenio 300</t>
+          <t>Tarifas 2026 LE</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -1622,28 +1642,28 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>3 MESES $1,899</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>633</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>04-03-2026 17:39:25</t>
+          <t>02-03-2026 10:03:52</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>03-04-2026 23:59:59</t>
+          <t>01-06-2026 23:59:59</t>
         </is>
       </c>
       <c r="T9" t="inlineStr"/>
       <c r="U9" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="V9" t="inlineStr"/>
@@ -1654,27 +1674,19 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>26150522891430002392</t>
-        </is>
-      </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>GISSEL ANAHY REYES GERMAN</t>
-        </is>
-      </c>
+          <t>26150522787060002251</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr"/>
+      <c r="Z9" t="inlineStr"/>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>1899</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>Johan Osvaldo Beltran Quiros</t>
+          <t>Juan Eduardo Torres Alcantar</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
@@ -1686,12 +1698,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>347479</t>
+          <t>347762</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>89644</t>
+          <t>89927</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1701,17 +1713,17 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t xml:space="preserve">LISA </t>
+          <t>ROMAN ISAAC</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>FLORES</t>
+          <t xml:space="preserve">GOMEZ </t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>YESCAS</t>
+          <t>COTA</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -1721,33 +1733,33 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>6531711682</t>
+          <t>6221718560</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>26-10-1975</t>
+          <t>07-02-1989</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>VYBRASILISA@GMAIL.COM</t>
+          <t>ROMANG89@LIVE.COM.MX</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>02-03-2026 10:01:44</t>
+          <t>02-03-2026 17:42:58</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>Tarifas 2026 LE</t>
+          <t>convenio 300</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -1757,28 +1769,28 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>3 MESES $1,899</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>633</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>02-03-2026 10:03:52</t>
+          <t>04-03-2026 17:39:25</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>01-06-2026 23:59:59</t>
+          <t>03-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T10" t="inlineStr"/>
       <c r="U10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="V10" t="inlineStr"/>
@@ -1789,19 +1801,27 @@
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>26150522787060002251</t>
-        </is>
-      </c>
-      <c r="Y10" t="inlineStr"/>
-      <c r="Z10" t="inlineStr"/>
+          <t>26150522891430002392</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>GISSEL ANAHY REYES GERMAN</t>
+        </is>
+      </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>1899</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>Juan Eduardo Torres Alcantar</t>
+          <t>Johan Osvaldo Beltran Quiros</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
@@ -1813,12 +1833,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>347998</t>
+          <t>347775</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>90163</t>
+          <t>89940</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1828,17 +1848,17 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>DAHENA DARLENE</t>
+          <t>KAREM PAOLA</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>VEGA</t>
+          <t>DUARTE</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>MONTIZO</t>
+          <t>RODRIGUEZ</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -1848,14 +1868,10 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>6531111880</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>AV CARRANZA 29 Y 30</t>
-        </is>
-      </c>
+          <t>6531128069</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -1863,32 +1879,32 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>04-06-1992</t>
+          <t>22-12-1996</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>SUPERVICION.FRUTAL@GMAIL.COM</t>
+          <t>PAO.DUARTE.ROD@GMAIL.COM</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>03-03-2026 10:11:47</t>
+          <t>02-03-2026 17:55:45</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>Inscripcion $150</t>
+          <t>convenio 300</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
@@ -1898,29 +1914,21 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>03-03-2026 10:21:09</t>
+          <t>02-03-2026 17:58:23</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>02-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T11" t="inlineStr">
-        <is>
-          <t>03-03-2026 10:20:10</t>
-        </is>
-      </c>
+          <t>01-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr"/>
       <c r="U11" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V11" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="V11" t="inlineStr"/>
       <c r="W11" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -1928,7 +1936,7 @@
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>26150522836290002334</t>
+          <t>26150522809500002290</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr"/>
@@ -1940,12 +1948,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>Juan Eduardo Torres Alcantar</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
@@ -2079,12 +2087,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>348143</t>
+          <t>347867</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>90308</t>
+          <t>90032</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -2094,17 +2102,17 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>JAQUELINE</t>
+          <t>ADRIANA</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>OZUNA</t>
+          <t>ESQUER</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>CASTRO</t>
+          <t>TERAN</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -2114,12 +2122,12 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>6531299473</t>
+          <t>6865432785</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>CJON MORELOS Y JUAREZ</t>
+          <t>OBREGON Y 20</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -2129,17 +2137,17 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>05-04-1999</t>
+          <t>04-12-1969</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>OZUNA052024@OUTLOOK.COM</t>
+          <t>AET89@GMAIL.COM</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>03-03-2026 17:02:29</t>
+          <t>02-03-2026 19:24:40</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
@@ -2164,17 +2172,17 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>03-03-2026 17:05:49</t>
+          <t>04-03-2026 18:23:35</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>02-04-2026 23:59:59</t>
+          <t>03-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>03-03-2026 17:05:17</t>
+          <t>04-03-2026 18:22:20</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
@@ -2184,7 +2192,7 @@
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W13" t="inlineStr">
@@ -2194,11 +2202,19 @@
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>26150522849130002352</t>
-        </is>
-      </c>
-      <c r="Y13" t="inlineStr"/>
-      <c r="Z13" t="inlineStr"/>
+          <t>26150522894140002400</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>GISSEL ANAHY REYES GERMAN</t>
+        </is>
+      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>549</t>
@@ -2206,7 +2222,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>Juan Pablo Romero Andrade</t>
+          <t>Johan Osvaldo Beltran Quiros</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
@@ -2218,12 +2234,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>348842</t>
+          <t>348143</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>91007</t>
+          <t>90308</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -2233,17 +2249,17 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>EZAU</t>
+          <t>JAQUELINE</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>RODRIGUEZ</t>
+          <t>OZUNA</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>SOTELO</t>
+          <t>CASTRO</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -2253,32 +2269,32 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>6531755736</t>
+          <t>6531299473</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>CJON QUINTANA ROO 4 Y 5</t>
+          <t>CJON MORELOS Y JUAREZ</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>20-11-1995</t>
+          <t>05-04-1999</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>EZAURODRIGUEZ814@GMAIL.COM</t>
+          <t>OZUNA052024@OUTLOOK.COM</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>06-03-2026 07:40:32</t>
+          <t>03-03-2026 17:02:29</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
@@ -2303,17 +2319,17 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>06-03-2026 08:13:26</t>
+          <t>03-03-2026 17:05:49</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>05-04-2026 23:59:59</t>
+          <t>02-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>06-03-2026 07:54:34</t>
+          <t>03-03-2026 17:05:17</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
@@ -2333,7 +2349,7 @@
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>26150522944300002450</t>
+          <t>26150522849130002352</t>
         </is>
       </c>
       <c r="Y14" t="inlineStr"/>
@@ -2345,24 +2361,24 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Juan Pablo Romero Andrade</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>349000</t>
+          <t>347998</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>91165</t>
+          <t>90163</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -2372,17 +2388,17 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>FELIPE ANTONIO</t>
+          <t>DAHENA DARLENE</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>DAVILA</t>
+          <t>VEGA</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>PELON</t>
+          <t>MONTIZO</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -2392,43 +2408,47 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>6535343327</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>6531111880</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>AV CARRANZA 29 Y 30</t>
+        </is>
+      </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>14-05-1953</t>
+          <t>04-06-1992</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>SOLMARI22@GMAIL.COM</t>
+          <t>SUPERVICION.FRUTAL@GMAIL.COM</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>06-03-2026 17:33:34</t>
+          <t>03-03-2026 10:11:47</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>convenio 300</t>
+          <t>Inscripcion $150</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
@@ -2438,21 +2458,29 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>06-03-2026 17:35:50</t>
+          <t>03-03-2026 10:21:09</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>05-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T15" t="inlineStr"/>
+          <t>02-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>03-03-2026 10:20:10</t>
+        </is>
+      </c>
       <c r="U15" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V15" t="inlineStr"/>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="W15" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -2460,7 +2488,7 @@
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>26150522956910002465</t>
+          <t>26150522836290002334</t>
         </is>
       </c>
       <c r="Y15" t="inlineStr"/>
@@ -2472,12 +2500,2855 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
+          <t>Juan Eduardo Torres Alcantar</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>348842</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>91007</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>SAN LUIS</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>EZAU</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>RODRIGUEZ</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>SOTELO</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>6531755736</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>CJON QUINTANA ROO 4 Y 5</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>20-11-1995</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>EZAURODRIGUEZ814@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>06-03-2026 07:40:32</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>Inscripcion $150</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>06-03-2026 08:13:26</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>05-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>06-03-2026 07:54:34</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>26150522944300002450</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr"/>
+      <c r="Z16" t="inlineStr"/>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
           <t>N/D</t>
         </is>
       </c>
-      <c r="AC15" t="inlineStr">
+      <c r="AC16" t="inlineStr">
         <is>
           <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>349604</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>91769</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>SAN LUIS</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>SARA</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>RIOS</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>BRITO</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>6531191528</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AV DALIAS </t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>15-06-1979</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>SARA_RBRITO@HOTMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>09-03-2026 18:22:06</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>Inscripcion $150</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>09-03-2026 18:31:03</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>08-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>09-03-2026 18:29:58</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>26150523022720002539</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr"/>
+      <c r="Z17" t="inlineStr"/>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>Juan Pablo Romero Andrade</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>349000</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>91165</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>SAN LUIS</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>FELIPE ANTONIO</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>DAVILA</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>TELON</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>6535343327</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>14-05-1953</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>SOLMARI22@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>06-03-2026 17:33:34</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>convenio 300</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>CONVENIOS $549</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>06-03-2026 17:35:50</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>05-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr"/>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr"/>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>26150522956910002465</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr"/>
+      <c r="Z18" t="inlineStr"/>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>349303</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>91468</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>SAN LUIS</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>JESUS</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>HERNANDEZ</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>ARAGON</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>6538495218</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>AV CARRANZA #2606</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>09-07-1982</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>JESUSHERNANDEZARAGON@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>09-03-2026 07:27:59</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>Inscripcion $150</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>09-03-2026 07:32:21</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>08-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>09-03-2026 07:30:39</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>26150522999200002499</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr"/>
+      <c r="Z19" t="inlineStr"/>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>Juan Eduardo Torres Alcantar</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>349324</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>91489</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>SAN LUIS</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>MARIA ELVIRA</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>MEDEL</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>ARANDA</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>6531076310</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>26-10-1962</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>MARIAMEDEL173@YAHOO.COM</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>09-03-2026 08:44:01</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>convenio 300</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>CONVENIOS $549</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>18-03-2026 08:03:04</t>
+        </is>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>17-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr"/>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr"/>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>26150523285070002882</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>RAUL FELIX VAZQUEZ</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>349515</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>91680</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>SAN LUIS</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LUIS JORGE </t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>MONTOYA</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>RAMIREZ</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>6538490929</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>03-03-1992</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>LURGEMDRK@HOTMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>09-03-2026 16:43:33</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>3 MESES $1,899</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>633</t>
+        </is>
+      </c>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>09-03-2026 16:45:01</t>
+        </is>
+      </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>08-06-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T21" t="inlineStr"/>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr"/>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>26150523015010002526</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr"/>
+      <c r="Z21" t="inlineStr"/>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>1899</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>349648</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>91813</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>SAN LUIS</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EVANGELINA </t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>LOPEZ</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>MACHUCA</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>6531166484</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AV CHIAPAS Y 9 </t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>23-08-1995</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>LOPEZEVANGELINA34@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>09-03-2026 19:07:10</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>No Forzoso</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>RECURRENTE $649 LE</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>649</t>
+        </is>
+      </c>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>09-03-2026 19:28:58</t>
+        </is>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>08-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>09-03-2026 19:17:27</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>26150523027720002546</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr"/>
+      <c r="Z22" t="inlineStr"/>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>649</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>Johan Osvaldo Beltran Quiros</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>349316</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>91481</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>SAN LUIS</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>MISSAEL</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>ORTIZ</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>SANCHEZ</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>6532077103</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>DURANGO Y 25</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>25-10-2001</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>OMISSAEL125@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>09-03-2026 08:20:50</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>No Forzoso</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>RECURRENTE $649 LE</t>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>649</t>
+        </is>
+      </c>
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>09-03-2026 08:29:30</t>
+        </is>
+      </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>08-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>09-03-2026 08:29:03</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>26150523000590002503</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr"/>
+      <c r="Z23" t="inlineStr"/>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>649</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>349632</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>91797</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>SAN LUIS</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>ANA</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>CASTRO</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>ESPARZA</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>9283663034</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>17-11-1995</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>CASTROANA.7771@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>09-03-2026 18:52:23</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>3 MESES $1,899</t>
+        </is>
+      </c>
+      <c r="Q24" t="inlineStr">
+        <is>
+          <t>633</t>
+        </is>
+      </c>
+      <c r="R24" t="inlineStr">
+        <is>
+          <t>09-03-2026 18:53:40</t>
+        </is>
+      </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>08-06-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T24" t="inlineStr"/>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr"/>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>26150523024670002542</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr"/>
+      <c r="Z24" t="inlineStr"/>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>1899</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>349611</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>91776</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>SAN LUIS</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>IRVIN YASIR</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>UTRERA</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>RIOS</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>6535383177</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>AV DALIAS 11</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>27-10-2005</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>IRVINYASIRUTRERA@GAMIAL.COM</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>09-03-2026 18:29:17</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>Inscripcion $150</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+        </is>
+      </c>
+      <c r="Q25" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R25" t="inlineStr">
+        <is>
+          <t>09-03-2026 18:34:14</t>
+        </is>
+      </c>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>08-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>09-03-2026 18:33:21</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>26150523022910002540</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr"/>
+      <c r="Z25" t="inlineStr"/>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>Juan Pablo Romero Andrade</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>349721</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>91886</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>SAN LUIS</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>ABRAHAM</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>CORTEZ</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>SALAZAR</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>6535382221</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>03-11-1989</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>NEGRO_CORTEZ01@HOTMAILO.COM</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>09-03-2026 20:41:54</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>convenio 300</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>CONVENIOS $549</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>09-03-2026 20:44:08</t>
+        </is>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>08-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr"/>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr"/>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>26150523032300002557</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr"/>
+      <c r="Z26" t="inlineStr"/>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>350057</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>92222</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>SAN LUIS</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>GUADALUPE</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>GRAGEDA</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>CARBAJAL</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>6531072462</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>19-04-1960</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>GGRAGEDA31@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>11-03-2026 09:15:32</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>convenio 300</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>CONVENIOS $549</t>
+        </is>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R27" t="inlineStr">
+        <is>
+          <t>18-03-2026 09:21:56</t>
+        </is>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>17-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T27" t="inlineStr"/>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr"/>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>26150523287060002884</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>RAUL FELIX VAZQUEZ</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>350343</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>92507</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>SAN LUIS</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>LORENA</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>HIGUERA</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>RODRIGUEZ</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>6531338028</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>CJN CRISANTEMAS B 20 Y21</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>12-09-1983</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>LORENA4250HIGUERA@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>12-03-2026 14:27:32</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>Inscripcion $150</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>12-03-2026 14:30:20</t>
+        </is>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>11-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>12-03-2026 14:29:48</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>26150523123480002680</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr"/>
+      <c r="Z28" t="inlineStr"/>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>Juan Pablo Romero Andrade</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>349906</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>92071</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>SAN LUIS</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>ANGELICA LIZETH</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>FLORES</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>ROJAS</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>6531765576</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>11-01-2010</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>FORESROJASANGELICALIZETH@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>10-03-2026 17:31:43</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>convenio 300</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>CONVENIOS $549</t>
+        </is>
+      </c>
+      <c r="Q29" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R29" t="inlineStr">
+        <is>
+          <t>10-03-2026 17:32:55</t>
+        </is>
+      </c>
+      <c r="S29" t="inlineStr">
+        <is>
+          <t>09-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T29" t="inlineStr"/>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr"/>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>26150523060120002589</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr"/>
+      <c r="Z29" t="inlineStr"/>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>350257</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>92421</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>SAN LUIS</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>ABRAHAM ANTONIO</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>JUAREZ</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>BELTRAN</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>6531166314</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>19-01-2012</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>ANONTIONIOJUAREZ@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>12-03-2026 07:04:36</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>convenio 300</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>CONVENIOS $549</t>
+        </is>
+      </c>
+      <c r="Q30" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R30" t="inlineStr">
+        <is>
+          <t>16-03-2026 07:23:47</t>
+        </is>
+      </c>
+      <c r="S30" t="inlineStr">
+        <is>
+          <t>15-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T30" t="inlineStr"/>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr"/>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>26150523202920002745</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>RAUL FELIX VAZQUEZ</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>350034</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>92199</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>SAN LUIS</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>JESUS HUMBERTO</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>SALAZAR</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>SALAZAR</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>9283231886</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>NAYARIT Y 21</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>27-11-1989</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>JESUSHUMBERTO27@HOTMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>11-03-2026 06:55:38</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>Inscripcion $150</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+        </is>
+      </c>
+      <c r="Q31" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R31" t="inlineStr">
+        <is>
+          <t>13-03-2026 10:25:55</t>
+        </is>
+      </c>
+      <c r="S31" t="inlineStr">
+        <is>
+          <t>12-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>13-03-2026 10:25:16</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>26150523149820002700</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>RAUL FELIX VAZQUEZ</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>351650</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>93814</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>SAN LUIS</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>YALUI</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>GARCIA</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>RODRIGUEZ</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>6531651010</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>02-07-2012</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>YALUIGARCIA2@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>17-03-2026 18:33:38</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>convenio 300</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>CONVENIOS $549</t>
+        </is>
+      </c>
+      <c r="Q32" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R32" t="inlineStr">
+        <is>
+          <t>19-03-2026 18:36:05</t>
+        </is>
+      </c>
+      <c r="S32" t="inlineStr">
+        <is>
+          <t>18-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T32" t="inlineStr"/>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr"/>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>26150523338650002960</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>GISSEL ANAHY REYES GERMAN</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>351652</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>93816</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>SAN LUIS</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>NIGEL</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PATIÑO </t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>LEON</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>6531140204</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>08-02-2011</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>KAAREENLEON91@GMAI.COM</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>17-03-2026 18:39:20</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>convenio 300</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>CONVENIOS $549</t>
+        </is>
+      </c>
+      <c r="Q33" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R33" t="inlineStr">
+        <is>
+          <t>19-03-2026 18:34:10</t>
+        </is>
+      </c>
+      <c r="S33" t="inlineStr">
+        <is>
+          <t>18-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T33" t="inlineStr"/>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr"/>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>26150523338530002959</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>GISSEL ANAHY REYES GERMAN</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>351383</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>93547</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>SAN LUIS</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>BRAYAN URIEL</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>NUÑEZ</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>ROMERO</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>6531076077</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>TORREON 4 Y 5</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>17-01-2011</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>BRAYYAN1701@ICLOUD.COM</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>16-03-2026 21:16:06</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>Inscripcion $150</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+        </is>
+      </c>
+      <c r="Q34" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R34" t="inlineStr">
+        <is>
+          <t>18-03-2026 20:14:03</t>
+        </is>
+      </c>
+      <c r="S34" t="inlineStr">
+        <is>
+          <t>17-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>18-03-2026 20:13:39</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X34" t="inlineStr">
+        <is>
+          <t>26150523309000002923</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>GISSEL ANAHY REYES GERMAN</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>351441</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>93605</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>SAN LUIS</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>JUAN RAMON</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>ALCALA</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>GONZALEZ</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>6531103138</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>LE DE ALFABETIZACION Y CALLE 35 Y 36</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>13-09-2000</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>JUANRAMONALCALAGONZALEZ4@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>17-03-2026 09:39:59</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>No Forzoso</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>RECURRENTE $649 LE</t>
+        </is>
+      </c>
+      <c r="Q35" t="inlineStr">
+        <is>
+          <t>649</t>
+        </is>
+      </c>
+      <c r="R35" t="inlineStr">
+        <is>
+          <t>17-03-2026 09:45:16</t>
+        </is>
+      </c>
+      <c r="S35" t="inlineStr">
+        <is>
+          <t>16-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>17-03-2026 09:44:34</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X35" t="inlineStr">
+        <is>
+          <t>26150523248650002812</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr"/>
+      <c r="Z35" t="inlineStr"/>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>649</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>Martin Ramiro Quiñonez Jauregui</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>351973</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>94137</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>SAN LUIS</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>LALEYN FERNANDA</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>MORALES</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>LOPEZ</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>6531095698</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>18-10-2006</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>LALEYN.MORALES.LOPEZ@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>18-03-2026 19:25:43</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>1 MES $899</t>
+        </is>
+      </c>
+      <c r="Q36" t="inlineStr">
+        <is>
+          <t>899</t>
+        </is>
+      </c>
+      <c r="R36" t="inlineStr">
+        <is>
+          <t>18-03-2026 19:27:39</t>
+        </is>
+      </c>
+      <c r="S36" t="inlineStr">
+        <is>
+          <t>17-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T36" t="inlineStr"/>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr"/>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X36" t="inlineStr">
+        <is>
+          <t>26150523306660002916</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr"/>
+      <c r="Z36" t="inlineStr"/>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>899</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>Johan Osvaldo Beltran Quiros</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>con rutina</t>
         </is>
       </c>
     </row>

--- a/data/rutinas/sucursales/Socios_con_y_sin_rutina__SAN LUIS.xlsx
+++ b/data/rutinas/sucursales/Socios_con_y_sin_rutina__SAN LUIS.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC36"/>
+  <dimension ref="A1:AC53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -578,12 +578,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>324734</t>
+          <t>242735</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>21673</t>
+          <t>40240</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -593,99 +593,87 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">JESSICA </t>
+          <t>GUILLERMO</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>HERNANDEZ</t>
+          <t xml:space="preserve">GARCIA </t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>MORA</t>
+          <t>FELIX</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>52</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>9282915246</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>CJN JALISCO 2 Y 3</t>
-        </is>
-      </c>
+          <t>9286557144</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>22-11-1994</t>
+          <t>13-10-1998</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>AYORAWDY123@GMAIL.COM</t>
+          <t>GGARCIA10012267@GMAIL.COM</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>22-11-2025 08:37:32</t>
+          <t>29-06-2024 12:42:31</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>Inscripcion $150</t>
+          <t>Tarifas 2026 LE</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+          <t>1 MES $899</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>899</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>10-03-2026 15:11:19</t>
+          <t>20-03-2026 08:27:03</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>09-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T2" t="inlineStr">
-        <is>
-          <t>10-03-2026 15:09:42</t>
-        </is>
-      </c>
+          <t>19-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr"/>
       <c r="U2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="V2" t="inlineStr"/>
       <c r="W2" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -693,22 +681,14 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>26150523054390002580</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>RAUL FELIX VAZQUEZ</t>
-        </is>
-      </c>
+          <t>26030523359410003689</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr"/>
+      <c r="Z2" t="inlineStr"/>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>899</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -725,12 +705,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>335330</t>
+          <t>317637</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>24555</t>
+          <t>15134</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -740,17 +720,17 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>DIEGO</t>
+          <t xml:space="preserve">OSCAR RAUL </t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>VAZQUEZ</t>
+          <t>ARIZONA</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>CELIS</t>
+          <t>RIVAS</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -760,43 +740,47 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>6531649951</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>6531608695</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>CJN COLIMA 40 Y 41</t>
+        </is>
+      </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>12-09-2007</t>
+          <t>26-09-1988</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>DIEGOVAZQUEZ1209@GMAIL.COM</t>
+          <t>OSCAR.RA27@GMAIL.COM</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>16-01-2026 14:12:31</t>
+          <t>07-10-2025 09:09:30</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>convenio 300</t>
+          <t>Inscripcion $150</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
@@ -806,21 +790,29 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>04-03-2026 18:45:03</t>
+          <t>12-03-2026 14:25:09</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>03-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T3" t="inlineStr"/>
+          <t>11-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>12-03-2026 14:24:06</t>
+        </is>
+      </c>
       <c r="U3" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr"/>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W3" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -828,7 +820,7 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>26150522895500002404</t>
+          <t>26150523123370002679</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -838,7 +830,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>RAUL FELIX VAZQUEZ</t>
+          <t>PERLA YANIRA MANZO VILLA</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -860,12 +852,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>317637</t>
+          <t>346761</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>15134</t>
+          <t>88926</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -875,17 +867,17 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">OSCAR RAUL </t>
+          <t xml:space="preserve">JOSE LUIS </t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>ARIZONA</t>
+          <t>RAMIREZ</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>RIVAS</t>
+          <t>SANCHEZ</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -895,32 +887,32 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>6531608695</t>
+          <t>6531068319</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>CJN COLIMA 40 Y 41</t>
+          <t>CJON 5 DE MAYO 3302</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>26-09-1988</t>
+          <t>17-03-1993</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>OSCAR.RA27@GMAIL.COM</t>
+          <t>JR555204@GMAIL.COM</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>07-10-2025 09:09:30</t>
+          <t>26-02-2026 17:00:06</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -945,17 +937,17 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>12-03-2026 14:25:09</t>
+          <t>02-03-2026 18:43:58</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>11-04-2026 23:59:59</t>
+          <t>01-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>12-03-2026 14:24:06</t>
+          <t>02-03-2026 18:43:08</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -975,7 +967,7 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>26150523123370002679</t>
+          <t>26150522813580002301</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
@@ -985,7 +977,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>PERLA YANIRA MANZO VILLA</t>
+          <t>GISSEL ANAHY REYES GERMAN</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1142,12 +1134,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>346761</t>
+          <t>345643</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>88926</t>
+          <t>87808</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1157,32 +1149,32 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">JOSE LUIS </t>
+          <t>ESTEBAN</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>RAMIREZ</t>
+          <t xml:space="preserve">PANELA </t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>SANCHEZ</t>
+          <t>MARTINEZ</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>6531068319</t>
+          <t>7602355132</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>CJON 5 DE MAYO 3302</t>
+          <t>COAHUILA A Y 45</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1192,52 +1184,52 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>17-03-1993</t>
+          <t>17-02-1997</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>JR555204@GMAIL.COM</t>
+          <t>STEVENPANELA00@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>26-02-2026 17:00:06</t>
+          <t>23-02-2026 05:17:26</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>Inscripcion $150</t>
+          <t>Tarifas 2026 LE</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>No Forzoso</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+          <t>RECURRENTE $649 LE</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>649</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>02-03-2026 18:43:58</t>
+          <t>25-03-2026 09:20:05</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>01-04-2026 23:59:59</t>
+          <t>25-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>02-03-2026 18:43:08</t>
+          <t>25-03-2026 09:19:23</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -1257,7 +1249,7 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>26150522813580002301</t>
+          <t>26150523496880003157</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
@@ -1267,12 +1259,12 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>GISSEL ANAHY REYES GERMAN</t>
+          <t>RAUL FELIX VAZQUEZ</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>649</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -1289,12 +1281,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>347389</t>
+          <t>324734</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>89554</t>
+          <t>21673</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1304,52 +1296,52 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>MARTIN</t>
+          <t xml:space="preserve">JESSICA </t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>LIRA</t>
+          <t>HERNANDEZ</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>SORIA</t>
+          <t>MORA</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>6531197369</t>
+          <t>9282915246</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>CJON LAZARO CARDENAS 41 Y42</t>
+          <t>CJN JALISCO 2 Y 3</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>25-05-1974</t>
+          <t>22-11-1994</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>AUTOELECTRICOGDL1977@GMAIL.COM</t>
+          <t>AYORAWDY123@GMAIL.COM</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>02-03-2026 05:39:01</t>
+          <t>22-11-2025 08:37:32</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -1374,17 +1366,17 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>05-03-2026 05:22:25</t>
+          <t>10-03-2026 15:11:19</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>04-04-2026 23:59:59</t>
+          <t>09-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>05-03-2026 05:21:13</t>
+          <t>10-03-2026 15:09:42</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
@@ -1404,7 +1396,7 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>26150522901950002416</t>
+          <t>26150523054390002580</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
@@ -1436,12 +1428,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>346790</t>
+          <t>335330</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>88955</t>
+          <t>24555</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1451,27 +1443,27 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>ABRAHAM</t>
+          <t>DIEGO</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>QUINTERO</t>
+          <t>VAZQUEZ</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>QUINTERO</t>
+          <t>CELIS</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>52</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>8315665944</t>
+          <t>6531649951</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1482,22 +1474,22 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>17-05-1993</t>
+          <t>12-09-2007</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>ABRAHAMQUINT66@GMAIL.COM</t>
+          <t>DIEGOVAZQUEZ1209@GMAIL.COM</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>26-02-2026 17:53:31</t>
+          <t>16-01-2026 14:12:31</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>Tarifas 2026 LE</t>
+          <t>convenio 300</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -1507,17 +1499,17 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>1 MES $899</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>04-03-2026 18:31:38</t>
+          <t>04-03-2026 18:45:03</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
@@ -1539,7 +1531,7 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>26150522894600002401</t>
+          <t>26150522895500002404</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
@@ -1549,34 +1541,34 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>GISSEL ANAHY REYES GERMAN</t>
+          <t>RAUL FELIX VAZQUEZ</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>Johan Osvaldo Beltran Quiros</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>347479</t>
+          <t>346790</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>89644</t>
+          <t>88955</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1586,48 +1578,48 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t xml:space="preserve">LISA </t>
+          <t>ABRAHAM</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>FLORES</t>
+          <t>QUINTERO</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>YESCAS</t>
+          <t>QUINTERO</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>6531711682</t>
+          <t>8315665944</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>26-10-1975</t>
+          <t>17-05-1993</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>VYBRASILISA@GMAIL.COM</t>
+          <t>ABRAHAMQUINT66@GMAIL.COM</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>02-03-2026 10:01:44</t>
+          <t>26-02-2026 17:53:31</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1642,28 +1634,28 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>3 MESES $1,899</t>
+          <t>1 MES $899</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>633</t>
+          <t>899</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>02-03-2026 10:03:52</t>
+          <t>04-03-2026 18:31:38</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>01-06-2026 23:59:59</t>
+          <t>03-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T9" t="inlineStr"/>
       <c r="U9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="V9" t="inlineStr"/>
@@ -1674,19 +1666,27 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>26150522787060002251</t>
-        </is>
-      </c>
-      <c r="Y9" t="inlineStr"/>
-      <c r="Z9" t="inlineStr"/>
+          <t>26150522894600002401</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>GISSEL ANAHY REYES GERMAN</t>
+        </is>
+      </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>1899</t>
+          <t>899</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>Juan Eduardo Torres Alcantar</t>
+          <t>Johan Osvaldo Beltran Quiros</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
@@ -1698,12 +1698,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>347762</t>
+          <t>347479</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>89927</t>
+          <t>89644</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1713,17 +1713,17 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>ROMAN ISAAC</t>
+          <t xml:space="preserve">LISA </t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t xml:space="preserve">GOMEZ </t>
+          <t>FLORES</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>COTA</t>
+          <t>YESCAS</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -1733,33 +1733,33 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>6221718560</t>
+          <t>6531711682</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>07-02-1989</t>
+          <t>26-10-1975</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>ROMANG89@LIVE.COM.MX</t>
+          <t>VYBRASILISA@GMAIL.COM</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>02-03-2026 17:42:58</t>
+          <t>02-03-2026 10:01:44</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>convenio 300</t>
+          <t>Tarifas 2026 LE</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -1769,28 +1769,28 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>3 MESES $1,899</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>633</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>04-03-2026 17:39:25</t>
+          <t>02-03-2026 10:03:52</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>03-04-2026 23:59:59</t>
+          <t>01-06-2026 23:59:59</t>
         </is>
       </c>
       <c r="T10" t="inlineStr"/>
       <c r="U10" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="V10" t="inlineStr"/>
@@ -1801,27 +1801,19 @@
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>26150522891430002392</t>
-        </is>
-      </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>GISSEL ANAHY REYES GERMAN</t>
-        </is>
-      </c>
+          <t>26150522787060002251</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr"/>
+      <c r="Z10" t="inlineStr"/>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>1899</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>Johan Osvaldo Beltran Quiros</t>
+          <t>Juan Eduardo Torres Alcantar</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
@@ -1833,12 +1825,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>347775</t>
+          <t>347389</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>89940</t>
+          <t>89554</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1848,17 +1840,17 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>KAREM PAOLA</t>
+          <t>MARTIN</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>DUARTE</t>
+          <t>LIRA</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>RODRIGUEZ</t>
+          <t>SORIA</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -1868,43 +1860,47 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>6531128069</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>6531197369</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>CJON LAZARO CARDENAS 41 Y42</t>
+        </is>
+      </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>22-12-1996</t>
+          <t>25-05-1974</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>PAO.DUARTE.ROD@GMAIL.COM</t>
+          <t>AUTOELECTRICOGDL1977@GMAIL.COM</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>02-03-2026 17:55:45</t>
+          <t>02-03-2026 05:39:01</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>convenio 300</t>
+          <t>Inscripcion $150</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
@@ -1914,21 +1910,29 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>02-03-2026 17:58:23</t>
+          <t>05-03-2026 05:22:25</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>01-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T11" t="inlineStr"/>
+          <t>04-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>05-03-2026 05:21:13</t>
+        </is>
+      </c>
       <c r="U11" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V11" t="inlineStr"/>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W11" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -1936,11 +1940,19 @@
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>26150522809500002290</t>
-        </is>
-      </c>
-      <c r="Y11" t="inlineStr"/>
-      <c r="Z11" t="inlineStr"/>
+          <t>26150522901950002416</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>RAUL FELIX VAZQUEZ</t>
+        </is>
+      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>549</t>
@@ -2087,12 +2099,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>347867</t>
+          <t>347762</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>90032</t>
+          <t>89927</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -2102,17 +2114,17 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>ADRIANA</t>
+          <t>ROMAN ISAAC</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>ESQUER</t>
+          <t xml:space="preserve">GOMEZ </t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>TERAN</t>
+          <t>COTA</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -2122,47 +2134,43 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>6865432785</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>OBREGON Y 20</t>
-        </is>
-      </c>
+          <t>6221718560</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>04-12-1969</t>
+          <t>07-02-1989</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>AET89@GMAIL.COM</t>
+          <t>ROMANG89@LIVE.COM.MX</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>02-03-2026 19:24:40</t>
+          <t>02-03-2026 17:42:58</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>Inscripcion $150</t>
+          <t>convenio 300</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
@@ -2172,7 +2180,7 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>04-03-2026 18:23:35</t>
+          <t>04-03-2026 17:39:25</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
@@ -2180,21 +2188,13 @@
           <t>03-04-2026 23:59:59</t>
         </is>
       </c>
-      <c r="T13" t="inlineStr">
-        <is>
-          <t>04-03-2026 18:22:20</t>
-        </is>
-      </c>
+      <c r="T13" t="inlineStr"/>
       <c r="U13" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V13" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="V13" t="inlineStr"/>
       <c r="W13" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -2202,7 +2202,7 @@
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>26150522894140002400</t>
+          <t>26150522891430002392</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr">
@@ -2234,12 +2234,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>348143</t>
+          <t>347867</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>90308</t>
+          <t>90032</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -2249,17 +2249,17 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>JAQUELINE</t>
+          <t>ADRIANA</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>OZUNA</t>
+          <t>ESQUER</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>CASTRO</t>
+          <t>TERAN</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -2269,12 +2269,12 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>6531299473</t>
+          <t>6865432785</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>CJON MORELOS Y JUAREZ</t>
+          <t>OBREGON Y 20</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -2284,17 +2284,17 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>05-04-1999</t>
+          <t>04-12-1969</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>OZUNA052024@OUTLOOK.COM</t>
+          <t>AET89@GMAIL.COM</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>03-03-2026 17:02:29</t>
+          <t>02-03-2026 19:24:40</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
@@ -2319,17 +2319,17 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>03-03-2026 17:05:49</t>
+          <t>04-03-2026 18:23:35</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>02-04-2026 23:59:59</t>
+          <t>03-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>03-03-2026 17:05:17</t>
+          <t>04-03-2026 18:22:20</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
@@ -2339,7 +2339,7 @@
       </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W14" t="inlineStr">
@@ -2349,11 +2349,19 @@
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>26150522849130002352</t>
-        </is>
-      </c>
-      <c r="Y14" t="inlineStr"/>
-      <c r="Z14" t="inlineStr"/>
+          <t>26150522894140002400</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>GISSEL ANAHY REYES GERMAN</t>
+        </is>
+      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>549</t>
@@ -2361,7 +2369,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>Juan Pablo Romero Andrade</t>
+          <t>Johan Osvaldo Beltran Quiros</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
@@ -2373,12 +2381,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>347998</t>
+          <t>347775</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>90163</t>
+          <t>89940</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -2388,17 +2396,17 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>DAHENA DARLENE</t>
+          <t>KAREM PAOLA</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>VEGA</t>
+          <t>DUARTE</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>MONTIZO</t>
+          <t>RODRIGUEZ</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -2408,14 +2416,10 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>6531111880</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>AV CARRANZA 29 Y 30</t>
-        </is>
-      </c>
+          <t>6531128069</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -2423,32 +2427,32 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>04-06-1992</t>
+          <t>22-12-1996</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>SUPERVICION.FRUTAL@GMAIL.COM</t>
+          <t>PAO.DUARTE.ROD@GMAIL.COM</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>03-03-2026 10:11:47</t>
+          <t>02-03-2026 17:55:45</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>Inscripcion $150</t>
+          <t>convenio 300</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
@@ -2458,29 +2462,21 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>03-03-2026 10:21:09</t>
+          <t>02-03-2026 17:58:23</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>02-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T15" t="inlineStr">
-        <is>
-          <t>03-03-2026 10:20:10</t>
-        </is>
-      </c>
+          <t>01-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr"/>
       <c r="U15" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V15" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="V15" t="inlineStr"/>
       <c r="W15" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -2488,7 +2484,7 @@
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>26150522836290002334</t>
+          <t>26150522809500002290</t>
         </is>
       </c>
       <c r="Y15" t="inlineStr"/>
@@ -2500,24 +2496,24 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>Juan Eduardo Torres Alcantar</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>348842</t>
+          <t>348143</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>91007</t>
+          <t>90308</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -2527,17 +2523,17 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>EZAU</t>
+          <t>JAQUELINE</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>RODRIGUEZ</t>
+          <t>OZUNA</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>SOTELO</t>
+          <t>CASTRO</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -2547,32 +2543,32 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>6531755736</t>
+          <t>6531299473</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>CJON QUINTANA ROO 4 Y 5</t>
+          <t>CJON MORELOS Y JUAREZ</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>20-11-1995</t>
+          <t>05-04-1999</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>EZAURODRIGUEZ814@GMAIL.COM</t>
+          <t>OZUNA052024@OUTLOOK.COM</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>06-03-2026 07:40:32</t>
+          <t>03-03-2026 17:02:29</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
@@ -2597,17 +2593,17 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>06-03-2026 08:13:26</t>
+          <t>03-03-2026 17:05:49</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>05-04-2026 23:59:59</t>
+          <t>02-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>06-03-2026 07:54:34</t>
+          <t>03-03-2026 17:05:17</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
@@ -2627,7 +2623,7 @@
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>26150522944300002450</t>
+          <t>26150522849130002352</t>
         </is>
       </c>
       <c r="Y16" t="inlineStr"/>
@@ -2639,24 +2635,24 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Juan Pablo Romero Andrade</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>349604</t>
+          <t>347998</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>91769</t>
+          <t>90163</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -2666,17 +2662,17 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>SARA</t>
+          <t>DAHENA DARLENE</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>RIOS</t>
+          <t>VEGA</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>BRITO</t>
+          <t>MONTIZO</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -2686,12 +2682,12 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>6531191528</t>
+          <t>6531111880</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t xml:space="preserve">AV DALIAS </t>
+          <t>AV CARRANZA 29 Y 30</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -2701,17 +2697,17 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>15-06-1979</t>
+          <t>04-06-1992</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>SARA_RBRITO@HOTMAIL.COM</t>
+          <t>SUPERVICION.FRUTAL@GMAIL.COM</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>09-03-2026 18:22:06</t>
+          <t>03-03-2026 10:11:47</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
@@ -2736,17 +2732,17 @@
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>09-03-2026 18:31:03</t>
+          <t>03-03-2026 10:21:09</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>08-04-2026 23:59:59</t>
+          <t>02-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>09-03-2026 18:29:58</t>
+          <t>03-03-2026 10:20:10</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
@@ -2766,7 +2762,7 @@
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>26150523022720002539</t>
+          <t>26150522836290002334</t>
         </is>
       </c>
       <c r="Y17" t="inlineStr"/>
@@ -2778,7 +2774,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>Juan Pablo Romero Andrade</t>
+          <t>Juan Eduardo Torres Alcantar</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
@@ -2790,12 +2786,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>349000</t>
+          <t>348842</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>91165</t>
+          <t>91007</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -2805,17 +2801,17 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>FELIPE ANTONIO</t>
+          <t>EZAU</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>DAVILA</t>
+          <t>RODRIGUEZ</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>TELON</t>
+          <t>SOTELO</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -2825,10 +2821,14 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>6535343327</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>6531755736</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>CJON QUINTANA ROO 4 Y 5</t>
+        </is>
+      </c>
       <c r="J18" t="inlineStr">
         <is>
           <t>Masculino</t>
@@ -2836,32 +2836,32 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>14-05-1953</t>
+          <t>20-11-1995</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>SOLMARI22@GMAIL.COM</t>
+          <t>EZAURODRIGUEZ814@GMAIL.COM</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>06-03-2026 17:33:34</t>
+          <t>06-03-2026 07:40:32</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>convenio 300</t>
+          <t>Inscripcion $150</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
@@ -2871,7 +2871,7 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>06-03-2026 17:35:50</t>
+          <t>06-03-2026 08:13:26</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
@@ -2879,13 +2879,21 @@
           <t>05-04-2026 23:59:59</t>
         </is>
       </c>
-      <c r="T18" t="inlineStr"/>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>06-03-2026 07:54:34</t>
+        </is>
+      </c>
       <c r="U18" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V18" t="inlineStr"/>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W18" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -2893,7 +2901,7 @@
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>26150522956910002465</t>
+          <t>26150522944300002450</t>
         </is>
       </c>
       <c r="Y18" t="inlineStr"/>
@@ -2917,12 +2925,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>349303</t>
+          <t>349000</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>91468</t>
+          <t>91165</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -2932,17 +2940,17 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>JESUS</t>
+          <t>FELIPE ANTONIO</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>HERNANDEZ</t>
+          <t>DAVILA</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>ARAGON</t>
+          <t>TELON</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -2952,14 +2960,10 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>6538495218</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>AV CARRANZA #2606</t>
-        </is>
-      </c>
+          <t>6535343327</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr">
         <is>
           <t>Masculino</t>
@@ -2967,32 +2971,32 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>09-07-1982</t>
+          <t>14-05-1953</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>JESUSHERNANDEZARAGON@GMAIL.COM</t>
+          <t>SOLMARI22@GMAIL.COM</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>09-03-2026 07:27:59</t>
+          <t>06-03-2026 17:33:34</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>Inscripcion $150</t>
+          <t>convenio 300</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
@@ -3002,29 +3006,21 @@
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>09-03-2026 07:32:21</t>
+          <t>06-03-2026 17:35:50</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>08-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T19" t="inlineStr">
-        <is>
-          <t>09-03-2026 07:30:39</t>
-        </is>
-      </c>
+          <t>05-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr"/>
       <c r="U19" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V19" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="V19" t="inlineStr"/>
       <c r="W19" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -3032,7 +3028,7 @@
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>26150522999200002499</t>
+          <t>26150522956910002465</t>
         </is>
       </c>
       <c r="Y19" t="inlineStr"/>
@@ -3044,24 +3040,24 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>Juan Eduardo Torres Alcantar</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>349324</t>
+          <t>349648</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>91489</t>
+          <t>91813</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -3071,17 +3067,17 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>MARIA ELVIRA</t>
+          <t xml:space="preserve">EVANGELINA </t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>MEDEL</t>
+          <t>LOPEZ</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>ARANDA</t>
+          <t>MACHUCA</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -3091,10 +3087,14 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>6531076310</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>6531166484</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AV CHIAPAS Y 9 </t>
+        </is>
+      </c>
       <c r="J20" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -3102,56 +3102,64 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>26-10-1962</t>
+          <t>23-08-1995</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>MARIAMEDEL173@YAHOO.COM</t>
+          <t>LOPEZEVANGELINA34@GMAIL.COM</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>09-03-2026 08:44:01</t>
+          <t>09-03-2026 19:07:10</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>convenio 300</t>
+          <t>Tarifas 2026 LE</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>No Forzoso</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>RECURRENTE $649 LE</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>649</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>18-03-2026 08:03:04</t>
+          <t>09-03-2026 19:28:58</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>17-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T20" t="inlineStr"/>
+          <t>08-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>09-03-2026 19:17:27</t>
+        </is>
+      </c>
       <c r="U20" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="V20" t="inlineStr"/>
       <c r="W20" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -3159,44 +3167,36 @@
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>26150523285070002882</t>
-        </is>
-      </c>
-      <c r="Y20" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>RAUL FELIX VAZQUEZ</t>
-        </is>
-      </c>
+          <t>26150523027720002546</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr"/>
+      <c r="Z20" t="inlineStr"/>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>649</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Johan Osvaldo Beltran Quiros</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>349515</t>
+          <t>349604</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>91680</t>
+          <t>91769</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -3206,17 +3206,17 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t xml:space="preserve">LUIS JORGE </t>
+          <t>SARA</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>MONTOYA</t>
+          <t>RIOS</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>RAMIREZ</t>
+          <t>BRITO</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -3226,10 +3226,14 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>6538490929</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>6531191528</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AV DALIAS </t>
+        </is>
+      </c>
       <c r="J21" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -3237,56 +3241,64 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>03-03-1992</t>
+          <t>15-06-1979</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>LURGEMDRK@HOTMAIL.COM</t>
+          <t>SARA_RBRITO@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>09-03-2026 16:43:33</t>
+          <t>09-03-2026 18:22:06</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>Tarifas 2026 LE</t>
+          <t>Inscripcion $150</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>3 MESES $1,899</t>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>633</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>09-03-2026 16:45:01</t>
+          <t>09-03-2026 18:31:03</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>08-06-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T21" t="inlineStr"/>
+          <t>08-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>09-03-2026 18:29:58</t>
+        </is>
+      </c>
       <c r="U21" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V21" t="inlineStr"/>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="W21" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -3294,36 +3306,36 @@
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>26150523015010002526</t>
+          <t>26150523022720002539</t>
         </is>
       </c>
       <c r="Y21" t="inlineStr"/>
       <c r="Z21" t="inlineStr"/>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>1899</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Juan Pablo Romero Andrade</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>349648</t>
+          <t>349611</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>91813</t>
+          <t>91776</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -3333,17 +3345,17 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t xml:space="preserve">EVANGELINA </t>
+          <t>IRVIN YASIR</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>LOPEZ</t>
+          <t>UTRERA</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>MACHUCA</t>
+          <t>RIOS</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -3353,57 +3365,57 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>6531166484</t>
+          <t>6535383177</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t xml:space="preserve">AV CHIAPAS Y 9 </t>
+          <t>AV DALIAS 11</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>23-08-1995</t>
+          <t>27-10-2005</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>LOPEZEVANGELINA34@GMAIL.COM</t>
+          <t>IRVINYASIRUTRERA@GAMIAL.COM</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>09-03-2026 19:07:10</t>
+          <t>09-03-2026 18:29:17</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>Tarifas 2026 LE</t>
+          <t>Inscripcion $150</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>No Forzoso</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>RECURRENTE $649 LE</t>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>09-03-2026 19:28:58</t>
+          <t>09-03-2026 18:34:14</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
@@ -3413,7 +3425,7 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>09-03-2026 19:17:27</t>
+          <t>09-03-2026 18:33:21</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
@@ -3423,7 +3435,7 @@
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W22" t="inlineStr">
@@ -3433,19 +3445,19 @@
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>26150523027720002546</t>
+          <t>26150523022910002540</t>
         </is>
       </c>
       <c r="Y22" t="inlineStr"/>
       <c r="Z22" t="inlineStr"/>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>Johan Osvaldo Beltran Quiros</t>
+          <t>Juan Pablo Romero Andrade</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
@@ -3457,12 +3469,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>349316</t>
+          <t>349721</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>91481</t>
+          <t>91886</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -3472,17 +3484,17 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>MISSAEL</t>
+          <t>ABRAHAM</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>ORTIZ</t>
+          <t>CORTEZ</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>SANCHEZ</t>
+          <t>SALAZAR</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -3492,57 +3504,53 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>6532077103</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>DURANGO Y 25</t>
-        </is>
-      </c>
+          <t>6535382221</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>25-10-2001</t>
+          <t>03-11-1989</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>OMISSAEL125@GMAIL.COM</t>
+          <t>NEGRO_CORTEZ01@HOTMAILO.COM</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>09-03-2026 08:20:50</t>
+          <t>09-03-2026 20:41:54</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>Tarifas 2026 LE</t>
+          <t>convenio 300</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>No Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>RECURRENTE $649 LE</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>09-03-2026 08:29:30</t>
+          <t>09-03-2026 20:44:08</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
@@ -3550,21 +3558,13 @@
           <t>08-04-2026 23:59:59</t>
         </is>
       </c>
-      <c r="T23" t="inlineStr">
-        <is>
-          <t>09-03-2026 08:29:03</t>
-        </is>
-      </c>
+      <c r="T23" t="inlineStr"/>
       <c r="U23" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V23" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="V23" t="inlineStr"/>
       <c r="W23" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -3572,14 +3572,14 @@
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>26150523000590002503</t>
+          <t>26150523032300002557</t>
         </is>
       </c>
       <c r="Y23" t="inlineStr"/>
       <c r="Z23" t="inlineStr"/>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
@@ -3596,12 +3596,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>349632</t>
+          <t>349316</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>91797</t>
+          <t>91481</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -3611,87 +3611,99 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>ANA</t>
+          <t>MISSAEL</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>CASTRO</t>
+          <t>ORTIZ</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>ESPARZA</t>
+          <t>SANCHEZ</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>6532077103</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>DURANGO Y 25</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>25-10-2001</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>OMISSAEL125@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>09-03-2026 08:20:50</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>No Forzoso</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>RECURRENTE $649 LE</t>
+        </is>
+      </c>
+      <c r="Q24" t="inlineStr">
+        <is>
+          <t>649</t>
+        </is>
+      </c>
+      <c r="R24" t="inlineStr">
+        <is>
+          <t>09-03-2026 08:29:30</t>
+        </is>
+      </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>08-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>09-03-2026 08:29:03</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>9283663034</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>Femenino</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>17-11-1995</t>
-        </is>
-      </c>
-      <c r="L24" t="inlineStr">
-        <is>
-          <t>CASTROANA.7771@GMAIL.COM</t>
-        </is>
-      </c>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>09-03-2026 18:52:23</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr">
-        <is>
-          <t>Tarifas 2026 LE</t>
-        </is>
-      </c>
-      <c r="O24" t="inlineStr">
-        <is>
-          <t>Sin contrato</t>
-        </is>
-      </c>
-      <c r="P24" t="inlineStr">
-        <is>
-          <t>3 MESES $1,899</t>
-        </is>
-      </c>
-      <c r="Q24" t="inlineStr">
-        <is>
-          <t>633</t>
-        </is>
-      </c>
-      <c r="R24" t="inlineStr">
-        <is>
-          <t>09-03-2026 18:53:40</t>
-        </is>
-      </c>
-      <c r="S24" t="inlineStr">
-        <is>
-          <t>08-06-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T24" t="inlineStr"/>
-      <c r="U24" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V24" t="inlineStr"/>
       <c r="W24" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -3699,14 +3711,14 @@
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>26150523024670002542</t>
+          <t>26150523000590002503</t>
         </is>
       </c>
       <c r="Y24" t="inlineStr"/>
       <c r="Z24" t="inlineStr"/>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>1899</t>
+          <t>649</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
@@ -3723,12 +3735,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>349611</t>
+          <t>349632</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>91776</t>
+          <t>91797</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -3738,99 +3750,87 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>IRVIN YASIR</t>
+          <t>ANA</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>UTRERA</t>
+          <t>CASTRO</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>RIOS</t>
+          <t>ESPARZA</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>6535383177</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>AV DALIAS 11</t>
-        </is>
-      </c>
+          <t>9283663034</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>27-10-2005</t>
+          <t>17-11-1995</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>IRVINYASIRUTRERA@GAMIAL.COM</t>
+          <t>CASTROANA.7771@GMAIL.COM</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>09-03-2026 18:29:17</t>
+          <t>09-03-2026 18:52:23</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>Inscripcion $150</t>
+          <t>Tarifas 2026 LE</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+          <t>3 MESES $1,899</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>633</t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>09-03-2026 18:34:14</t>
+          <t>09-03-2026 18:53:40</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>08-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T25" t="inlineStr">
-        <is>
-          <t>09-03-2026 18:33:21</t>
-        </is>
-      </c>
+          <t>08-06-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T25" t="inlineStr"/>
       <c r="U25" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V25" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="V25" t="inlineStr"/>
       <c r="W25" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -3838,36 +3838,36 @@
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>26150523022910002540</t>
+          <t>26150523024670002542</t>
         </is>
       </c>
       <c r="Y25" t="inlineStr"/>
       <c r="Z25" t="inlineStr"/>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>1899</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>Juan Pablo Romero Andrade</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>349721</t>
+          <t>350257</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>91886</t>
+          <t>92421</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -3877,17 +3877,17 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>ABRAHAM</t>
+          <t>ABRAHAM ANTONIO</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>CORTEZ</t>
+          <t>JUAREZ</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>SALAZAR</t>
+          <t>BELTRAN</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -3897,28 +3897,28 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>6535382221</t>
+          <t>6531166314</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>03-11-1989</t>
+          <t>19-01-2012</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>NEGRO_CORTEZ01@HOTMAILO.COM</t>
+          <t>ANONTIONIOJUAREZ@GMAIL.COM</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>09-03-2026 20:41:54</t>
+          <t>12-03-2026 07:04:36</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
@@ -3943,12 +3943,12 @@
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>09-03-2026 20:44:08</t>
+          <t>16-03-2026 07:23:47</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
         <is>
-          <t>08-04-2026 23:59:59</t>
+          <t>15-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T26" t="inlineStr"/>
@@ -3965,11 +3965,19 @@
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>26150523032300002557</t>
-        </is>
-      </c>
-      <c r="Y26" t="inlineStr"/>
-      <c r="Z26" t="inlineStr"/>
+          <t>26150523202920002745</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>RAUL FELIX VAZQUEZ</t>
+        </is>
+      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>549</t>
@@ -4112,24 +4120,24 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Martin Ramiro Quiñonez Jauregui</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>350343</t>
+          <t>349906</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>92507</t>
+          <t>92071</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -4139,17 +4147,17 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LORENA</t>
+          <t>ANGELICA LIZETH</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>HIGUERA</t>
+          <t>FLORES</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>RODRIGUEZ</t>
+          <t>ROJAS</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -4159,14 +4167,10 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>6531338028</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>CJN CRISANTEMAS B 20 Y21</t>
-        </is>
-      </c>
+          <t>6531765576</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="J28" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -4174,32 +4178,32 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>12-09-1983</t>
+          <t>11-01-2010</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>LORENA4250HIGUERA@GMAIL.COM</t>
+          <t>FORESROJASANGELICALIZETH@GMAIL.COM</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>12-03-2026 14:27:32</t>
+          <t>10-03-2026 17:31:43</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>Inscripcion $150</t>
+          <t>convenio 300</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
@@ -4209,29 +4213,21 @@
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>12-03-2026 14:30:20</t>
+          <t>10-03-2026 17:32:55</t>
         </is>
       </c>
       <c r="S28" t="inlineStr">
         <is>
-          <t>11-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T28" t="inlineStr">
-        <is>
-          <t>12-03-2026 14:29:48</t>
-        </is>
-      </c>
+          <t>09-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr"/>
       <c r="U28" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V28" t="inlineStr">
-        <is>
           <t>1</t>
         </is>
       </c>
+      <c r="V28" t="inlineStr"/>
       <c r="W28" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -4239,7 +4235,7 @@
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>26150523123480002680</t>
+          <t>26150523060120002589</t>
         </is>
       </c>
       <c r="Y28" t="inlineStr"/>
@@ -4251,24 +4247,24 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>Juan Pablo Romero Andrade</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>349906</t>
+          <t>351383</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>92071</t>
+          <t>93547</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -4278,17 +4274,17 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>ANGELICA LIZETH</t>
+          <t>BRAYAN URIEL</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>FLORES</t>
+          <t>NUÑEZ</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>ROJAS</t>
+          <t>ROMERO</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -4298,43 +4294,47 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>6531765576</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
+          <t>6531076077</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>TORREON 4 Y 5</t>
+        </is>
+      </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>11-01-2010</t>
+          <t>17-01-2011</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>FORESROJASANGELICALIZETH@GMAIL.COM</t>
+          <t>BRAYYAN1701@ICLOUD.COM</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>10-03-2026 17:31:43</t>
+          <t>16-03-2026 21:16:06</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>convenio 300</t>
+          <t>Inscripcion $150</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
@@ -4344,21 +4344,29 @@
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>10-03-2026 17:32:55</t>
+          <t>18-03-2026 20:14:03</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>09-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T29" t="inlineStr"/>
+          <t>17-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>18-03-2026 20:13:39</t>
+        </is>
+      </c>
       <c r="U29" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="V29" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="W29" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -4366,11 +4374,19 @@
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>26150523060120002589</t>
-        </is>
-      </c>
-      <c r="Y29" t="inlineStr"/>
-      <c r="Z29" t="inlineStr"/>
+          <t>26150523309000002923</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>GISSEL ANAHY REYES GERMAN</t>
+        </is>
+      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>549</t>
@@ -4390,12 +4406,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>350257</t>
+          <t>351441</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>92421</t>
+          <t>93605</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -4405,17 +4421,17 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>ABRAHAM ANTONIO</t>
+          <t>JUAN RAMON</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>JUAREZ</t>
+          <t>ALCALA</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>BELTRAN</t>
+          <t>GONZALEZ</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -4425,10 +4441,14 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>6531166314</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
+          <t>6531103138</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>LE DE ALFABETIZACION Y CALLE 35 Y 36</t>
+        </is>
+      </c>
       <c r="J30" t="inlineStr">
         <is>
           <t>Masculino</t>
@@ -4436,56 +4456,64 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>19-01-2012</t>
+          <t>13-09-2000</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>ANONTIONIOJUAREZ@GMAIL.COM</t>
+          <t>JUANRAMONALCALAGONZALEZ4@GMAIL.COM</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>12-03-2026 07:04:36</t>
+          <t>17-03-2026 09:39:59</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>convenio 300</t>
+          <t>Tarifas 2026 LE</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>No Forzoso</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>RECURRENTE $649 LE</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>649</t>
         </is>
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>16-03-2026 07:23:47</t>
+          <t>17-03-2026 09:45:16</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>15-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T30" t="inlineStr"/>
+          <t>16-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>17-03-2026 09:44:34</t>
+        </is>
+      </c>
       <c r="U30" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V30" t="inlineStr"/>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W30" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -4493,44 +4521,36 @@
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>26150523202920002745</t>
-        </is>
-      </c>
-      <c r="Y30" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>RAUL FELIX VAZQUEZ</t>
-        </is>
-      </c>
+          <t>26150523248650002812</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr"/>
+      <c r="Z30" t="inlineStr"/>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>649</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Martin Ramiro Quiñonez Jauregui</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>350034</t>
+          <t>351652</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>92199</t>
+          <t>93816</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -4540,34 +4560,30 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>JESUS HUMBERTO</t>
+          <t>NIGEL</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>SALAZAR</t>
+          <t xml:space="preserve">PATIÑO </t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>SALAZAR</t>
+          <t>LEON</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>52</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>9283231886</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>NAYARIT Y 21</t>
-        </is>
-      </c>
+          <t>6531140204</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
       <c r="J31" t="inlineStr">
         <is>
           <t>Masculino</t>
@@ -4575,32 +4591,32 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>27-11-1989</t>
+          <t>08-02-2011</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>JESUSHUMBERTO27@HOTMAIL.COM</t>
+          <t>KAAREENLEON91@GMAI.COM</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>11-03-2026 06:55:38</t>
+          <t>17-03-2026 18:39:20</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>Inscripcion $150</t>
+          <t>convenio 300</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
@@ -4610,29 +4626,21 @@
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>13-03-2026 10:25:55</t>
+          <t>19-03-2026 18:34:10</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
         <is>
-          <t>12-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T31" t="inlineStr">
-        <is>
-          <t>13-03-2026 10:25:16</t>
-        </is>
-      </c>
+          <t>18-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T31" t="inlineStr"/>
       <c r="U31" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V31" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="V31" t="inlineStr"/>
       <c r="W31" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -4640,7 +4648,7 @@
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>26150523149820002700</t>
+          <t>26150523338530002959</t>
         </is>
       </c>
       <c r="Y31" t="inlineStr">
@@ -4650,7 +4658,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>RAUL FELIX VAZQUEZ</t>
+          <t>GISSEL ANAHY REYES GERMAN</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4660,24 +4668,24 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Johan Osvaldo Beltran Quiros</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>351650</t>
+          <t>350343</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>93814</t>
+          <t>92507</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -4687,12 +4695,12 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>YALUI</t>
+          <t>LORENA</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>GARCIA</t>
+          <t>HIGUERA</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -4707,43 +4715,47 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>6531651010</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
+          <t>6531338028</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>CJN CRISANTEMAS B 20 Y21</t>
+        </is>
+      </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>02-07-2012</t>
+          <t>12-09-1983</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>YALUIGARCIA2@GMAIL.COM</t>
+          <t>LORENA4250HIGUERA@GMAIL.COM</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>17-03-2026 18:33:38</t>
+          <t>12-03-2026 14:27:32</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>convenio 300</t>
+          <t>Inscripcion $150</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
@@ -4753,21 +4765,29 @@
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>19-03-2026 18:36:05</t>
+          <t>12-03-2026 14:30:20</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>18-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T32" t="inlineStr"/>
+          <t>11-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>12-03-2026 14:29:48</t>
+        </is>
+      </c>
       <c r="U32" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V32" t="inlineStr"/>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W32" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -4775,19 +4795,11 @@
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>26150523338650002960</t>
-        </is>
-      </c>
-      <c r="Y32" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>GISSEL ANAHY REYES GERMAN</t>
-        </is>
-      </c>
+          <t>26150523123480002680</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr"/>
+      <c r="Z32" t="inlineStr"/>
       <c r="AA32" t="inlineStr">
         <is>
           <t>549</t>
@@ -4795,24 +4807,24 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Juan Pablo Romero Andrade</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>351652</t>
+          <t>351605</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>93816</t>
+          <t>93769</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -4822,87 +4834,99 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NIGEL</t>
+          <t>CAMILA</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t xml:space="preserve">PATIÑO </t>
+          <t>RIVERA</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>LEON</t>
+          <t>GALLARDO</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>6531140204</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
+          <t>9282599519</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>TORREON B 13 Y 14</t>
+        </is>
+      </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>08-02-2011</t>
+          <t>16-12-2005</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>KAAREENLEON91@GMAI.COM</t>
+          <t>CAMILARG0315@GMAIL.COM</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>17-03-2026 18:39:20</t>
+          <t>17-03-2026 17:46:48</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>convenio 300</t>
+          <t>Tarifas 2026 LE</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>No Forzoso</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>RECURRENTE $649 LE</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>649</t>
         </is>
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>19-03-2026 18:34:10</t>
+          <t>20-03-2026 17:45:24</t>
         </is>
       </c>
       <c r="S33" t="inlineStr">
         <is>
-          <t>18-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T33" t="inlineStr"/>
+          <t>19-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>20-03-2026 17:44:47</t>
+        </is>
+      </c>
       <c r="U33" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V33" t="inlineStr"/>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W33" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -4910,7 +4934,7 @@
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>26150523338530002959</t>
+          <t>26150523371290002993</t>
         </is>
       </c>
       <c r="Y33" t="inlineStr">
@@ -4925,7 +4949,7 @@
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>649</t>
         </is>
       </c>
       <c r="AB33" t="inlineStr">
@@ -4942,12 +4966,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>351383</t>
+          <t>351607</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>93547</t>
+          <t>93771</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -4957,87 +4981,87 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>BRAYAN URIEL</t>
+          <t>ALMA LUCERO</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>NUÑEZ</t>
+          <t xml:space="preserve">CRUZ </t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>ROMERO</t>
+          <t>ROJO</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>6531076077</t>
+          <t>9285030507</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>TORREON 4 Y 5</t>
+          <t>AMAPOLAS B 27 Y 28</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>17-01-2011</t>
+          <t>07-09-2005</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>BRAYYAN1701@ICLOUD.COM</t>
+          <t>LUCEROCRUZZ7@GMAIL.COM</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>16-03-2026 21:16:06</t>
+          <t>17-03-2026 17:49:15</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>Inscripcion $150</t>
+          <t>Tarifas 2026 LE</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>No Forzoso</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+          <t>RECURRENTE $649 LE</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>649</t>
         </is>
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>18-03-2026 20:14:03</t>
+          <t>20-03-2026 17:41:11</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
         <is>
-          <t>17-04-2026 23:59:59</t>
+          <t>19-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>18-03-2026 20:13:39</t>
+          <t>20-03-2026 17:40:17</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
@@ -5047,7 +5071,7 @@
       </c>
       <c r="V34" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W34" t="inlineStr">
@@ -5057,7 +5081,7 @@
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>26150523309000002923</t>
+          <t>26150523371090002992</t>
         </is>
       </c>
       <c r="Y34" t="inlineStr">
@@ -5072,7 +5096,7 @@
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>649</t>
         </is>
       </c>
       <c r="AB34" t="inlineStr">
@@ -5089,12 +5113,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>351441</t>
+          <t>352752</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>93605</t>
+          <t>94916</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -5104,17 +5128,17 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>JUAN RAMON</t>
+          <t>GERARDO</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>ALCALA</t>
+          <t>RAMIREZ</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>GONZALEZ</t>
+          <t>LANDA</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -5124,12 +5148,12 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>6531103138</t>
+          <t>6531463427</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>LE DE ALFABETIZACION Y CALLE 35 Y 36</t>
+          <t>CJON LIBERTAD 21 Y 22</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -5139,52 +5163,52 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>13-09-2000</t>
+          <t>19-01-1978</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>JUANRAMONALCALAGONZALEZ4@GMAIL.COM</t>
+          <t>GJERRY119@GMAIL.COM</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>17-03-2026 09:39:59</t>
+          <t>23-03-2026 13:09:57</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>Tarifas 2026 LE</t>
+          <t>Inscripcion $150</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>No Forzoso</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>RECURRENTE $649 LE</t>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>17-03-2026 09:45:16</t>
+          <t>23-03-2026 13:17:49</t>
         </is>
       </c>
       <c r="S35" t="inlineStr">
         <is>
-          <t>16-04-2026 23:59:59</t>
+          <t>22-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>17-03-2026 09:44:34</t>
+          <t>23-03-2026 13:17:10</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
@@ -5204,19 +5228,19 @@
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>26150523248650002812</t>
+          <t>26150523425620003044</t>
         </is>
       </c>
       <c r="Y35" t="inlineStr"/>
       <c r="Z35" t="inlineStr"/>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>Martin Ramiro Quiñonez Jauregui</t>
+          <t>Juan Eduardo Torres Alcantar</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
@@ -5349,6 +5373,2341 @@
       <c r="AC36" t="inlineStr">
         <is>
           <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>350034</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>92199</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>SAN LUIS</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>JESUS HUMBERTO</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>SALAZAR</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>SALAZAR</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>9283231886</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>NAYARIT Y 21</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>27-11-1989</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>JESUSHUMBERTO27@HOTMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>11-03-2026 06:55:38</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>Inscripcion $150</t>
+        </is>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+        </is>
+      </c>
+      <c r="Q37" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R37" t="inlineStr">
+        <is>
+          <t>13-03-2026 10:25:55</t>
+        </is>
+      </c>
+      <c r="S37" t="inlineStr">
+        <is>
+          <t>12-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>13-03-2026 10:25:16</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X37" t="inlineStr">
+        <is>
+          <t>26150523149820002700</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>RAUL FELIX VAZQUEZ</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>349303</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>91468</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>SAN LUIS</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>JESUS</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>HERNANDEZ</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>ARAGON</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>6538495218</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>AV CARRANZA #2606</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>09-07-1982</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>JESUSHERNANDEZARAGON@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>09-03-2026 07:27:59</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>Inscripcion $150</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+        </is>
+      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R38" t="inlineStr">
+        <is>
+          <t>09-03-2026 07:32:21</t>
+        </is>
+      </c>
+      <c r="S38" t="inlineStr">
+        <is>
+          <t>08-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>09-03-2026 07:30:39</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X38" t="inlineStr">
+        <is>
+          <t>26150522999200002499</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr"/>
+      <c r="Z38" t="inlineStr"/>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>Juan Eduardo Torres Alcantar</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>349324</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>91489</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>SAN LUIS</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>MARIA ELVIRA</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>MEDEL</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>ARANDA</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>6531076310</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>26-10-1962</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>MARIAMEDEL173@YAHOO.COM</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>09-03-2026 08:44:01</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>convenio 300</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>CONVENIOS $549</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R39" t="inlineStr">
+        <is>
+          <t>18-03-2026 08:03:04</t>
+        </is>
+      </c>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>17-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T39" t="inlineStr"/>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr"/>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>26150523285070002882</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>RAUL FELIX VAZQUEZ</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>352710</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>94874</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>SAN LUIS</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>MARIA JESUS</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>AMAYA</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>PEÑA</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>6531018906</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>AV ZACATECAS 4 Y 5</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>23-05-1967</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>MJ_AMAYA@YAHOO.COM</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>23-03-2026 10:46:13</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>No Forzoso</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>RECURRENTE $649 LE</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>649</t>
+        </is>
+      </c>
+      <c r="R40" t="inlineStr">
+        <is>
+          <t>29-03-2026 13:39:13</t>
+        </is>
+      </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>28-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>29-03-2026 13:38:25</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>26150523606720003294</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>RAUL FELIX VAZQUEZ</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>649</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>Juan Eduardo Torres Alcantar</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>352835</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>94999</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>SAN LUIS</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>ANDREA ZIZANIA</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>MOSQUEDA</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>ZAMORA</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>6531759045</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>MERIDA Y 25</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>14-07-2006</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>ANNSITAZAMORA@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>23-03-2026 16:56:36</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>No Forzoso</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>RECURRENTE $649 LE</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>649</t>
+        </is>
+      </c>
+      <c r="R41" t="inlineStr">
+        <is>
+          <t>23-03-2026 17:02:11</t>
+        </is>
+      </c>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>22-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>23-03-2026 17:00:38</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>26150523433970003061</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr"/>
+      <c r="Z41" t="inlineStr"/>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>649</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>352256</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>94420</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>SAN LUIS</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>EMMANUEL</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BRAVO </t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>LOPEZ</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>6531276950</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>CJON FELIX CONTRERAS 23 Y 24</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>15-11-1989</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>DN12MKT@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>20-03-2026 08:06:33</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>Inscripcion $150</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R42" t="inlineStr">
+        <is>
+          <t>24-03-2026 08:19:47</t>
+        </is>
+      </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>23-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>24-03-2026 08:19:12</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>26150523460200003104</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>RAUL FELIX VAZQUEZ</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>354156</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>96320</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>SAN LUIS</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>ARACELI</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>LOPEZ</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>URBALEJO</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>6531300170</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>AV 5 DE MAYO 38 Y 39</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>29-10-1993</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>ARA29OCT93@ICLOUD.COM</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>30-03-2026 11:32:55</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>Inscripcion $150</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R43" t="inlineStr">
+        <is>
+          <t>30-03-2026 11:43:49</t>
+        </is>
+      </c>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>29-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>30-03-2026 11:42:42</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>26150523625160003311</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr"/>
+      <c r="Z43" t="inlineStr"/>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>Martin Ramiro Quiñonez Jauregui</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>349515</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>91680</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>SAN LUIS</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LUIS JORGE </t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>MONTOYA</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>RAMIREZ</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>6538490929</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>03-03-1992</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>LURGEMDRK@HOTMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>09-03-2026 16:43:33</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>3 MESES $1,899</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>633</t>
+        </is>
+      </c>
+      <c r="R44" t="inlineStr">
+        <is>
+          <t>09-03-2026 16:45:01</t>
+        </is>
+      </c>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>08-06-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T44" t="inlineStr"/>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr"/>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>26150523015010002526</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr"/>
+      <c r="Z44" t="inlineStr"/>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>1899</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>353187</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>95351</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>SAN LUIS</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>ROSA ORIANA</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LOPEZ </t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>MUCHUCA</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>6531049141</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>CHIAPAS 9 Y 10</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>19-07-1997</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>OREANA.1923@ICLOUD.COM</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>24-03-2026 18:32:32</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>No Forzoso</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>RECURRENTE $649 LE</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>649</t>
+        </is>
+      </c>
+      <c r="R45" t="inlineStr">
+        <is>
+          <t>24-03-2026 18:36:32</t>
+        </is>
+      </c>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>23-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>24-03-2026 18:34:37</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>26150523478760003125</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr"/>
+      <c r="Z45" t="inlineStr"/>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>649</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>354164</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>96328</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>SAN LUIS</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>MARCO ANTONIO</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>TORRES</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>LOPEZ</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>6531308115</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>08-12-2014</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>KILITORRESLOPEZ@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>30-03-2026 11:46:45</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>convenio 300</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>CONVENIOS $549</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R46" t="inlineStr">
+        <is>
+          <t>30-03-2026 11:49:28</t>
+        </is>
+      </c>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>29-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T46" t="inlineStr"/>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr"/>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>26150523625310003312</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr"/>
+      <c r="Z46" t="inlineStr"/>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>353663</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>95827</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>SAN LUIS</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>ALDRIN GIBRAN</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CASAS </t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>CONTRRAS</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>6531661836</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>23-12-2005</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>ALDRANCASAS@ICLOUD.COM</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>26-03-2026 20:56:14</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>1 MES $899</t>
+        </is>
+      </c>
+      <c r="Q47" t="inlineStr">
+        <is>
+          <t>899</t>
+        </is>
+      </c>
+      <c r="R47" t="inlineStr">
+        <is>
+          <t>26-03-2026 20:57:35</t>
+        </is>
+      </c>
+      <c r="S47" t="inlineStr">
+        <is>
+          <t>25-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T47" t="inlineStr"/>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr"/>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X47" t="inlineStr">
+        <is>
+          <t>26150523549370003238</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr"/>
+      <c r="Z47" t="inlineStr"/>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>899</t>
+        </is>
+      </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>354409</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>96573</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>SAN LUIS</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>HECTOR</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>MARTINEZ</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>MARRON</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>9286559993</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>29-02-2012</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>HECTOROMTZ@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>30-03-2026 19:14:24</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>convenio 300</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>CONVENIOS $549</t>
+        </is>
+      </c>
+      <c r="Q48" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R48" t="inlineStr">
+        <is>
+          <t>30-03-2026 19:17:50</t>
+        </is>
+      </c>
+      <c r="S48" t="inlineStr">
+        <is>
+          <t>29-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T48" t="inlineStr"/>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr"/>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X48" t="inlineStr">
+        <is>
+          <t>26150523646460003355</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr"/>
+      <c r="Z48" t="inlineStr"/>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>352255</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>94419</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>SAN LUIS</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>EDLIN KAREL</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>CAÑEZ</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>ORTIZ</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>6532093742</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>CJON FELIX CONTRERAS 23 Y 24</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>13-01-1999</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>CANEZOFICIAL@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>20-03-2026 08:02:17</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>Inscripcion $150</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+        </is>
+      </c>
+      <c r="Q49" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R49" t="inlineStr">
+        <is>
+          <t>24-03-2026 08:15:39</t>
+        </is>
+      </c>
+      <c r="S49" t="inlineStr">
+        <is>
+          <t>23-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>24-03-2026 08:14:27</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X49" t="inlineStr">
+        <is>
+          <t>26150523460080003103</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>RAUL FELIX VAZQUEZ</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>351650</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>93814</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>SAN LUIS</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>YALUI</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>GARCIA</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>RODRIGUEZ</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>6531651010</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>02-07-2012</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>YALUIGARCIA2@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>17-03-2026 18:33:38</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>convenio 300</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>CONVENIOS $549</t>
+        </is>
+      </c>
+      <c r="Q50" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R50" t="inlineStr">
+        <is>
+          <t>19-03-2026 18:36:05</t>
+        </is>
+      </c>
+      <c r="S50" t="inlineStr">
+        <is>
+          <t>18-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T50" t="inlineStr"/>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr"/>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X50" t="inlineStr">
+        <is>
+          <t>26150523338650002960</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>GISSEL ANAHY REYES GERMAN</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>Martin Ramiro Quiñonez Jauregui</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>352932</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>95096</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>SAN LUIS</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>MICHELLE</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>VALTIERRA</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>FLORES</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>6531053981</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>CJN CHIAPAS 45 Y 46</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>05-11-1996</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>FEVELLE@YAHOO.COM</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>23-03-2026 18:58:06</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>No Forzoso</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>RECURRENTE $649 LE</t>
+        </is>
+      </c>
+      <c r="Q51" t="inlineStr">
+        <is>
+          <t>649</t>
+        </is>
+      </c>
+      <c r="R51" t="inlineStr">
+        <is>
+          <t>25-03-2026 19:01:38</t>
+        </is>
+      </c>
+      <c r="S51" t="inlineStr">
+        <is>
+          <t>24-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>25-03-2026 19:00:35</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X51" t="inlineStr">
+        <is>
+          <t>26150523513800003185</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>MANUEL DIAZ RECEPCION</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>649</t>
+        </is>
+      </c>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>353764</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>95928</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>SAN LUIS</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>ALBERTO JORGE</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>DIAZ</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>ORTEGA</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>6531211742</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>20-10-1981</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>IKERSANTY1823@OUTLOOK.COM</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>27-03-2026 15:23:21</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>convenio 300</t>
+        </is>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>2 MESES X $ 1250</t>
+        </is>
+      </c>
+      <c r="Q52" t="inlineStr">
+        <is>
+          <t>625</t>
+        </is>
+      </c>
+      <c r="R52" t="inlineStr">
+        <is>
+          <t>27-03-2026 15:26:56</t>
+        </is>
+      </c>
+      <c r="S52" t="inlineStr">
+        <is>
+          <t>26-05-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T52" t="inlineStr"/>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr"/>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X52" t="inlineStr">
+        <is>
+          <t>26150523566490003253</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr"/>
+      <c r="Z52" t="inlineStr"/>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>1250</t>
+        </is>
+      </c>
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>Juan Eduardo Torres Alcantar</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>354363</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>96527</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>SAN LUIS</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MELISSA </t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>LOPEZ</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>SANCHEZ</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>6531148685</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>CJN CHIAPAS 17 Y 18</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>30-09-1986</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>MELI-LOQUESEA@HOTMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>30-03-2026 18:18:26</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>Inscripcion $150</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+        </is>
+      </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R53" t="inlineStr">
+        <is>
+          <t>30-03-2026 18:22:51</t>
+        </is>
+      </c>
+      <c r="S53" t="inlineStr">
+        <is>
+          <t>29-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>30-03-2026 18:22:13</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X53" t="inlineStr">
+        <is>
+          <t>26150523642100003346</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr"/>
+      <c r="Z53" t="inlineStr"/>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
